--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5712" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5718" uniqueCount="597">
   <si>
     <t>trade_time</t>
   </si>
@@ -778,19 +778,16 @@
     <t>2021-07-13</t>
   </si>
   <si>
+    <t>2021-07-28</t>
+  </si>
+  <si>
     <t>2021-08-03</t>
   </si>
   <si>
     <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-07-28</t>
-  </si>
-  <si>
     <t>2021-09-16</t>
-  </si>
-  <si>
-    <t>2021-07-20</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -803,6 +800,9 @@
   </si>
   <si>
     <t>2021-09-02</t>
+  </si>
+  <si>
+    <t>2021-09-10</t>
   </si>
   <si>
     <t>2021-09-23</t>
@@ -1288,6 +1288,9 @@
     <t>2021-07-16</t>
   </si>
   <si>
+    <t>2021-07-20</t>
+  </si>
+  <si>
     <t>2021-07-26</t>
   </si>
   <si>
@@ -1327,10 +1330,7 @@
     <t>2021-08-20</t>
   </si>
   <si>
-    <t>2021-08-13</t>
-  </si>
-  <si>
-    <t>2021-09-27</t>
+    <t>2021-09-28</t>
   </si>
   <si>
     <t>2016-09-08</t>
@@ -2162,7 +2162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1900"/>
+  <dimension ref="A1:P1902"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -86523,7 +86523,7 @@
         <v>2.436796568569724</v>
       </c>
       <c r="D1688" t="s">
-        <v>258</v>
+        <v>424</v>
       </c>
       <c r="E1688">
         <v>2.360835494290209</v>
@@ -86573,7 +86573,7 @@
         <v>2.53780345100582</v>
       </c>
       <c r="D1689" t="s">
-        <v>258</v>
+        <v>424</v>
       </c>
       <c r="E1689">
         <v>2.360835494290209</v>
@@ -86623,7 +86623,7 @@
         <v>2.410046032408744</v>
       </c>
       <c r="D1690" t="s">
-        <v>258</v>
+        <v>424</v>
       </c>
       <c r="E1690">
         <v>2.360835494290209</v>
@@ -87673,7 +87673,7 @@
         <v>2.431411491361336</v>
       </c>
       <c r="D1711" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E1711">
         <v>2.538213707664756</v>
@@ -87723,7 +87723,7 @@
         <v>2.532009684902152</v>
       </c>
       <c r="D1712" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E1712">
         <v>2.538213707664756</v>
@@ -87773,7 +87773,7 @@
         <v>2.427002049221179</v>
       </c>
       <c r="D1713" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E1713">
         <v>2.538213707664756</v>
@@ -87823,7 +87823,7 @@
         <v>2.549425366108334</v>
       </c>
       <c r="D1714" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E1714">
         <v>2.538213707664756</v>
@@ -87973,7 +87973,7 @@
         <v>2.421714751688319</v>
       </c>
       <c r="D1717" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E1717">
         <v>2.408329586091149</v>
@@ -88023,7 +88023,7 @@
         <v>2.617934203930899</v>
       </c>
       <c r="D1718" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E1718">
         <v>2.408329586091149</v>
@@ -88073,7 +88073,7 @@
         <v>2.521577031950379</v>
       </c>
       <c r="D1719" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E1719">
         <v>2.408329586091149</v>
@@ -88123,7 +88123,7 @@
         <v>2.415855127498849</v>
       </c>
       <c r="D1720" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E1720">
         <v>2.408329586091149</v>
@@ -88173,7 +88173,7 @@
         <v>2.538191866353209</v>
       </c>
       <c r="D1721" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E1721">
         <v>2.408329586091149</v>
@@ -88323,7 +88323,7 @@
         <v>2.414674676865828</v>
       </c>
       <c r="D1724" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E1724">
         <v>2.260591844169942</v>
@@ -88373,7 +88373,7 @@
         <v>2.609919833039224</v>
       </c>
       <c r="D1725" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E1725">
         <v>2.260591844169942</v>
@@ -88423,7 +88423,7 @@
         <v>2.514002665735109</v>
       </c>
       <c r="D1726" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E1726">
         <v>2.260591844169942</v>
@@ -88473,7 +88473,7 @@
         <v>2.40776218434353</v>
       </c>
       <c r="D1727" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E1727">
         <v>2.260591844169942</v>
@@ -88523,7 +88523,7 @@
         <v>2.530036065386974</v>
       </c>
       <c r="D1728" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E1728">
         <v>2.260591844169942</v>
@@ -88723,7 +88723,7 @@
         <v>2.40248530336921</v>
       </c>
       <c r="D1732" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E1732">
         <v>2.390759562397951</v>
@@ -88773,7 +88773,7 @@
         <v>2.596043537317628</v>
       </c>
       <c r="D1733" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E1733">
         <v>2.390759562397951</v>
@@ -88823,7 +88823,7 @@
         <v>2.500888205857052</v>
       </c>
       <c r="D1734" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E1734">
         <v>2.390759562397951</v>
@@ -88873,7 +88873,7 @@
         <v>2.393749846507016</v>
       </c>
       <c r="D1735" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E1735">
         <v>2.390759562397951</v>
@@ -88923,7 +88923,7 @@
         <v>2.515914893858527</v>
       </c>
       <c r="D1736" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E1736">
         <v>2.390759562397951</v>
@@ -89323,7 +89323,7 @@
         <v>2.398284925004891</v>
       </c>
       <c r="D1744" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E1744">
         <v>2.323815452683986</v>
@@ -89373,7 +89373,7 @@
         <v>2.59126185659039</v>
       </c>
       <c r="D1745" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E1745">
         <v>2.323815452683986</v>
@@ -89423,7 +89423,7 @@
         <v>2.470622778409881</v>
       </c>
       <c r="D1746" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E1746">
         <v>2.323815452683986</v>
@@ -89473,7 +89473,7 @@
         <v>2.496369048777584</v>
       </c>
       <c r="D1747" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E1747">
         <v>2.323815452683986</v>
@@ -89523,7 +89523,7 @@
         <v>2.511048830530219</v>
       </c>
       <c r="D1748" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E1748">
         <v>2.323815452683986</v>
@@ -89573,7 +89573,7 @@
         <v>2.657431462449994</v>
       </c>
       <c r="D1749" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E1749">
         <v>2.323815452683986</v>
@@ -89673,7 +89673,7 @@
         <v>2.401940005148124</v>
       </c>
       <c r="D1751" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E1751">
         <v>2.192740898235095</v>
@@ -89723,7 +89723,7 @@
         <v>2.595422773717731</v>
       </c>
       <c r="D1752" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E1752">
         <v>2.192740898235095</v>
@@ -89773,7 +89773,7 @@
         <v>2.47500397938514</v>
       </c>
       <c r="D1753" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E1753">
         <v>2.192740898235095</v>
@@ -89823,7 +89823,7 @@
         <v>2.500301523395974</v>
       </c>
       <c r="D1754" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E1754">
         <v>2.192740898235095</v>
@@ -89873,7 +89873,7 @@
         <v>2.515283175606867</v>
       </c>
       <c r="D1755" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E1755">
         <v>2.192740898235095</v>
@@ -89923,7 +89923,7 @@
         <v>2.66176371145905</v>
       </c>
       <c r="D1756" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E1756">
         <v>2.192740898235095</v>
@@ -90023,7 +90023,7 @@
         <v>2.463448425880314</v>
       </c>
       <c r="D1758" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E1758">
         <v>2.25587749011751</v>
@@ -90073,7 +90073,7 @@
         <v>2.605970569024249</v>
       </c>
       <c r="D1759" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E1759">
         <v>2.25587749011751</v>
@@ -90123,7 +90123,7 @@
         <v>2.486110187384356</v>
       </c>
       <c r="D1760" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E1760">
         <v>2.25587749011751</v>
@@ -90173,7 +90173,7 @@
         <v>2.510270224058211</v>
       </c>
       <c r="D1761" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E1761">
         <v>2.25587749011751</v>
@@ -90223,7 +90223,7 @@
         <v>2.526017108477618</v>
       </c>
       <c r="D1762" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E1762">
         <v>2.25587749011751</v>
@@ -90273,7 +90273,7 @@
         <v>2.672745827748777</v>
       </c>
       <c r="D1763" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E1763">
         <v>2.25587749011751</v>
@@ -90373,7 +90373,7 @@
         <v>2.47470153211695</v>
       </c>
       <c r="D1765" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E1765">
         <v>2.200468937898246</v>
@@ -90423,7 +90423,7 @@
         <v>2.618667657919568</v>
       </c>
       <c r="D1766" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E1766">
         <v>2.200468937898246</v>
@@ -90473,7 +90473,7 @@
         <v>2.499479475103545</v>
       </c>
       <c r="D1767" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E1767">
         <v>2.200468937898246</v>
@@ -90523,7 +90523,7 @@
         <v>2.522270217876925</v>
       </c>
       <c r="D1768" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E1768">
         <v>2.200468937898246</v>
@@ -90573,7 +90573,7 @@
         <v>2.53893826364756</v>
       </c>
       <c r="D1769" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E1769">
         <v>2.200468937898246</v>
@@ -90623,7 +90623,7 @@
         <v>2.68596573795155</v>
       </c>
       <c r="D1770" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E1770">
         <v>2.200468937898246</v>
@@ -90723,7 +90723,7 @@
         <v>2.485925008440852</v>
       </c>
       <c r="D1772" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E1772">
         <v>2.299849068754274</v>
@@ -90773,7 +90773,7 @@
         <v>2.631331314833706</v>
       </c>
       <c r="D1773" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E1773">
         <v>2.299849068754274</v>
@@ -90823,7 +90823,7 @@
         <v>2.512813560913137</v>
       </c>
       <c r="D1774" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E1774">
         <v>2.299849068754274</v>
@@ -90873,7 +90873,7 @@
         <v>2.534238615195777</v>
       </c>
       <c r="D1775" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E1775">
         <v>2.299849068754274</v>
@@ -90923,7 +90923,7 @@
         <v>2.551825396860183</v>
       </c>
       <c r="D1776" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E1776">
         <v>2.299849068754274</v>
@@ -90973,7 +90973,7 @@
         <v>2.699150839562153</v>
       </c>
       <c r="D1777" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E1777">
         <v>2.299849068754274</v>
@@ -91023,7 +91023,7 @@
         <v>2.503825014856535</v>
       </c>
       <c r="D1778" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E1778">
         <v>2.106425236226947</v>
@@ -91073,7 +91073,7 @@
         <v>2.651528224727507</v>
       </c>
       <c r="D1779" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E1779">
         <v>2.106425236226947</v>
@@ -91123,7 +91123,7 @@
         <v>2.534079718977786</v>
       </c>
       <c r="D1780" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E1780">
         <v>2.106425236226947</v>
@@ -91173,7 +91173,7 @@
         <v>2.553326675134624</v>
       </c>
       <c r="D1781" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E1781">
         <v>2.423776287736403</v>
@@ -91223,7 +91223,7 @@
         <v>2.572378722810933</v>
       </c>
       <c r="D1782" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E1782">
         <v>2.423776287736403</v>
@@ -91273,7 +91273,7 @@
         <v>2.720179386922169</v>
       </c>
       <c r="D1783" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E1783">
         <v>2.423776287736403</v>
@@ -91323,7 +91323,7 @@
         <v>2.522756364898781</v>
       </c>
       <c r="D1784" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E1784">
         <v>2.133514530710647</v>
@@ -91373,7 +91373,7 @@
         <v>2.672888818801723</v>
       </c>
       <c r="D1785" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E1785">
         <v>2.133514530710647</v>
@@ -91423,7 +91423,7 @@
         <v>2.556571168032402</v>
       </c>
       <c r="D1786" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E1786">
         <v>2.133514530710647</v>
@@ -91473,7 +91473,7 @@
         <v>2.573514530710648</v>
       </c>
       <c r="D1787" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E1787">
         <v>2.416125858174998</v>
@@ -91523,7 +91523,7 @@
         <v>2.594116268545282</v>
       </c>
       <c r="D1788" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E1788">
         <v>2.416125858174998</v>
@@ -91573,7 +91573,7 @@
         <v>2.742419534870029</v>
       </c>
       <c r="D1789" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E1789">
         <v>2.416125858174998</v>
@@ -92423,7 +92423,7 @@
         <v>2.650772333597536</v>
       </c>
       <c r="D1806" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E1806">
         <v>2.833383571522591</v>
@@ -92473,7 +92473,7 @@
         <v>2.677304649662077</v>
       </c>
       <c r="D1807" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E1807">
         <v>2.833383571522591</v>
@@ -92523,7 +92523,7 @@
         <v>2.827531346764091</v>
       </c>
       <c r="D1808" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E1808">
         <v>2.833383571522591</v>
@@ -92573,7 +92573,7 @@
         <v>2.653895750628072</v>
       </c>
       <c r="D1809" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E1809">
         <v>2.833383571522591</v>
@@ -92873,7 +92873,7 @@
         <v>2.665898029451891</v>
       </c>
       <c r="D1815" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E1815">
         <v>2.879475052520711</v>
@@ -92923,7 +92923,7 @@
         <v>2.693591446650479</v>
       </c>
       <c r="D1816" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E1816">
         <v>2.879475052520711</v>
@@ -92973,7 +92973,7 @@
         <v>2.844194717093266</v>
       </c>
       <c r="D1817" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E1817">
         <v>2.879475052520711</v>
@@ -93023,7 +93023,7 @@
         <v>2.670057023169551</v>
       </c>
       <c r="D1818" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E1818">
         <v>2.879475052520711</v>
@@ -93873,7 +93873,7 @@
         <v>2.725439960257261</v>
       </c>
       <c r="D1835" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E1835">
         <v>2.901935221062048</v>
@@ -93923,7 +93923,7 @@
         <v>2.876779612517545</v>
       </c>
       <c r="D1836" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E1836">
         <v>2.901935221062048</v>
@@ -93973,7 +93973,7 @@
         <v>2.701660076170499</v>
       </c>
       <c r="D1837" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E1837">
         <v>2.901935221062048</v>
@@ -94323,7 +94323,7 @@
         <v>2.73783687074571</v>
       </c>
       <c r="D1844" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E1844">
         <v>2.956210584716908</v>
@@ -94373,7 +94373,7 @@
         <v>2.889463156774513</v>
       </c>
       <c r="D1845" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E1845">
         <v>2.956210584716908</v>
@@ -94423,7 +94423,7 @@
         <v>2.713961442069443</v>
       </c>
       <c r="D1846" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E1846">
         <v>2.956210584716908</v>
@@ -94923,7 +94923,7 @@
         <v>3.407374629880873</v>
       </c>
       <c r="D1856" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E1856">
         <v>4.283476499208186</v>
@@ -94973,7 +94973,7 @@
         <v>3.452558829275786</v>
       </c>
       <c r="D1857" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E1857">
         <v>4.283476499208186</v>
@@ -95023,7 +95023,7 @@
         <v>3.353761115905974</v>
       </c>
       <c r="D1858" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E1858">
         <v>4.283476499208186</v>
@@ -95123,7 +95123,7 @@
         <v>3.389125787556829</v>
       </c>
       <c r="D1860" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E1860">
         <v>4.260082306604806</v>
@@ -95173,7 +95173,7 @@
         <v>3.433761149588613</v>
       </c>
       <c r="D1861" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E1861">
         <v>4.260082306604806</v>
@@ -95223,7 +95223,7 @@
         <v>3.334174482509303</v>
       </c>
       <c r="D1862" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E1862">
         <v>4.260082306604806</v>
@@ -95323,7 +95323,7 @@
         <v>3.382043198388447</v>
       </c>
       <c r="D1864" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E1864">
         <v>4.251002746806242</v>
@@ -95373,7 +95373,7 @@
         <v>3.426465550219678</v>
       </c>
       <c r="D1865" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E1865">
         <v>4.251002746806242</v>
@@ -95423,7 +95423,7 @@
         <v>3.326572680977073</v>
       </c>
       <c r="D1866" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E1866">
         <v>4.251002746806242</v>
@@ -95520,40 +95520,40 @@
         <v>254</v>
       </c>
       <c r="C1868">
-        <v>0.6568702640387971</v>
+        <v>0.6849364223984344</v>
       </c>
       <c r="D1868" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E1868">
-        <v>0.9191412611209433</v>
+        <v>0.9943002933764404</v>
       </c>
       <c r="F1868">
         <v>1</v>
       </c>
       <c r="G1868">
-        <v>0.007903129735961203</v>
+        <v>0.008055063577601565</v>
       </c>
       <c r="H1868">
-        <v>0.009140858738879057</v>
+        <v>0.009045699706623559</v>
       </c>
       <c r="I1868">
-        <v>0.2622709970821462</v>
+        <v>0.309363870978006</v>
       </c>
       <c r="J1868">
         <v>0.7741730205045306</v>
       </c>
       <c r="K1868">
-        <v>4.68</v>
+        <v>4.76</v>
       </c>
       <c r="L1868">
-        <v>4.28</v>
+        <v>4.37</v>
       </c>
       <c r="M1868">
-        <v>5.31</v>
+        <v>5.2</v>
       </c>
       <c r="N1868">
-        <v>5.03</v>
+        <v>5.02</v>
       </c>
       <c r="O1868">
         <v>1</v>
@@ -95570,40 +95570,40 @@
         <v>255</v>
       </c>
       <c r="C1869">
-        <v>1.340140000159101</v>
+        <v>0.6568702640387971</v>
       </c>
       <c r="D1869" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E1869">
-        <v>1.292678152603479</v>
+        <v>0.9943002933764404</v>
       </c>
       <c r="F1869">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1869">
-        <v>0.0118998599998409</v>
+        <v>0.007903129735961203</v>
       </c>
       <c r="H1869">
-        <v>0.00864732184739652</v>
+        <v>0.009045699706623559</v>
       </c>
       <c r="I1869">
-        <v>0.04746184755562188</v>
+        <v>0.3374300293376433</v>
       </c>
       <c r="J1869">
         <v>0.7741730205045306</v>
       </c>
       <c r="K1869">
-        <v>6.82</v>
+        <v>4.68</v>
       </c>
       <c r="L1869">
-        <v>6.62</v>
+        <v>4.28</v>
       </c>
       <c r="M1869">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="N1869">
-        <v>4.97</v>
+        <v>5.02</v>
       </c>
       <c r="O1869">
         <v>1</v>
@@ -95614,146 +95614,146 @@
     </row>
     <row r="1870" spans="1:16">
       <c r="A1870" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1870" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C1870">
-        <v>0.5331535880095641</v>
+        <v>1.340140000159101</v>
       </c>
       <c r="D1870" t="s">
-        <v>246</v>
+        <v>438</v>
       </c>
       <c r="E1870">
-        <v>0.9386915979436754</v>
+        <v>1.22106873911771</v>
       </c>
       <c r="F1870">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1870">
-        <v>0.008546846411990437</v>
+        <v>0.0118998599998409</v>
       </c>
       <c r="H1870">
-        <v>0.009061308402056325</v>
+        <v>0.008838931260882291</v>
       </c>
       <c r="I1870">
-        <v>0.4055380099341113</v>
+        <v>0.1190712610413915</v>
       </c>
       <c r="J1870">
-        <v>0.7780284295127059</v>
+        <v>0.7741730205045306</v>
       </c>
       <c r="K1870">
-        <v>5.15</v>
+        <v>6.82</v>
       </c>
       <c r="L1870">
-        <v>4.54</v>
+        <v>6.62</v>
       </c>
       <c r="M1870">
-        <v>5.22</v>
+        <v>4.92</v>
       </c>
       <c r="N1870">
-        <v>5</v>
+        <v>5.03</v>
       </c>
       <c r="O1870">
         <v>1</v>
       </c>
       <c r="P1870" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="1871" spans="1:16">
       <c r="A1871" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B1871" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1871">
-        <v>0.6665846755195202</v>
+        <v>1.233994956152635</v>
       </c>
       <c r="D1871" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E1871">
-        <v>0.9742521665339288</v>
+        <v>1.22106873911771</v>
       </c>
       <c r="F1871">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1871">
-        <v>0.008073415324480481</v>
+        <v>0.01058600504384737</v>
       </c>
       <c r="H1871">
-        <v>0.009065747833466069</v>
+        <v>0.008838931260882291</v>
       </c>
       <c r="I1871">
-        <v>0.3076674910144086</v>
+        <v>0.0129262170349258</v>
       </c>
       <c r="J1871">
-        <v>0.7780284295127059</v>
+        <v>0.7741730205045306</v>
       </c>
       <c r="K1871">
-        <v>4.76</v>
+        <v>6.04</v>
       </c>
       <c r="L1871">
-        <v>4.37</v>
+        <v>5.91</v>
       </c>
       <c r="M1871">
-        <v>5.2</v>
+        <v>4.92</v>
       </c>
       <c r="N1871">
-        <v>5.02</v>
+        <v>5.03</v>
       </c>
       <c r="O1871">
         <v>1</v>
       </c>
       <c r="P1871" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="1872" spans="1:16">
       <c r="A1872" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1872" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C1872">
-        <v>0.6388269498805368</v>
+        <v>0.5331535880095641</v>
       </c>
       <c r="D1872" t="s">
-        <v>434</v>
+        <v>246</v>
       </c>
       <c r="E1872">
-        <v>0.9742521665339288</v>
+        <v>0.9386915979436754</v>
       </c>
       <c r="F1872">
         <v>1</v>
       </c>
       <c r="G1872">
-        <v>0.007921173050119464</v>
+        <v>0.008546846411990437</v>
       </c>
       <c r="H1872">
-        <v>0.009065747833466069</v>
+        <v>0.009061308402056325</v>
       </c>
       <c r="I1872">
-        <v>0.335425216653392</v>
+        <v>0.4055380099341113</v>
       </c>
       <c r="J1872">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1872">
-        <v>4.68</v>
+        <v>5.15</v>
       </c>
       <c r="L1872">
-        <v>4.28</v>
+        <v>4.54</v>
       </c>
       <c r="M1872">
-        <v>5.2</v>
+        <v>5.22</v>
       </c>
       <c r="N1872">
-        <v>5.02</v>
+        <v>5</v>
       </c>
       <c r="O1872">
         <v>1</v>
@@ -95764,46 +95764,46 @@
     </row>
     <row r="1873" spans="1:16">
       <c r="A1873" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1873" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C1873">
-        <v>1.313846110723346</v>
+        <v>0.6665846755195202</v>
       </c>
       <c r="D1873" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E1873">
-        <v>1.274364959814647</v>
+        <v>0.9742521665339288</v>
       </c>
       <c r="F1873">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1873">
-        <v>0.01192615388927666</v>
+        <v>0.008073415324480481</v>
       </c>
       <c r="H1873">
-        <v>0.008665635040185355</v>
+        <v>0.009065747833466069</v>
       </c>
       <c r="I1873">
-        <v>0.03948115090869919</v>
+        <v>0.3076674910144086</v>
       </c>
       <c r="J1873">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1873">
-        <v>6.82</v>
+        <v>4.76</v>
       </c>
       <c r="L1873">
-        <v>6.62</v>
+        <v>4.37</v>
       </c>
       <c r="M1873">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="N1873">
-        <v>4.97</v>
+        <v>5.02</v>
       </c>
       <c r="O1873">
         <v>1</v>
@@ -95814,46 +95814,46 @@
     </row>
     <row r="1874" spans="1:16">
       <c r="A1874" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1874" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C1874">
-        <v>1.210708285743256</v>
+        <v>0.6388269498805368</v>
       </c>
       <c r="D1874" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E1874">
-        <v>1.274364959814647</v>
+        <v>0.9742521665339288</v>
       </c>
       <c r="F1874">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1874">
-        <v>0.01060929171425675</v>
+        <v>0.007921173050119464</v>
       </c>
       <c r="H1874">
-        <v>0.008665635040185355</v>
+        <v>0.009065747833466069</v>
       </c>
       <c r="I1874">
-        <v>-0.06365667407139064</v>
+        <v>0.335425216653392</v>
       </c>
       <c r="J1874">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1874">
-        <v>6.04</v>
+        <v>4.68</v>
       </c>
       <c r="L1874">
-        <v>5.91</v>
+        <v>4.28</v>
       </c>
       <c r="M1874">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="N1874">
-        <v>4.97</v>
+        <v>5.02</v>
       </c>
       <c r="O1874">
         <v>1</v>
@@ -95864,116 +95864,116 @@
     </row>
     <row r="1875" spans="1:16">
       <c r="A1875" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1875" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C1875">
-        <v>0.6331641874895779</v>
+        <v>1.313846110723346</v>
       </c>
       <c r="D1875" t="s">
-        <v>246</v>
+        <v>438</v>
       </c>
       <c r="E1875">
-        <v>0.8906095068071913</v>
+        <v>1.202100126797487</v>
       </c>
       <c r="F1875">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1875">
-        <v>0.008426835812510422</v>
+        <v>0.01192615388927666</v>
       </c>
       <c r="H1875">
-        <v>0.00910939049319281</v>
+        <v>0.008857899873202513</v>
       </c>
       <c r="I1875">
-        <v>0.2574453193176134</v>
+        <v>0.1117459839258585</v>
       </c>
       <c r="J1875">
-        <v>0.7872395580829136</v>
+        <v>0.7780284295127059</v>
       </c>
       <c r="K1875">
-        <v>4.95</v>
+        <v>6.82</v>
       </c>
       <c r="L1875">
-        <v>4.53</v>
+        <v>6.62</v>
       </c>
       <c r="M1875">
-        <v>5.22</v>
+        <v>4.92</v>
       </c>
       <c r="N1875">
-        <v>5</v>
+        <v>5.03</v>
       </c>
       <c r="O1875">
         <v>1</v>
       </c>
       <c r="P1875" t="s">
-        <v>253</v>
+        <v>421</v>
       </c>
     </row>
     <row r="1876" spans="1:16">
       <c r="A1876" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B1876" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1876">
-        <v>0.6227397035253315</v>
+        <v>1.210708285743256</v>
       </c>
       <c r="D1876" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E1876">
-        <v>0.9263542979688486</v>
+        <v>1.202100126797487</v>
       </c>
       <c r="F1876">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1876">
-        <v>0.008117260296474669</v>
+        <v>0.01060929171425675</v>
       </c>
       <c r="H1876">
-        <v>0.00911364570203115</v>
+        <v>0.008857899873202513</v>
       </c>
       <c r="I1876">
-        <v>0.3036145944435171</v>
+        <v>0.008608158945768718</v>
       </c>
       <c r="J1876">
-        <v>0.7872395580829136</v>
+        <v>0.7780284295127059</v>
       </c>
       <c r="K1876">
-        <v>4.76</v>
+        <v>6.04</v>
       </c>
       <c r="L1876">
-        <v>4.37</v>
+        <v>5.91</v>
       </c>
       <c r="M1876">
-        <v>5.2</v>
+        <v>4.92</v>
       </c>
       <c r="N1876">
-        <v>5.02</v>
+        <v>5.03</v>
       </c>
       <c r="O1876">
         <v>1</v>
       </c>
       <c r="P1876" t="s">
-        <v>253</v>
+        <v>421</v>
       </c>
     </row>
     <row r="1877" spans="1:16">
       <c r="A1877" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1877" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C1877">
-        <v>0.6352917919087488</v>
+        <v>0.6227397035253315</v>
       </c>
       <c r="D1877" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E1877">
         <v>0.9263542979688486</v>
@@ -95982,22 +95982,22 @@
         <v>1</v>
       </c>
       <c r="G1877">
-        <v>0.008444708208091251</v>
+        <v>0.008117260296474669</v>
       </c>
       <c r="H1877">
         <v>0.00911364570203115</v>
       </c>
       <c r="I1877">
-        <v>0.2910625060600998</v>
+        <v>0.3036145944435171</v>
       </c>
       <c r="J1877">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1877">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="L1877">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1877">
         <v>5.2</v>
@@ -96014,46 +96014,46 @@
     </row>
     <row r="1878" spans="1:16">
       <c r="A1878" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1878" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C1878">
-        <v>1.251026213874529</v>
+        <v>0.6352917919087488</v>
       </c>
       <c r="D1878" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E1878">
-        <v>1.23061209910616</v>
+        <v>0.9263542979688486</v>
       </c>
       <c r="F1878">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1878">
-        <v>0.01198897378612547</v>
+        <v>0.008444708208091251</v>
       </c>
       <c r="H1878">
-        <v>0.008709387900893839</v>
+        <v>0.00911364570203115</v>
       </c>
       <c r="I1878">
-        <v>0.02041411476836874</v>
+        <v>0.2910625060600998</v>
       </c>
       <c r="J1878">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1878">
-        <v>6.82</v>
+        <v>4.96</v>
       </c>
       <c r="L1878">
-        <v>6.62</v>
+        <v>4.54</v>
       </c>
       <c r="M1878">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="N1878">
-        <v>4.97</v>
+        <v>5.02</v>
       </c>
       <c r="O1878">
         <v>1</v>
@@ -96064,46 +96064,46 @@
     </row>
     <row r="1879" spans="1:16">
       <c r="A1879" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1879" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1879">
-        <v>1.155073069179202</v>
+        <v>1.251026213874529</v>
       </c>
       <c r="D1879" t="s">
         <v>438</v>
       </c>
       <c r="E1879">
-        <v>1.23061209910616</v>
+        <v>1.156781374232065</v>
       </c>
       <c r="F1879">
         <v>-1</v>
       </c>
       <c r="G1879">
-        <v>0.0106649269308208</v>
+        <v>0.01198897378612547</v>
       </c>
       <c r="H1879">
-        <v>0.008709387900893839</v>
+        <v>0.008903218625767935</v>
       </c>
       <c r="I1879">
-        <v>-0.07553902992695871</v>
+        <v>0.09424483964246377</v>
       </c>
       <c r="J1879">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1879">
-        <v>6.04</v>
+        <v>6.82</v>
       </c>
       <c r="L1879">
-        <v>5.91</v>
+        <v>6.62</v>
       </c>
       <c r="M1879">
-        <v>4.75</v>
+        <v>4.92</v>
       </c>
       <c r="N1879">
-        <v>4.97</v>
+        <v>5.03</v>
       </c>
       <c r="O1879">
         <v>1</v>
@@ -96114,66 +96114,66 @@
     </row>
     <row r="1880" spans="1:16">
       <c r="A1880" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1880" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1880">
-        <v>0.5854580999890051</v>
+        <v>1.155073069179202</v>
       </c>
       <c r="D1880" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E1880">
-        <v>0.8856264957863074</v>
+        <v>1.156781374232065</v>
       </c>
       <c r="F1880">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1880">
-        <v>0.008154541900010996</v>
+        <v>0.0106649269308208</v>
       </c>
       <c r="H1880">
-        <v>0.00915437350421369</v>
+        <v>0.008903218625767935</v>
       </c>
       <c r="I1880">
-        <v>0.3001683957973023</v>
+        <v>-0.001708305052863679</v>
       </c>
       <c r="J1880">
-        <v>0.7950718277334023</v>
+        <v>0.7872395580829136</v>
       </c>
       <c r="K1880">
-        <v>4.76</v>
+        <v>6.04</v>
       </c>
       <c r="L1880">
-        <v>4.37</v>
+        <v>5.91</v>
       </c>
       <c r="M1880">
-        <v>5.2</v>
+        <v>4.92</v>
       </c>
       <c r="N1880">
-        <v>5.02</v>
+        <v>5.03</v>
       </c>
       <c r="O1880">
         <v>1</v>
       </c>
       <c r="P1880" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
     </row>
     <row r="1881" spans="1:16">
       <c r="A1881" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1881" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C1881">
-        <v>0.5964437344423246</v>
+        <v>0.5854580999890051</v>
       </c>
       <c r="D1881" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E1881">
         <v>0.8856264957863074</v>
@@ -96182,22 +96182,22 @@
         <v>1</v>
       </c>
       <c r="G1881">
-        <v>0.008483556265557676</v>
+        <v>0.008154541900010996</v>
       </c>
       <c r="H1881">
         <v>0.00915437350421369</v>
       </c>
       <c r="I1881">
-        <v>0.2891827613439828</v>
+        <v>0.3001683957973023</v>
       </c>
       <c r="J1881">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1881">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="L1881">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1881">
         <v>5.2</v>
@@ -96214,46 +96214,46 @@
     </row>
     <row r="1882" spans="1:16">
       <c r="A1882" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1882" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C1882">
-        <v>1.197610134858196</v>
+        <v>0.5964437344423246</v>
       </c>
       <c r="D1882" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E1882">
-        <v>1.193408818266338</v>
+        <v>0.8856264957863074</v>
       </c>
       <c r="F1882">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1882">
-        <v>0.0120423898651418</v>
+        <v>0.008483556265557676</v>
       </c>
       <c r="H1882">
-        <v>0.008746591181733661</v>
+        <v>0.00915437350421369</v>
       </c>
       <c r="I1882">
-        <v>0.004201316591857296</v>
+        <v>0.2891827613439828</v>
       </c>
       <c r="J1882">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1882">
-        <v>6.82</v>
+        <v>4.96</v>
       </c>
       <c r="L1882">
-        <v>6.62</v>
+        <v>4.54</v>
       </c>
       <c r="M1882">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="N1882">
-        <v>4.97</v>
+        <v>5.02</v>
       </c>
       <c r="O1882">
         <v>1</v>
@@ -96264,46 +96264,46 @@
     </row>
     <row r="1883" spans="1:16">
       <c r="A1883" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1883" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C1883">
-        <v>1.200061850826246</v>
+        <v>1.197610134858196</v>
       </c>
       <c r="D1883" t="s">
         <v>438</v>
       </c>
       <c r="E1883">
-        <v>1.193408818266338</v>
+        <v>1.118246607551661</v>
       </c>
       <c r="F1883">
         <v>-1</v>
       </c>
       <c r="G1883">
-        <v>0.01089993814917375</v>
+        <v>0.0120423898651418</v>
       </c>
       <c r="H1883">
-        <v>0.008746591181733661</v>
+        <v>0.008941753392448341</v>
       </c>
       <c r="I1883">
-        <v>0.006653032559907235</v>
+        <v>0.07936352730653518</v>
       </c>
       <c r="J1883">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1883">
-        <v>6.1</v>
+        <v>6.82</v>
       </c>
       <c r="L1883">
-        <v>6.05</v>
+        <v>6.62</v>
       </c>
       <c r="M1883">
-        <v>4.75</v>
+        <v>4.92</v>
       </c>
       <c r="N1883">
-        <v>4.97</v>
+        <v>5.03</v>
       </c>
       <c r="O1883">
         <v>1</v>
@@ -96314,46 +96314,46 @@
     </row>
     <row r="1884" spans="1:16">
       <c r="A1884" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1884" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C1884">
-        <v>1.10776616049025</v>
+        <v>1.200061850826246</v>
       </c>
       <c r="D1884" t="s">
         <v>438</v>
       </c>
       <c r="E1884">
-        <v>1.193408818266338</v>
+        <v>1.118246607551661</v>
       </c>
       <c r="F1884">
         <v>-1</v>
       </c>
       <c r="G1884">
-        <v>0.01071223383950975</v>
+        <v>0.01089993814917375</v>
       </c>
       <c r="H1884">
-        <v>0.008746591181733661</v>
+        <v>0.008941753392448341</v>
       </c>
       <c r="I1884">
-        <v>-0.08564265777608826</v>
+        <v>0.08181524327458511</v>
       </c>
       <c r="J1884">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1884">
-        <v>6.04</v>
+        <v>6.1</v>
       </c>
       <c r="L1884">
-        <v>5.91</v>
+        <v>6.05</v>
       </c>
       <c r="M1884">
-        <v>4.75</v>
+        <v>4.92</v>
       </c>
       <c r="N1884">
-        <v>4.97</v>
+        <v>5.03</v>
       </c>
       <c r="O1884">
         <v>1</v>
@@ -96364,66 +96364,66 @@
     </row>
     <row r="1885" spans="1:16">
       <c r="A1885" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1885" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1885">
-        <v>0.5696561779646796</v>
+        <v>1.10776616049025</v>
       </c>
       <c r="D1885" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E1885">
-        <v>0.8683638918941865</v>
+        <v>1.118246607551661</v>
       </c>
       <c r="F1885">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1885">
-        <v>0.00817034382203532</v>
+        <v>0.01071223383950975</v>
       </c>
       <c r="H1885">
-        <v>0.009171636108105811</v>
+        <v>0.008941753392448341</v>
       </c>
       <c r="I1885">
-        <v>0.2987077139295069</v>
+        <v>-0.01048044706141038</v>
       </c>
       <c r="J1885">
-        <v>0.7983915592511178</v>
+        <v>0.7950718277334023</v>
       </c>
       <c r="K1885">
-        <v>4.76</v>
+        <v>6.04</v>
       </c>
       <c r="L1885">
-        <v>4.37</v>
+        <v>5.91</v>
       </c>
       <c r="M1885">
-        <v>5.2</v>
+        <v>4.92</v>
       </c>
       <c r="N1885">
-        <v>5.02</v>
+        <v>5.03</v>
       </c>
       <c r="O1885">
         <v>1</v>
       </c>
       <c r="P1885" t="s">
-        <v>423</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1886" spans="1:16">
       <c r="A1886" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1886" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C1886">
-        <v>0.5799778661144557</v>
+        <v>0.5696561779646796</v>
       </c>
       <c r="D1886" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E1886">
         <v>0.8683638918941865</v>
@@ -96432,22 +96432,22 @@
         <v>1</v>
       </c>
       <c r="G1886">
-        <v>0.008500022133885544</v>
+        <v>0.00817034382203532</v>
       </c>
       <c r="H1886">
         <v>0.009171636108105811</v>
       </c>
       <c r="I1886">
-        <v>0.2883860257797308</v>
+        <v>0.2987077139295069</v>
       </c>
       <c r="J1886">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1886">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="L1886">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1886">
         <v>5.2</v>
@@ -96464,16 +96464,16 @@
     </row>
     <row r="1887" spans="1:16">
       <c r="A1887" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1887" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1887">
-        <v>0.6039296128919895</v>
+        <v>0.5799778661144557</v>
       </c>
       <c r="D1887" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E1887">
         <v>0.8683638918941865</v>
@@ -96482,19 +96482,19 @@
         <v>1</v>
       </c>
       <c r="G1887">
-        <v>0.008476070387108009</v>
+        <v>0.008500022133885544</v>
       </c>
       <c r="H1887">
         <v>0.009171636108105811</v>
       </c>
       <c r="I1887">
-        <v>0.264434279002197</v>
+        <v>0.2883860257797308</v>
       </c>
       <c r="J1887">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1887">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="L1887">
         <v>4.54</v>
@@ -96514,46 +96514,46 @@
     </row>
     <row r="1888" spans="1:16">
       <c r="A1888" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1888" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C1888">
-        <v>1.174969565907376</v>
+        <v>0.6039296128919895</v>
       </c>
       <c r="D1888" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E1888">
-        <v>1.17764009355719</v>
+        <v>0.8683638918941865</v>
       </c>
       <c r="F1888">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1888">
-        <v>0.01206503043409262</v>
+        <v>0.008476070387108009</v>
       </c>
       <c r="H1888">
-        <v>0.008762359906442809</v>
+        <v>0.009171636108105811</v>
       </c>
       <c r="I1888">
-        <v>-0.002670527649814236</v>
+        <v>0.264434279002197</v>
       </c>
       <c r="J1888">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1888">
-        <v>6.82</v>
+        <v>4.93</v>
       </c>
       <c r="L1888">
-        <v>6.62</v>
+        <v>4.54</v>
       </c>
       <c r="M1888">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="N1888">
-        <v>4.97</v>
+        <v>5.02</v>
       </c>
       <c r="O1888">
         <v>1</v>
@@ -96564,46 +96564,46 @@
     </row>
     <row r="1889" spans="1:16">
       <c r="A1889" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1889" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C1889">
-        <v>1.179811488568181</v>
+        <v>1.174969565907376</v>
       </c>
       <c r="D1889" t="s">
         <v>438</v>
       </c>
       <c r="E1889">
-        <v>1.17764009355719</v>
+        <v>1.101913528484501</v>
       </c>
       <c r="F1889">
         <v>-1</v>
       </c>
       <c r="G1889">
-        <v>0.01092018851143182</v>
+        <v>0.01206503043409262</v>
       </c>
       <c r="H1889">
-        <v>0.008762359906442809</v>
+        <v>0.008958086471515501</v>
       </c>
       <c r="I1889">
-        <v>0.002171395010991173</v>
+        <v>0.07305603742287525</v>
       </c>
       <c r="J1889">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1889">
-        <v>6.1</v>
+        <v>6.82</v>
       </c>
       <c r="L1889">
-        <v>6.05</v>
+        <v>6.62</v>
       </c>
       <c r="M1889">
-        <v>4.75</v>
+        <v>4.92</v>
       </c>
       <c r="N1889">
-        <v>4.97</v>
+        <v>5.03</v>
       </c>
       <c r="O1889">
         <v>1</v>
@@ -96614,46 +96614,46 @@
     </row>
     <row r="1890" spans="1:16">
       <c r="A1890" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1890" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C1890">
-        <v>1.087714982123249</v>
+        <v>1.179811488568181</v>
       </c>
       <c r="D1890" t="s">
         <v>438</v>
       </c>
       <c r="E1890">
-        <v>1.17764009355719</v>
+        <v>1.101913528484501</v>
       </c>
       <c r="F1890">
         <v>-1</v>
       </c>
       <c r="G1890">
-        <v>0.01073228501787675</v>
+        <v>0.01092018851143182</v>
       </c>
       <c r="H1890">
-        <v>0.008762359906442809</v>
+        <v>0.008958086471515501</v>
       </c>
       <c r="I1890">
-        <v>-0.08992511143394166</v>
+        <v>0.07789796008368066</v>
       </c>
       <c r="J1890">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1890">
-        <v>6.04</v>
+        <v>6.1</v>
       </c>
       <c r="L1890">
-        <v>5.91</v>
+        <v>6.05</v>
       </c>
       <c r="M1890">
-        <v>4.75</v>
+        <v>4.92</v>
       </c>
       <c r="N1890">
-        <v>4.97</v>
+        <v>5.03</v>
       </c>
       <c r="O1890">
         <v>1</v>
@@ -96664,66 +96664,66 @@
     </row>
     <row r="1891" spans="1:16">
       <c r="A1891" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1891" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1891">
-        <v>0.4754849636079563</v>
+        <v>1.087714982123249</v>
       </c>
       <c r="D1891" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E1891">
-        <v>0.7654877753700351</v>
+        <v>1.101913528484501</v>
       </c>
       <c r="F1891">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1891">
-        <v>0.008264515036392044</v>
+        <v>0.01073228501787675</v>
       </c>
       <c r="H1891">
-        <v>0.009274512224629964</v>
+        <v>0.008958086471515501</v>
       </c>
       <c r="I1891">
-        <v>0.2900028117620788</v>
+        <v>-0.01419854636125217</v>
       </c>
       <c r="J1891">
-        <v>0.8181754278134546</v>
+        <v>0.7983915592511178</v>
       </c>
       <c r="K1891">
-        <v>4.76</v>
+        <v>6.04</v>
       </c>
       <c r="L1891">
-        <v>4.37</v>
+        <v>5.91</v>
       </c>
       <c r="M1891">
-        <v>5.2</v>
+        <v>4.92</v>
       </c>
       <c r="N1891">
-        <v>5.02</v>
+        <v>5.03</v>
       </c>
       <c r="O1891">
         <v>1</v>
       </c>
       <c r="P1891" t="s">
-        <v>246</v>
+        <v>423</v>
       </c>
     </row>
     <row r="1892" spans="1:16">
       <c r="A1892" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1892" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C1892">
-        <v>0.4818498780452654</v>
+        <v>0.4754849636079563</v>
       </c>
       <c r="D1892" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E1892">
         <v>0.7654877753700351</v>
@@ -96732,22 +96732,22 @@
         <v>1</v>
       </c>
       <c r="G1892">
-        <v>0.008598150121954735</v>
+        <v>0.008264515036392044</v>
       </c>
       <c r="H1892">
         <v>0.009274512224629964</v>
       </c>
       <c r="I1892">
-        <v>0.2836378973247697</v>
+        <v>0.2900028117620788</v>
       </c>
       <c r="J1892">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1892">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="L1892">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1892">
         <v>5.2</v>
@@ -96764,16 +96764,16 @@
     </row>
     <row r="1893" spans="1:16">
       <c r="A1893" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1893" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1893">
-        <v>0.5063951408796692</v>
+        <v>0.4818498780452654</v>
       </c>
       <c r="D1893" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E1893">
         <v>0.7654877753700351</v>
@@ -96782,19 +96782,19 @@
         <v>1</v>
       </c>
       <c r="G1893">
-        <v>0.008573604859120331</v>
+        <v>0.008598150121954735</v>
       </c>
       <c r="H1893">
         <v>0.009274512224629964</v>
       </c>
       <c r="I1893">
-        <v>0.2590926344903659</v>
+        <v>0.2836378973247697</v>
       </c>
       <c r="J1893">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1893">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="L1893">
         <v>4.54</v>
@@ -96814,46 +96814,46 @@
     </row>
     <row r="1894" spans="1:16">
       <c r="A1894" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1894" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C1894">
-        <v>1.040043582312239</v>
+        <v>0.5063951408796692</v>
       </c>
       <c r="D1894" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E1894">
-        <v>1.08366671788609</v>
+        <v>0.7654877753700351</v>
       </c>
       <c r="F1894">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1894">
-        <v>0.01219995641768776</v>
+        <v>0.008573604859120331</v>
       </c>
       <c r="H1894">
-        <v>0.008856333282113908</v>
+        <v>0.009274512224629964</v>
       </c>
       <c r="I1894">
-        <v>-0.043623135573851</v>
+        <v>0.2590926344903659</v>
       </c>
       <c r="J1894">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1894">
-        <v>6.82</v>
+        <v>4.93</v>
       </c>
       <c r="L1894">
-        <v>6.62</v>
+        <v>4.54</v>
       </c>
       <c r="M1894">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="N1894">
-        <v>4.97</v>
+        <v>5.02</v>
       </c>
       <c r="O1894">
         <v>1</v>
@@ -96864,46 +96864,46 @@
     </row>
     <row r="1895" spans="1:16">
       <c r="A1895" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1895" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C1895">
-        <v>1.059129890337926</v>
+        <v>1.040043582312239</v>
       </c>
       <c r="D1895" t="s">
         <v>438</v>
       </c>
       <c r="E1895">
-        <v>1.08366671788609</v>
+        <v>1.004576895157803</v>
       </c>
       <c r="F1895">
         <v>-1</v>
       </c>
       <c r="G1895">
-        <v>0.01104087010966207</v>
+        <v>0.01219995641768776</v>
       </c>
       <c r="H1895">
-        <v>0.008856333282113908</v>
+        <v>0.009055423104842199</v>
       </c>
       <c r="I1895">
-        <v>-0.02453682754816366</v>
+        <v>0.03546668715443602</v>
       </c>
       <c r="J1895">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1895">
-        <v>6.1</v>
+        <v>6.82</v>
       </c>
       <c r="L1895">
-        <v>6.05</v>
+        <v>6.62</v>
       </c>
       <c r="M1895">
-        <v>4.75</v>
+        <v>4.92</v>
       </c>
       <c r="N1895">
-        <v>4.97</v>
+        <v>5.03</v>
       </c>
       <c r="O1895">
         <v>1</v>
@@ -96914,46 +96914,46 @@
     </row>
     <row r="1896" spans="1:16">
       <c r="A1896" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1896" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C1896">
-        <v>0.9682204160067345</v>
+        <v>1.059129890337926</v>
       </c>
       <c r="D1896" t="s">
         <v>438</v>
       </c>
       <c r="E1896">
-        <v>1.08366671788609</v>
+        <v>1.004576895157803</v>
       </c>
       <c r="F1896">
         <v>-1</v>
       </c>
       <c r="G1896">
-        <v>0.01085177958399327</v>
+        <v>0.01104087010966207</v>
       </c>
       <c r="H1896">
-        <v>0.008856333282113908</v>
+        <v>0.009055423104842199</v>
       </c>
       <c r="I1896">
-        <v>-0.1154463018793557</v>
+        <v>0.05455299518012335</v>
       </c>
       <c r="J1896">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1896">
-        <v>6.04</v>
+        <v>6.1</v>
       </c>
       <c r="L1896">
-        <v>5.91</v>
+        <v>6.05</v>
       </c>
       <c r="M1896">
-        <v>4.75</v>
+        <v>4.92</v>
       </c>
       <c r="N1896">
-        <v>4.97</v>
+        <v>5.03</v>
       </c>
       <c r="O1896">
         <v>1</v>
@@ -96964,66 +96964,66 @@
     </row>
     <row r="1897" spans="1:16">
       <c r="A1897" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1897" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C1897">
-        <v>0.479362541377431</v>
+        <v>0.9682204160067345</v>
       </c>
       <c r="D1897" t="s">
-        <v>255</v>
+        <v>438</v>
       </c>
       <c r="E1897">
-        <v>0.8503069233264586</v>
+        <v>1.004576895157803</v>
       </c>
       <c r="F1897">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1897">
-        <v>0.01014063745862257</v>
+        <v>0.01085177958399327</v>
       </c>
       <c r="H1897">
-        <v>0.01238969307667354</v>
+        <v>0.009055423104842199</v>
       </c>
       <c r="I1897">
-        <v>0.3709443819490277</v>
+        <v>-0.03635647915106865</v>
       </c>
       <c r="J1897">
-        <v>0.8459960522981732</v>
+        <v>0.8181754278134546</v>
       </c>
       <c r="K1897">
-        <v>5.71</v>
+        <v>6.04</v>
       </c>
       <c r="L1897">
-        <v>5.31</v>
+        <v>5.91</v>
       </c>
       <c r="M1897">
-        <v>6.82</v>
+        <v>4.92</v>
       </c>
       <c r="N1897">
-        <v>6.62</v>
+        <v>5.03</v>
       </c>
       <c r="O1897">
         <v>1</v>
       </c>
       <c r="P1897" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="1898" spans="1:16">
       <c r="A1898" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1898" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C1898">
-        <v>0.4840236862109606</v>
+        <v>0.479362541377431</v>
       </c>
       <c r="D1898" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E1898">
         <v>0.8503069233264586</v>
@@ -97032,22 +97032,22 @@
         <v>1</v>
       </c>
       <c r="G1898">
-        <v>0.01063597631378904</v>
+        <v>0.01014063745862257</v>
       </c>
       <c r="H1898">
         <v>0.01238969307667354</v>
       </c>
       <c r="I1898">
-        <v>0.366283237115498</v>
+        <v>0.3709443819490277</v>
       </c>
       <c r="J1898">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1898">
-        <v>6</v>
+        <v>5.71</v>
       </c>
       <c r="L1898">
-        <v>5.56</v>
+        <v>5.31</v>
       </c>
       <c r="M1898">
         <v>6.82</v>
@@ -97064,46 +97064,46 @@
     </row>
     <row r="1899" spans="1:16">
       <c r="A1899" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1899" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1899">
-        <v>0.8894240809811436</v>
+        <v>0.4840236862109606</v>
       </c>
       <c r="D1899" t="s">
-        <v>438</v>
+        <v>256</v>
       </c>
       <c r="E1899">
-        <v>0.9515187515836772</v>
+        <v>0.8503069233264586</v>
       </c>
       <c r="F1899">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1899">
-        <v>0.01121057591901886</v>
+        <v>0.01063597631378904</v>
       </c>
       <c r="H1899">
-        <v>0.008988481248416322</v>
+        <v>0.01238969307667354</v>
       </c>
       <c r="I1899">
-        <v>-0.0620946706025336</v>
+        <v>0.366283237115498</v>
       </c>
       <c r="J1899">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1899">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="L1899">
-        <v>6.05</v>
+        <v>5.56</v>
       </c>
       <c r="M1899">
-        <v>4.75</v>
+        <v>6.82</v>
       </c>
       <c r="N1899">
-        <v>4.97</v>
+        <v>6.62</v>
       </c>
       <c r="O1899">
         <v>1</v>
@@ -97114,51 +97114,151 @@
     </row>
     <row r="1900" spans="1:16">
       <c r="A1900" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1900" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1900">
-        <v>1.019321514974956</v>
+        <v>0.9041057390159111</v>
       </c>
       <c r="D1900" t="s">
         <v>438</v>
       </c>
       <c r="E1900">
-        <v>0.9515187515836772</v>
+        <v>0.8676994226929882</v>
       </c>
       <c r="F1900">
         <v>-1</v>
       </c>
       <c r="G1900">
-        <v>0.01024067848502504</v>
+        <v>0.01193589426098409</v>
       </c>
       <c r="H1900">
-        <v>0.008988481248416322</v>
+        <v>0.009192300577307012</v>
       </c>
       <c r="I1900">
-        <v>0.06780276339127855</v>
+        <v>0.0364063163229229</v>
       </c>
       <c r="J1900">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1900">
+        <v>6.52</v>
+      </c>
+      <c r="L1900">
+        <v>6.42</v>
+      </c>
+      <c r="M1900">
+        <v>4.92</v>
+      </c>
+      <c r="N1900">
+        <v>5.03</v>
+      </c>
+      <c r="O1900">
+        <v>1</v>
+      </c>
+      <c r="P1900" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:16">
+      <c r="A1901" s="1">
+        <v>3</v>
+      </c>
+      <c r="B1901" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1901">
+        <v>0.8894240809811436</v>
+      </c>
+      <c r="D1901" t="s">
+        <v>438</v>
+      </c>
+      <c r="E1901">
+        <v>0.8676994226929882</v>
+      </c>
+      <c r="F1901">
+        <v>-1</v>
+      </c>
+      <c r="G1901">
+        <v>0.01121057591901886</v>
+      </c>
+      <c r="H1901">
+        <v>0.009192300577307012</v>
+      </c>
+      <c r="I1901">
+        <v>0.0217246582881554</v>
+      </c>
+      <c r="J1901">
+        <v>0.8459960522981732</v>
+      </c>
+      <c r="K1901">
+        <v>6.1</v>
+      </c>
+      <c r="L1901">
+        <v>6.05</v>
+      </c>
+      <c r="M1901">
+        <v>4.92</v>
+      </c>
+      <c r="N1901">
+        <v>5.03</v>
+      </c>
+      <c r="O1901">
+        <v>1</v>
+      </c>
+      <c r="P1901" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:16">
+      <c r="A1902" s="1">
+        <v>4</v>
+      </c>
+      <c r="B1902" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1902">
+        <v>1.019321514974956</v>
+      </c>
+      <c r="D1902" t="s">
+        <v>438</v>
+      </c>
+      <c r="E1902">
+        <v>0.8676994226929882</v>
+      </c>
+      <c r="F1902">
+        <v>-1</v>
+      </c>
+      <c r="G1902">
+        <v>0.01024067848502504</v>
+      </c>
+      <c r="H1902">
+        <v>0.009192300577307012</v>
+      </c>
+      <c r="I1902">
+        <v>0.1516220922819675</v>
+      </c>
+      <c r="J1902">
+        <v>0.8459960522981732</v>
+      </c>
+      <c r="K1902">
         <v>5.45</v>
       </c>
-      <c r="L1900">
+      <c r="L1902">
         <v>5.63</v>
       </c>
-      <c r="M1900">
-        <v>4.75</v>
-      </c>
-      <c r="N1900">
-        <v>4.97</v>
-      </c>
-      <c r="O1900">
-        <v>1</v>
-      </c>
-      <c r="P1900" t="s">
+      <c r="M1902">
+        <v>4.92</v>
+      </c>
+      <c r="N1902">
+        <v>5.03</v>
+      </c>
+      <c r="O1902">
+        <v>1</v>
+      </c>
+      <c r="P1902" t="s">
         <v>247</v>
       </c>
     </row>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -793,10 +793,10 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-09-14</t>
+    <t>2021-08-10</t>
   </si>
   <si>
-    <t>2021-08-10</t>
+    <t>2021-09-14</t>
   </si>
   <si>
     <t>2021-09-06</t>
@@ -1336,7 +1336,7 @@
     <t>2021-08-20</t>
   </si>
   <si>
-    <t>2021-10-12</t>
+    <t>2021-10-18</t>
   </si>
   <si>
     <t>2021-09-07</t>
@@ -91485,7 +91485,7 @@
         <v>2.573514530710648</v>
       </c>
       <c r="D1787" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E1787">
         <v>2.416125858174998</v>
@@ -91535,7 +91535,7 @@
         <v>2.594116268545282</v>
       </c>
       <c r="D1788" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E1788">
         <v>2.416125858174998</v>
@@ -91585,7 +91585,7 @@
         <v>2.742419534870029</v>
       </c>
       <c r="D1789" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E1789">
         <v>2.416125858174998</v>
@@ -95638,7 +95638,7 @@
         <v>440</v>
       </c>
       <c r="E1870">
-        <v>1.021704868139703</v>
+        <v>1.03364507342366</v>
       </c>
       <c r="F1870">
         <v>-1</v>
@@ -95647,10 +95647,10 @@
         <v>0.0118998599998409</v>
       </c>
       <c r="H1870">
-        <v>0.007958295131860299</v>
+        <v>0.008326354926576339</v>
       </c>
       <c r="I1870">
-        <v>0.3184351320193985</v>
+        <v>0.3064949267354407</v>
       </c>
       <c r="J1870">
         <v>0.7741730205045306</v>
@@ -95662,10 +95662,10 @@
         <v>6.62</v>
       </c>
       <c r="M1870">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1870">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1870">
         <v>1</v>
@@ -95688,7 +95688,7 @@
         <v>440</v>
       </c>
       <c r="E1871">
-        <v>1.021704868139703</v>
+        <v>1.03364507342366</v>
       </c>
       <c r="F1871">
         <v>-1</v>
@@ -95697,10 +95697,10 @@
         <v>0.01058600504384737</v>
       </c>
       <c r="H1871">
-        <v>0.007958295131860299</v>
+        <v>0.008326354926576339</v>
       </c>
       <c r="I1871">
-        <v>0.2122900880129328</v>
+        <v>0.2003498827289749</v>
       </c>
       <c r="J1871">
         <v>0.7741730205045306</v>
@@ -95712,10 +95712,10 @@
         <v>5.91</v>
       </c>
       <c r="M1871">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1871">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1871">
         <v>1</v>
@@ -95738,7 +95738,7 @@
         <v>440</v>
       </c>
       <c r="E1872">
-        <v>1.021704868139703</v>
+        <v>1.03364507342366</v>
       </c>
       <c r="F1872">
         <v>-1</v>
@@ -95747,10 +95747,10 @@
         <v>0.008158295131860298</v>
       </c>
       <c r="H1872">
-        <v>0.007958295131860299</v>
+        <v>0.008326354926576339</v>
       </c>
       <c r="I1872">
-        <v>0.2000000000000002</v>
+        <v>0.1880597947160423</v>
       </c>
       <c r="J1872">
         <v>0.7741730205045306</v>
@@ -95762,10 +95762,10 @@
         <v>4.69</v>
       </c>
       <c r="M1872">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1872">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1872">
         <v>1</v>
@@ -95779,43 +95779,43 @@
         <v>0</v>
       </c>
       <c r="B1873" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C1873">
-        <v>0.5331535880095641</v>
+        <v>0.6665846755195202</v>
       </c>
       <c r="D1873" t="s">
-        <v>246</v>
+        <v>437</v>
       </c>
       <c r="E1873">
-        <v>0.9386915979436754</v>
+        <v>0.9742521665339288</v>
       </c>
       <c r="F1873">
         <v>1</v>
       </c>
       <c r="G1873">
-        <v>0.008546846411990437</v>
+        <v>0.008073415324480481</v>
       </c>
       <c r="H1873">
-        <v>0.009061308402056325</v>
+        <v>0.009065747833466069</v>
       </c>
       <c r="I1873">
-        <v>0.4055380099341113</v>
+        <v>0.3076674910144086</v>
       </c>
       <c r="J1873">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1873">
-        <v>5.15</v>
+        <v>4.76</v>
       </c>
       <c r="L1873">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1873">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="N1873">
-        <v>5</v>
+        <v>5.02</v>
       </c>
       <c r="O1873">
         <v>1</v>
@@ -95829,10 +95829,10 @@
         <v>1</v>
       </c>
       <c r="B1874" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C1874">
-        <v>0.6665846755195202</v>
+        <v>0.6809789896169787</v>
       </c>
       <c r="D1874" t="s">
         <v>437</v>
@@ -95844,22 +95844,22 @@
         <v>1</v>
       </c>
       <c r="G1874">
-        <v>0.008073415324480481</v>
+        <v>0.008399021010383022</v>
       </c>
       <c r="H1874">
         <v>0.009065747833466069</v>
       </c>
       <c r="I1874">
-        <v>0.3076674910144086</v>
+        <v>0.2932731769169501</v>
       </c>
       <c r="J1874">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1874">
-        <v>4.76</v>
+        <v>4.96</v>
       </c>
       <c r="L1874">
-        <v>4.37</v>
+        <v>4.54</v>
       </c>
       <c r="M1874">
         <v>5.2</v>
@@ -95879,43 +95879,43 @@
         <v>2</v>
       </c>
       <c r="B1875" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C1875">
-        <v>0.6809789896169787</v>
+        <v>1.313846110723346</v>
       </c>
       <c r="D1875" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E1875">
-        <v>0.9742521665339288</v>
+        <v>1.015486096995155</v>
       </c>
       <c r="F1875">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1875">
-        <v>0.008399021010383022</v>
+        <v>0.01192615388927666</v>
       </c>
       <c r="H1875">
-        <v>0.009065747833466069</v>
+        <v>0.008344513903004846</v>
       </c>
       <c r="I1875">
-        <v>0.2932731769169501</v>
+        <v>0.2983600137281908</v>
       </c>
       <c r="J1875">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1875">
-        <v>4.96</v>
+        <v>6.82</v>
       </c>
       <c r="L1875">
-        <v>4.54</v>
+        <v>6.62</v>
       </c>
       <c r="M1875">
-        <v>5.2</v>
+        <v>4.71</v>
       </c>
       <c r="N1875">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="O1875">
         <v>1</v>
@@ -95929,43 +95929,43 @@
         <v>3</v>
       </c>
       <c r="B1876" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1876">
-        <v>1.313846110723346</v>
+        <v>1.210708285743256</v>
       </c>
       <c r="D1876" t="s">
         <v>440</v>
       </c>
       <c r="E1876">
-        <v>1.004432635783077</v>
+        <v>1.015486096995155</v>
       </c>
       <c r="F1876">
         <v>-1</v>
       </c>
       <c r="G1876">
-        <v>0.01192615388927666</v>
+        <v>0.01060929171425675</v>
       </c>
       <c r="H1876">
-        <v>0.007975567364216923</v>
+        <v>0.008344513903004846</v>
       </c>
       <c r="I1876">
-        <v>0.3094134749402686</v>
+        <v>0.1952221887481009</v>
       </c>
       <c r="J1876">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1876">
-        <v>6.82</v>
+        <v>6.04</v>
       </c>
       <c r="L1876">
-        <v>6.62</v>
+        <v>5.91</v>
       </c>
       <c r="M1876">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1876">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1876">
         <v>1</v>
@@ -95979,43 +95979,43 @@
         <v>4</v>
       </c>
       <c r="B1877" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1877">
-        <v>1.210708285743256</v>
+        <v>1.204432635783077</v>
       </c>
       <c r="D1877" t="s">
         <v>440</v>
       </c>
       <c r="E1877">
-        <v>1.004432635783077</v>
+        <v>1.015486096995155</v>
       </c>
       <c r="F1877">
         <v>-1</v>
       </c>
       <c r="G1877">
-        <v>0.01060929171425675</v>
+        <v>0.008175567364216924</v>
       </c>
       <c r="H1877">
-        <v>0.007975567364216923</v>
+        <v>0.008344513903004846</v>
       </c>
       <c r="I1877">
-        <v>0.2062756499601788</v>
+        <v>0.1889465387879223</v>
       </c>
       <c r="J1877">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1877">
-        <v>6.04</v>
+        <v>4.48</v>
       </c>
       <c r="L1877">
-        <v>5.91</v>
+        <v>4.69</v>
       </c>
       <c r="M1877">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1877">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1877">
         <v>1</v>
@@ -96026,63 +96026,63 @@
     </row>
     <row r="1878" spans="1:16">
       <c r="A1878" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1878" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C1878">
-        <v>1.204432635783077</v>
+        <v>0.6227397035253315</v>
       </c>
       <c r="D1878" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E1878">
-        <v>1.004432635783077</v>
+        <v>0.9263542979688486</v>
       </c>
       <c r="F1878">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1878">
-        <v>0.008175567364216924</v>
+        <v>0.008117260296474669</v>
       </c>
       <c r="H1878">
-        <v>0.007975567364216923</v>
+        <v>0.00911364570203115</v>
       </c>
       <c r="I1878">
-        <v>0.2000000000000002</v>
+        <v>0.3036145944435171</v>
       </c>
       <c r="J1878">
-        <v>0.7780284295127059</v>
+        <v>0.7872395580829136</v>
       </c>
       <c r="K1878">
-        <v>4.48</v>
+        <v>4.76</v>
       </c>
       <c r="L1878">
-        <v>4.69</v>
+        <v>4.37</v>
       </c>
       <c r="M1878">
-        <v>4.48</v>
+        <v>5.2</v>
       </c>
       <c r="N1878">
-        <v>4.49</v>
+        <v>5.02</v>
       </c>
       <c r="O1878">
         <v>1</v>
       </c>
       <c r="P1878" t="s">
-        <v>422</v>
+        <v>253</v>
       </c>
     </row>
     <row r="1879" spans="1:16">
       <c r="A1879" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1879" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C1879">
-        <v>0.6227397035253315</v>
+        <v>0.6352917919087488</v>
       </c>
       <c r="D1879" t="s">
         <v>437</v>
@@ -96094,22 +96094,22 @@
         <v>1</v>
       </c>
       <c r="G1879">
-        <v>0.008117260296474669</v>
+        <v>0.008444708208091251</v>
       </c>
       <c r="H1879">
         <v>0.00911364570203115</v>
       </c>
       <c r="I1879">
-        <v>0.3036145944435171</v>
+        <v>0.2910625060600998</v>
       </c>
       <c r="J1879">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1879">
-        <v>4.76</v>
+        <v>4.96</v>
       </c>
       <c r="L1879">
-        <v>4.37</v>
+        <v>4.54</v>
       </c>
       <c r="M1879">
         <v>5.2</v>
@@ -96126,13 +96126,13 @@
     </row>
     <row r="1880" spans="1:16">
       <c r="A1880" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1880" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C1880">
-        <v>0.6352917919087488</v>
+        <v>0.6589089786512363</v>
       </c>
       <c r="D1880" t="s">
         <v>437</v>
@@ -96144,19 +96144,19 @@
         <v>1</v>
       </c>
       <c r="G1880">
-        <v>0.008444708208091251</v>
+        <v>0.008421091021348763</v>
       </c>
       <c r="H1880">
         <v>0.00911364570203115</v>
       </c>
       <c r="I1880">
-        <v>0.2910625060600998</v>
+        <v>0.2674453193176123</v>
       </c>
       <c r="J1880">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1880">
-        <v>4.96</v>
+        <v>4.93</v>
       </c>
       <c r="L1880">
         <v>4.54</v>
@@ -96176,7 +96176,7 @@
     </row>
     <row r="1881" spans="1:16">
       <c r="A1881" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1881" t="s">
         <v>256</v>
@@ -96188,7 +96188,7 @@
         <v>440</v>
       </c>
       <c r="E1881">
-        <v>0.9631667797885473</v>
+        <v>0.9721016814294767</v>
       </c>
       <c r="F1881">
         <v>-1</v>
@@ -96197,10 +96197,10 @@
         <v>0.01198897378612547</v>
       </c>
       <c r="H1881">
-        <v>0.008016833220211452</v>
+        <v>0.008387898318570524</v>
       </c>
       <c r="I1881">
-        <v>0.2878594340859819</v>
+        <v>0.2789245324450524</v>
       </c>
       <c r="J1881">
         <v>0.7872395580829136</v>
@@ -96212,10 +96212,10 @@
         <v>6.62</v>
       </c>
       <c r="M1881">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1881">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1881">
         <v>1</v>
@@ -96226,10 +96226,10 @@
     </row>
     <row r="1882" spans="1:16">
       <c r="A1882" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1882" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C1882">
         <v>1.247838695694227</v>
@@ -96238,7 +96238,7 @@
         <v>440</v>
       </c>
       <c r="E1882">
-        <v>0.9631667797885473</v>
+        <v>0.9721016814294767</v>
       </c>
       <c r="F1882">
         <v>-1</v>
@@ -96247,10 +96247,10 @@
         <v>0.01085216130430577</v>
       </c>
       <c r="H1882">
-        <v>0.008016833220211452</v>
+        <v>0.008387898318570524</v>
       </c>
       <c r="I1882">
-        <v>0.2846719159056801</v>
+        <v>0.2757370142647506</v>
       </c>
       <c r="J1882">
         <v>0.7872395580829136</v>
@@ -96262,10 +96262,10 @@
         <v>6.05</v>
       </c>
       <c r="M1882">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1882">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1882">
         <v>1</v>
@@ -96276,7 +96276,7 @@
     </row>
     <row r="1883" spans="1:16">
       <c r="A1883" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1883" t="s">
         <v>257</v>
@@ -96288,7 +96288,7 @@
         <v>440</v>
       </c>
       <c r="E1883">
-        <v>0.9631667797885473</v>
+        <v>0.9721016814294767</v>
       </c>
       <c r="F1883">
         <v>-1</v>
@@ -96297,10 +96297,10 @@
         <v>0.0106649269308208</v>
       </c>
       <c r="H1883">
-        <v>0.008016833220211452</v>
+        <v>0.008387898318570524</v>
       </c>
       <c r="I1883">
-        <v>0.1919062893906545</v>
+        <v>0.182971387749725</v>
       </c>
       <c r="J1883">
         <v>0.7872395580829136</v>
@@ -96312,10 +96312,10 @@
         <v>5.91</v>
       </c>
       <c r="M1883">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1883">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1883">
         <v>1</v>
@@ -96326,7 +96326,7 @@
     </row>
     <row r="1884" spans="1:16">
       <c r="A1884" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1884" t="s">
         <v>258</v>
@@ -96338,7 +96338,7 @@
         <v>440</v>
       </c>
       <c r="E1884">
-        <v>0.9631667797885473</v>
+        <v>0.9721016814294767</v>
       </c>
       <c r="F1884">
         <v>-1</v>
@@ -96347,10 +96347,10 @@
         <v>0.008216833220211455</v>
       </c>
       <c r="H1884">
-        <v>0.008016833220211452</v>
+        <v>0.008387898318570524</v>
       </c>
       <c r="I1884">
-        <v>0.2000000000000002</v>
+        <v>0.1910650983590707</v>
       </c>
       <c r="J1884">
         <v>0.7872395580829136</v>
@@ -96362,10 +96362,10 @@
         <v>4.69</v>
       </c>
       <c r="M1884">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1884">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1884">
         <v>1</v>
@@ -96479,7 +96479,7 @@
         <v>2</v>
       </c>
       <c r="B1887" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C1887">
         <v>0.6202958892743267</v>
@@ -96538,7 +96538,7 @@
         <v>440</v>
       </c>
       <c r="E1888">
-        <v>0.9280782117543573</v>
+        <v>0.9352116913756747</v>
       </c>
       <c r="F1888">
         <v>-1</v>
@@ -96547,10 +96547,10 @@
         <v>0.0120423898651418</v>
       </c>
       <c r="H1888">
-        <v>0.008051921788245642</v>
+        <v>0.008424788308624327</v>
       </c>
       <c r="I1888">
-        <v>0.2695319231038384</v>
+        <v>0.2623984434825211</v>
       </c>
       <c r="J1888">
         <v>0.7950718277334023</v>
@@ -96562,10 +96562,10 @@
         <v>6.62</v>
       </c>
       <c r="M1888">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1888">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1888">
         <v>1</v>
@@ -96579,7 +96579,7 @@
         <v>4</v>
       </c>
       <c r="B1889" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C1889">
         <v>1.200061850826246</v>
@@ -96588,7 +96588,7 @@
         <v>440</v>
       </c>
       <c r="E1889">
-        <v>0.9280782117543573</v>
+        <v>0.9352116913756747</v>
       </c>
       <c r="F1889">
         <v>-1</v>
@@ -96597,10 +96597,10 @@
         <v>0.01089993814917375</v>
       </c>
       <c r="H1889">
-        <v>0.008051921788245642</v>
+        <v>0.008424788308624327</v>
       </c>
       <c r="I1889">
-        <v>0.2719836390718884</v>
+        <v>0.264850159450571</v>
       </c>
       <c r="J1889">
         <v>0.7950718277334023</v>
@@ -96612,10 +96612,10 @@
         <v>6.05</v>
       </c>
       <c r="M1889">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1889">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1889">
         <v>1</v>
@@ -96638,7 +96638,7 @@
         <v>440</v>
       </c>
       <c r="E1890">
-        <v>0.9280782117543573</v>
+        <v>0.9352116913756747</v>
       </c>
       <c r="F1890">
         <v>-1</v>
@@ -96647,10 +96647,10 @@
         <v>0.01071223383950975</v>
       </c>
       <c r="H1890">
-        <v>0.008051921788245642</v>
+        <v>0.008424788308624327</v>
       </c>
       <c r="I1890">
-        <v>0.1796879487358929</v>
+        <v>0.1725544691145755</v>
       </c>
       <c r="J1890">
         <v>0.7950718277334023</v>
@@ -96662,10 +96662,10 @@
         <v>5.91</v>
       </c>
       <c r="M1890">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1890">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1890">
         <v>1</v>
@@ -96688,7 +96688,7 @@
         <v>440</v>
       </c>
       <c r="E1891">
-        <v>0.9280782117543573</v>
+        <v>0.9352116913756747</v>
       </c>
       <c r="F1891">
         <v>-1</v>
@@ -96697,10 +96697,10 @@
         <v>0.008251921788245643</v>
       </c>
       <c r="H1891">
-        <v>0.008051921788245642</v>
+        <v>0.008424788308624327</v>
       </c>
       <c r="I1891">
-        <v>0.2000000000000002</v>
+        <v>0.1928665203786828</v>
       </c>
       <c r="J1891">
         <v>0.7950718277334023</v>
@@ -96712,10 +96712,10 @@
         <v>4.69</v>
       </c>
       <c r="M1891">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1891">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1891">
         <v>1</v>
@@ -96829,7 +96829,7 @@
         <v>2</v>
       </c>
       <c r="B1894" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C1894">
         <v>0.6039296128919895</v>
@@ -96888,7 +96888,7 @@
         <v>440</v>
       </c>
       <c r="E1895">
-        <v>0.9132058145549919</v>
+        <v>0.9195757559272346</v>
       </c>
       <c r="F1895">
         <v>-1</v>
@@ -96897,10 +96897,10 @@
         <v>0.01206503043409262</v>
       </c>
       <c r="H1895">
-        <v>0.008066794185445009</v>
+        <v>0.008440424244072766</v>
       </c>
       <c r="I1895">
-        <v>0.2617637513523841</v>
+        <v>0.2553938099801414</v>
       </c>
       <c r="J1895">
         <v>0.7983915592511178</v>
@@ -96912,10 +96912,10 @@
         <v>6.62</v>
       </c>
       <c r="M1895">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1895">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1895">
         <v>1</v>
@@ -96929,7 +96929,7 @@
         <v>4</v>
       </c>
       <c r="B1896" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C1896">
         <v>1.179811488568181</v>
@@ -96938,7 +96938,7 @@
         <v>440</v>
       </c>
       <c r="E1896">
-        <v>0.9132058145549919</v>
+        <v>0.9195757559272346</v>
       </c>
       <c r="F1896">
         <v>-1</v>
@@ -96947,10 +96947,10 @@
         <v>0.01092018851143182</v>
       </c>
       <c r="H1896">
-        <v>0.008066794185445009</v>
+        <v>0.008440424244072766</v>
       </c>
       <c r="I1896">
-        <v>0.2666056740131895</v>
+        <v>0.2602357326409468</v>
       </c>
       <c r="J1896">
         <v>0.7983915592511178</v>
@@ -96962,10 +96962,10 @@
         <v>6.05</v>
       </c>
       <c r="M1896">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1896">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1896">
         <v>1</v>
@@ -96988,7 +96988,7 @@
         <v>440</v>
       </c>
       <c r="E1897">
-        <v>0.9132058145549919</v>
+        <v>0.9195757559272346</v>
       </c>
       <c r="F1897">
         <v>-1</v>
@@ -96997,10 +96997,10 @@
         <v>0.01073228501787675</v>
       </c>
       <c r="H1897">
-        <v>0.008066794185445009</v>
+        <v>0.008440424244072766</v>
       </c>
       <c r="I1897">
-        <v>0.1745091675682566</v>
+        <v>0.168139226196014</v>
       </c>
       <c r="J1897">
         <v>0.7983915592511178</v>
@@ -97012,10 +97012,10 @@
         <v>5.91</v>
       </c>
       <c r="M1897">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1897">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1897">
         <v>1</v>
@@ -97038,7 +97038,7 @@
         <v>440</v>
       </c>
       <c r="E1898">
-        <v>0.9132058145549919</v>
+        <v>0.9195757559272346</v>
       </c>
       <c r="F1898">
         <v>-1</v>
@@ -97047,10 +97047,10 @@
         <v>0.008266794185445007</v>
       </c>
       <c r="H1898">
-        <v>0.008066794185445009</v>
+        <v>0.008440424244072766</v>
       </c>
       <c r="I1898">
-        <v>0.2000000000000002</v>
+        <v>0.1936300586277575</v>
       </c>
       <c r="J1898">
         <v>0.7983915592511178</v>
@@ -97062,10 +97062,10 @@
         <v>4.69</v>
       </c>
       <c r="M1898">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1898">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1898">
         <v>1</v>
@@ -97085,10 +97085,10 @@
         <v>0.4754849636079563</v>
       </c>
       <c r="D1899" t="s">
-        <v>437</v>
+        <v>250</v>
       </c>
       <c r="E1899">
-        <v>0.7654877753700351</v>
+        <v>0.8773067240324215</v>
       </c>
       <c r="F1899">
         <v>1</v>
@@ -97097,10 +97097,10 @@
         <v>0.008264515036392044</v>
       </c>
       <c r="H1899">
-        <v>0.009274512224629964</v>
+        <v>0.009582693275967578</v>
       </c>
       <c r="I1899">
-        <v>0.2900028117620788</v>
+        <v>0.4018217604244652</v>
       </c>
       <c r="J1899">
         <v>0.8181754278134546</v>
@@ -97112,10 +97112,10 @@
         <v>4.37</v>
       </c>
       <c r="M1899">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="N1899">
-        <v>5.02</v>
+        <v>5.23</v>
       </c>
       <c r="O1899">
         <v>1</v>
@@ -97135,10 +97135,10 @@
         <v>0.4818498780452654</v>
       </c>
       <c r="D1900" t="s">
-        <v>437</v>
+        <v>250</v>
       </c>
       <c r="E1900">
-        <v>0.7654877753700351</v>
+        <v>0.8773067240324215</v>
       </c>
       <c r="F1900">
         <v>1</v>
@@ -97147,10 +97147,10 @@
         <v>0.008598150121954735</v>
       </c>
       <c r="H1900">
-        <v>0.009274512224629964</v>
+        <v>0.009582693275967578</v>
       </c>
       <c r="I1900">
-        <v>0.2836378973247697</v>
+        <v>0.3954568459871561</v>
       </c>
       <c r="J1900">
         <v>0.8181754278134546</v>
@@ -97162,10 +97162,10 @@
         <v>4.54</v>
       </c>
       <c r="M1900">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="N1900">
-        <v>5.02</v>
+        <v>5.23</v>
       </c>
       <c r="O1900">
         <v>1</v>
@@ -97179,16 +97179,16 @@
         <v>2</v>
       </c>
       <c r="B1901" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C1901">
         <v>0.5063951408796692</v>
       </c>
       <c r="D1901" t="s">
-        <v>437</v>
+        <v>250</v>
       </c>
       <c r="E1901">
-        <v>0.7654877753700351</v>
+        <v>0.8773067240324215</v>
       </c>
       <c r="F1901">
         <v>1</v>
@@ -97197,10 +97197,10 @@
         <v>0.008573604859120331</v>
       </c>
       <c r="H1901">
-        <v>0.009274512224629964</v>
+        <v>0.009582693275967578</v>
       </c>
       <c r="I1901">
-        <v>0.2590926344903659</v>
+        <v>0.3709115831527523</v>
       </c>
       <c r="J1901">
         <v>0.8181754278134546</v>
@@ -97212,10 +97212,10 @@
         <v>4.54</v>
       </c>
       <c r="M1901">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="N1901">
-        <v>5.02</v>
+        <v>5.23</v>
       </c>
       <c r="O1901">
         <v>1</v>
@@ -97288,7 +97288,7 @@
         <v>440</v>
       </c>
       <c r="E1903">
-        <v>0.8245740833957229</v>
+        <v>0.8263937349986286</v>
       </c>
       <c r="F1903">
         <v>-1</v>
@@ -97297,10 +97297,10 @@
         <v>0.01219995641768776</v>
       </c>
       <c r="H1903">
-        <v>0.008155425916604278</v>
+        <v>0.008533606265001371</v>
       </c>
       <c r="I1903">
-        <v>0.2154694989165162</v>
+        <v>0.2136498473136106</v>
       </c>
       <c r="J1903">
         <v>0.8181754278134546</v>
@@ -97312,10 +97312,10 @@
         <v>6.62</v>
       </c>
       <c r="M1903">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1903">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1903">
         <v>1</v>
@@ -97329,7 +97329,7 @@
         <v>5</v>
       </c>
       <c r="B1904" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C1904">
         <v>1.059129890337926</v>
@@ -97338,7 +97338,7 @@
         <v>440</v>
       </c>
       <c r="E1904">
-        <v>0.8245740833957229</v>
+        <v>0.8263937349986286</v>
       </c>
       <c r="F1904">
         <v>-1</v>
@@ -97347,10 +97347,10 @@
         <v>0.01104087010966207</v>
       </c>
       <c r="H1904">
-        <v>0.008155425916604278</v>
+        <v>0.008533606265001371</v>
       </c>
       <c r="I1904">
-        <v>0.2345558069422036</v>
+        <v>0.2327361553392979</v>
       </c>
       <c r="J1904">
         <v>0.8181754278134546</v>
@@ -97362,10 +97362,10 @@
         <v>6.05</v>
       </c>
       <c r="M1904">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1904">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1904">
         <v>1</v>
@@ -97388,7 +97388,7 @@
         <v>440</v>
       </c>
       <c r="E1905">
-        <v>0.8245740833957229</v>
+        <v>0.8263937349986286</v>
       </c>
       <c r="F1905">
         <v>-1</v>
@@ -97397,10 +97397,10 @@
         <v>0.01085177958399327</v>
       </c>
       <c r="H1905">
-        <v>0.008155425916604278</v>
+        <v>0.008533606265001371</v>
       </c>
       <c r="I1905">
-        <v>0.1436463326110116</v>
+        <v>0.1418266810081059</v>
       </c>
       <c r="J1905">
         <v>0.8181754278134546</v>
@@ -97412,10 +97412,10 @@
         <v>5.91</v>
       </c>
       <c r="M1905">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1905">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1905">
         <v>1</v>
@@ -97438,7 +97438,7 @@
         <v>440</v>
       </c>
       <c r="E1906">
-        <v>0.8245740833957229</v>
+        <v>0.8263937349986286</v>
       </c>
       <c r="F1906">
         <v>-1</v>
@@ -97447,10 +97447,10 @@
         <v>0.008355425916604278</v>
       </c>
       <c r="H1906">
-        <v>0.008155425916604278</v>
+        <v>0.008533606265001371</v>
       </c>
       <c r="I1906">
-        <v>0.2000000000000002</v>
+        <v>0.1981803483970945</v>
       </c>
       <c r="J1906">
         <v>0.8181754278134546</v>
@@ -97462,10 +97462,10 @@
         <v>4.69</v>
       </c>
       <c r="M1906">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1906">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1906">
         <v>1</v>
@@ -97638,7 +97638,7 @@
         <v>440</v>
       </c>
       <c r="E1910">
-        <v>0.6999376857041839</v>
+        <v>0.6953585936756039</v>
       </c>
       <c r="F1910">
         <v>-1</v>
@@ -97647,10 +97647,10 @@
         <v>0.01024067848502504</v>
       </c>
       <c r="H1910">
-        <v>0.008280062314295816</v>
+        <v>0.008664641406324397</v>
       </c>
       <c r="I1910">
-        <v>0.3193838292707718</v>
+        <v>0.3239629212993518</v>
       </c>
       <c r="J1910">
         <v>0.8459960522981732</v>
@@ -97662,10 +97662,10 @@
         <v>5.63</v>
       </c>
       <c r="M1910">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1910">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1910">
         <v>1</v>
@@ -97688,7 +97688,7 @@
         <v>440</v>
       </c>
       <c r="E1911">
-        <v>0.6999376857041839</v>
+        <v>0.6953585936756039</v>
       </c>
       <c r="F1911">
         <v>-1</v>
@@ -97697,10 +97697,10 @@
         <v>0.008480062314295817</v>
       </c>
       <c r="H1911">
-        <v>0.008280062314295816</v>
+        <v>0.008664641406324397</v>
       </c>
       <c r="I1911">
-        <v>0.2000000000000002</v>
+        <v>0.2045790920285802</v>
       </c>
       <c r="J1911">
         <v>0.8459960522981732</v>
@@ -97712,10 +97712,10 @@
         <v>4.69</v>
       </c>
       <c r="M1911">
-        <v>4.48</v>
+        <v>4.71</v>
       </c>
       <c r="N1911">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="O1911">
         <v>1</v>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5742" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5745" uniqueCount="604">
   <si>
     <t>trade_time</t>
   </si>
@@ -1342,7 +1342,7 @@
     <t>2021-08-20</t>
   </si>
   <si>
-    <t>2021-10-20</t>
+    <t>2021-10-21</t>
   </si>
   <si>
     <t>2021-09-07</t>
@@ -2183,7 +2183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1910"/>
+  <dimension ref="A1:P1911"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -95597,7 +95597,7 @@
         <v>442</v>
       </c>
       <c r="E1869">
-        <v>1.157512756704385</v>
+        <v>1.160737947319522</v>
       </c>
       <c r="F1869">
         <v>-1</v>
@@ -95606,10 +95606,10 @@
         <v>0.0118998599998409</v>
       </c>
       <c r="H1869">
-        <v>0.008202487243295614</v>
+        <v>0.008159262052680478</v>
       </c>
       <c r="I1869">
-        <v>0.1826272434547156</v>
+        <v>0.179402052839579</v>
       </c>
       <c r="J1869">
         <v>0.7741730205045306</v>
@@ -95621,10 +95621,10 @@
         <v>6.62</v>
       </c>
       <c r="M1869">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1869">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1869">
         <v>1</v>
@@ -95647,7 +95647,7 @@
         <v>442</v>
       </c>
       <c r="E1870">
-        <v>1.157512756704385</v>
+        <v>1.160737947319522</v>
       </c>
       <c r="F1870">
         <v>-1</v>
@@ -95656,10 +95656,10 @@
         <v>0.01058600504384737</v>
       </c>
       <c r="H1870">
-        <v>0.008202487243295614</v>
+        <v>0.008159262052680478</v>
       </c>
       <c r="I1870">
-        <v>0.07648219944824985</v>
+        <v>0.07325700883311326</v>
       </c>
       <c r="J1870">
         <v>0.7741730205045306</v>
@@ -95671,10 +95671,10 @@
         <v>5.91</v>
       </c>
       <c r="M1870">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1870">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1870">
         <v>1</v>
@@ -95697,7 +95697,7 @@
         <v>442</v>
       </c>
       <c r="E1871">
-        <v>1.157512756704385</v>
+        <v>1.160737947319522</v>
       </c>
       <c r="F1871">
         <v>-1</v>
@@ -95706,10 +95706,10 @@
         <v>0.008158295131860298</v>
       </c>
       <c r="H1871">
-        <v>0.008202487243295614</v>
+        <v>0.008159262052680478</v>
       </c>
       <c r="I1871">
-        <v>0.06419211143531722</v>
+        <v>0.06096692082018063</v>
       </c>
       <c r="J1871">
         <v>0.7741730205045306</v>
@@ -95721,10 +95721,10 @@
         <v>4.69</v>
       </c>
       <c r="M1871">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1871">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1871">
         <v>1</v>
@@ -95897,7 +95897,7 @@
         <v>442</v>
       </c>
       <c r="E1875">
-        <v>1.139970645717188</v>
+        <v>1.14331149860257</v>
       </c>
       <c r="F1875">
         <v>-1</v>
@@ -95906,10 +95906,10 @@
         <v>0.01192615388927666</v>
       </c>
       <c r="H1875">
-        <v>0.008220029354282812</v>
+        <v>0.00817668850139743</v>
       </c>
       <c r="I1875">
-        <v>0.1738754650061578</v>
+        <v>0.1705346121207763</v>
       </c>
       <c r="J1875">
         <v>0.7780284295127059</v>
@@ -95921,10 +95921,10 @@
         <v>6.62</v>
       </c>
       <c r="M1875">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1875">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1875">
         <v>1</v>
@@ -95938,43 +95938,43 @@
         <v>4</v>
       </c>
       <c r="B1876" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C1876">
-        <v>1.210708285743256</v>
+        <v>1.304026579972494</v>
       </c>
       <c r="D1876" t="s">
         <v>442</v>
       </c>
       <c r="E1876">
-        <v>1.139970645717188</v>
+        <v>1.14331149860257</v>
       </c>
       <c r="F1876">
         <v>-1</v>
       </c>
       <c r="G1876">
-        <v>0.01060929171425675</v>
+        <v>0.0107959734200275</v>
       </c>
       <c r="H1876">
-        <v>0.008220029354282812</v>
+        <v>0.00817668850139743</v>
       </c>
       <c r="I1876">
-        <v>0.07073764002606797</v>
+        <v>0.1607150813699247</v>
       </c>
       <c r="J1876">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1876">
-        <v>6.04</v>
+        <v>6.1</v>
       </c>
       <c r="L1876">
-        <v>5.91</v>
+        <v>6.05</v>
       </c>
       <c r="M1876">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1876">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1876">
         <v>1</v>
@@ -95988,43 +95988,43 @@
         <v>5</v>
       </c>
       <c r="B1877" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1877">
-        <v>1.204432635783077</v>
+        <v>1.210708285743256</v>
       </c>
       <c r="D1877" t="s">
         <v>442</v>
       </c>
       <c r="E1877">
-        <v>1.139970645717188</v>
+        <v>1.14331149860257</v>
       </c>
       <c r="F1877">
         <v>-1</v>
       </c>
       <c r="G1877">
-        <v>0.008175567364216924</v>
+        <v>0.01060929171425675</v>
       </c>
       <c r="H1877">
-        <v>0.008220029354282812</v>
+        <v>0.00817668850139743</v>
       </c>
       <c r="I1877">
-        <v>0.06446199006588937</v>
+        <v>0.06739678714068642</v>
       </c>
       <c r="J1877">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1877">
-        <v>4.48</v>
+        <v>6.04</v>
       </c>
       <c r="L1877">
-        <v>4.69</v>
+        <v>5.91</v>
       </c>
       <c r="M1877">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1877">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1877">
         <v>1</v>
@@ -96035,63 +96035,63 @@
     </row>
     <row r="1878" spans="1:16">
       <c r="A1878" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1878" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C1878">
-        <v>0.6227397035253315</v>
+        <v>1.204432635783077</v>
       </c>
       <c r="D1878" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E1878">
-        <v>0.9263542979688486</v>
+        <v>1.14331149860257</v>
       </c>
       <c r="F1878">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1878">
-        <v>0.008117260296474669</v>
+        <v>0.008175567364216924</v>
       </c>
       <c r="H1878">
-        <v>0.00911364570203115</v>
+        <v>0.00817668850139743</v>
       </c>
       <c r="I1878">
-        <v>0.3036145944435171</v>
+        <v>0.06112113718050782</v>
       </c>
       <c r="J1878">
-        <v>0.7872395580829136</v>
+        <v>0.7780284295127059</v>
       </c>
       <c r="K1878">
-        <v>4.76</v>
+        <v>4.48</v>
       </c>
       <c r="L1878">
-        <v>4.37</v>
+        <v>4.69</v>
       </c>
       <c r="M1878">
-        <v>5.2</v>
+        <v>4.52</v>
       </c>
       <c r="N1878">
-        <v>5.02</v>
+        <v>4.66</v>
       </c>
       <c r="O1878">
         <v>1</v>
       </c>
       <c r="P1878" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="1879" spans="1:16">
       <c r="A1879" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1879" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C1879">
-        <v>0.6352917919087488</v>
+        <v>0.6227397035253315</v>
       </c>
       <c r="D1879" t="s">
         <v>439</v>
@@ -96103,22 +96103,22 @@
         <v>1</v>
       </c>
       <c r="G1879">
-        <v>0.008444708208091251</v>
+        <v>0.008117260296474669</v>
       </c>
       <c r="H1879">
         <v>0.00911364570203115</v>
       </c>
       <c r="I1879">
-        <v>0.2910625060600998</v>
+        <v>0.3036145944435171</v>
       </c>
       <c r="J1879">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1879">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="L1879">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1879">
         <v>5.2</v>
@@ -96135,13 +96135,13 @@
     </row>
     <row r="1880" spans="1:16">
       <c r="A1880" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1880" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C1880">
-        <v>0.6589089786512363</v>
+        <v>0.6352917919087488</v>
       </c>
       <c r="D1880" t="s">
         <v>439</v>
@@ -96153,19 +96153,19 @@
         <v>1</v>
       </c>
       <c r="G1880">
-        <v>0.008421091021348763</v>
+        <v>0.008444708208091251</v>
       </c>
       <c r="H1880">
         <v>0.00911364570203115</v>
       </c>
       <c r="I1880">
-        <v>0.2674453193176123</v>
+        <v>0.2910625060600998</v>
       </c>
       <c r="J1880">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1880">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="L1880">
         <v>4.54</v>
@@ -96185,46 +96185,46 @@
     </row>
     <row r="1881" spans="1:16">
       <c r="A1881" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1881" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C1881">
-        <v>1.251026213874529</v>
+        <v>0.6589089786512363</v>
       </c>
       <c r="D1881" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E1881">
-        <v>1.098060010722743</v>
+        <v>0.9263542979688486</v>
       </c>
       <c r="F1881">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1881">
-        <v>0.01198897378612547</v>
+        <v>0.008421091021348763</v>
       </c>
       <c r="H1881">
-        <v>0.008261939989277255</v>
+        <v>0.00911364570203115</v>
       </c>
       <c r="I1881">
-        <v>0.1529662031517862</v>
+        <v>0.2674453193176123</v>
       </c>
       <c r="J1881">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1881">
-        <v>6.82</v>
+        <v>4.93</v>
       </c>
       <c r="L1881">
-        <v>6.62</v>
+        <v>4.54</v>
       </c>
       <c r="M1881">
-        <v>4.55</v>
+        <v>5.2</v>
       </c>
       <c r="N1881">
-        <v>4.68</v>
+        <v>5.02</v>
       </c>
       <c r="O1881">
         <v>1</v>
@@ -96235,46 +96235,46 @@
     </row>
     <row r="1882" spans="1:16">
       <c r="A1882" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1882" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C1882">
-        <v>1.247838695694227</v>
+        <v>1.251026213874529</v>
       </c>
       <c r="D1882" t="s">
         <v>442</v>
       </c>
       <c r="E1882">
-        <v>1.098060010722743</v>
+        <v>1.101677197465231</v>
       </c>
       <c r="F1882">
         <v>-1</v>
       </c>
       <c r="G1882">
-        <v>0.01085216130430577</v>
+        <v>0.01198897378612547</v>
       </c>
       <c r="H1882">
-        <v>0.008261939989277255</v>
+        <v>0.008218322802534768</v>
       </c>
       <c r="I1882">
-        <v>0.1497786849714844</v>
+        <v>0.1493490164092979</v>
       </c>
       <c r="J1882">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1882">
-        <v>6.1</v>
+        <v>6.82</v>
       </c>
       <c r="L1882">
-        <v>6.05</v>
+        <v>6.62</v>
       </c>
       <c r="M1882">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1882">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1882">
         <v>1</v>
@@ -96285,46 +96285,46 @@
     </row>
     <row r="1883" spans="1:16">
       <c r="A1883" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1883" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C1883">
-        <v>1.155073069179202</v>
+        <v>1.247838695694227</v>
       </c>
       <c r="D1883" t="s">
         <v>442</v>
       </c>
       <c r="E1883">
-        <v>1.098060010722743</v>
+        <v>1.101677197465231</v>
       </c>
       <c r="F1883">
         <v>-1</v>
       </c>
       <c r="G1883">
-        <v>0.0106649269308208</v>
+        <v>0.01085216130430577</v>
       </c>
       <c r="H1883">
-        <v>0.008261939989277255</v>
+        <v>0.008218322802534768</v>
       </c>
       <c r="I1883">
-        <v>0.05701305845645877</v>
+        <v>0.146161498228996</v>
       </c>
       <c r="J1883">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1883">
-        <v>6.04</v>
+        <v>6.1</v>
       </c>
       <c r="L1883">
-        <v>5.91</v>
+        <v>6.05</v>
       </c>
       <c r="M1883">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1883">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1883">
         <v>1</v>
@@ -96335,46 +96335,46 @@
     </row>
     <row r="1884" spans="1:16">
       <c r="A1884" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1884" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1884">
-        <v>1.163166779788547</v>
+        <v>1.155073069179202</v>
       </c>
       <c r="D1884" t="s">
         <v>442</v>
       </c>
       <c r="E1884">
-        <v>1.098060010722743</v>
+        <v>1.101677197465231</v>
       </c>
       <c r="F1884">
         <v>-1</v>
       </c>
       <c r="G1884">
-        <v>0.008216833220211455</v>
+        <v>0.0106649269308208</v>
       </c>
       <c r="H1884">
-        <v>0.008261939989277255</v>
+        <v>0.008218322802534768</v>
       </c>
       <c r="I1884">
-        <v>0.06510676906580448</v>
+        <v>0.05339587171397042</v>
       </c>
       <c r="J1884">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1884">
-        <v>4.48</v>
+        <v>6.04</v>
       </c>
       <c r="L1884">
-        <v>4.69</v>
+        <v>5.91</v>
       </c>
       <c r="M1884">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1884">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1884">
         <v>1</v>
@@ -96385,63 +96385,63 @@
     </row>
     <row r="1885" spans="1:16">
       <c r="A1885" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1885" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C1885">
-        <v>0.5854580999890051</v>
+        <v>1.163166779788547</v>
       </c>
       <c r="D1885" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E1885">
-        <v>0.8856264957863074</v>
+        <v>1.101677197465231</v>
       </c>
       <c r="F1885">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1885">
-        <v>0.008154541900010996</v>
+        <v>0.008216833220211455</v>
       </c>
       <c r="H1885">
-        <v>0.00915437350421369</v>
+        <v>0.008218322802534768</v>
       </c>
       <c r="I1885">
-        <v>0.3001683957973023</v>
+        <v>0.06148958232331614</v>
       </c>
       <c r="J1885">
-        <v>0.7950718277334023</v>
+        <v>0.7872395580829136</v>
       </c>
       <c r="K1885">
-        <v>4.76</v>
+        <v>4.48</v>
       </c>
       <c r="L1885">
-        <v>4.37</v>
+        <v>4.69</v>
       </c>
       <c r="M1885">
-        <v>5.2</v>
+        <v>4.52</v>
       </c>
       <c r="N1885">
-        <v>5.02</v>
+        <v>4.66</v>
       </c>
       <c r="O1885">
         <v>1</v>
       </c>
       <c r="P1885" t="s">
-        <v>225</v>
+        <v>424</v>
       </c>
     </row>
     <row r="1886" spans="1:16">
       <c r="A1886" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1886" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C1886">
-        <v>0.5964437344423246</v>
+        <v>0.5854580999890051</v>
       </c>
       <c r="D1886" t="s">
         <v>439</v>
@@ -96453,22 +96453,22 @@
         <v>1</v>
       </c>
       <c r="G1886">
-        <v>0.008483556265557676</v>
+        <v>0.008154541900010996</v>
       </c>
       <c r="H1886">
         <v>0.00915437350421369</v>
       </c>
       <c r="I1886">
-        <v>0.2891827613439828</v>
+        <v>0.3001683957973023</v>
       </c>
       <c r="J1886">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1886">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="L1886">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1886">
         <v>5.2</v>
@@ -96485,13 +96485,13 @@
     </row>
     <row r="1887" spans="1:16">
       <c r="A1887" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1887" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C1887">
-        <v>0.6202958892743267</v>
+        <v>0.5964437344423246</v>
       </c>
       <c r="D1887" t="s">
         <v>439</v>
@@ -96503,19 +96503,19 @@
         <v>1</v>
       </c>
       <c r="G1887">
-        <v>0.008459704110725675</v>
+        <v>0.008483556265557676</v>
       </c>
       <c r="H1887">
         <v>0.00915437350421369</v>
       </c>
       <c r="I1887">
-        <v>0.2653306065119807</v>
+        <v>0.2891827613439828</v>
       </c>
       <c r="J1887">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1887">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="L1887">
         <v>4.54</v>
@@ -96535,46 +96535,46 @@
     </row>
     <row r="1888" spans="1:16">
       <c r="A1888" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1888" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C1888">
-        <v>1.197610134858196</v>
+        <v>0.6202958892743267</v>
       </c>
       <c r="D1888" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E1888">
-        <v>1.062423183813019</v>
+        <v>0.8856264957863074</v>
       </c>
       <c r="F1888">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1888">
-        <v>0.0120423898651418</v>
+        <v>0.008459704110725675</v>
       </c>
       <c r="H1888">
-        <v>0.00829757681618698</v>
+        <v>0.00915437350421369</v>
       </c>
       <c r="I1888">
-        <v>0.1351869510451764</v>
+        <v>0.2653306065119807</v>
       </c>
       <c r="J1888">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1888">
-        <v>6.82</v>
+        <v>4.93</v>
       </c>
       <c r="L1888">
-        <v>6.62</v>
+        <v>4.54</v>
       </c>
       <c r="M1888">
-        <v>4.55</v>
+        <v>5.2</v>
       </c>
       <c r="N1888">
-        <v>4.68</v>
+        <v>5.02</v>
       </c>
       <c r="O1888">
         <v>1</v>
@@ -96585,46 +96585,46 @@
     </row>
     <row r="1889" spans="1:16">
       <c r="A1889" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1889" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C1889">
-        <v>1.200061850826246</v>
+        <v>1.197610134858196</v>
       </c>
       <c r="D1889" t="s">
         <v>442</v>
       </c>
       <c r="E1889">
-        <v>1.062423183813019</v>
+        <v>1.066275338645022</v>
       </c>
       <c r="F1889">
         <v>-1</v>
       </c>
       <c r="G1889">
-        <v>0.01089993814917375</v>
+        <v>0.0120423898651418</v>
       </c>
       <c r="H1889">
-        <v>0.00829757681618698</v>
+        <v>0.008253724661354978</v>
       </c>
       <c r="I1889">
-        <v>0.1376386670132264</v>
+        <v>0.1313347962131739</v>
       </c>
       <c r="J1889">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1889">
-        <v>6.1</v>
+        <v>6.82</v>
       </c>
       <c r="L1889">
-        <v>6.05</v>
+        <v>6.62</v>
       </c>
       <c r="M1889">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1889">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1889">
         <v>1</v>
@@ -96635,46 +96635,46 @@
     </row>
     <row r="1890" spans="1:16">
       <c r="A1890" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1890" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C1890">
-        <v>1.10776616049025</v>
+        <v>1.200061850826246</v>
       </c>
       <c r="D1890" t="s">
         <v>442</v>
       </c>
       <c r="E1890">
-        <v>1.062423183813019</v>
+        <v>1.066275338645022</v>
       </c>
       <c r="F1890">
         <v>-1</v>
       </c>
       <c r="G1890">
-        <v>0.01071223383950975</v>
+        <v>0.01089993814917375</v>
       </c>
       <c r="H1890">
-        <v>0.00829757681618698</v>
+        <v>0.008253724661354978</v>
       </c>
       <c r="I1890">
-        <v>0.04534297667723086</v>
+        <v>0.1337865121812238</v>
       </c>
       <c r="J1890">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1890">
-        <v>6.04</v>
+        <v>6.1</v>
       </c>
       <c r="L1890">
-        <v>5.91</v>
+        <v>6.05</v>
       </c>
       <c r="M1890">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1890">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1890">
         <v>1</v>
@@ -96685,46 +96685,46 @@
     </row>
     <row r="1891" spans="1:16">
       <c r="A1891" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1891" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1891">
-        <v>1.128078211754358</v>
+        <v>1.10776616049025</v>
       </c>
       <c r="D1891" t="s">
         <v>442</v>
       </c>
       <c r="E1891">
-        <v>1.062423183813019</v>
+        <v>1.066275338645022</v>
       </c>
       <c r="F1891">
         <v>-1</v>
       </c>
       <c r="G1891">
-        <v>0.008251921788245643</v>
+        <v>0.01071223383950975</v>
       </c>
       <c r="H1891">
-        <v>0.00829757681618698</v>
+        <v>0.008253724661354978</v>
       </c>
       <c r="I1891">
-        <v>0.06565502794133815</v>
+        <v>0.04149082184522834</v>
       </c>
       <c r="J1891">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1891">
-        <v>4.48</v>
+        <v>6.04</v>
       </c>
       <c r="L1891">
-        <v>4.69</v>
+        <v>5.91</v>
       </c>
       <c r="M1891">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1891">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1891">
         <v>1</v>
@@ -96735,63 +96735,63 @@
     </row>
     <row r="1892" spans="1:16">
       <c r="A1892" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1892" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C1892">
-        <v>0.5696561779646796</v>
+        <v>1.128078211754358</v>
       </c>
       <c r="D1892" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E1892">
-        <v>0.8683638918941865</v>
+        <v>1.066275338645022</v>
       </c>
       <c r="F1892">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1892">
-        <v>0.00817034382203532</v>
+        <v>0.008251921788245643</v>
       </c>
       <c r="H1892">
-        <v>0.009171636108105811</v>
+        <v>0.008253724661354978</v>
       </c>
       <c r="I1892">
-        <v>0.2987077139295069</v>
+        <v>0.06180287310933563</v>
       </c>
       <c r="J1892">
-        <v>0.7983915592511178</v>
+        <v>0.7950718277334023</v>
       </c>
       <c r="K1892">
-        <v>4.76</v>
+        <v>4.48</v>
       </c>
       <c r="L1892">
-        <v>4.37</v>
+        <v>4.69</v>
       </c>
       <c r="M1892">
-        <v>5.2</v>
+        <v>4.52</v>
       </c>
       <c r="N1892">
-        <v>5.02</v>
+        <v>4.66</v>
       </c>
       <c r="O1892">
         <v>1</v>
       </c>
       <c r="P1892" t="s">
-        <v>426</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1893" spans="1:16">
       <c r="A1893" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1893" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C1893">
-        <v>0.5799778661144557</v>
+        <v>0.5696561779646796</v>
       </c>
       <c r="D1893" t="s">
         <v>439</v>
@@ -96803,22 +96803,22 @@
         <v>1</v>
       </c>
       <c r="G1893">
-        <v>0.008500022133885544</v>
+        <v>0.00817034382203532</v>
       </c>
       <c r="H1893">
         <v>0.009171636108105811</v>
       </c>
       <c r="I1893">
-        <v>0.2883860257797308</v>
+        <v>0.2987077139295069</v>
       </c>
       <c r="J1893">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1893">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="L1893">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1893">
         <v>5.2</v>
@@ -96835,13 +96835,13 @@
     </row>
     <row r="1894" spans="1:16">
       <c r="A1894" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1894" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C1894">
-        <v>0.6039296128919895</v>
+        <v>0.5799778661144557</v>
       </c>
       <c r="D1894" t="s">
         <v>439</v>
@@ -96853,19 +96853,19 @@
         <v>1</v>
       </c>
       <c r="G1894">
-        <v>0.008476070387108009</v>
+        <v>0.008500022133885544</v>
       </c>
       <c r="H1894">
         <v>0.009171636108105811</v>
       </c>
       <c r="I1894">
-        <v>0.264434279002197</v>
+        <v>0.2883860257797308</v>
       </c>
       <c r="J1894">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1894">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="L1894">
         <v>4.54</v>
@@ -96885,46 +96885,46 @@
     </row>
     <row r="1895" spans="1:16">
       <c r="A1895" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1895" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C1895">
-        <v>1.174969565907376</v>
+        <v>0.6039296128919895</v>
       </c>
       <c r="D1895" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E1895">
-        <v>1.047318405407414</v>
+        <v>0.8683638918941865</v>
       </c>
       <c r="F1895">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1895">
-        <v>0.01206503043409262</v>
+        <v>0.008476070387108009</v>
       </c>
       <c r="H1895">
-        <v>0.008312681594592586</v>
+        <v>0.009171636108105811</v>
       </c>
       <c r="I1895">
-        <v>0.1276511604999624</v>
+        <v>0.264434279002197</v>
       </c>
       <c r="J1895">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1895">
-        <v>6.82</v>
+        <v>4.93</v>
       </c>
       <c r="L1895">
-        <v>6.62</v>
+        <v>4.54</v>
       </c>
       <c r="M1895">
-        <v>4.55</v>
+        <v>5.2</v>
       </c>
       <c r="N1895">
-        <v>4.68</v>
+        <v>5.02</v>
       </c>
       <c r="O1895">
         <v>1</v>
@@ -96935,46 +96935,46 @@
     </row>
     <row r="1896" spans="1:16">
       <c r="A1896" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1896" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C1896">
-        <v>1.179811488568181</v>
+        <v>1.174969565907376</v>
       </c>
       <c r="D1896" t="s">
         <v>442</v>
       </c>
       <c r="E1896">
-        <v>1.047318405407414</v>
+        <v>1.051270152184948</v>
       </c>
       <c r="F1896">
         <v>-1</v>
       </c>
       <c r="G1896">
-        <v>0.01092018851143182</v>
+        <v>0.01206503043409262</v>
       </c>
       <c r="H1896">
-        <v>0.008312681594592586</v>
+        <v>0.008268729847815053</v>
       </c>
       <c r="I1896">
-        <v>0.1324930831607678</v>
+        <v>0.1236994137224281</v>
       </c>
       <c r="J1896">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1896">
-        <v>6.1</v>
+        <v>6.82</v>
       </c>
       <c r="L1896">
-        <v>6.05</v>
+        <v>6.62</v>
       </c>
       <c r="M1896">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1896">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1896">
         <v>1</v>
@@ -96985,46 +96985,46 @@
     </row>
     <row r="1897" spans="1:16">
       <c r="A1897" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1897" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C1897">
-        <v>1.087714982123249</v>
+        <v>1.179811488568181</v>
       </c>
       <c r="D1897" t="s">
         <v>442</v>
       </c>
       <c r="E1897">
-        <v>1.047318405407414</v>
+        <v>1.051270152184948</v>
       </c>
       <c r="F1897">
         <v>-1</v>
       </c>
       <c r="G1897">
-        <v>0.01073228501787675</v>
+        <v>0.01092018851143182</v>
       </c>
       <c r="H1897">
-        <v>0.008312681594592586</v>
+        <v>0.008268729847815053</v>
       </c>
       <c r="I1897">
-        <v>0.04039657671583496</v>
+        <v>0.1285413363832335</v>
       </c>
       <c r="J1897">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1897">
-        <v>6.04</v>
+        <v>6.1</v>
       </c>
       <c r="L1897">
-        <v>5.91</v>
+        <v>6.05</v>
       </c>
       <c r="M1897">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1897">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1897">
         <v>1</v>
@@ -97035,46 +97035,46 @@
     </row>
     <row r="1898" spans="1:16">
       <c r="A1898" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1898" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1898">
-        <v>1.113205814554992</v>
+        <v>1.087714982123249</v>
       </c>
       <c r="D1898" t="s">
         <v>442</v>
       </c>
       <c r="E1898">
-        <v>1.047318405407414</v>
+        <v>1.051270152184948</v>
       </c>
       <c r="F1898">
         <v>-1</v>
       </c>
       <c r="G1898">
-        <v>0.008266794185445007</v>
+        <v>0.01073228501787675</v>
       </c>
       <c r="H1898">
-        <v>0.008312681594592586</v>
+        <v>0.008268729847815053</v>
       </c>
       <c r="I1898">
-        <v>0.06588740914757851</v>
+        <v>0.03644482993830067</v>
       </c>
       <c r="J1898">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1898">
-        <v>4.48</v>
+        <v>6.04</v>
       </c>
       <c r="L1898">
-        <v>4.69</v>
+        <v>5.91</v>
       </c>
       <c r="M1898">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1898">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1898">
         <v>1</v>
@@ -97085,63 +97085,63 @@
     </row>
     <row r="1899" spans="1:16">
       <c r="A1899" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1899" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C1899">
-        <v>0.4754849636079563</v>
+        <v>1.113205814554992</v>
       </c>
       <c r="D1899" t="s">
-        <v>250</v>
+        <v>442</v>
       </c>
       <c r="E1899">
-        <v>0.8773067240324215</v>
+        <v>1.051270152184948</v>
       </c>
       <c r="F1899">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1899">
-        <v>0.008264515036392044</v>
+        <v>0.008266794185445007</v>
       </c>
       <c r="H1899">
-        <v>0.009582693275967578</v>
+        <v>0.008268729847815053</v>
       </c>
       <c r="I1899">
-        <v>0.4018217604244652</v>
+        <v>0.06193566237004422</v>
       </c>
       <c r="J1899">
-        <v>0.8181754278134546</v>
+        <v>0.7983915592511178</v>
       </c>
       <c r="K1899">
-        <v>4.76</v>
+        <v>4.48</v>
       </c>
       <c r="L1899">
-        <v>4.37</v>
+        <v>4.69</v>
       </c>
       <c r="M1899">
-        <v>5.32</v>
+        <v>4.52</v>
       </c>
       <c r="N1899">
-        <v>5.23</v>
+        <v>4.66</v>
       </c>
       <c r="O1899">
         <v>1</v>
       </c>
       <c r="P1899" t="s">
-        <v>246</v>
+        <v>426</v>
       </c>
     </row>
     <row r="1900" spans="1:16">
       <c r="A1900" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1900" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C1900">
-        <v>0.4818498780452654</v>
+        <v>0.4754849636079563</v>
       </c>
       <c r="D1900" t="s">
         <v>250</v>
@@ -97153,22 +97153,22 @@
         <v>1</v>
       </c>
       <c r="G1900">
-        <v>0.008598150121954735</v>
+        <v>0.008264515036392044</v>
       </c>
       <c r="H1900">
         <v>0.009582693275967578</v>
       </c>
       <c r="I1900">
-        <v>0.3954568459871561</v>
+        <v>0.4018217604244652</v>
       </c>
       <c r="J1900">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1900">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="L1900">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1900">
         <v>5.32</v>
@@ -97185,13 +97185,13 @@
     </row>
     <row r="1901" spans="1:16">
       <c r="A1901" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1901" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C1901">
-        <v>0.5063951408796692</v>
+        <v>0.4818498780452654</v>
       </c>
       <c r="D1901" t="s">
         <v>250</v>
@@ -97203,19 +97203,19 @@
         <v>1</v>
       </c>
       <c r="G1901">
-        <v>0.008573604859120331</v>
+        <v>0.008598150121954735</v>
       </c>
       <c r="H1901">
         <v>0.009582693275967578</v>
       </c>
       <c r="I1901">
-        <v>0.3709115831527523</v>
+        <v>0.3954568459871561</v>
       </c>
       <c r="J1901">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1901">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="L1901">
         <v>4.54</v>
@@ -97235,46 +97235,46 @@
     </row>
     <row r="1902" spans="1:16">
       <c r="A1902" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1902" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C1902">
-        <v>0.5518576103909849</v>
+        <v>0.5063951408796692</v>
       </c>
       <c r="D1902" t="s">
-        <v>443</v>
+        <v>250</v>
       </c>
       <c r="E1902">
-        <v>0.7845874392656027</v>
+        <v>0.8773067240324215</v>
       </c>
       <c r="F1902">
         <v>1</v>
       </c>
       <c r="G1902">
-        <v>0.01064814238960901</v>
+        <v>0.008573604859120331</v>
       </c>
       <c r="H1902">
-        <v>0.0115354125607344</v>
+        <v>0.009582693275967578</v>
       </c>
       <c r="I1902">
-        <v>0.2327298288746178</v>
+        <v>0.3709115831527523</v>
       </c>
       <c r="J1902">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1902">
-        <v>6.17</v>
+        <v>4.93</v>
       </c>
       <c r="L1902">
-        <v>5.6</v>
+        <v>4.54</v>
       </c>
       <c r="M1902">
-        <v>6.57</v>
+        <v>5.32</v>
       </c>
       <c r="N1902">
-        <v>6.16</v>
+        <v>5.23</v>
       </c>
       <c r="O1902">
         <v>1</v>
@@ -97285,46 +97285,46 @@
     </row>
     <row r="1903" spans="1:16">
       <c r="A1903" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1903" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C1903">
-        <v>1.059129890337926</v>
+        <v>0.5518576103909849</v>
       </c>
       <c r="D1903" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E1903">
-        <v>0.957301803448781</v>
+        <v>0.7845874392656027</v>
       </c>
       <c r="F1903">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1903">
-        <v>0.01104087010966207</v>
+        <v>0.01064814238960901</v>
       </c>
       <c r="H1903">
-        <v>0.00840269819655122</v>
+        <v>0.0115354125607344</v>
       </c>
       <c r="I1903">
-        <v>0.1018280868891455</v>
+        <v>0.2327298288746178</v>
       </c>
       <c r="J1903">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1903">
-        <v>6.1</v>
+        <v>6.17</v>
       </c>
       <c r="L1903">
-        <v>6.05</v>
+        <v>5.6</v>
       </c>
       <c r="M1903">
-        <v>4.55</v>
+        <v>6.57</v>
       </c>
       <c r="N1903">
-        <v>4.68</v>
+        <v>6.16</v>
       </c>
       <c r="O1903">
         <v>1</v>
@@ -97335,46 +97335,46 @@
     </row>
     <row r="1904" spans="1:16">
       <c r="A1904" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1904" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C1904">
-        <v>0.9864000614633088</v>
+        <v>1.059129890337926</v>
       </c>
       <c r="D1904" t="s">
         <v>442</v>
       </c>
       <c r="E1904">
-        <v>0.957301803448781</v>
+        <v>0.9618470662831853</v>
       </c>
       <c r="F1904">
         <v>-1</v>
       </c>
       <c r="G1904">
-        <v>0.01031359993853669</v>
+        <v>0.01104087010966207</v>
       </c>
       <c r="H1904">
-        <v>0.00840269819655122</v>
+        <v>0.008358152933716815</v>
       </c>
       <c r="I1904">
-        <v>0.02909825801452781</v>
+        <v>0.0972828240547412</v>
       </c>
       <c r="J1904">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1904">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="L1904">
-        <v>5.65</v>
+        <v>6.05</v>
       </c>
       <c r="M1904">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1904">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1904">
         <v>1</v>
@@ -97385,46 +97385,46 @@
     </row>
     <row r="1905" spans="1:16">
       <c r="A1905" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1905" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C1905">
-        <v>1.024574083395723</v>
+        <v>0.9864000614633088</v>
       </c>
       <c r="D1905" t="s">
         <v>442</v>
       </c>
       <c r="E1905">
-        <v>0.957301803448781</v>
+        <v>0.9618470662831853</v>
       </c>
       <c r="F1905">
         <v>-1</v>
       </c>
       <c r="G1905">
-        <v>0.008355425916604278</v>
+        <v>0.01031359993853669</v>
       </c>
       <c r="H1905">
-        <v>0.00840269819655122</v>
+        <v>0.008358152933716815</v>
       </c>
       <c r="I1905">
-        <v>0.06727227994694207</v>
+        <v>0.02455299518012355</v>
       </c>
       <c r="J1905">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1905">
-        <v>4.48</v>
+        <v>5.7</v>
       </c>
       <c r="L1905">
-        <v>4.69</v>
+        <v>5.65</v>
       </c>
       <c r="M1905">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="N1905">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="O1905">
         <v>1</v>
@@ -97435,63 +97435,63 @@
     </row>
     <row r="1906" spans="1:16">
       <c r="A1906" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1906" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C1906">
-        <v>0.545481672883029</v>
+        <v>1.024574083395723</v>
       </c>
       <c r="D1906" t="s">
-        <v>255</v>
+        <v>442</v>
       </c>
       <c r="E1906">
-        <v>0.8503069233264586</v>
+        <v>0.9618470662831853</v>
       </c>
       <c r="F1906">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1906">
-        <v>0.009834518327116971</v>
+        <v>0.008355425916604278</v>
       </c>
       <c r="H1906">
-        <v>0.01238969307667354</v>
+        <v>0.008358152933716815</v>
       </c>
       <c r="I1906">
-        <v>0.3048252504434297</v>
+        <v>0.06272701711253781</v>
       </c>
       <c r="J1906">
-        <v>0.8459960522981732</v>
+        <v>0.8181754278134546</v>
       </c>
       <c r="K1906">
-        <v>5.49</v>
+        <v>4.48</v>
       </c>
       <c r="L1906">
-        <v>5.19</v>
+        <v>4.69</v>
       </c>
       <c r="M1906">
-        <v>6.82</v>
+        <v>4.52</v>
       </c>
       <c r="N1906">
-        <v>6.62</v>
+        <v>4.66</v>
       </c>
       <c r="O1906">
         <v>1</v>
       </c>
       <c r="P1906" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="1907" spans="1:16">
       <c r="A1907" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1907" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1907">
-        <v>0.4840236862109606</v>
+        <v>0.545481672883029</v>
       </c>
       <c r="D1907" t="s">
         <v>255</v>
@@ -97503,22 +97503,22 @@
         <v>1</v>
       </c>
       <c r="G1907">
-        <v>0.01063597631378904</v>
+        <v>0.009834518327116971</v>
       </c>
       <c r="H1907">
         <v>0.01238969307667354</v>
       </c>
       <c r="I1907">
-        <v>0.366283237115498</v>
+        <v>0.3048252504434297</v>
       </c>
       <c r="J1907">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1907">
-        <v>6</v>
+        <v>5.49</v>
       </c>
       <c r="L1907">
-        <v>5.56</v>
+        <v>5.19</v>
       </c>
       <c r="M1907">
         <v>6.82</v>
@@ -97535,46 +97535,46 @@
     </row>
     <row r="1908" spans="1:16">
       <c r="A1908" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1908" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C1908">
-        <v>0.9041057390159111</v>
+        <v>0.4840236862109606</v>
       </c>
       <c r="D1908" t="s">
-        <v>444</v>
+        <v>255</v>
       </c>
       <c r="E1908">
-        <v>0.6972268443724223</v>
+        <v>0.8503069233264586</v>
       </c>
       <c r="F1908">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1908">
-        <v>0.01193589426098409</v>
+        <v>0.01063597631378904</v>
       </c>
       <c r="H1908">
-        <v>0.01220277315562758</v>
+        <v>0.01238969307667354</v>
       </c>
       <c r="I1908">
-        <v>0.2068788946434887</v>
+        <v>0.366283237115498</v>
       </c>
       <c r="J1908">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1908">
-        <v>6.52</v>
+        <v>6</v>
       </c>
       <c r="L1908">
-        <v>6.42</v>
+        <v>5.56</v>
       </c>
       <c r="M1908">
-        <v>6.8</v>
+        <v>6.82</v>
       </c>
       <c r="N1908">
-        <v>6.45</v>
+        <v>6.62</v>
       </c>
       <c r="O1908">
         <v>1</v>
@@ -97585,46 +97585,46 @@
     </row>
     <row r="1909" spans="1:16">
       <c r="A1909" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1909" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1909">
-        <v>1.019321514974956</v>
+        <v>0.9041057390159111</v>
       </c>
       <c r="D1909" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E1909">
-        <v>0.6999376857041839</v>
+        <v>0.6972268443724223</v>
       </c>
       <c r="F1909">
         <v>-1</v>
       </c>
       <c r="G1909">
-        <v>0.01024067848502504</v>
+        <v>0.01193589426098409</v>
       </c>
       <c r="H1909">
-        <v>0.008280062314295816</v>
+        <v>0.01220277315562758</v>
       </c>
       <c r="I1909">
-        <v>0.3193838292707718</v>
+        <v>0.2068788946434887</v>
       </c>
       <c r="J1909">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1909">
-        <v>5.45</v>
+        <v>6.52</v>
       </c>
       <c r="L1909">
-        <v>5.63</v>
+        <v>6.42</v>
       </c>
       <c r="M1909">
-        <v>4.48</v>
+        <v>6.8</v>
       </c>
       <c r="N1909">
-        <v>4.49</v>
+        <v>6.45</v>
       </c>
       <c r="O1909">
         <v>1</v>
@@ -97635,13 +97635,13 @@
     </row>
     <row r="1910" spans="1:16">
       <c r="A1910" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1910" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C1910">
-        <v>0.8999376857041841</v>
+        <v>1.019321514974956</v>
       </c>
       <c r="D1910" t="s">
         <v>445</v>
@@ -97653,22 +97653,22 @@
         <v>-1</v>
       </c>
       <c r="G1910">
-        <v>0.008480062314295817</v>
+        <v>0.01024067848502504</v>
       </c>
       <c r="H1910">
         <v>0.008280062314295816</v>
       </c>
       <c r="I1910">
-        <v>0.2000000000000002</v>
+        <v>0.3193838292707718</v>
       </c>
       <c r="J1910">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1910">
-        <v>4.48</v>
+        <v>5.45</v>
       </c>
       <c r="L1910">
-        <v>4.69</v>
+        <v>5.63</v>
       </c>
       <c r="M1910">
         <v>4.48</v>
@@ -97680,6 +97680,56 @@
         <v>1</v>
       </c>
       <c r="P1910" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:16">
+      <c r="A1911" s="1">
+        <v>4</v>
+      </c>
+      <c r="B1911" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1911">
+        <v>0.8999376857041841</v>
+      </c>
+      <c r="D1911" t="s">
+        <v>445</v>
+      </c>
+      <c r="E1911">
+        <v>0.6999376857041839</v>
+      </c>
+      <c r="F1911">
+        <v>-1</v>
+      </c>
+      <c r="G1911">
+        <v>0.008480062314295817</v>
+      </c>
+      <c r="H1911">
+        <v>0.008280062314295816</v>
+      </c>
+      <c r="I1911">
+        <v>0.2000000000000002</v>
+      </c>
+      <c r="J1911">
+        <v>0.8459960522981732</v>
+      </c>
+      <c r="K1911">
+        <v>4.48</v>
+      </c>
+      <c r="L1911">
+        <v>4.69</v>
+      </c>
+      <c r="M1911">
+        <v>4.48</v>
+      </c>
+      <c r="N1911">
+        <v>4.49</v>
+      </c>
+      <c r="O1911">
+        <v>1</v>
+      </c>
+      <c r="P1911" t="s">
         <v>247</v>
       </c>
     </row>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -1342,7 +1342,7 @@
     <t>2021-08-20</t>
   </si>
   <si>
-    <t>2021-10-25</t>
+    <t>2021-10-26</t>
   </si>
   <si>
     <t>2021-09-07</t>
@@ -95647,7 +95647,7 @@
         <v>442</v>
       </c>
       <c r="E1870">
-        <v>1.088155249369974</v>
+        <v>1.031380439985111</v>
       </c>
       <c r="F1870">
         <v>-1</v>
@@ -95656,10 +95656,10 @@
         <v>0.0118998599998409</v>
       </c>
       <c r="H1870">
-        <v>0.007931844750630026</v>
+        <v>0.007828619560014889</v>
       </c>
       <c r="I1870">
-        <v>0.2519847507891266</v>
+        <v>0.3087595601739905</v>
       </c>
       <c r="J1870">
         <v>0.7741730205045306</v>
@@ -95671,10 +95671,10 @@
         <v>6.62</v>
       </c>
       <c r="M1870">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1870">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1870">
         <v>1</v>
@@ -95697,7 +95697,7 @@
         <v>442</v>
       </c>
       <c r="E1871">
-        <v>1.088155249369974</v>
+        <v>1.031380439985111</v>
       </c>
       <c r="F1871">
         <v>-1</v>
@@ -95706,10 +95706,10 @@
         <v>0.01058600504384737</v>
       </c>
       <c r="H1871">
-        <v>0.007931844750630026</v>
+        <v>0.007828619560014889</v>
       </c>
       <c r="I1871">
-        <v>0.1458397067826609</v>
+        <v>0.2026145161675248</v>
       </c>
       <c r="J1871">
         <v>0.7741730205045306</v>
@@ -95721,10 +95721,10 @@
         <v>5.91</v>
       </c>
       <c r="M1871">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1871">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1871">
         <v>1</v>
@@ -95747,7 +95747,7 @@
         <v>442</v>
       </c>
       <c r="E1872">
-        <v>1.088155249369974</v>
+        <v>1.031380439985111</v>
       </c>
       <c r="F1872">
         <v>-1</v>
@@ -95756,10 +95756,10 @@
         <v>0.008158295131860298</v>
       </c>
       <c r="H1872">
-        <v>0.007931844750630026</v>
+        <v>0.007828619560014889</v>
       </c>
       <c r="I1872">
-        <v>0.1335496187697283</v>
+        <v>0.1903244281545922</v>
       </c>
       <c r="J1872">
         <v>0.7741730205045306</v>
@@ -95771,10 +95771,10 @@
         <v>4.69</v>
       </c>
       <c r="M1872">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1872">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1872">
         <v>1</v>
@@ -95947,7 +95947,7 @@
         <v>442</v>
       </c>
       <c r="E1876">
-        <v>1.07111434155384</v>
+        <v>1.014455194439221</v>
       </c>
       <c r="F1876">
         <v>-1</v>
@@ -95956,10 +95956,10 @@
         <v>0.01192615388927666</v>
       </c>
       <c r="H1876">
-        <v>0.007948885658446161</v>
+        <v>0.007845544805560779</v>
       </c>
       <c r="I1876">
-        <v>0.2427317691695063</v>
+        <v>0.2993909162841248</v>
       </c>
       <c r="J1876">
         <v>0.7780284295127059</v>
@@ -95971,10 +95971,10 @@
         <v>6.62</v>
       </c>
       <c r="M1876">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1876">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1876">
         <v>1</v>
@@ -95997,7 +95997,7 @@
         <v>442</v>
       </c>
       <c r="E1877">
-        <v>1.07111434155384</v>
+        <v>1.014455194439221</v>
       </c>
       <c r="F1877">
         <v>-1</v>
@@ -96006,10 +96006,10 @@
         <v>0.0107959734200275</v>
       </c>
       <c r="H1877">
-        <v>0.007948885658446161</v>
+        <v>0.007845544805560779</v>
       </c>
       <c r="I1877">
-        <v>0.2329122384186548</v>
+        <v>0.2895713855332733</v>
       </c>
       <c r="J1877">
         <v>0.7780284295127059</v>
@@ -96021,10 +96021,10 @@
         <v>6.05</v>
       </c>
       <c r="M1877">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1877">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1877">
         <v>1</v>
@@ -96047,7 +96047,7 @@
         <v>442</v>
       </c>
       <c r="E1878">
-        <v>1.07111434155384</v>
+        <v>1.014455194439221</v>
       </c>
       <c r="F1878">
         <v>-1</v>
@@ -96056,10 +96056,10 @@
         <v>0.01060929171425675</v>
       </c>
       <c r="H1878">
-        <v>0.007948885658446161</v>
+        <v>0.007845544805560779</v>
       </c>
       <c r="I1878">
-        <v>0.1395939441894165</v>
+        <v>0.196253091304035</v>
       </c>
       <c r="J1878">
         <v>0.7780284295127059</v>
@@ -96071,10 +96071,10 @@
         <v>5.91</v>
       </c>
       <c r="M1878">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1878">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1878">
         <v>1</v>
@@ -96097,7 +96097,7 @@
         <v>442</v>
       </c>
       <c r="E1879">
-        <v>1.07111434155384</v>
+        <v>1.014455194439221</v>
       </c>
       <c r="F1879">
         <v>-1</v>
@@ -96106,10 +96106,10 @@
         <v>0.008175567364216924</v>
       </c>
       <c r="H1879">
-        <v>0.007948885658446161</v>
+        <v>0.007845544805560779</v>
       </c>
       <c r="I1879">
-        <v>0.1333182942292379</v>
+        <v>0.1899774413438564</v>
       </c>
       <c r="J1879">
         <v>0.7780284295127059</v>
@@ -96121,10 +96121,10 @@
         <v>4.69</v>
       </c>
       <c r="M1879">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1879">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1879">
         <v>1</v>
@@ -96297,7 +96297,7 @@
         <v>442</v>
       </c>
       <c r="E1883">
-        <v>1.030401153273522</v>
+        <v>0.9740183400160092</v>
       </c>
       <c r="F1883">
         <v>-1</v>
@@ -96306,10 +96306,10 @@
         <v>0.01198897378612547</v>
       </c>
       <c r="H1883">
-        <v>0.007989598846726478</v>
+        <v>0.00788598165998399</v>
       </c>
       <c r="I1883">
-        <v>0.2206250606010074</v>
+        <v>0.27700787385852</v>
       </c>
       <c r="J1883">
         <v>0.7872395580829136</v>
@@ -96321,10 +96321,10 @@
         <v>6.62</v>
       </c>
       <c r="M1883">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1883">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1883">
         <v>1</v>
@@ -96347,7 +96347,7 @@
         <v>442</v>
       </c>
       <c r="E1884">
-        <v>1.030401153273522</v>
+        <v>0.9740183400160092</v>
       </c>
       <c r="F1884">
         <v>-1</v>
@@ -96356,10 +96356,10 @@
         <v>0.01085216130430577</v>
       </c>
       <c r="H1884">
-        <v>0.007989598846726478</v>
+        <v>0.00788598165998399</v>
       </c>
       <c r="I1884">
-        <v>0.2174375424207056</v>
+        <v>0.2738203556782182</v>
       </c>
       <c r="J1884">
         <v>0.7872395580829136</v>
@@ -96371,10 +96371,10 @@
         <v>6.05</v>
       </c>
       <c r="M1884">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1884">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1884">
         <v>1</v>
@@ -96397,7 +96397,7 @@
         <v>442</v>
       </c>
       <c r="E1885">
-        <v>1.030401153273522</v>
+        <v>0.9740183400160092</v>
       </c>
       <c r="F1885">
         <v>-1</v>
@@ -96406,10 +96406,10 @@
         <v>0.0106649269308208</v>
       </c>
       <c r="H1885">
-        <v>0.007989598846726478</v>
+        <v>0.00788598165998399</v>
       </c>
       <c r="I1885">
-        <v>0.1246719159056799</v>
+        <v>0.1810547291631925</v>
       </c>
       <c r="J1885">
         <v>0.7872395580829136</v>
@@ -96421,10 +96421,10 @@
         <v>5.91</v>
       </c>
       <c r="M1885">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1885">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1885">
         <v>1</v>
@@ -96447,7 +96447,7 @@
         <v>442</v>
       </c>
       <c r="E1886">
-        <v>1.030401153273522</v>
+        <v>0.9740183400160092</v>
       </c>
       <c r="F1886">
         <v>-1</v>
@@ -96456,10 +96456,10 @@
         <v>0.008216833220211455</v>
       </c>
       <c r="H1886">
-        <v>0.007989598846726478</v>
+        <v>0.00788598165998399</v>
       </c>
       <c r="I1886">
-        <v>0.1327656265150257</v>
+        <v>0.1891484397725383</v>
       </c>
       <c r="J1886">
         <v>0.7872395580829136</v>
@@ -96471,10 +96471,10 @@
         <v>4.69</v>
       </c>
       <c r="M1886">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1886">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1886">
         <v>1</v>
@@ -96647,7 +96647,7 @@
         <v>442</v>
       </c>
       <c r="E1890">
-        <v>0.9957825214183615</v>
+        <v>0.9396346762503636</v>
       </c>
       <c r="F1890">
         <v>-1</v>
@@ -96656,10 +96656,10 @@
         <v>0.0120423898651418</v>
       </c>
       <c r="H1890">
-        <v>0.008024217478581638</v>
+        <v>0.007920365323749635</v>
       </c>
       <c r="I1890">
-        <v>0.2018276134398342</v>
+        <v>0.2579754586078322</v>
       </c>
       <c r="J1890">
         <v>0.7950718277334023</v>
@@ -96671,10 +96671,10 @@
         <v>6.62</v>
       </c>
       <c r="M1890">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1890">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1890">
         <v>1</v>
@@ -96697,7 +96697,7 @@
         <v>442</v>
       </c>
       <c r="E1891">
-        <v>0.9957825214183615</v>
+        <v>0.9396346762503636</v>
       </c>
       <c r="F1891">
         <v>-1</v>
@@ -96706,10 +96706,10 @@
         <v>0.01089993814917375</v>
       </c>
       <c r="H1891">
-        <v>0.008024217478581638</v>
+        <v>0.007920365323749635</v>
       </c>
       <c r="I1891">
-        <v>0.2042793294078842</v>
+        <v>0.2604271745758822</v>
       </c>
       <c r="J1891">
         <v>0.7950718277334023</v>
@@ -96721,10 +96721,10 @@
         <v>6.05</v>
       </c>
       <c r="M1891">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1891">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1891">
         <v>1</v>
@@ -96747,7 +96747,7 @@
         <v>442</v>
       </c>
       <c r="E1892">
-        <v>0.9957825214183615</v>
+        <v>0.9396346762503636</v>
       </c>
       <c r="F1892">
         <v>-1</v>
@@ -96756,10 +96756,10 @@
         <v>0.01071223383950975</v>
       </c>
       <c r="H1892">
-        <v>0.008024217478581638</v>
+        <v>0.007920365323749635</v>
       </c>
       <c r="I1892">
-        <v>0.1119836390718887</v>
+        <v>0.1681314842398867</v>
       </c>
       <c r="J1892">
         <v>0.7950718277334023</v>
@@ -96771,10 +96771,10 @@
         <v>5.91</v>
       </c>
       <c r="M1892">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1892">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1892">
         <v>1</v>
@@ -96797,7 +96797,7 @@
         <v>442</v>
       </c>
       <c r="E1893">
-        <v>0.9957825214183615</v>
+        <v>0.9396346762503636</v>
       </c>
       <c r="F1893">
         <v>-1</v>
@@ -96806,10 +96806,10 @@
         <v>0.008251921788245643</v>
       </c>
       <c r="H1893">
-        <v>0.008024217478581638</v>
+        <v>0.007920365323749635</v>
       </c>
       <c r="I1893">
-        <v>0.132295690335996</v>
+        <v>0.188443535503994</v>
       </c>
       <c r="J1893">
         <v>0.7950718277334023</v>
@@ -96821,10 +96821,10 @@
         <v>4.69</v>
       </c>
       <c r="M1893">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1893">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1893">
         <v>1</v>
@@ -96997,7 +96997,7 @@
         <v>442</v>
       </c>
       <c r="E1897">
-        <v>0.9811093081100593</v>
+        <v>0.9250610548875926</v>
       </c>
       <c r="F1897">
         <v>-1</v>
@@ -97006,10 +97006,10 @@
         <v>0.01206503043409262</v>
       </c>
       <c r="H1897">
-        <v>0.008038890691889939</v>
+        <v>0.007934938945112407</v>
       </c>
       <c r="I1897">
-        <v>0.1938602577973167</v>
+        <v>0.2499085110197834</v>
       </c>
       <c r="J1897">
         <v>0.7983915592511178</v>
@@ -97021,10 +97021,10 @@
         <v>6.62</v>
       </c>
       <c r="M1897">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1897">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1897">
         <v>1</v>
@@ -97047,7 +97047,7 @@
         <v>442</v>
       </c>
       <c r="E1898">
-        <v>0.9811093081100593</v>
+        <v>0.9250610548875926</v>
       </c>
       <c r="F1898">
         <v>-1</v>
@@ -97056,10 +97056,10 @@
         <v>0.01092018851143182</v>
       </c>
       <c r="H1898">
-        <v>0.008038890691889939</v>
+        <v>0.007934938945112407</v>
       </c>
       <c r="I1898">
-        <v>0.1987021804581222</v>
+        <v>0.2547504336805888</v>
       </c>
       <c r="J1898">
         <v>0.7983915592511178</v>
@@ -97071,10 +97071,10 @@
         <v>6.05</v>
       </c>
       <c r="M1898">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1898">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1898">
         <v>1</v>
@@ -97097,7 +97097,7 @@
         <v>442</v>
       </c>
       <c r="E1899">
-        <v>0.9811093081100593</v>
+        <v>0.9250610548875926</v>
       </c>
       <c r="F1899">
         <v>-1</v>
@@ -97106,10 +97106,10 @@
         <v>0.01073228501787675</v>
       </c>
       <c r="H1899">
-        <v>0.008038890691889939</v>
+        <v>0.007934938945112407</v>
       </c>
       <c r="I1899">
-        <v>0.1066056740131893</v>
+        <v>0.162653927235656</v>
       </c>
       <c r="J1899">
         <v>0.7983915592511178</v>
@@ -97121,10 +97121,10 @@
         <v>5.91</v>
       </c>
       <c r="M1899">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1899">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1899">
         <v>1</v>
@@ -97147,7 +97147,7 @@
         <v>442</v>
       </c>
       <c r="E1900">
-        <v>0.9811093081100593</v>
+        <v>0.9250610548875926</v>
       </c>
       <c r="F1900">
         <v>-1</v>
@@ -97156,10 +97156,10 @@
         <v>0.008266794185445007</v>
       </c>
       <c r="H1900">
-        <v>0.008038890691889939</v>
+        <v>0.007934938945112407</v>
       </c>
       <c r="I1900">
-        <v>0.1320965064449329</v>
+        <v>0.1881447596673995</v>
       </c>
       <c r="J1900">
         <v>0.7983915592511178</v>
@@ -97171,10 +97171,10 @@
         <v>4.69</v>
       </c>
       <c r="M1900">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1900">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1900">
         <v>1</v>
@@ -97397,7 +97397,7 @@
         <v>442</v>
       </c>
       <c r="E1905">
-        <v>0.8936646090645302</v>
+        <v>0.8382098718989339</v>
       </c>
       <c r="F1905">
         <v>-1</v>
@@ -97406,10 +97406,10 @@
         <v>0.01104087010966207</v>
       </c>
       <c r="H1905">
-        <v>0.00812633539093547</v>
+        <v>0.008021790128101065</v>
       </c>
       <c r="I1905">
-        <v>0.1654652812733963</v>
+        <v>0.2209200184389926</v>
       </c>
       <c r="J1905">
         <v>0.8181754278134546</v>
@@ -97421,10 +97421,10 @@
         <v>6.05</v>
       </c>
       <c r="M1905">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1905">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1905">
         <v>1</v>
@@ -97447,7 +97447,7 @@
         <v>442</v>
       </c>
       <c r="E1906">
-        <v>0.8936646090645302</v>
+        <v>0.8382098718989339</v>
       </c>
       <c r="F1906">
         <v>-1</v>
@@ -97456,10 +97456,10 @@
         <v>0.01031359993853669</v>
       </c>
       <c r="H1906">
-        <v>0.00812633539093547</v>
+        <v>0.008021790128101065</v>
       </c>
       <c r="I1906">
-        <v>0.09273545239877867</v>
+        <v>0.1481901895643749</v>
       </c>
       <c r="J1906">
         <v>0.8181754278134546</v>
@@ -97471,10 +97471,10 @@
         <v>5.65</v>
       </c>
       <c r="M1906">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1906">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1906">
         <v>1</v>
@@ -97497,7 +97497,7 @@
         <v>442</v>
       </c>
       <c r="E1907">
-        <v>0.8936646090645302</v>
+        <v>0.8382098718989339</v>
       </c>
       <c r="F1907">
         <v>-1</v>
@@ -97506,10 +97506,10 @@
         <v>0.008355425916604278</v>
       </c>
       <c r="H1907">
-        <v>0.00812633539093547</v>
+        <v>0.008021790128101065</v>
       </c>
       <c r="I1907">
-        <v>0.1309094743311929</v>
+        <v>0.1863642114967892</v>
       </c>
       <c r="J1907">
         <v>0.8181754278134546</v>
@@ -97521,10 +97521,10 @@
         <v>4.69</v>
       </c>
       <c r="M1907">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="N1907">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="O1907">
         <v>1</v>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -1342,7 +1342,7 @@
     <t>2021-08-20</t>
   </si>
   <si>
-    <t>2021-10-26</t>
+    <t>2021-10-27</t>
   </si>
   <si>
     <t>2021-09-07</t>
@@ -95647,7 +95647,7 @@
         <v>442</v>
       </c>
       <c r="E1870">
-        <v>1.031380439985111</v>
+        <v>1.0320229326507</v>
       </c>
       <c r="F1870">
         <v>-1</v>
@@ -95656,10 +95656,10 @@
         <v>0.0118998599998409</v>
       </c>
       <c r="H1870">
-        <v>0.007828619560014889</v>
+        <v>0.007627977067349301</v>
       </c>
       <c r="I1870">
-        <v>0.3087595601739905</v>
+        <v>0.3081170675084013</v>
       </c>
       <c r="J1870">
         <v>0.7741730205045306</v>
@@ -95671,10 +95671,10 @@
         <v>6.62</v>
       </c>
       <c r="M1870">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1870">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1870">
         <v>1</v>
@@ -95697,7 +95697,7 @@
         <v>442</v>
       </c>
       <c r="E1871">
-        <v>1.031380439985111</v>
+        <v>1.0320229326507</v>
       </c>
       <c r="F1871">
         <v>-1</v>
@@ -95706,10 +95706,10 @@
         <v>0.01058600504384737</v>
       </c>
       <c r="H1871">
-        <v>0.007828619560014889</v>
+        <v>0.007627977067349301</v>
       </c>
       <c r="I1871">
-        <v>0.2026145161675248</v>
+        <v>0.2019720235019355</v>
       </c>
       <c r="J1871">
         <v>0.7741730205045306</v>
@@ -95721,10 +95721,10 @@
         <v>5.91</v>
       </c>
       <c r="M1871">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1871">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1871">
         <v>1</v>
@@ -95747,7 +95747,7 @@
         <v>442</v>
       </c>
       <c r="E1872">
-        <v>1.031380439985111</v>
+        <v>1.0320229326507</v>
       </c>
       <c r="F1872">
         <v>-1</v>
@@ -95756,10 +95756,10 @@
         <v>0.008158295131860298</v>
       </c>
       <c r="H1872">
-        <v>0.007828619560014889</v>
+        <v>0.007627977067349301</v>
       </c>
       <c r="I1872">
-        <v>0.1903244281545922</v>
+        <v>0.1896819354890029</v>
       </c>
       <c r="J1872">
         <v>0.7741730205045306</v>
@@ -95771,10 +95771,10 @@
         <v>4.69</v>
       </c>
       <c r="M1872">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1872">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1872">
         <v>1</v>
@@ -95947,7 +95947,7 @@
         <v>442</v>
       </c>
       <c r="E1876">
-        <v>1.014455194439221</v>
+        <v>1.015598890275873</v>
       </c>
       <c r="F1876">
         <v>-1</v>
@@ -95956,10 +95956,10 @@
         <v>0.01192615388927666</v>
       </c>
       <c r="H1876">
-        <v>0.007845544805560779</v>
+        <v>0.007644401109724127</v>
       </c>
       <c r="I1876">
-        <v>0.2993909162841248</v>
+        <v>0.2982472204474726</v>
       </c>
       <c r="J1876">
         <v>0.7780284295127059</v>
@@ -95971,10 +95971,10 @@
         <v>6.62</v>
       </c>
       <c r="M1876">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1876">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1876">
         <v>1</v>
@@ -95997,7 +95997,7 @@
         <v>442</v>
       </c>
       <c r="E1877">
-        <v>1.014455194439221</v>
+        <v>1.015598890275873</v>
       </c>
       <c r="F1877">
         <v>-1</v>
@@ -96006,10 +96006,10 @@
         <v>0.0107959734200275</v>
       </c>
       <c r="H1877">
-        <v>0.007845544805560779</v>
+        <v>0.007644401109724127</v>
       </c>
       <c r="I1877">
-        <v>0.2895713855332733</v>
+        <v>0.2884276896966211</v>
       </c>
       <c r="J1877">
         <v>0.7780284295127059</v>
@@ -96021,10 +96021,10 @@
         <v>6.05</v>
       </c>
       <c r="M1877">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1877">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1877">
         <v>1</v>
@@ -96047,7 +96047,7 @@
         <v>442</v>
       </c>
       <c r="E1878">
-        <v>1.014455194439221</v>
+        <v>1.015598890275873</v>
       </c>
       <c r="F1878">
         <v>-1</v>
@@ -96056,10 +96056,10 @@
         <v>0.01060929171425675</v>
       </c>
       <c r="H1878">
-        <v>0.007845544805560779</v>
+        <v>0.007644401109724127</v>
       </c>
       <c r="I1878">
-        <v>0.196253091304035</v>
+        <v>0.1951093954673828</v>
       </c>
       <c r="J1878">
         <v>0.7780284295127059</v>
@@ -96071,10 +96071,10 @@
         <v>5.91</v>
       </c>
       <c r="M1878">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1878">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1878">
         <v>1</v>
@@ -96097,7 +96097,7 @@
         <v>442</v>
       </c>
       <c r="E1879">
-        <v>1.014455194439221</v>
+        <v>1.015598890275873</v>
       </c>
       <c r="F1879">
         <v>-1</v>
@@ -96106,10 +96106,10 @@
         <v>0.008175567364216924</v>
       </c>
       <c r="H1879">
-        <v>0.007845544805560779</v>
+        <v>0.007644401109724127</v>
       </c>
       <c r="I1879">
-        <v>0.1899774413438564</v>
+        <v>0.1888337455072042</v>
       </c>
       <c r="J1879">
         <v>0.7780284295127059</v>
@@ -96121,10 +96121,10 @@
         <v>4.69</v>
       </c>
       <c r="M1879">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1879">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1879">
         <v>1</v>
@@ -96297,7 +96297,7 @@
         <v>442</v>
       </c>
       <c r="E1883">
-        <v>0.9740183400160092</v>
+        <v>0.9763594825667883</v>
       </c>
       <c r="F1883">
         <v>-1</v>
@@ -96306,10 +96306,10 @@
         <v>0.01198897378612547</v>
       </c>
       <c r="H1883">
-        <v>0.00788598165998399</v>
+        <v>0.007683640517433212</v>
       </c>
       <c r="I1883">
-        <v>0.27700787385852</v>
+        <v>0.2746667313077409</v>
       </c>
       <c r="J1883">
         <v>0.7872395580829136</v>
@@ -96321,10 +96321,10 @@
         <v>6.62</v>
       </c>
       <c r="M1883">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1883">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1883">
         <v>1</v>
@@ -96347,7 +96347,7 @@
         <v>442</v>
       </c>
       <c r="E1884">
-        <v>0.9740183400160092</v>
+        <v>0.9763594825667883</v>
       </c>
       <c r="F1884">
         <v>-1</v>
@@ -96356,10 +96356,10 @@
         <v>0.01085216130430577</v>
       </c>
       <c r="H1884">
-        <v>0.00788598165998399</v>
+        <v>0.007683640517433212</v>
       </c>
       <c r="I1884">
-        <v>0.2738203556782182</v>
+        <v>0.2714792131274391</v>
       </c>
       <c r="J1884">
         <v>0.7872395580829136</v>
@@ -96371,10 +96371,10 @@
         <v>6.05</v>
       </c>
       <c r="M1884">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1884">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1884">
         <v>1</v>
@@ -96397,7 +96397,7 @@
         <v>442</v>
       </c>
       <c r="E1885">
-        <v>0.9740183400160092</v>
+        <v>0.9763594825667883</v>
       </c>
       <c r="F1885">
         <v>-1</v>
@@ -96406,10 +96406,10 @@
         <v>0.0106649269308208</v>
       </c>
       <c r="H1885">
-        <v>0.00788598165998399</v>
+        <v>0.007683640517433212</v>
       </c>
       <c r="I1885">
-        <v>0.1810547291631925</v>
+        <v>0.1787135866124134</v>
       </c>
       <c r="J1885">
         <v>0.7872395580829136</v>
@@ -96421,10 +96421,10 @@
         <v>5.91</v>
       </c>
       <c r="M1885">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1885">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1885">
         <v>1</v>
@@ -96447,7 +96447,7 @@
         <v>442</v>
       </c>
       <c r="E1886">
-        <v>0.9740183400160092</v>
+        <v>0.9763594825667883</v>
       </c>
       <c r="F1886">
         <v>-1</v>
@@ -96456,10 +96456,10 @@
         <v>0.008216833220211455</v>
       </c>
       <c r="H1886">
-        <v>0.00788598165998399</v>
+        <v>0.007683640517433212</v>
       </c>
       <c r="I1886">
-        <v>0.1891484397725383</v>
+        <v>0.1868072972217591</v>
       </c>
       <c r="J1886">
         <v>0.7872395580829136</v>
@@ -96471,10 +96471,10 @@
         <v>4.69</v>
       </c>
       <c r="M1886">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1886">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1886">
         <v>1</v>
@@ -96647,7 +96647,7 @@
         <v>442</v>
       </c>
       <c r="E1890">
-        <v>0.9396346762503636</v>
+        <v>0.942994013855706</v>
       </c>
       <c r="F1890">
         <v>-1</v>
@@ -96656,10 +96656,10 @@
         <v>0.0120423898651418</v>
       </c>
       <c r="H1890">
-        <v>0.007920365323749635</v>
+        <v>0.007717005986144294</v>
       </c>
       <c r="I1890">
-        <v>0.2579754586078322</v>
+        <v>0.2546161210024898</v>
       </c>
       <c r="J1890">
         <v>0.7950718277334023</v>
@@ -96671,10 +96671,10 @@
         <v>6.62</v>
       </c>
       <c r="M1890">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1890">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1890">
         <v>1</v>
@@ -96697,7 +96697,7 @@
         <v>442</v>
       </c>
       <c r="E1891">
-        <v>0.9396346762503636</v>
+        <v>0.942994013855706</v>
       </c>
       <c r="F1891">
         <v>-1</v>
@@ -96706,10 +96706,10 @@
         <v>0.01089993814917375</v>
       </c>
       <c r="H1891">
-        <v>0.007920365323749635</v>
+        <v>0.007717005986144294</v>
       </c>
       <c r="I1891">
-        <v>0.2604271745758822</v>
+        <v>0.2570678369705397</v>
       </c>
       <c r="J1891">
         <v>0.7950718277334023</v>
@@ -96721,10 +96721,10 @@
         <v>6.05</v>
       </c>
       <c r="M1891">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1891">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1891">
         <v>1</v>
@@ -96747,7 +96747,7 @@
         <v>442</v>
       </c>
       <c r="E1892">
-        <v>0.9396346762503636</v>
+        <v>0.942994013855706</v>
       </c>
       <c r="F1892">
         <v>-1</v>
@@ -96756,10 +96756,10 @@
         <v>0.01071223383950975</v>
       </c>
       <c r="H1892">
-        <v>0.007920365323749635</v>
+        <v>0.007717005986144294</v>
       </c>
       <c r="I1892">
-        <v>0.1681314842398867</v>
+        <v>0.1647721466345442</v>
       </c>
       <c r="J1892">
         <v>0.7950718277334023</v>
@@ -96771,10 +96771,10 @@
         <v>5.91</v>
       </c>
       <c r="M1892">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1892">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1892">
         <v>1</v>
@@ -96797,7 +96797,7 @@
         <v>442</v>
       </c>
       <c r="E1893">
-        <v>0.9396346762503636</v>
+        <v>0.942994013855706</v>
       </c>
       <c r="F1893">
         <v>-1</v>
@@ -96806,10 +96806,10 @@
         <v>0.008251921788245643</v>
       </c>
       <c r="H1893">
-        <v>0.007920365323749635</v>
+        <v>0.007717005986144294</v>
       </c>
       <c r="I1893">
-        <v>0.188443535503994</v>
+        <v>0.1850841978986515</v>
       </c>
       <c r="J1893">
         <v>0.7950718277334023</v>
@@ -96821,10 +96821,10 @@
         <v>4.69</v>
       </c>
       <c r="M1893">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1893">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1893">
         <v>1</v>
@@ -96997,7 +96997,7 @@
         <v>442</v>
       </c>
       <c r="E1897">
-        <v>0.9250610548875926</v>
+        <v>0.9288519575902385</v>
       </c>
       <c r="F1897">
         <v>-1</v>
@@ -97006,10 +97006,10 @@
         <v>0.01206503043409262</v>
       </c>
       <c r="H1897">
-        <v>0.007934938945112407</v>
+        <v>0.007731148042409763</v>
       </c>
       <c r="I1897">
-        <v>0.2499085110197834</v>
+        <v>0.2461176083171375</v>
       </c>
       <c r="J1897">
         <v>0.7983915592511178</v>
@@ -97021,10 +97021,10 @@
         <v>6.62</v>
       </c>
       <c r="M1897">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1897">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1897">
         <v>1</v>
@@ -97047,7 +97047,7 @@
         <v>442</v>
       </c>
       <c r="E1898">
-        <v>0.9250610548875926</v>
+        <v>0.9288519575902385</v>
       </c>
       <c r="F1898">
         <v>-1</v>
@@ -97056,10 +97056,10 @@
         <v>0.01092018851143182</v>
       </c>
       <c r="H1898">
-        <v>0.007934938945112407</v>
+        <v>0.007731148042409763</v>
       </c>
       <c r="I1898">
-        <v>0.2547504336805888</v>
+        <v>0.2509595309779429</v>
       </c>
       <c r="J1898">
         <v>0.7983915592511178</v>
@@ -97071,10 +97071,10 @@
         <v>6.05</v>
       </c>
       <c r="M1898">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1898">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1898">
         <v>1</v>
@@ -97097,7 +97097,7 @@
         <v>442</v>
       </c>
       <c r="E1899">
-        <v>0.9250610548875926</v>
+        <v>0.9288519575902385</v>
       </c>
       <c r="F1899">
         <v>-1</v>
@@ -97106,10 +97106,10 @@
         <v>0.01073228501787675</v>
       </c>
       <c r="H1899">
-        <v>0.007934938945112407</v>
+        <v>0.007731148042409763</v>
       </c>
       <c r="I1899">
-        <v>0.162653927235656</v>
+        <v>0.15886302453301</v>
       </c>
       <c r="J1899">
         <v>0.7983915592511178</v>
@@ -97121,10 +97121,10 @@
         <v>5.91</v>
       </c>
       <c r="M1899">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1899">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1899">
         <v>1</v>
@@ -97147,7 +97147,7 @@
         <v>442</v>
       </c>
       <c r="E1900">
-        <v>0.9250610548875926</v>
+        <v>0.9288519575902385</v>
       </c>
       <c r="F1900">
         <v>-1</v>
@@ -97156,10 +97156,10 @@
         <v>0.008266794185445007</v>
       </c>
       <c r="H1900">
-        <v>0.007934938945112407</v>
+        <v>0.007731148042409763</v>
       </c>
       <c r="I1900">
-        <v>0.1881447596673995</v>
+        <v>0.1843538569647536</v>
       </c>
       <c r="J1900">
         <v>0.7983915592511178</v>
@@ -97171,10 +97171,10 @@
         <v>4.69</v>
       </c>
       <c r="M1900">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1900">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1900">
         <v>1</v>
@@ -97397,7 +97397,7 @@
         <v>442</v>
       </c>
       <c r="E1905">
-        <v>0.8382098718989339</v>
+        <v>0.8445726775146833</v>
       </c>
       <c r="F1905">
         <v>-1</v>
@@ -97406,10 +97406,10 @@
         <v>0.01104087010966207</v>
       </c>
       <c r="H1905">
-        <v>0.008021790128101065</v>
+        <v>0.007815427322485316</v>
       </c>
       <c r="I1905">
-        <v>0.2209200184389926</v>
+        <v>0.2145572128232431</v>
       </c>
       <c r="J1905">
         <v>0.8181754278134546</v>
@@ -97421,10 +97421,10 @@
         <v>6.05</v>
       </c>
       <c r="M1905">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1905">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1905">
         <v>1</v>
@@ -97447,7 +97447,7 @@
         <v>442</v>
       </c>
       <c r="E1906">
-        <v>0.8382098718989339</v>
+        <v>0.8445726775146833</v>
       </c>
       <c r="F1906">
         <v>-1</v>
@@ -97456,10 +97456,10 @@
         <v>0.01031359993853669</v>
       </c>
       <c r="H1906">
-        <v>0.008021790128101065</v>
+        <v>0.007815427322485316</v>
       </c>
       <c r="I1906">
-        <v>0.1481901895643749</v>
+        <v>0.1418273839486255</v>
       </c>
       <c r="J1906">
         <v>0.8181754278134546</v>
@@ -97471,10 +97471,10 @@
         <v>5.65</v>
       </c>
       <c r="M1906">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1906">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1906">
         <v>1</v>
@@ -97497,7 +97497,7 @@
         <v>442</v>
       </c>
       <c r="E1907">
-        <v>0.8382098718989339</v>
+        <v>0.8445726775146833</v>
       </c>
       <c r="F1907">
         <v>-1</v>
@@ -97506,10 +97506,10 @@
         <v>0.008355425916604278</v>
       </c>
       <c r="H1907">
-        <v>0.008021790128101065</v>
+        <v>0.007815427322485316</v>
       </c>
       <c r="I1907">
-        <v>0.1863642114967892</v>
+        <v>0.1800014058810397</v>
       </c>
       <c r="J1907">
         <v>0.8181754278134546</v>
@@ -97521,10 +97521,10 @@
         <v>4.69</v>
       </c>
       <c r="M1907">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="N1907">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="O1907">
         <v>1</v>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -1342,7 +1342,7 @@
     <t>2021-08-20</t>
   </si>
   <si>
-    <t>2021-10-27</t>
+    <t>2021-10-28</t>
   </si>
   <si>
     <t>2021-09-07</t>
@@ -95647,7 +95647,7 @@
         <v>442</v>
       </c>
       <c r="E1870">
-        <v>1.0320229326507</v>
+        <v>0.9862150440860167</v>
       </c>
       <c r="F1870">
         <v>-1</v>
@@ -95656,10 +95656,10 @@
         <v>0.0118998599998409</v>
       </c>
       <c r="H1870">
-        <v>0.007627977067349301</v>
+        <v>0.007473784955913985</v>
       </c>
       <c r="I1870">
-        <v>0.3081170675084013</v>
+        <v>0.3539249560730844</v>
       </c>
       <c r="J1870">
         <v>0.7741730205045306</v>
@@ -95671,10 +95671,10 @@
         <v>6.62</v>
       </c>
       <c r="M1870">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1870">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1870">
         <v>1</v>
@@ -95697,7 +95697,7 @@
         <v>442</v>
       </c>
       <c r="E1871">
-        <v>1.0320229326507</v>
+        <v>0.9862150440860167</v>
       </c>
       <c r="F1871">
         <v>-1</v>
@@ -95706,10 +95706,10 @@
         <v>0.01058600504384737</v>
       </c>
       <c r="H1871">
-        <v>0.007627977067349301</v>
+        <v>0.007473784955913985</v>
       </c>
       <c r="I1871">
-        <v>0.2019720235019355</v>
+        <v>0.2477799120666186</v>
       </c>
       <c r="J1871">
         <v>0.7741730205045306</v>
@@ -95721,10 +95721,10 @@
         <v>5.91</v>
       </c>
       <c r="M1871">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1871">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1871">
         <v>1</v>
@@ -95747,7 +95747,7 @@
         <v>442</v>
       </c>
       <c r="E1872">
-        <v>1.0320229326507</v>
+        <v>0.9862150440860167</v>
       </c>
       <c r="F1872">
         <v>-1</v>
@@ -95756,10 +95756,10 @@
         <v>0.008158295131860298</v>
       </c>
       <c r="H1872">
-        <v>0.007627977067349301</v>
+        <v>0.007473784955913985</v>
       </c>
       <c r="I1872">
-        <v>0.1896819354890029</v>
+        <v>0.235489824053686</v>
       </c>
       <c r="J1872">
         <v>0.7741730205045306</v>
@@ -95771,10 +95771,10 @@
         <v>4.69</v>
       </c>
       <c r="M1872">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1872">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1872">
         <v>1</v>
@@ -95947,7 +95947,7 @@
         <v>442</v>
       </c>
       <c r="E1876">
-        <v>1.015598890275873</v>
+        <v>0.9700608803417623</v>
       </c>
       <c r="F1876">
         <v>-1</v>
@@ -95956,10 +95956,10 @@
         <v>0.01192615388927666</v>
       </c>
       <c r="H1876">
-        <v>0.007644401109724127</v>
+        <v>0.007489939119658238</v>
       </c>
       <c r="I1876">
-        <v>0.2982472204474726</v>
+        <v>0.3437852303815836</v>
       </c>
       <c r="J1876">
         <v>0.7780284295127059</v>
@@ -95971,10 +95971,10 @@
         <v>6.62</v>
       </c>
       <c r="M1876">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1876">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1876">
         <v>1</v>
@@ -95997,7 +95997,7 @@
         <v>442</v>
       </c>
       <c r="E1877">
-        <v>1.015598890275873</v>
+        <v>0.9700608803417623</v>
       </c>
       <c r="F1877">
         <v>-1</v>
@@ -96006,10 +96006,10 @@
         <v>0.0107959734200275</v>
       </c>
       <c r="H1877">
-        <v>0.007644401109724127</v>
+        <v>0.007489939119658238</v>
       </c>
       <c r="I1877">
-        <v>0.2884276896966211</v>
+        <v>0.3339656996307321</v>
       </c>
       <c r="J1877">
         <v>0.7780284295127059</v>
@@ -96021,10 +96021,10 @@
         <v>6.05</v>
       </c>
       <c r="M1877">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1877">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1877">
         <v>1</v>
@@ -96047,7 +96047,7 @@
         <v>442</v>
       </c>
       <c r="E1878">
-        <v>1.015598890275873</v>
+        <v>0.9700608803417623</v>
       </c>
       <c r="F1878">
         <v>-1</v>
@@ -96056,10 +96056,10 @@
         <v>0.01060929171425675</v>
       </c>
       <c r="H1878">
-        <v>0.007644401109724127</v>
+        <v>0.007489939119658238</v>
       </c>
       <c r="I1878">
-        <v>0.1951093954673828</v>
+        <v>0.2406474054014938</v>
       </c>
       <c r="J1878">
         <v>0.7780284295127059</v>
@@ -96071,10 +96071,10 @@
         <v>5.91</v>
       </c>
       <c r="M1878">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1878">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1878">
         <v>1</v>
@@ -96097,7 +96097,7 @@
         <v>442</v>
       </c>
       <c r="E1879">
-        <v>1.015598890275873</v>
+        <v>0.9700608803417623</v>
       </c>
       <c r="F1879">
         <v>-1</v>
@@ -96106,10 +96106,10 @@
         <v>0.008175567364216924</v>
       </c>
       <c r="H1879">
-        <v>0.007644401109724127</v>
+        <v>0.007489939119658238</v>
       </c>
       <c r="I1879">
-        <v>0.1888337455072042</v>
+        <v>0.2343717554413152</v>
       </c>
       <c r="J1879">
         <v>0.7780284295127059</v>
@@ -96121,10 +96121,10 @@
         <v>4.69</v>
       </c>
       <c r="M1879">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1879">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1879">
         <v>1</v>
@@ -96297,7 +96297,7 @@
         <v>442</v>
       </c>
       <c r="E1883">
-        <v>0.9763594825667883</v>
+        <v>0.9314662516325924</v>
       </c>
       <c r="F1883">
         <v>-1</v>
@@ -96306,10 +96306,10 @@
         <v>0.01198897378612547</v>
       </c>
       <c r="H1883">
-        <v>0.007683640517433212</v>
+        <v>0.007528533748367408</v>
       </c>
       <c r="I1883">
-        <v>0.2746667313077409</v>
+        <v>0.3195599622419367</v>
       </c>
       <c r="J1883">
         <v>0.7872395580829136</v>
@@ -96321,10 +96321,10 @@
         <v>6.62</v>
       </c>
       <c r="M1883">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1883">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1883">
         <v>1</v>
@@ -96347,7 +96347,7 @@
         <v>442</v>
       </c>
       <c r="E1884">
-        <v>0.9763594825667883</v>
+        <v>0.9314662516325924</v>
       </c>
       <c r="F1884">
         <v>-1</v>
@@ -96356,10 +96356,10 @@
         <v>0.01085216130430577</v>
       </c>
       <c r="H1884">
-        <v>0.007683640517433212</v>
+        <v>0.007528533748367408</v>
       </c>
       <c r="I1884">
-        <v>0.2714792131274391</v>
+        <v>0.3163724440616349</v>
       </c>
       <c r="J1884">
         <v>0.7872395580829136</v>
@@ -96371,10 +96371,10 @@
         <v>6.05</v>
       </c>
       <c r="M1884">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1884">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1884">
         <v>1</v>
@@ -96397,7 +96397,7 @@
         <v>442</v>
       </c>
       <c r="E1885">
-        <v>0.9763594825667883</v>
+        <v>0.9314662516325924</v>
       </c>
       <c r="F1885">
         <v>-1</v>
@@ -96406,10 +96406,10 @@
         <v>0.0106649269308208</v>
       </c>
       <c r="H1885">
-        <v>0.007683640517433212</v>
+        <v>0.007528533748367408</v>
       </c>
       <c r="I1885">
-        <v>0.1787135866124134</v>
+        <v>0.2236068175466093</v>
       </c>
       <c r="J1885">
         <v>0.7872395580829136</v>
@@ -96421,10 +96421,10 @@
         <v>5.91</v>
       </c>
       <c r="M1885">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1885">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1885">
         <v>1</v>
@@ -96447,7 +96447,7 @@
         <v>442</v>
       </c>
       <c r="E1886">
-        <v>0.9763594825667883</v>
+        <v>0.9314662516325924</v>
       </c>
       <c r="F1886">
         <v>-1</v>
@@ -96456,10 +96456,10 @@
         <v>0.008216833220211455</v>
       </c>
       <c r="H1886">
-        <v>0.007683640517433212</v>
+        <v>0.007528533748367408</v>
       </c>
       <c r="I1886">
-        <v>0.1868072972217591</v>
+        <v>0.231700528155955</v>
       </c>
       <c r="J1886">
         <v>0.7872395580829136</v>
@@ -96471,10 +96471,10 @@
         <v>4.69</v>
       </c>
       <c r="M1886">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1886">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1886">
         <v>1</v>
@@ -96647,7 +96647,7 @@
         <v>442</v>
       </c>
       <c r="E1890">
-        <v>0.942994013855706</v>
+        <v>0.8986490417970443</v>
       </c>
       <c r="F1890">
         <v>-1</v>
@@ -96656,10 +96656,10 @@
         <v>0.0120423898651418</v>
       </c>
       <c r="H1890">
-        <v>0.007717005986144294</v>
+        <v>0.007561350958202956</v>
       </c>
       <c r="I1890">
-        <v>0.2546161210024898</v>
+        <v>0.2989610930611515</v>
       </c>
       <c r="J1890">
         <v>0.7950718277334023</v>
@@ -96671,10 +96671,10 @@
         <v>6.62</v>
       </c>
       <c r="M1890">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1890">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1890">
         <v>1</v>
@@ -96697,7 +96697,7 @@
         <v>442</v>
       </c>
       <c r="E1891">
-        <v>0.942994013855706</v>
+        <v>0.8986490417970443</v>
       </c>
       <c r="F1891">
         <v>-1</v>
@@ -96706,10 +96706,10 @@
         <v>0.01089993814917375</v>
       </c>
       <c r="H1891">
-        <v>0.007717005986144294</v>
+        <v>0.007561350958202956</v>
       </c>
       <c r="I1891">
-        <v>0.2570678369705397</v>
+        <v>0.3014128090292014</v>
       </c>
       <c r="J1891">
         <v>0.7950718277334023</v>
@@ -96721,10 +96721,10 @@
         <v>6.05</v>
       </c>
       <c r="M1891">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1891">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1891">
         <v>1</v>
@@ -96747,7 +96747,7 @@
         <v>442</v>
       </c>
       <c r="E1892">
-        <v>0.942994013855706</v>
+        <v>0.8986490417970443</v>
       </c>
       <c r="F1892">
         <v>-1</v>
@@ -96756,10 +96756,10 @@
         <v>0.01071223383950975</v>
       </c>
       <c r="H1892">
-        <v>0.007717005986144294</v>
+        <v>0.007561350958202956</v>
       </c>
       <c r="I1892">
-        <v>0.1647721466345442</v>
+        <v>0.2091171186932059</v>
       </c>
       <c r="J1892">
         <v>0.7950718277334023</v>
@@ -96771,10 +96771,10 @@
         <v>5.91</v>
       </c>
       <c r="M1892">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1892">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1892">
         <v>1</v>
@@ -96797,7 +96797,7 @@
         <v>442</v>
       </c>
       <c r="E1893">
-        <v>0.942994013855706</v>
+        <v>0.8986490417970443</v>
       </c>
       <c r="F1893">
         <v>-1</v>
@@ -96806,10 +96806,10 @@
         <v>0.008251921788245643</v>
       </c>
       <c r="H1893">
-        <v>0.007717005986144294</v>
+        <v>0.007561350958202956</v>
       </c>
       <c r="I1893">
-        <v>0.1850841978986515</v>
+        <v>0.2294291699573132</v>
       </c>
       <c r="J1893">
         <v>0.7950718277334023</v>
@@ -96821,10 +96821,10 @@
         <v>4.69</v>
       </c>
       <c r="M1893">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1893">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1893">
         <v>1</v>
@@ -96997,7 +96997,7 @@
         <v>442</v>
       </c>
       <c r="E1897">
-        <v>0.9288519575902385</v>
+        <v>0.8847393667378163</v>
       </c>
       <c r="F1897">
         <v>-1</v>
@@ -97006,10 +97006,10 @@
         <v>0.01206503043409262</v>
       </c>
       <c r="H1897">
-        <v>0.007731148042409763</v>
+        <v>0.007575260633262184</v>
       </c>
       <c r="I1897">
-        <v>0.2461176083171375</v>
+        <v>0.2902301991695597</v>
       </c>
       <c r="J1897">
         <v>0.7983915592511178</v>
@@ -97021,10 +97021,10 @@
         <v>6.62</v>
       </c>
       <c r="M1897">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1897">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1897">
         <v>1</v>
@@ -97047,7 +97047,7 @@
         <v>442</v>
       </c>
       <c r="E1898">
-        <v>0.9288519575902385</v>
+        <v>0.8847393667378163</v>
       </c>
       <c r="F1898">
         <v>-1</v>
@@ -97056,10 +97056,10 @@
         <v>0.01092018851143182</v>
       </c>
       <c r="H1898">
-        <v>0.007731148042409763</v>
+        <v>0.007575260633262184</v>
       </c>
       <c r="I1898">
-        <v>0.2509595309779429</v>
+        <v>0.2950721218303651</v>
       </c>
       <c r="J1898">
         <v>0.7983915592511178</v>
@@ -97071,10 +97071,10 @@
         <v>6.05</v>
       </c>
       <c r="M1898">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1898">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1898">
         <v>1</v>
@@ -97097,7 +97097,7 @@
         <v>442</v>
       </c>
       <c r="E1899">
-        <v>0.9288519575902385</v>
+        <v>0.8847393667378163</v>
       </c>
       <c r="F1899">
         <v>-1</v>
@@ -97106,10 +97106,10 @@
         <v>0.01073228501787675</v>
       </c>
       <c r="H1899">
-        <v>0.007731148042409763</v>
+        <v>0.007575260633262184</v>
       </c>
       <c r="I1899">
-        <v>0.15886302453301</v>
+        <v>0.2029756153854323</v>
       </c>
       <c r="J1899">
         <v>0.7983915592511178</v>
@@ -97121,10 +97121,10 @@
         <v>5.91</v>
       </c>
       <c r="M1899">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1899">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1899">
         <v>1</v>
@@ -97147,7 +97147,7 @@
         <v>442</v>
       </c>
       <c r="E1900">
-        <v>0.9288519575902385</v>
+        <v>0.8847393667378163</v>
       </c>
       <c r="F1900">
         <v>-1</v>
@@ -97156,10 +97156,10 @@
         <v>0.008266794185445007</v>
       </c>
       <c r="H1900">
-        <v>0.007731148042409763</v>
+        <v>0.007575260633262184</v>
       </c>
       <c r="I1900">
-        <v>0.1843538569647536</v>
+        <v>0.2284664478171758</v>
       </c>
       <c r="J1900">
         <v>0.7983915592511178</v>
@@ -97171,10 +97171,10 @@
         <v>4.69</v>
       </c>
       <c r="M1900">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1900">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1900">
         <v>1</v>
@@ -97397,7 +97397,7 @@
         <v>442</v>
       </c>
       <c r="E1905">
-        <v>0.8445726775146833</v>
+        <v>0.8018449574616251</v>
       </c>
       <c r="F1905">
         <v>-1</v>
@@ -97406,10 +97406,10 @@
         <v>0.01104087010966207</v>
       </c>
       <c r="H1905">
-        <v>0.007815427322485316</v>
+        <v>0.007658155042538375</v>
       </c>
       <c r="I1905">
-        <v>0.2145572128232431</v>
+        <v>0.2572849328763014</v>
       </c>
       <c r="J1905">
         <v>0.8181754278134546</v>
@@ -97421,10 +97421,10 @@
         <v>6.05</v>
       </c>
       <c r="M1905">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1905">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1905">
         <v>1</v>
@@ -97447,7 +97447,7 @@
         <v>442</v>
       </c>
       <c r="E1906">
-        <v>0.8445726775146833</v>
+        <v>0.8018449574616251</v>
       </c>
       <c r="F1906">
         <v>-1</v>
@@ -97456,10 +97456,10 @@
         <v>0.01031359993853669</v>
       </c>
       <c r="H1906">
-        <v>0.007815427322485316</v>
+        <v>0.007658155042538375</v>
       </c>
       <c r="I1906">
-        <v>0.1418273839486255</v>
+        <v>0.1845551040016837</v>
       </c>
       <c r="J1906">
         <v>0.8181754278134546</v>
@@ -97471,10 +97471,10 @@
         <v>5.65</v>
       </c>
       <c r="M1906">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1906">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1906">
         <v>1</v>
@@ -97497,7 +97497,7 @@
         <v>442</v>
       </c>
       <c r="E1907">
-        <v>0.8445726775146833</v>
+        <v>0.8018449574616251</v>
       </c>
       <c r="F1907">
         <v>-1</v>
@@ -97506,10 +97506,10 @@
         <v>0.008355425916604278</v>
       </c>
       <c r="H1907">
-        <v>0.007815427322485316</v>
+        <v>0.007658155042538375</v>
       </c>
       <c r="I1907">
-        <v>0.1800014058810397</v>
+        <v>0.222729125934098</v>
       </c>
       <c r="J1907">
         <v>0.8181754278134546</v>
@@ -97521,10 +97521,10 @@
         <v>4.69</v>
       </c>
       <c r="M1907">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="N1907">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="O1907">
         <v>1</v>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -1342,7 +1342,7 @@
     <t>2021-08-20</t>
   </si>
   <si>
-    <t>2021-10-28</t>
+    <t>2021-11-01</t>
   </si>
   <si>
     <t>2021-09-07</t>
@@ -95647,7 +95647,7 @@
         <v>442</v>
       </c>
       <c r="E1870">
-        <v>0.9862150440860167</v>
+        <v>1.014599266956651</v>
       </c>
       <c r="F1870">
         <v>-1</v>
@@ -95656,10 +95656,10 @@
         <v>0.0118998599998409</v>
       </c>
       <c r="H1870">
-        <v>0.007473784955913985</v>
+        <v>0.00728540073304335</v>
       </c>
       <c r="I1870">
-        <v>0.3539249560730844</v>
+        <v>0.3255407332024496</v>
       </c>
       <c r="J1870">
         <v>0.7741730205045306</v>
@@ -95671,10 +95671,10 @@
         <v>6.62</v>
       </c>
       <c r="M1870">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1870">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1870">
         <v>1</v>
@@ -95697,7 +95697,7 @@
         <v>442</v>
       </c>
       <c r="E1871">
-        <v>0.9862150440860167</v>
+        <v>1.014599266956651</v>
       </c>
       <c r="F1871">
         <v>-1</v>
@@ -95706,10 +95706,10 @@
         <v>0.01058600504384737</v>
       </c>
       <c r="H1871">
-        <v>0.007473784955913985</v>
+        <v>0.00728540073304335</v>
       </c>
       <c r="I1871">
-        <v>0.2477799120666186</v>
+        <v>0.2193956891959838</v>
       </c>
       <c r="J1871">
         <v>0.7741730205045306</v>
@@ -95721,10 +95721,10 @@
         <v>5.91</v>
       </c>
       <c r="M1871">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1871">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1871">
         <v>1</v>
@@ -95747,7 +95747,7 @@
         <v>442</v>
       </c>
       <c r="E1872">
-        <v>0.9862150440860167</v>
+        <v>1.014599266956651</v>
       </c>
       <c r="F1872">
         <v>-1</v>
@@ -95756,10 +95756,10 @@
         <v>0.008158295131860298</v>
       </c>
       <c r="H1872">
-        <v>0.007473784955913985</v>
+        <v>0.00728540073304335</v>
       </c>
       <c r="I1872">
-        <v>0.235489824053686</v>
+        <v>0.2071056011830512</v>
       </c>
       <c r="J1872">
         <v>0.7741730205045306</v>
@@ -95771,10 +95771,10 @@
         <v>4.69</v>
       </c>
       <c r="M1872">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1872">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1872">
         <v>1</v>
@@ -95947,7 +95947,7 @@
         <v>442</v>
       </c>
       <c r="E1876">
-        <v>0.9700608803417623</v>
+        <v>0.9989848604735414</v>
       </c>
       <c r="F1876">
         <v>-1</v>
@@ -95956,10 +95956,10 @@
         <v>0.01192615388927666</v>
       </c>
       <c r="H1876">
-        <v>0.007489939119658238</v>
+        <v>0.007301015139526459</v>
       </c>
       <c r="I1876">
-        <v>0.3437852303815836</v>
+        <v>0.3148612502498045</v>
       </c>
       <c r="J1876">
         <v>0.7780284295127059</v>
@@ -95971,10 +95971,10 @@
         <v>6.62</v>
       </c>
       <c r="M1876">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1876">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1876">
         <v>1</v>
@@ -95997,7 +95997,7 @@
         <v>442</v>
       </c>
       <c r="E1877">
-        <v>0.9700608803417623</v>
+        <v>0.9989848604735414</v>
       </c>
       <c r="F1877">
         <v>-1</v>
@@ -96006,10 +96006,10 @@
         <v>0.0107959734200275</v>
       </c>
       <c r="H1877">
-        <v>0.007489939119658238</v>
+        <v>0.007301015139526459</v>
       </c>
       <c r="I1877">
-        <v>0.3339656996307321</v>
+        <v>0.305041719498953</v>
       </c>
       <c r="J1877">
         <v>0.7780284295127059</v>
@@ -96021,10 +96021,10 @@
         <v>6.05</v>
       </c>
       <c r="M1877">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1877">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1877">
         <v>1</v>
@@ -96047,7 +96047,7 @@
         <v>442</v>
       </c>
       <c r="E1878">
-        <v>0.9700608803417623</v>
+        <v>0.9989848604735414</v>
       </c>
       <c r="F1878">
         <v>-1</v>
@@ -96056,10 +96056,10 @@
         <v>0.01060929171425675</v>
       </c>
       <c r="H1878">
-        <v>0.007489939119658238</v>
+        <v>0.007301015139526459</v>
       </c>
       <c r="I1878">
-        <v>0.2406474054014938</v>
+        <v>0.2117234252697147</v>
       </c>
       <c r="J1878">
         <v>0.7780284295127059</v>
@@ -96071,10 +96071,10 @@
         <v>5.91</v>
       </c>
       <c r="M1878">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1878">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1878">
         <v>1</v>
@@ -96097,7 +96097,7 @@
         <v>442</v>
       </c>
       <c r="E1879">
-        <v>0.9700608803417623</v>
+        <v>0.9989848604735414</v>
       </c>
       <c r="F1879">
         <v>-1</v>
@@ -96106,10 +96106,10 @@
         <v>0.008175567364216924</v>
       </c>
       <c r="H1879">
-        <v>0.007489939119658238</v>
+        <v>0.007301015139526459</v>
       </c>
       <c r="I1879">
-        <v>0.2343717554413152</v>
+        <v>0.2054477753095361</v>
       </c>
       <c r="J1879">
         <v>0.7780284295127059</v>
@@ -96121,10 +96121,10 @@
         <v>4.69</v>
       </c>
       <c r="M1879">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1879">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1879">
         <v>1</v>
@@ -96297,7 +96297,7 @@
         <v>442</v>
       </c>
       <c r="E1883">
-        <v>0.9314662516325924</v>
+        <v>0.9616797897642004</v>
       </c>
       <c r="F1883">
         <v>-1</v>
@@ -96306,10 +96306,10 @@
         <v>0.01198897378612547</v>
       </c>
       <c r="H1883">
-        <v>0.007528533748367408</v>
+        <v>0.0073383202102358</v>
       </c>
       <c r="I1883">
-        <v>0.3195599622419367</v>
+        <v>0.2893464241103287</v>
       </c>
       <c r="J1883">
         <v>0.7872395580829136</v>
@@ -96321,10 +96321,10 @@
         <v>6.62</v>
       </c>
       <c r="M1883">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1883">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1883">
         <v>1</v>
@@ -96347,7 +96347,7 @@
         <v>442</v>
       </c>
       <c r="E1884">
-        <v>0.9314662516325924</v>
+        <v>0.9616797897642004</v>
       </c>
       <c r="F1884">
         <v>-1</v>
@@ -96356,10 +96356,10 @@
         <v>0.01085216130430577</v>
       </c>
       <c r="H1884">
-        <v>0.007528533748367408</v>
+        <v>0.0073383202102358</v>
       </c>
       <c r="I1884">
-        <v>0.3163724440616349</v>
+        <v>0.2861589059300269</v>
       </c>
       <c r="J1884">
         <v>0.7872395580829136</v>
@@ -96371,10 +96371,10 @@
         <v>6.05</v>
       </c>
       <c r="M1884">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1884">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1884">
         <v>1</v>
@@ -96397,7 +96397,7 @@
         <v>442</v>
       </c>
       <c r="E1885">
-        <v>0.9314662516325924</v>
+        <v>0.9616797897642004</v>
       </c>
       <c r="F1885">
         <v>-1</v>
@@ -96406,10 +96406,10 @@
         <v>0.0106649269308208</v>
       </c>
       <c r="H1885">
-        <v>0.007528533748367408</v>
+        <v>0.0073383202102358</v>
       </c>
       <c r="I1885">
-        <v>0.2236068175466093</v>
+        <v>0.1933932794150013</v>
       </c>
       <c r="J1885">
         <v>0.7872395580829136</v>
@@ -96421,10 +96421,10 @@
         <v>5.91</v>
       </c>
       <c r="M1885">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1885">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1885">
         <v>1</v>
@@ -96447,7 +96447,7 @@
         <v>442</v>
       </c>
       <c r="E1886">
-        <v>0.9314662516325924</v>
+        <v>0.9616797897642004</v>
       </c>
       <c r="F1886">
         <v>-1</v>
@@ -96456,10 +96456,10 @@
         <v>0.008216833220211455</v>
       </c>
       <c r="H1886">
-        <v>0.007528533748367408</v>
+        <v>0.0073383202102358</v>
       </c>
       <c r="I1886">
-        <v>0.231700528155955</v>
+        <v>0.201486990024347</v>
       </c>
       <c r="J1886">
         <v>0.7872395580829136</v>
@@ -96471,10 +96471,10 @@
         <v>4.69</v>
       </c>
       <c r="M1886">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1886">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1886">
         <v>1</v>
@@ -96647,7 +96647,7 @@
         <v>442</v>
       </c>
       <c r="E1890">
-        <v>0.8986490417970443</v>
+        <v>0.929959097679721</v>
       </c>
       <c r="F1890">
         <v>-1</v>
@@ -96656,10 +96656,10 @@
         <v>0.0120423898651418</v>
       </c>
       <c r="H1890">
-        <v>0.007561350958202956</v>
+        <v>0.007370040902320281</v>
       </c>
       <c r="I1890">
-        <v>0.2989610930611515</v>
+        <v>0.2676510371784748</v>
       </c>
       <c r="J1890">
         <v>0.7950718277334023</v>
@@ -96671,10 +96671,10 @@
         <v>6.62</v>
       </c>
       <c r="M1890">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1890">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1890">
         <v>1</v>
@@ -96697,7 +96697,7 @@
         <v>442</v>
       </c>
       <c r="E1891">
-        <v>0.8986490417970443</v>
+        <v>0.929959097679721</v>
       </c>
       <c r="F1891">
         <v>-1</v>
@@ -96706,10 +96706,10 @@
         <v>0.01089993814917375</v>
       </c>
       <c r="H1891">
-        <v>0.007561350958202956</v>
+        <v>0.007370040902320281</v>
       </c>
       <c r="I1891">
-        <v>0.3014128090292014</v>
+        <v>0.2701027531465248</v>
       </c>
       <c r="J1891">
         <v>0.7950718277334023</v>
@@ -96721,10 +96721,10 @@
         <v>6.05</v>
       </c>
       <c r="M1891">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1891">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1891">
         <v>1</v>
@@ -96747,7 +96747,7 @@
         <v>442</v>
       </c>
       <c r="E1892">
-        <v>0.8986490417970443</v>
+        <v>0.929959097679721</v>
       </c>
       <c r="F1892">
         <v>-1</v>
@@ -96756,10 +96756,10 @@
         <v>0.01071223383950975</v>
       </c>
       <c r="H1892">
-        <v>0.007561350958202956</v>
+        <v>0.007370040902320281</v>
       </c>
       <c r="I1892">
-        <v>0.2091171186932059</v>
+        <v>0.1778070628105293</v>
       </c>
       <c r="J1892">
         <v>0.7950718277334023</v>
@@ -96771,10 +96771,10 @@
         <v>5.91</v>
       </c>
       <c r="M1892">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1892">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1892">
         <v>1</v>
@@ -96797,7 +96797,7 @@
         <v>442</v>
       </c>
       <c r="E1893">
-        <v>0.8986490417970443</v>
+        <v>0.929959097679721</v>
       </c>
       <c r="F1893">
         <v>-1</v>
@@ -96806,10 +96806,10 @@
         <v>0.008251921788245643</v>
       </c>
       <c r="H1893">
-        <v>0.007561350958202956</v>
+        <v>0.007370040902320281</v>
       </c>
       <c r="I1893">
-        <v>0.2294291699573132</v>
+        <v>0.1981191140746366</v>
       </c>
       <c r="J1893">
         <v>0.7950718277334023</v>
@@ -96821,10 +96821,10 @@
         <v>4.69</v>
       </c>
       <c r="M1893">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1893">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1893">
         <v>1</v>
@@ -96997,7 +96997,7 @@
         <v>442</v>
       </c>
       <c r="E1897">
-        <v>0.8847393667378163</v>
+        <v>0.9165141850329732</v>
       </c>
       <c r="F1897">
         <v>-1</v>
@@ -97006,10 +97006,10 @@
         <v>0.01206503043409262</v>
       </c>
       <c r="H1897">
-        <v>0.007575260633262184</v>
+        <v>0.007383485814967027</v>
       </c>
       <c r="I1897">
-        <v>0.2902301991695597</v>
+        <v>0.2584553808744028</v>
       </c>
       <c r="J1897">
         <v>0.7983915592511178</v>
@@ -97021,10 +97021,10 @@
         <v>6.62</v>
       </c>
       <c r="M1897">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1897">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1897">
         <v>1</v>
@@ -97047,7 +97047,7 @@
         <v>442</v>
       </c>
       <c r="E1898">
-        <v>0.8847393667378163</v>
+        <v>0.9165141850329732</v>
       </c>
       <c r="F1898">
         <v>-1</v>
@@ -97056,10 +97056,10 @@
         <v>0.01092018851143182</v>
       </c>
       <c r="H1898">
-        <v>0.007575260633262184</v>
+        <v>0.007383485814967027</v>
       </c>
       <c r="I1898">
-        <v>0.2950721218303651</v>
+        <v>0.2632973035352082</v>
       </c>
       <c r="J1898">
         <v>0.7983915592511178</v>
@@ -97071,10 +97071,10 @@
         <v>6.05</v>
       </c>
       <c r="M1898">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1898">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1898">
         <v>1</v>
@@ -97097,7 +97097,7 @@
         <v>442</v>
       </c>
       <c r="E1899">
-        <v>0.8847393667378163</v>
+        <v>0.9165141850329732</v>
       </c>
       <c r="F1899">
         <v>-1</v>
@@ -97106,10 +97106,10 @@
         <v>0.01073228501787675</v>
       </c>
       <c r="H1899">
-        <v>0.007575260633262184</v>
+        <v>0.007383485814967027</v>
       </c>
       <c r="I1899">
-        <v>0.2029756153854323</v>
+        <v>0.1712007970902754</v>
       </c>
       <c r="J1899">
         <v>0.7983915592511178</v>
@@ -97121,10 +97121,10 @@
         <v>5.91</v>
       </c>
       <c r="M1899">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1899">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1899">
         <v>1</v>
@@ -97147,7 +97147,7 @@
         <v>442</v>
       </c>
       <c r="E1900">
-        <v>0.8847393667378163</v>
+        <v>0.9165141850329732</v>
       </c>
       <c r="F1900">
         <v>-1</v>
@@ -97156,10 +97156,10 @@
         <v>0.008266794185445007</v>
       </c>
       <c r="H1900">
-        <v>0.007575260633262184</v>
+        <v>0.007383485814967027</v>
       </c>
       <c r="I1900">
-        <v>0.2284664478171758</v>
+        <v>0.1966916295220189</v>
       </c>
       <c r="J1900">
         <v>0.7983915592511178</v>
@@ -97171,10 +97171,10 @@
         <v>4.69</v>
       </c>
       <c r="M1900">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1900">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1900">
         <v>1</v>
@@ -97397,7 +97397,7 @@
         <v>442</v>
       </c>
       <c r="E1905">
-        <v>0.8018449574616251</v>
+        <v>0.8363895173555091</v>
       </c>
       <c r="F1905">
         <v>-1</v>
@@ -97406,10 +97406,10 @@
         <v>0.01104087010966207</v>
       </c>
       <c r="H1905">
-        <v>0.007658155042538375</v>
+        <v>0.007463610482644492</v>
       </c>
       <c r="I1905">
-        <v>0.2572849328763014</v>
+        <v>0.2227403729824173</v>
       </c>
       <c r="J1905">
         <v>0.8181754278134546</v>
@@ -97421,10 +97421,10 @@
         <v>6.05</v>
       </c>
       <c r="M1905">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1905">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1905">
         <v>1</v>
@@ -97447,7 +97447,7 @@
         <v>442</v>
       </c>
       <c r="E1906">
-        <v>0.8018449574616251</v>
+        <v>0.8363895173555091</v>
       </c>
       <c r="F1906">
         <v>-1</v>
@@ -97456,10 +97456,10 @@
         <v>0.01031359993853669</v>
       </c>
       <c r="H1906">
-        <v>0.007658155042538375</v>
+        <v>0.007463610482644492</v>
       </c>
       <c r="I1906">
-        <v>0.1845551040016837</v>
+        <v>0.1500105441077997</v>
       </c>
       <c r="J1906">
         <v>0.8181754278134546</v>
@@ -97471,10 +97471,10 @@
         <v>5.65</v>
       </c>
       <c r="M1906">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1906">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1906">
         <v>1</v>
@@ -97497,7 +97497,7 @@
         <v>442</v>
       </c>
       <c r="E1907">
-        <v>0.8018449574616251</v>
+        <v>0.8363895173555091</v>
       </c>
       <c r="F1907">
         <v>-1</v>
@@ -97506,10 +97506,10 @@
         <v>0.008355425916604278</v>
       </c>
       <c r="H1907">
-        <v>0.007658155042538375</v>
+        <v>0.007463610482644492</v>
       </c>
       <c r="I1907">
-        <v>0.222729125934098</v>
+        <v>0.1881845660402139</v>
       </c>
       <c r="J1907">
         <v>0.8181754278134546</v>
@@ -97521,10 +97521,10 @@
         <v>4.69</v>
       </c>
       <c r="M1907">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="N1907">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="O1907">
         <v>1</v>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5748" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5745" uniqueCount="604">
   <si>
     <t>trade_time</t>
   </si>
@@ -1342,7 +1342,7 @@
     <t>2021-08-20</t>
   </si>
   <si>
-    <t>2021-11-01</t>
+    <t>2021-11-02</t>
   </si>
   <si>
     <t>2021-09-07</t>
@@ -2183,7 +2183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1912"/>
+  <dimension ref="A1:P1911"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -95647,7 +95647,7 @@
         <v>442</v>
       </c>
       <c r="E1870">
-        <v>1.014599266956651</v>
+        <v>0.9671756012626025</v>
       </c>
       <c r="F1870">
         <v>-1</v>
@@ -95656,10 +95656,10 @@
         <v>0.0118998599998409</v>
       </c>
       <c r="H1870">
-        <v>0.00728540073304335</v>
+        <v>0.006912824398737398</v>
       </c>
       <c r="I1870">
-        <v>0.3255407332024496</v>
+        <v>0.3729643988964986</v>
       </c>
       <c r="J1870">
         <v>0.7741730205045306</v>
@@ -95671,10 +95671,10 @@
         <v>6.62</v>
       </c>
       <c r="M1870">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1870">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1870">
         <v>1</v>
@@ -95697,7 +95697,7 @@
         <v>442</v>
       </c>
       <c r="E1871">
-        <v>1.014599266956651</v>
+        <v>0.9671756012626025</v>
       </c>
       <c r="F1871">
         <v>-1</v>
@@ -95706,10 +95706,10 @@
         <v>0.01058600504384737</v>
       </c>
       <c r="H1871">
-        <v>0.00728540073304335</v>
+        <v>0.006912824398737398</v>
       </c>
       <c r="I1871">
-        <v>0.2193956891959838</v>
+        <v>0.2668193548900328</v>
       </c>
       <c r="J1871">
         <v>0.7741730205045306</v>
@@ -95721,10 +95721,10 @@
         <v>5.91</v>
       </c>
       <c r="M1871">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1871">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1871">
         <v>1</v>
@@ -95747,7 +95747,7 @@
         <v>442</v>
       </c>
       <c r="E1872">
-        <v>1.014599266956651</v>
+        <v>0.9671756012626025</v>
       </c>
       <c r="F1872">
         <v>-1</v>
@@ -95756,10 +95756,10 @@
         <v>0.008158295131860298</v>
       </c>
       <c r="H1872">
-        <v>0.00728540073304335</v>
+        <v>0.006912824398737398</v>
       </c>
       <c r="I1872">
-        <v>0.2071056011830512</v>
+        <v>0.2545292668771002</v>
       </c>
       <c r="J1872">
         <v>0.7741730205045306</v>
@@ -95771,10 +95771,10 @@
         <v>4.69</v>
       </c>
       <c r="M1872">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1872">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1872">
         <v>1</v>
@@ -95947,7 +95947,7 @@
         <v>442</v>
       </c>
       <c r="E1876">
-        <v>0.9989848604735414</v>
+        <v>0.9523708306712093</v>
       </c>
       <c r="F1876">
         <v>-1</v>
@@ -95956,10 +95956,10 @@
         <v>0.01192615388927666</v>
       </c>
       <c r="H1876">
-        <v>0.007301015139526459</v>
+        <v>0.006927629169328791</v>
       </c>
       <c r="I1876">
-        <v>0.3148612502498045</v>
+        <v>0.3614752800521366</v>
       </c>
       <c r="J1876">
         <v>0.7780284295127059</v>
@@ -95971,10 +95971,10 @@
         <v>6.62</v>
       </c>
       <c r="M1876">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1876">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1876">
         <v>1</v>
@@ -95988,43 +95988,43 @@
         <v>4</v>
       </c>
       <c r="B1877" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C1877">
-        <v>1.304026579972494</v>
+        <v>1.210708285743256</v>
       </c>
       <c r="D1877" t="s">
         <v>442</v>
       </c>
       <c r="E1877">
-        <v>0.9989848604735414</v>
+        <v>0.9523708306712093</v>
       </c>
       <c r="F1877">
         <v>-1</v>
       </c>
       <c r="G1877">
-        <v>0.0107959734200275</v>
+        <v>0.01060929171425675</v>
       </c>
       <c r="H1877">
-        <v>0.007301015139526459</v>
+        <v>0.006927629169328791</v>
       </c>
       <c r="I1877">
-        <v>0.305041719498953</v>
+        <v>0.2583374550720468</v>
       </c>
       <c r="J1877">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1877">
-        <v>6.1</v>
+        <v>6.04</v>
       </c>
       <c r="L1877">
-        <v>6.05</v>
+        <v>5.91</v>
       </c>
       <c r="M1877">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1877">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1877">
         <v>1</v>
@@ -96038,43 +96038,43 @@
         <v>5</v>
       </c>
       <c r="B1878" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1878">
-        <v>1.210708285743256</v>
+        <v>1.204432635783077</v>
       </c>
       <c r="D1878" t="s">
         <v>442</v>
       </c>
       <c r="E1878">
-        <v>0.9989848604735414</v>
+        <v>0.9523708306712093</v>
       </c>
       <c r="F1878">
         <v>-1</v>
       </c>
       <c r="G1878">
-        <v>0.01060929171425675</v>
+        <v>0.008175567364216924</v>
       </c>
       <c r="H1878">
-        <v>0.007301015139526459</v>
+        <v>0.006927629169328791</v>
       </c>
       <c r="I1878">
-        <v>0.2117234252697147</v>
+        <v>0.2520618051118682</v>
       </c>
       <c r="J1878">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1878">
-        <v>6.04</v>
+        <v>4.48</v>
       </c>
       <c r="L1878">
-        <v>5.91</v>
+        <v>4.69</v>
       </c>
       <c r="M1878">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1878">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1878">
         <v>1</v>
@@ -96085,63 +96085,63 @@
     </row>
     <row r="1879" spans="1:16">
       <c r="A1879" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1879" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C1879">
-        <v>1.204432635783077</v>
+        <v>0.6227397035253315</v>
       </c>
       <c r="D1879" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E1879">
-        <v>0.9989848604735414</v>
+        <v>0.9263542979688486</v>
       </c>
       <c r="F1879">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1879">
-        <v>0.008175567364216924</v>
+        <v>0.008117260296474669</v>
       </c>
       <c r="H1879">
-        <v>0.007301015139526459</v>
+        <v>0.00911364570203115</v>
       </c>
       <c r="I1879">
-        <v>0.2054477753095361</v>
+        <v>0.3036145944435171</v>
       </c>
       <c r="J1879">
-        <v>0.7780284295127059</v>
+        <v>0.7872395580829136</v>
       </c>
       <c r="K1879">
-        <v>4.48</v>
+        <v>4.76</v>
       </c>
       <c r="L1879">
-        <v>4.69</v>
+        <v>4.37</v>
       </c>
       <c r="M1879">
-        <v>4.05</v>
+        <v>5.2</v>
       </c>
       <c r="N1879">
-        <v>4.15</v>
+        <v>5.02</v>
       </c>
       <c r="O1879">
         <v>1</v>
       </c>
       <c r="P1879" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="1880" spans="1:16">
       <c r="A1880" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1880" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C1880">
-        <v>0.6227397035253315</v>
+        <v>0.6352917919087488</v>
       </c>
       <c r="D1880" t="s">
         <v>439</v>
@@ -96153,22 +96153,22 @@
         <v>1</v>
       </c>
       <c r="G1880">
-        <v>0.008117260296474669</v>
+        <v>0.008444708208091251</v>
       </c>
       <c r="H1880">
         <v>0.00911364570203115</v>
       </c>
       <c r="I1880">
-        <v>0.3036145944435171</v>
+        <v>0.2910625060600998</v>
       </c>
       <c r="J1880">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1880">
-        <v>4.76</v>
+        <v>4.96</v>
       </c>
       <c r="L1880">
-        <v>4.37</v>
+        <v>4.54</v>
       </c>
       <c r="M1880">
         <v>5.2</v>
@@ -96185,13 +96185,13 @@
     </row>
     <row r="1881" spans="1:16">
       <c r="A1881" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1881" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C1881">
-        <v>0.6352917919087488</v>
+        <v>0.6589089786512363</v>
       </c>
       <c r="D1881" t="s">
         <v>439</v>
@@ -96203,19 +96203,19 @@
         <v>1</v>
       </c>
       <c r="G1881">
-        <v>0.008444708208091251</v>
+        <v>0.008421091021348763</v>
       </c>
       <c r="H1881">
         <v>0.00911364570203115</v>
       </c>
       <c r="I1881">
-        <v>0.2910625060600998</v>
+        <v>0.2674453193176123</v>
       </c>
       <c r="J1881">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1881">
-        <v>4.96</v>
+        <v>4.93</v>
       </c>
       <c r="L1881">
         <v>4.54</v>
@@ -96235,46 +96235,46 @@
     </row>
     <row r="1882" spans="1:16">
       <c r="A1882" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1882" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C1882">
-        <v>0.6589089786512363</v>
+        <v>1.251026213874529</v>
       </c>
       <c r="D1882" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E1882">
-        <v>0.9263542979688486</v>
+        <v>0.9170000969616119</v>
       </c>
       <c r="F1882">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1882">
-        <v>0.008421091021348763</v>
+        <v>0.01198897378612547</v>
       </c>
       <c r="H1882">
-        <v>0.00911364570203115</v>
+        <v>0.006962999903038388</v>
       </c>
       <c r="I1882">
-        <v>0.2674453193176123</v>
+        <v>0.3340261169129173</v>
       </c>
       <c r="J1882">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1882">
-        <v>4.93</v>
+        <v>6.82</v>
       </c>
       <c r="L1882">
-        <v>4.54</v>
+        <v>6.62</v>
       </c>
       <c r="M1882">
-        <v>5.2</v>
+        <v>3.84</v>
       </c>
       <c r="N1882">
-        <v>5.02</v>
+        <v>3.94</v>
       </c>
       <c r="O1882">
         <v>1</v>
@@ -96285,46 +96285,46 @@
     </row>
     <row r="1883" spans="1:16">
       <c r="A1883" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1883" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C1883">
-        <v>1.251026213874529</v>
+        <v>1.247838695694227</v>
       </c>
       <c r="D1883" t="s">
         <v>442</v>
       </c>
       <c r="E1883">
-        <v>0.9616797897642004</v>
+        <v>0.9170000969616119</v>
       </c>
       <c r="F1883">
         <v>-1</v>
       </c>
       <c r="G1883">
-        <v>0.01198897378612547</v>
+        <v>0.01085216130430577</v>
       </c>
       <c r="H1883">
-        <v>0.0073383202102358</v>
+        <v>0.006962999903038388</v>
       </c>
       <c r="I1883">
-        <v>0.2893464241103287</v>
+        <v>0.3308385987326155</v>
       </c>
       <c r="J1883">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1883">
-        <v>6.82</v>
+        <v>6.1</v>
       </c>
       <c r="L1883">
-        <v>6.62</v>
+        <v>6.05</v>
       </c>
       <c r="M1883">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1883">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1883">
         <v>1</v>
@@ -96335,46 +96335,46 @@
     </row>
     <row r="1884" spans="1:16">
       <c r="A1884" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1884" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C1884">
-        <v>1.247838695694227</v>
+        <v>1.155073069179202</v>
       </c>
       <c r="D1884" t="s">
         <v>442</v>
       </c>
       <c r="E1884">
-        <v>0.9616797897642004</v>
+        <v>0.9170000969616119</v>
       </c>
       <c r="F1884">
         <v>-1</v>
       </c>
       <c r="G1884">
-        <v>0.01085216130430577</v>
+        <v>0.0106649269308208</v>
       </c>
       <c r="H1884">
-        <v>0.0073383202102358</v>
+        <v>0.006962999903038388</v>
       </c>
       <c r="I1884">
-        <v>0.2861589059300269</v>
+        <v>0.2380729722175898</v>
       </c>
       <c r="J1884">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1884">
-        <v>6.1</v>
+        <v>6.04</v>
       </c>
       <c r="L1884">
-        <v>6.05</v>
+        <v>5.91</v>
       </c>
       <c r="M1884">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1884">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1884">
         <v>1</v>
@@ -96385,46 +96385,46 @@
     </row>
     <row r="1885" spans="1:16">
       <c r="A1885" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1885" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1885">
-        <v>1.155073069179202</v>
+        <v>1.163166779788547</v>
       </c>
       <c r="D1885" t="s">
         <v>442</v>
       </c>
       <c r="E1885">
-        <v>0.9616797897642004</v>
+        <v>0.9170000969616119</v>
       </c>
       <c r="F1885">
         <v>-1</v>
       </c>
       <c r="G1885">
-        <v>0.0106649269308208</v>
+        <v>0.008216833220211455</v>
       </c>
       <c r="H1885">
-        <v>0.0073383202102358</v>
+        <v>0.006962999903038388</v>
       </c>
       <c r="I1885">
-        <v>0.1933932794150013</v>
+        <v>0.2461666828269355</v>
       </c>
       <c r="J1885">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1885">
-        <v>6.04</v>
+        <v>4.48</v>
       </c>
       <c r="L1885">
-        <v>5.91</v>
+        <v>4.69</v>
       </c>
       <c r="M1885">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1885">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1885">
         <v>1</v>
@@ -96435,63 +96435,63 @@
     </row>
     <row r="1886" spans="1:16">
       <c r="A1886" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1886" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C1886">
-        <v>1.163166779788547</v>
+        <v>0.5854580999890051</v>
       </c>
       <c r="D1886" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E1886">
-        <v>0.9616797897642004</v>
+        <v>0.8856264957863074</v>
       </c>
       <c r="F1886">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1886">
-        <v>0.008216833220211455</v>
+        <v>0.008154541900010996</v>
       </c>
       <c r="H1886">
-        <v>0.0073383202102358</v>
+        <v>0.00915437350421369</v>
       </c>
       <c r="I1886">
-        <v>0.201486990024347</v>
+        <v>0.3001683957973023</v>
       </c>
       <c r="J1886">
-        <v>0.7872395580829136</v>
+        <v>0.7950718277334023</v>
       </c>
       <c r="K1886">
-        <v>4.48</v>
+        <v>4.76</v>
       </c>
       <c r="L1886">
-        <v>4.69</v>
+        <v>4.37</v>
       </c>
       <c r="M1886">
-        <v>4.05</v>
+        <v>5.2</v>
       </c>
       <c r="N1886">
-        <v>4.15</v>
+        <v>5.02</v>
       </c>
       <c r="O1886">
         <v>1</v>
       </c>
       <c r="P1886" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1887" spans="1:16">
       <c r="A1887" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1887" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C1887">
-        <v>0.5854580999890051</v>
+        <v>0.5964437344423246</v>
       </c>
       <c r="D1887" t="s">
         <v>439</v>
@@ -96503,22 +96503,22 @@
         <v>1</v>
       </c>
       <c r="G1887">
-        <v>0.008154541900010996</v>
+        <v>0.008483556265557676</v>
       </c>
       <c r="H1887">
         <v>0.00915437350421369</v>
       </c>
       <c r="I1887">
-        <v>0.3001683957973023</v>
+        <v>0.2891827613439828</v>
       </c>
       <c r="J1887">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1887">
-        <v>4.76</v>
+        <v>4.96</v>
       </c>
       <c r="L1887">
-        <v>4.37</v>
+        <v>4.54</v>
       </c>
       <c r="M1887">
         <v>5.2</v>
@@ -96535,13 +96535,13 @@
     </row>
     <row r="1888" spans="1:16">
       <c r="A1888" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1888" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C1888">
-        <v>0.5964437344423246</v>
+        <v>0.6202958892743267</v>
       </c>
       <c r="D1888" t="s">
         <v>439</v>
@@ -96553,19 +96553,19 @@
         <v>1</v>
       </c>
       <c r="G1888">
-        <v>0.008483556265557676</v>
+        <v>0.008459704110725675</v>
       </c>
       <c r="H1888">
         <v>0.00915437350421369</v>
       </c>
       <c r="I1888">
-        <v>0.2891827613439828</v>
+        <v>0.2653306065119807</v>
       </c>
       <c r="J1888">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1888">
-        <v>4.96</v>
+        <v>4.93</v>
       </c>
       <c r="L1888">
         <v>4.54</v>
@@ -96585,46 +96585,46 @@
     </row>
     <row r="1889" spans="1:16">
       <c r="A1889" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1889" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C1889">
-        <v>0.6202958892743267</v>
+        <v>1.197610134858196</v>
       </c>
       <c r="D1889" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E1889">
-        <v>0.8856264957863074</v>
+        <v>0.8869241815037352</v>
       </c>
       <c r="F1889">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1889">
-        <v>0.008459704110725675</v>
+        <v>0.0120423898651418</v>
       </c>
       <c r="H1889">
-        <v>0.00915437350421369</v>
+        <v>0.006993075818496265</v>
       </c>
       <c r="I1889">
-        <v>0.2653306065119807</v>
+        <v>0.3106859533544606</v>
       </c>
       <c r="J1889">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1889">
-        <v>4.93</v>
+        <v>6.82</v>
       </c>
       <c r="L1889">
-        <v>4.54</v>
+        <v>6.62</v>
       </c>
       <c r="M1889">
-        <v>5.2</v>
+        <v>3.84</v>
       </c>
       <c r="N1889">
-        <v>5.02</v>
+        <v>3.94</v>
       </c>
       <c r="O1889">
         <v>1</v>
@@ -96635,46 +96635,46 @@
     </row>
     <row r="1890" spans="1:16">
       <c r="A1890" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1890" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C1890">
-        <v>1.197610134858196</v>
+        <v>1.200061850826246</v>
       </c>
       <c r="D1890" t="s">
         <v>442</v>
       </c>
       <c r="E1890">
-        <v>0.929959097679721</v>
+        <v>0.8869241815037352</v>
       </c>
       <c r="F1890">
         <v>-1</v>
       </c>
       <c r="G1890">
-        <v>0.0120423898651418</v>
+        <v>0.01089993814917375</v>
       </c>
       <c r="H1890">
-        <v>0.007370040902320281</v>
+        <v>0.006993075818496265</v>
       </c>
       <c r="I1890">
-        <v>0.2676510371784748</v>
+        <v>0.3131376693225105</v>
       </c>
       <c r="J1890">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1890">
-        <v>6.82</v>
+        <v>6.1</v>
       </c>
       <c r="L1890">
-        <v>6.62</v>
+        <v>6.05</v>
       </c>
       <c r="M1890">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1890">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1890">
         <v>1</v>
@@ -96685,46 +96685,46 @@
     </row>
     <row r="1891" spans="1:16">
       <c r="A1891" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1891" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C1891">
-        <v>1.200061850826246</v>
+        <v>1.10776616049025</v>
       </c>
       <c r="D1891" t="s">
         <v>442</v>
       </c>
       <c r="E1891">
-        <v>0.929959097679721</v>
+        <v>0.8869241815037352</v>
       </c>
       <c r="F1891">
         <v>-1</v>
       </c>
       <c r="G1891">
-        <v>0.01089993814917375</v>
+        <v>0.01071223383950975</v>
       </c>
       <c r="H1891">
-        <v>0.007370040902320281</v>
+        <v>0.006993075818496265</v>
       </c>
       <c r="I1891">
-        <v>0.2701027531465248</v>
+        <v>0.220841978986515</v>
       </c>
       <c r="J1891">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1891">
-        <v>6.1</v>
+        <v>6.04</v>
       </c>
       <c r="L1891">
-        <v>6.05</v>
+        <v>5.91</v>
       </c>
       <c r="M1891">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1891">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1891">
         <v>1</v>
@@ -96735,46 +96735,46 @@
     </row>
     <row r="1892" spans="1:16">
       <c r="A1892" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1892" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1892">
-        <v>1.10776616049025</v>
+        <v>1.128078211754358</v>
       </c>
       <c r="D1892" t="s">
         <v>442</v>
       </c>
       <c r="E1892">
-        <v>0.929959097679721</v>
+        <v>0.8869241815037352</v>
       </c>
       <c r="F1892">
         <v>-1</v>
       </c>
       <c r="G1892">
-        <v>0.01071223383950975</v>
+        <v>0.008251921788245643</v>
       </c>
       <c r="H1892">
-        <v>0.007370040902320281</v>
+        <v>0.006993075818496265</v>
       </c>
       <c r="I1892">
-        <v>0.1778070628105293</v>
+        <v>0.2411540302506223</v>
       </c>
       <c r="J1892">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1892">
-        <v>6.04</v>
+        <v>4.48</v>
       </c>
       <c r="L1892">
-        <v>5.91</v>
+        <v>4.69</v>
       </c>
       <c r="M1892">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1892">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1892">
         <v>1</v>
@@ -96785,63 +96785,63 @@
     </row>
     <row r="1893" spans="1:16">
       <c r="A1893" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1893" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C1893">
-        <v>1.128078211754358</v>
+        <v>0.5696561779646796</v>
       </c>
       <c r="D1893" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E1893">
-        <v>0.929959097679721</v>
+        <v>0.8683638918941865</v>
       </c>
       <c r="F1893">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1893">
-        <v>0.008251921788245643</v>
+        <v>0.00817034382203532</v>
       </c>
       <c r="H1893">
-        <v>0.007370040902320281</v>
+        <v>0.009171636108105811</v>
       </c>
       <c r="I1893">
-        <v>0.1981191140746366</v>
+        <v>0.2987077139295069</v>
       </c>
       <c r="J1893">
-        <v>0.7950718277334023</v>
+        <v>0.7983915592511178</v>
       </c>
       <c r="K1893">
-        <v>4.48</v>
+        <v>4.76</v>
       </c>
       <c r="L1893">
-        <v>4.69</v>
+        <v>4.37</v>
       </c>
       <c r="M1893">
-        <v>4.05</v>
+        <v>5.2</v>
       </c>
       <c r="N1893">
-        <v>4.15</v>
+        <v>5.02</v>
       </c>
       <c r="O1893">
         <v>1</v>
       </c>
       <c r="P1893" t="s">
-        <v>225</v>
+        <v>427</v>
       </c>
     </row>
     <row r="1894" spans="1:16">
       <c r="A1894" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1894" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C1894">
-        <v>0.5696561779646796</v>
+        <v>0.5799778661144557</v>
       </c>
       <c r="D1894" t="s">
         <v>439</v>
@@ -96853,22 +96853,22 @@
         <v>1</v>
       </c>
       <c r="G1894">
-        <v>0.00817034382203532</v>
+        <v>0.008500022133885544</v>
       </c>
       <c r="H1894">
         <v>0.009171636108105811</v>
       </c>
       <c r="I1894">
-        <v>0.2987077139295069</v>
+        <v>0.2883860257797308</v>
       </c>
       <c r="J1894">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1894">
-        <v>4.76</v>
+        <v>4.96</v>
       </c>
       <c r="L1894">
-        <v>4.37</v>
+        <v>4.54</v>
       </c>
       <c r="M1894">
         <v>5.2</v>
@@ -96885,13 +96885,13 @@
     </row>
     <row r="1895" spans="1:16">
       <c r="A1895" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1895" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C1895">
-        <v>0.5799778661144557</v>
+        <v>0.6039296128919895</v>
       </c>
       <c r="D1895" t="s">
         <v>439</v>
@@ -96903,19 +96903,19 @@
         <v>1</v>
       </c>
       <c r="G1895">
-        <v>0.008500022133885544</v>
+        <v>0.008476070387108009</v>
       </c>
       <c r="H1895">
         <v>0.009171636108105811</v>
       </c>
       <c r="I1895">
-        <v>0.2883860257797308</v>
+        <v>0.264434279002197</v>
       </c>
       <c r="J1895">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1895">
-        <v>4.96</v>
+        <v>4.93</v>
       </c>
       <c r="L1895">
         <v>4.54</v>
@@ -96935,46 +96935,46 @@
     </row>
     <row r="1896" spans="1:16">
       <c r="A1896" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1896" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C1896">
-        <v>0.6039296128919895</v>
+        <v>1.174969565907376</v>
       </c>
       <c r="D1896" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E1896">
-        <v>0.8683638918941865</v>
+        <v>0.8741764124757077</v>
       </c>
       <c r="F1896">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1896">
-        <v>0.008476070387108009</v>
+        <v>0.01206503043409262</v>
       </c>
       <c r="H1896">
-        <v>0.009171636108105811</v>
+        <v>0.007005823587524292</v>
       </c>
       <c r="I1896">
-        <v>0.264434279002197</v>
+        <v>0.3007931534316683</v>
       </c>
       <c r="J1896">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1896">
-        <v>4.93</v>
+        <v>6.82</v>
       </c>
       <c r="L1896">
-        <v>4.54</v>
+        <v>6.62</v>
       </c>
       <c r="M1896">
-        <v>5.2</v>
+        <v>3.84</v>
       </c>
       <c r="N1896">
-        <v>5.02</v>
+        <v>3.94</v>
       </c>
       <c r="O1896">
         <v>1</v>
@@ -96985,46 +96985,46 @@
     </row>
     <row r="1897" spans="1:16">
       <c r="A1897" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1897" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C1897">
-        <v>1.174969565907376</v>
+        <v>1.179811488568181</v>
       </c>
       <c r="D1897" t="s">
         <v>442</v>
       </c>
       <c r="E1897">
-        <v>0.9165141850329732</v>
+        <v>0.8741764124757077</v>
       </c>
       <c r="F1897">
         <v>-1</v>
       </c>
       <c r="G1897">
-        <v>0.01206503043409262</v>
+        <v>0.01092018851143182</v>
       </c>
       <c r="H1897">
-        <v>0.007383485814967027</v>
+        <v>0.007005823587524292</v>
       </c>
       <c r="I1897">
-        <v>0.2584553808744028</v>
+        <v>0.3056350760924738</v>
       </c>
       <c r="J1897">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1897">
-        <v>6.82</v>
+        <v>6.1</v>
       </c>
       <c r="L1897">
-        <v>6.62</v>
+        <v>6.05</v>
       </c>
       <c r="M1897">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1897">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1897">
         <v>1</v>
@@ -97035,46 +97035,46 @@
     </row>
     <row r="1898" spans="1:16">
       <c r="A1898" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1898" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C1898">
-        <v>1.179811488568181</v>
+        <v>1.087714982123249</v>
       </c>
       <c r="D1898" t="s">
         <v>442</v>
       </c>
       <c r="E1898">
-        <v>0.9165141850329732</v>
+        <v>0.8741764124757077</v>
       </c>
       <c r="F1898">
         <v>-1</v>
       </c>
       <c r="G1898">
-        <v>0.01092018851143182</v>
+        <v>0.01073228501787675</v>
       </c>
       <c r="H1898">
-        <v>0.007383485814967027</v>
+        <v>0.007005823587524292</v>
       </c>
       <c r="I1898">
-        <v>0.2632973035352082</v>
+        <v>0.2135385696475409</v>
       </c>
       <c r="J1898">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1898">
-        <v>6.1</v>
+        <v>6.04</v>
       </c>
       <c r="L1898">
-        <v>6.05</v>
+        <v>5.91</v>
       </c>
       <c r="M1898">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1898">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1898">
         <v>1</v>
@@ -97085,46 +97085,46 @@
     </row>
     <row r="1899" spans="1:16">
       <c r="A1899" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1899" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1899">
-        <v>1.087714982123249</v>
+        <v>1.113205814554992</v>
       </c>
       <c r="D1899" t="s">
         <v>442</v>
       </c>
       <c r="E1899">
-        <v>0.9165141850329732</v>
+        <v>0.8741764124757077</v>
       </c>
       <c r="F1899">
         <v>-1</v>
       </c>
       <c r="G1899">
-        <v>0.01073228501787675</v>
+        <v>0.008266794185445007</v>
       </c>
       <c r="H1899">
-        <v>0.007383485814967027</v>
+        <v>0.007005823587524292</v>
       </c>
       <c r="I1899">
-        <v>0.1712007970902754</v>
+        <v>0.2390294020792845</v>
       </c>
       <c r="J1899">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1899">
-        <v>6.04</v>
+        <v>4.48</v>
       </c>
       <c r="L1899">
-        <v>5.91</v>
+        <v>4.69</v>
       </c>
       <c r="M1899">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1899">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1899">
         <v>1</v>
@@ -97135,63 +97135,63 @@
     </row>
     <row r="1900" spans="1:16">
       <c r="A1900" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1900" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C1900">
-        <v>1.113205814554992</v>
+        <v>0.580033038204439</v>
       </c>
       <c r="D1900" t="s">
-        <v>442</v>
+        <v>250</v>
       </c>
       <c r="E1900">
-        <v>0.9165141850329732</v>
+        <v>0.8773067240324215</v>
       </c>
       <c r="F1900">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1900">
-        <v>0.008266794185445007</v>
+        <v>0.00903996696179556</v>
       </c>
       <c r="H1900">
-        <v>0.007383485814967027</v>
+        <v>0.009582693275967578</v>
       </c>
       <c r="I1900">
-        <v>0.1966916295220189</v>
+        <v>0.2972736858279825</v>
       </c>
       <c r="J1900">
-        <v>0.7983915592511178</v>
+        <v>0.8181754278134546</v>
       </c>
       <c r="K1900">
-        <v>4.48</v>
+        <v>5.17</v>
       </c>
       <c r="L1900">
-        <v>4.69</v>
+        <v>4.81</v>
       </c>
       <c r="M1900">
-        <v>4.05</v>
+        <v>5.32</v>
       </c>
       <c r="N1900">
-        <v>4.15</v>
+        <v>5.23</v>
       </c>
       <c r="O1900">
         <v>1</v>
       </c>
       <c r="P1900" t="s">
-        <v>427</v>
+        <v>246</v>
       </c>
     </row>
     <row r="1901" spans="1:16">
       <c r="A1901" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1901" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C1901">
-        <v>0.580033038204439</v>
+        <v>0.4818498780452654</v>
       </c>
       <c r="D1901" t="s">
         <v>250</v>
@@ -97203,22 +97203,22 @@
         <v>1</v>
       </c>
       <c r="G1901">
-        <v>0.00903996696179556</v>
+        <v>0.008598150121954735</v>
       </c>
       <c r="H1901">
         <v>0.009582693275967578</v>
       </c>
       <c r="I1901">
-        <v>0.2972736858279825</v>
+        <v>0.3954568459871561</v>
       </c>
       <c r="J1901">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1901">
-        <v>5.17</v>
+        <v>4.96</v>
       </c>
       <c r="L1901">
-        <v>4.81</v>
+        <v>4.54</v>
       </c>
       <c r="M1901">
         <v>5.32</v>
@@ -97235,13 +97235,13 @@
     </row>
     <row r="1902" spans="1:16">
       <c r="A1902" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1902" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C1902">
-        <v>0.4818498780452654</v>
+        <v>0.5063951408796692</v>
       </c>
       <c r="D1902" t="s">
         <v>250</v>
@@ -97253,19 +97253,19 @@
         <v>1</v>
       </c>
       <c r="G1902">
-        <v>0.008598150121954735</v>
+        <v>0.008573604859120331</v>
       </c>
       <c r="H1902">
         <v>0.009582693275967578</v>
       </c>
       <c r="I1902">
-        <v>0.3954568459871561</v>
+        <v>0.3709115831527523</v>
       </c>
       <c r="J1902">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1902">
-        <v>4.96</v>
+        <v>4.93</v>
       </c>
       <c r="L1902">
         <v>4.54</v>
@@ -97285,46 +97285,46 @@
     </row>
     <row r="1903" spans="1:16">
       <c r="A1903" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1903" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C1903">
-        <v>0.5063951408796692</v>
+        <v>0.5518576103909849</v>
       </c>
       <c r="D1903" t="s">
-        <v>250</v>
+        <v>443</v>
       </c>
       <c r="E1903">
-        <v>0.8773067240324215</v>
+        <v>0.7845874392656027</v>
       </c>
       <c r="F1903">
         <v>1</v>
       </c>
       <c r="G1903">
-        <v>0.008573604859120331</v>
+        <v>0.01064814238960901</v>
       </c>
       <c r="H1903">
-        <v>0.009582693275967578</v>
+        <v>0.0115354125607344</v>
       </c>
       <c r="I1903">
-        <v>0.3709115831527523</v>
+        <v>0.2327298288746178</v>
       </c>
       <c r="J1903">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1903">
-        <v>4.93</v>
+        <v>6.17</v>
       </c>
       <c r="L1903">
-        <v>4.54</v>
+        <v>5.6</v>
       </c>
       <c r="M1903">
-        <v>5.32</v>
+        <v>6.57</v>
       </c>
       <c r="N1903">
-        <v>5.23</v>
+        <v>6.16</v>
       </c>
       <c r="O1903">
         <v>1</v>
@@ -97335,46 +97335,46 @@
     </row>
     <row r="1904" spans="1:16">
       <c r="A1904" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1904" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C1904">
-        <v>0.5518576103909849</v>
+        <v>1.059129890337926</v>
       </c>
       <c r="D1904" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E1904">
-        <v>0.7845874392656027</v>
+        <v>0.7982063571963343</v>
       </c>
       <c r="F1904">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1904">
-        <v>0.01064814238960901</v>
+        <v>0.01104087010966207</v>
       </c>
       <c r="H1904">
-        <v>0.0115354125607344</v>
+        <v>0.007081793642803666</v>
       </c>
       <c r="I1904">
-        <v>0.2327298288746178</v>
+        <v>0.2609235331415922</v>
       </c>
       <c r="J1904">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1904">
-        <v>6.17</v>
+        <v>6.1</v>
       </c>
       <c r="L1904">
-        <v>5.6</v>
+        <v>6.05</v>
       </c>
       <c r="M1904">
-        <v>6.57</v>
+        <v>3.84</v>
       </c>
       <c r="N1904">
-        <v>6.16</v>
+        <v>3.94</v>
       </c>
       <c r="O1904">
         <v>1</v>
@@ -97385,46 +97385,46 @@
     </row>
     <row r="1905" spans="1:16">
       <c r="A1905" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1905" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C1905">
-        <v>1.059129890337926</v>
+        <v>0.9864000614633088</v>
       </c>
       <c r="D1905" t="s">
         <v>442</v>
       </c>
       <c r="E1905">
-        <v>0.8363895173555091</v>
+        <v>0.7982063571963343</v>
       </c>
       <c r="F1905">
         <v>-1</v>
       </c>
       <c r="G1905">
-        <v>0.01104087010966207</v>
+        <v>0.01031359993853669</v>
       </c>
       <c r="H1905">
-        <v>0.007463610482644492</v>
+        <v>0.007081793642803666</v>
       </c>
       <c r="I1905">
-        <v>0.2227403729824173</v>
+        <v>0.1881937042669746</v>
       </c>
       <c r="J1905">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1905">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="L1905">
-        <v>6.05</v>
+        <v>5.65</v>
       </c>
       <c r="M1905">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1905">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1905">
         <v>1</v>
@@ -97435,46 +97435,46 @@
     </row>
     <row r="1906" spans="1:16">
       <c r="A1906" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1906" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C1906">
-        <v>0.9864000614633088</v>
+        <v>1.024574083395723</v>
       </c>
       <c r="D1906" t="s">
         <v>442</v>
       </c>
       <c r="E1906">
-        <v>0.8363895173555091</v>
+        <v>0.7982063571963343</v>
       </c>
       <c r="F1906">
         <v>-1</v>
       </c>
       <c r="G1906">
-        <v>0.01031359993853669</v>
+        <v>0.008355425916604278</v>
       </c>
       <c r="H1906">
-        <v>0.007463610482644492</v>
+        <v>0.007081793642803666</v>
       </c>
       <c r="I1906">
-        <v>0.1500105441077997</v>
+        <v>0.2263677261993888</v>
       </c>
       <c r="J1906">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1906">
-        <v>5.7</v>
+        <v>4.48</v>
       </c>
       <c r="L1906">
-        <v>5.65</v>
+        <v>4.69</v>
       </c>
       <c r="M1906">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="N1906">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="O1906">
         <v>1</v>
@@ -97485,63 +97485,63 @@
     </row>
     <row r="1907" spans="1:16">
       <c r="A1907" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1907" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C1907">
-        <v>1.024574083395723</v>
+        <v>0.545481672883029</v>
       </c>
       <c r="D1907" t="s">
-        <v>442</v>
+        <v>256</v>
       </c>
       <c r="E1907">
-        <v>0.8363895173555091</v>
+        <v>0.8503069233264586</v>
       </c>
       <c r="F1907">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1907">
-        <v>0.008355425916604278</v>
+        <v>0.009834518327116971</v>
       </c>
       <c r="H1907">
-        <v>0.007463610482644492</v>
+        <v>0.01238969307667354</v>
       </c>
       <c r="I1907">
-        <v>0.1881845660402139</v>
+        <v>0.3048252504434297</v>
       </c>
       <c r="J1907">
-        <v>0.8181754278134546</v>
+        <v>0.8459960522981732</v>
       </c>
       <c r="K1907">
-        <v>4.48</v>
+        <v>5.49</v>
       </c>
       <c r="L1907">
-        <v>4.69</v>
+        <v>5.19</v>
       </c>
       <c r="M1907">
-        <v>4.05</v>
+        <v>6.82</v>
       </c>
       <c r="N1907">
-        <v>4.15</v>
+        <v>6.62</v>
       </c>
       <c r="O1907">
         <v>1</v>
       </c>
       <c r="P1907" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1908" spans="1:16">
       <c r="A1908" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1908" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C1908">
-        <v>0.545481672883029</v>
+        <v>0.4840236862109606</v>
       </c>
       <c r="D1908" t="s">
         <v>256</v>
@@ -97553,22 +97553,22 @@
         <v>1</v>
       </c>
       <c r="G1908">
-        <v>0.009834518327116971</v>
+        <v>0.01063597631378904</v>
       </c>
       <c r="H1908">
         <v>0.01238969307667354</v>
       </c>
       <c r="I1908">
-        <v>0.3048252504434297</v>
+        <v>0.366283237115498</v>
       </c>
       <c r="J1908">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1908">
-        <v>5.49</v>
+        <v>6</v>
       </c>
       <c r="L1908">
-        <v>5.19</v>
+        <v>5.56</v>
       </c>
       <c r="M1908">
         <v>6.82</v>
@@ -97585,46 +97585,46 @@
     </row>
     <row r="1909" spans="1:16">
       <c r="A1909" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1909" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1909">
-        <v>0.4840236862109606</v>
+        <v>0.9041057390159111</v>
       </c>
       <c r="D1909" t="s">
-        <v>256</v>
+        <v>444</v>
       </c>
       <c r="E1909">
-        <v>0.8503069233264586</v>
+        <v>0.6972268443724223</v>
       </c>
       <c r="F1909">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1909">
-        <v>0.01063597631378904</v>
+        <v>0.01193589426098409</v>
       </c>
       <c r="H1909">
-        <v>0.01238969307667354</v>
+        <v>0.01220277315562758</v>
       </c>
       <c r="I1909">
-        <v>0.366283237115498</v>
+        <v>0.2068788946434887</v>
       </c>
       <c r="J1909">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1909">
-        <v>6</v>
+        <v>6.52</v>
       </c>
       <c r="L1909">
-        <v>5.56</v>
+        <v>6.42</v>
       </c>
       <c r="M1909">
-        <v>6.82</v>
+        <v>6.8</v>
       </c>
       <c r="N1909">
-        <v>6.62</v>
+        <v>6.45</v>
       </c>
       <c r="O1909">
         <v>1</v>
@@ -97635,46 +97635,46 @@
     </row>
     <row r="1910" spans="1:16">
       <c r="A1910" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1910" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C1910">
-        <v>0.9041057390159111</v>
+        <v>1.019321514974956</v>
       </c>
       <c r="D1910" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E1910">
-        <v>0.6972268443724223</v>
+        <v>0.6999376857041839</v>
       </c>
       <c r="F1910">
         <v>-1</v>
       </c>
       <c r="G1910">
-        <v>0.01193589426098409</v>
+        <v>0.01024067848502504</v>
       </c>
       <c r="H1910">
-        <v>0.01220277315562758</v>
+        <v>0.008280062314295816</v>
       </c>
       <c r="I1910">
-        <v>0.2068788946434887</v>
+        <v>0.3193838292707718</v>
       </c>
       <c r="J1910">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1910">
-        <v>6.52</v>
+        <v>5.45</v>
       </c>
       <c r="L1910">
-        <v>6.42</v>
+        <v>5.63</v>
       </c>
       <c r="M1910">
-        <v>6.8</v>
+        <v>4.48</v>
       </c>
       <c r="N1910">
-        <v>6.45</v>
+        <v>4.49</v>
       </c>
       <c r="O1910">
         <v>1</v>
@@ -97685,13 +97685,13 @@
     </row>
     <row r="1911" spans="1:16">
       <c r="A1911" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1911" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C1911">
-        <v>1.019321514974956</v>
+        <v>0.8999376857041841</v>
       </c>
       <c r="D1911" t="s">
         <v>445</v>
@@ -97703,22 +97703,22 @@
         <v>-1</v>
       </c>
       <c r="G1911">
-        <v>0.01024067848502504</v>
+        <v>0.008480062314295817</v>
       </c>
       <c r="H1911">
         <v>0.008280062314295816</v>
       </c>
       <c r="I1911">
-        <v>0.3193838292707718</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="J1911">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1911">
-        <v>5.45</v>
+        <v>4.48</v>
       </c>
       <c r="L1911">
-        <v>5.63</v>
+        <v>4.69</v>
       </c>
       <c r="M1911">
         <v>4.48</v>
@@ -97730,56 +97730,6 @@
         <v>1</v>
       </c>
       <c r="P1911" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="1912" spans="1:16">
-      <c r="A1912" s="1">
-        <v>4</v>
-      </c>
-      <c r="B1912" t="s">
-        <v>258</v>
-      </c>
-      <c r="C1912">
-        <v>0.8999376857041841</v>
-      </c>
-      <c r="D1912" t="s">
-        <v>445</v>
-      </c>
-      <c r="E1912">
-        <v>0.6999376857041839</v>
-      </c>
-      <c r="F1912">
-        <v>-1</v>
-      </c>
-      <c r="G1912">
-        <v>0.008480062314295817</v>
-      </c>
-      <c r="H1912">
-        <v>0.008280062314295816</v>
-      </c>
-      <c r="I1912">
-        <v>0.2000000000000002</v>
-      </c>
-      <c r="J1912">
-        <v>0.8459960522981732</v>
-      </c>
-      <c r="K1912">
-        <v>4.48</v>
-      </c>
-      <c r="L1912">
-        <v>4.69</v>
-      </c>
-      <c r="M1912">
-        <v>4.48</v>
-      </c>
-      <c r="N1912">
-        <v>4.49</v>
-      </c>
-      <c r="O1912">
-        <v>1</v>
-      </c>
-      <c r="P1912" t="s">
         <v>247</v>
       </c>
     </row>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5784" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5778" uniqueCount="606">
   <si>
     <t>trade_time</t>
   </si>
@@ -787,19 +787,16 @@
     <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-09-16</t>
-  </si>
-  <si>
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-10-21</t>
+    <t>2021-10-20</t>
   </si>
   <si>
     <t>2021-11-12</t>
   </si>
   <si>
-    <t>2021-10-20</t>
+    <t>2021-09-16</t>
   </si>
   <si>
     <t>2021-09-14</t>
@@ -815,6 +812,9 @@
   </si>
   <si>
     <t>2021-09-23</t>
+  </si>
+  <si>
+    <t>2021-10-21</t>
   </si>
   <si>
     <t>2021-11-10</t>
@@ -1348,7 +1348,7 @@
     <t>2021-11-04</t>
   </si>
   <si>
-    <t>2021-11-15</t>
+    <t>2021-11-16</t>
   </si>
   <si>
     <t>2021-09-07</t>
@@ -2189,7 +2189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1924"/>
+  <dimension ref="A1:P1922"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -87700,7 +87700,7 @@
         <v>2.431411491361336</v>
       </c>
       <c r="D1711" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E1711">
         <v>2.538213707664756</v>
@@ -87750,7 +87750,7 @@
         <v>2.532009684902152</v>
       </c>
       <c r="D1712" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E1712">
         <v>2.538213707664756</v>
@@ -87800,7 +87800,7 @@
         <v>2.427002049221179</v>
       </c>
       <c r="D1713" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E1713">
         <v>2.538213707664756</v>
@@ -87850,7 +87850,7 @@
         <v>2.549425366108334</v>
       </c>
       <c r="D1714" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E1714">
         <v>2.538213707664756</v>
@@ -95697,7 +95697,7 @@
         <v>257</v>
       </c>
       <c r="C1871">
-        <v>1.233994956152635</v>
+        <v>1.221704868139703</v>
       </c>
       <c r="D1871" t="s">
         <v>443</v>
@@ -95709,22 +95709,22 @@
         <v>-1</v>
       </c>
       <c r="G1871">
-        <v>0.01058600504384737</v>
+        <v>0.008158295131860298</v>
       </c>
       <c r="H1871">
         <v>0.006880566128942443</v>
       </c>
       <c r="I1871">
-        <v>0.3145610850950784</v>
+        <v>0.3022709970821458</v>
       </c>
       <c r="J1871">
         <v>0.7741730205045306</v>
       </c>
       <c r="K1871">
-        <v>6.04</v>
+        <v>4.48</v>
       </c>
       <c r="L1871">
-        <v>5.91</v>
+        <v>4.69</v>
       </c>
       <c r="M1871">
         <v>3.85</v>
@@ -95747,7 +95747,7 @@
         <v>258</v>
       </c>
       <c r="C1872">
-        <v>1.221704868139703</v>
+        <v>1.157512756704385</v>
       </c>
       <c r="D1872" t="s">
         <v>443</v>
@@ -95759,22 +95759,22 @@
         <v>-1</v>
       </c>
       <c r="G1872">
-        <v>0.008158295131860298</v>
+        <v>0.008202487243295614</v>
       </c>
       <c r="H1872">
         <v>0.006880566128942443</v>
       </c>
       <c r="I1872">
-        <v>0.3022709970821458</v>
+        <v>0.2380788856468286</v>
       </c>
       <c r="J1872">
         <v>0.7741730205045306</v>
       </c>
       <c r="K1872">
-        <v>4.48</v>
+        <v>4.55</v>
       </c>
       <c r="L1872">
-        <v>4.69</v>
+        <v>4.68</v>
       </c>
       <c r="M1872">
         <v>3.85</v>
@@ -95797,40 +95797,40 @@
         <v>259</v>
       </c>
       <c r="C1873">
-        <v>1.160737947319522</v>
+        <v>0.7126590616726931</v>
       </c>
       <c r="D1873" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E1873">
-        <v>0.9194338710575569</v>
+        <v>0.7487850147483726</v>
       </c>
       <c r="F1873">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1873">
-        <v>0.008159262052680478</v>
+        <v>0.006627340938327307</v>
       </c>
       <c r="H1873">
-        <v>0.006880566128942443</v>
+        <v>0.006431214985251627</v>
       </c>
       <c r="I1873">
-        <v>0.2413040762619652</v>
+        <v>0.03612595307567945</v>
       </c>
       <c r="J1873">
         <v>0.7741730205045306</v>
       </c>
       <c r="K1873">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="L1873">
-        <v>4.66</v>
+        <v>3.67</v>
       </c>
       <c r="M1873">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="N1873">
-        <v>3.9</v>
+        <v>3.59</v>
       </c>
       <c r="O1873">
         <v>1</v>
@@ -95841,63 +95841,63 @@
     </row>
     <row r="1874" spans="1:16">
       <c r="A1874" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1874" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C1874">
-        <v>0.7126590616726931</v>
+        <v>0.6665846755195202</v>
       </c>
       <c r="D1874" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E1874">
-        <v>0.7955598241332367</v>
+        <v>0.9742521665339288</v>
       </c>
       <c r="F1874">
         <v>1</v>
       </c>
       <c r="G1874">
-        <v>0.006627340938327307</v>
+        <v>0.008073415324480481</v>
       </c>
       <c r="H1874">
-        <v>0.006524440175866763</v>
+        <v>0.009065747833466069</v>
       </c>
       <c r="I1874">
-        <v>0.08290076246054356</v>
+        <v>0.3076674910144086</v>
       </c>
       <c r="J1874">
-        <v>0.7741730205045306</v>
+        <v>0.7780284295127059</v>
       </c>
       <c r="K1874">
-        <v>3.82</v>
+        <v>4.76</v>
       </c>
       <c r="L1874">
-        <v>3.67</v>
+        <v>4.37</v>
       </c>
       <c r="M1874">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="N1874">
-        <v>3.66</v>
+        <v>5.02</v>
       </c>
       <c r="O1874">
         <v>1</v>
       </c>
       <c r="P1874" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="1875" spans="1:16">
       <c r="A1875" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1875" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C1875">
-        <v>0.6665846755195202</v>
+        <v>0.6809789896169787</v>
       </c>
       <c r="D1875" t="s">
         <v>440</v>
@@ -95909,22 +95909,22 @@
         <v>1</v>
       </c>
       <c r="G1875">
-        <v>0.008073415324480481</v>
+        <v>0.008399021010383022</v>
       </c>
       <c r="H1875">
         <v>0.009065747833466069</v>
       </c>
       <c r="I1875">
-        <v>0.3076674910144086</v>
+        <v>0.2932731769169501</v>
       </c>
       <c r="J1875">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1875">
-        <v>4.76</v>
+        <v>4.96</v>
       </c>
       <c r="L1875">
-        <v>4.37</v>
+        <v>4.54</v>
       </c>
       <c r="M1875">
         <v>5.2</v>
@@ -95941,13 +95941,13 @@
     </row>
     <row r="1876" spans="1:16">
       <c r="A1876" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1876" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C1876">
-        <v>0.6809789896169787</v>
+        <v>0.7043198425023602</v>
       </c>
       <c r="D1876" t="s">
         <v>440</v>
@@ -95959,19 +95959,19 @@
         <v>1</v>
       </c>
       <c r="G1876">
-        <v>0.008399021010383022</v>
+        <v>0.008375680157497642</v>
       </c>
       <c r="H1876">
         <v>0.009065747833466069</v>
       </c>
       <c r="I1876">
-        <v>0.2932731769169501</v>
+        <v>0.2699323240315685</v>
       </c>
       <c r="J1876">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1876">
-        <v>4.96</v>
+        <v>4.93</v>
       </c>
       <c r="L1876">
         <v>4.54</v>
@@ -95991,46 +95991,46 @@
     </row>
     <row r="1877" spans="1:16">
       <c r="A1877" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1877" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C1877">
-        <v>0.7043198425023602</v>
+        <v>1.313846110723346</v>
       </c>
       <c r="D1877" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E1877">
-        <v>0.9742521665339288</v>
+        <v>0.9045905463760819</v>
       </c>
       <c r="F1877">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1877">
-        <v>0.008375680157497642</v>
+        <v>0.01192615388927666</v>
       </c>
       <c r="H1877">
-        <v>0.009065747833466069</v>
+        <v>0.006895409453623918</v>
       </c>
       <c r="I1877">
-        <v>0.2699323240315685</v>
+        <v>0.409255564347264</v>
       </c>
       <c r="J1877">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1877">
-        <v>4.93</v>
+        <v>6.82</v>
       </c>
       <c r="L1877">
-        <v>4.54</v>
+        <v>6.62</v>
       </c>
       <c r="M1877">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="N1877">
-        <v>5.02</v>
+        <v>3.9</v>
       </c>
       <c r="O1877">
         <v>1</v>
@@ -96041,13 +96041,13 @@
     </row>
     <row r="1878" spans="1:16">
       <c r="A1878" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1878" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C1878">
-        <v>1.313846110723346</v>
+        <v>1.210708285743256</v>
       </c>
       <c r="D1878" t="s">
         <v>443</v>
@@ -96059,22 +96059,22 @@
         <v>-1</v>
       </c>
       <c r="G1878">
-        <v>0.01192615388927666</v>
+        <v>0.01060929171425675</v>
       </c>
       <c r="H1878">
         <v>0.006895409453623918</v>
       </c>
       <c r="I1878">
-        <v>0.409255564347264</v>
+        <v>0.3061177393671741</v>
       </c>
       <c r="J1878">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1878">
-        <v>6.82</v>
+        <v>6.04</v>
       </c>
       <c r="L1878">
-        <v>6.62</v>
+        <v>5.91</v>
       </c>
       <c r="M1878">
         <v>3.85</v>
@@ -96091,13 +96091,13 @@
     </row>
     <row r="1879" spans="1:16">
       <c r="A1879" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1879" t="s">
         <v>257</v>
       </c>
       <c r="C1879">
-        <v>1.210708285743256</v>
+        <v>1.204432635783077</v>
       </c>
       <c r="D1879" t="s">
         <v>443</v>
@@ -96109,22 +96109,22 @@
         <v>-1</v>
       </c>
       <c r="G1879">
-        <v>0.01060929171425675</v>
+        <v>0.008175567364216924</v>
       </c>
       <c r="H1879">
         <v>0.006895409453623918</v>
       </c>
       <c r="I1879">
-        <v>0.3061177393671741</v>
+        <v>0.2998420894069955</v>
       </c>
       <c r="J1879">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1879">
-        <v>6.04</v>
+        <v>4.48</v>
       </c>
       <c r="L1879">
-        <v>5.91</v>
+        <v>4.69</v>
       </c>
       <c r="M1879">
         <v>3.85</v>
@@ -96141,13 +96141,13 @@
     </row>
     <row r="1880" spans="1:16">
       <c r="A1880" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1880" t="s">
         <v>258</v>
       </c>
       <c r="C1880">
-        <v>1.204432635783077</v>
+        <v>1.139970645717188</v>
       </c>
       <c r="D1880" t="s">
         <v>443</v>
@@ -96159,22 +96159,22 @@
         <v>-1</v>
       </c>
       <c r="G1880">
-        <v>0.008175567364216924</v>
+        <v>0.008220029354282812</v>
       </c>
       <c r="H1880">
         <v>0.006895409453623918</v>
       </c>
       <c r="I1880">
-        <v>0.2998420894069955</v>
+        <v>0.2353800993411062</v>
       </c>
       <c r="J1880">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1880">
-        <v>4.48</v>
+        <v>4.55</v>
       </c>
       <c r="L1880">
-        <v>4.69</v>
+        <v>4.68</v>
       </c>
       <c r="M1880">
         <v>3.85</v>
@@ -96191,46 +96191,46 @@
     </row>
     <row r="1881" spans="1:16">
       <c r="A1881" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1881" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C1881">
-        <v>1.139970645717188</v>
+        <v>0.6979313992614635</v>
       </c>
       <c r="D1881" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E1881">
-        <v>0.9045905463760819</v>
+        <v>0.7346356636883691</v>
       </c>
       <c r="F1881">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1881">
-        <v>0.008220029354282812</v>
+        <v>0.006642068600738536</v>
       </c>
       <c r="H1881">
-        <v>0.006895409453623918</v>
+        <v>0.006445364336311631</v>
       </c>
       <c r="I1881">
-        <v>0.2353800993411062</v>
+        <v>0.03670426442690555</v>
       </c>
       <c r="J1881">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1881">
-        <v>4.55</v>
+        <v>3.82</v>
       </c>
       <c r="L1881">
-        <v>4.68</v>
+        <v>3.67</v>
       </c>
       <c r="M1881">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="N1881">
-        <v>3.9</v>
+        <v>3.59</v>
       </c>
       <c r="O1881">
         <v>1</v>
@@ -96241,63 +96241,63 @@
     </row>
     <row r="1882" spans="1:16">
       <c r="A1882" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1882" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C1882">
-        <v>0.6979313992614635</v>
+        <v>0.6227397035253315</v>
       </c>
       <c r="D1882" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E1882">
-        <v>0.7812948108029882</v>
+        <v>0.9263542979688486</v>
       </c>
       <c r="F1882">
         <v>1</v>
       </c>
       <c r="G1882">
-        <v>0.006642068600738536</v>
+        <v>0.008117260296474669</v>
       </c>
       <c r="H1882">
-        <v>0.006538705189197012</v>
+        <v>0.00911364570203115</v>
       </c>
       <c r="I1882">
-        <v>0.08336341154152471</v>
+        <v>0.3036145944435171</v>
       </c>
       <c r="J1882">
-        <v>0.7780284295127059</v>
+        <v>0.7872395580829136</v>
       </c>
       <c r="K1882">
-        <v>3.82</v>
+        <v>4.76</v>
       </c>
       <c r="L1882">
-        <v>3.67</v>
+        <v>4.37</v>
       </c>
       <c r="M1882">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="N1882">
-        <v>3.66</v>
+        <v>5.02</v>
       </c>
       <c r="O1882">
         <v>1</v>
       </c>
       <c r="P1882" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="1883" spans="1:16">
       <c r="A1883" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1883" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C1883">
-        <v>0.6227397035253315</v>
+        <v>0.6352917919087488</v>
       </c>
       <c r="D1883" t="s">
         <v>440</v>
@@ -96309,22 +96309,22 @@
         <v>1</v>
       </c>
       <c r="G1883">
-        <v>0.008117260296474669</v>
+        <v>0.008444708208091251</v>
       </c>
       <c r="H1883">
         <v>0.00911364570203115</v>
       </c>
       <c r="I1883">
-        <v>0.3036145944435171</v>
+        <v>0.2910625060600998</v>
       </c>
       <c r="J1883">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1883">
-        <v>4.76</v>
+        <v>4.96</v>
       </c>
       <c r="L1883">
-        <v>4.37</v>
+        <v>4.54</v>
       </c>
       <c r="M1883">
         <v>5.2</v>
@@ -96341,13 +96341,13 @@
     </row>
     <row r="1884" spans="1:16">
       <c r="A1884" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1884" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C1884">
-        <v>0.6352917919087488</v>
+        <v>0.6589089786512363</v>
       </c>
       <c r="D1884" t="s">
         <v>440</v>
@@ -96359,19 +96359,19 @@
         <v>1</v>
       </c>
       <c r="G1884">
-        <v>0.008444708208091251</v>
+        <v>0.008421091021348763</v>
       </c>
       <c r="H1884">
         <v>0.00911364570203115</v>
       </c>
       <c r="I1884">
-        <v>0.2910625060600998</v>
+        <v>0.2674453193176123</v>
       </c>
       <c r="J1884">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1884">
-        <v>4.96</v>
+        <v>4.93</v>
       </c>
       <c r="L1884">
         <v>4.54</v>
@@ -96391,46 +96391,46 @@
     </row>
     <row r="1885" spans="1:16">
       <c r="A1885" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1885" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C1885">
-        <v>0.6589089786512363</v>
+        <v>1.251026213874529</v>
       </c>
       <c r="D1885" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E1885">
-        <v>0.9263542979688486</v>
+        <v>0.8691277013807825</v>
       </c>
       <c r="F1885">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1885">
-        <v>0.008421091021348763</v>
+        <v>0.01198897378612547</v>
       </c>
       <c r="H1885">
-        <v>0.00911364570203115</v>
+        <v>0.006930872298619217</v>
       </c>
       <c r="I1885">
-        <v>0.2674453193176123</v>
+        <v>0.3818985124937466</v>
       </c>
       <c r="J1885">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1885">
-        <v>4.93</v>
+        <v>6.82</v>
       </c>
       <c r="L1885">
-        <v>4.54</v>
+        <v>6.62</v>
       </c>
       <c r="M1885">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="N1885">
-        <v>5.02</v>
+        <v>3.9</v>
       </c>
       <c r="O1885">
         <v>1</v>
@@ -96441,13 +96441,13 @@
     </row>
     <row r="1886" spans="1:16">
       <c r="A1886" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1886" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C1886">
-        <v>1.251026213874529</v>
+        <v>1.155073069179202</v>
       </c>
       <c r="D1886" t="s">
         <v>443</v>
@@ -96459,22 +96459,22 @@
         <v>-1</v>
       </c>
       <c r="G1886">
-        <v>0.01198897378612547</v>
+        <v>0.0106649269308208</v>
       </c>
       <c r="H1886">
         <v>0.006930872298619217</v>
       </c>
       <c r="I1886">
-        <v>0.3818985124937466</v>
+        <v>0.2859453677984192</v>
       </c>
       <c r="J1886">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1886">
-        <v>6.82</v>
+        <v>6.04</v>
       </c>
       <c r="L1886">
-        <v>6.62</v>
+        <v>5.91</v>
       </c>
       <c r="M1886">
         <v>3.85</v>
@@ -96491,13 +96491,13 @@
     </row>
     <row r="1887" spans="1:16">
       <c r="A1887" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1887" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C1887">
-        <v>1.247838695694227</v>
+        <v>1.163166779788547</v>
       </c>
       <c r="D1887" t="s">
         <v>443</v>
@@ -96509,22 +96509,22 @@
         <v>-1</v>
       </c>
       <c r="G1887">
-        <v>0.01085216130430577</v>
+        <v>0.008216833220211455</v>
       </c>
       <c r="H1887">
         <v>0.006930872298619217</v>
       </c>
       <c r="I1887">
-        <v>0.3787109943134448</v>
+        <v>0.2940390784077649</v>
       </c>
       <c r="J1887">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1887">
-        <v>6.1</v>
+        <v>4.48</v>
       </c>
       <c r="L1887">
-        <v>6.05</v>
+        <v>4.69</v>
       </c>
       <c r="M1887">
         <v>3.85</v>
@@ -96541,13 +96541,13 @@
     </row>
     <row r="1888" spans="1:16">
       <c r="A1888" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1888" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1888">
-        <v>1.155073069179202</v>
+        <v>1.098060010722743</v>
       </c>
       <c r="D1888" t="s">
         <v>443</v>
@@ -96559,22 +96559,22 @@
         <v>-1</v>
       </c>
       <c r="G1888">
-        <v>0.0106649269308208</v>
+        <v>0.008261939989277255</v>
       </c>
       <c r="H1888">
         <v>0.006930872298619217</v>
       </c>
       <c r="I1888">
-        <v>0.2859453677984192</v>
+        <v>0.2289323093419604</v>
       </c>
       <c r="J1888">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1888">
-        <v>6.04</v>
+        <v>4.55</v>
       </c>
       <c r="L1888">
-        <v>5.91</v>
+        <v>4.68</v>
       </c>
       <c r="M1888">
         <v>3.85</v>
@@ -96591,46 +96591,46 @@
     </row>
     <row r="1889" spans="1:16">
       <c r="A1889" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1889" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C1889">
-        <v>1.163166779788547</v>
+        <v>0.66274488812327</v>
       </c>
       <c r="D1889" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E1889">
-        <v>0.8691277013807825</v>
+        <v>0.7008308218357073</v>
       </c>
       <c r="F1889">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1889">
-        <v>0.008216833220211455</v>
+        <v>0.00667725511187673</v>
       </c>
       <c r="H1889">
-        <v>0.006930872298619217</v>
+        <v>0.006479169178164293</v>
       </c>
       <c r="I1889">
-        <v>0.2940390784077649</v>
+        <v>0.03808593371243729</v>
       </c>
       <c r="J1889">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1889">
-        <v>4.48</v>
+        <v>3.82</v>
       </c>
       <c r="L1889">
-        <v>4.69</v>
+        <v>3.67</v>
       </c>
       <c r="M1889">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="N1889">
-        <v>3.9</v>
+        <v>3.59</v>
       </c>
       <c r="O1889">
         <v>1</v>
@@ -96641,113 +96641,113 @@
     </row>
     <row r="1890" spans="1:16">
       <c r="A1890" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1890" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C1890">
-        <v>1.098060010722743</v>
+        <v>0.5854580999890051</v>
       </c>
       <c r="D1890" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E1890">
-        <v>0.8691277013807825</v>
+        <v>0.8856264957863074</v>
       </c>
       <c r="F1890">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1890">
-        <v>0.008261939989277255</v>
+        <v>0.008154541900010996</v>
       </c>
       <c r="H1890">
-        <v>0.006930872298619217</v>
+        <v>0.00915437350421369</v>
       </c>
       <c r="I1890">
-        <v>0.2289323093419604</v>
+        <v>0.3001683957973023</v>
       </c>
       <c r="J1890">
-        <v>0.7872395580829136</v>
+        <v>0.7950718277334023</v>
       </c>
       <c r="K1890">
-        <v>4.55</v>
+        <v>4.76</v>
       </c>
       <c r="L1890">
-        <v>4.68</v>
+        <v>4.37</v>
       </c>
       <c r="M1890">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="N1890">
-        <v>3.9</v>
+        <v>5.02</v>
       </c>
       <c r="O1890">
         <v>1</v>
       </c>
       <c r="P1890" t="s">
-        <v>426</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1891" spans="1:16">
       <c r="A1891" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B1891" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C1891">
-        <v>0.66274488812327</v>
+        <v>0.5964437344423246</v>
       </c>
       <c r="D1891" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E1891">
-        <v>0.7472136350932197</v>
+        <v>0.8856264957863074</v>
       </c>
       <c r="F1891">
         <v>1</v>
       </c>
       <c r="G1891">
-        <v>0.00667725511187673</v>
+        <v>0.008483556265557676</v>
       </c>
       <c r="H1891">
-        <v>0.006572786364906781</v>
+        <v>0.00915437350421369</v>
       </c>
       <c r="I1891">
-        <v>0.08446874696994966</v>
+        <v>0.2891827613439828</v>
       </c>
       <c r="J1891">
-        <v>0.7872395580829136</v>
+        <v>0.7950718277334023</v>
       </c>
       <c r="K1891">
-        <v>3.82</v>
+        <v>4.96</v>
       </c>
       <c r="L1891">
-        <v>3.67</v>
+        <v>4.54</v>
       </c>
       <c r="M1891">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="N1891">
-        <v>3.66</v>
+        <v>5.02</v>
       </c>
       <c r="O1891">
         <v>1</v>
       </c>
       <c r="P1891" t="s">
-        <v>426</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1892" spans="1:16">
       <c r="A1892" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1892" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C1892">
-        <v>0.5854580999890051</v>
+        <v>0.6202958892743267</v>
       </c>
       <c r="D1892" t="s">
         <v>440</v>
@@ -96759,22 +96759,22 @@
         <v>1</v>
       </c>
       <c r="G1892">
-        <v>0.008154541900010996</v>
+        <v>0.008459704110725675</v>
       </c>
       <c r="H1892">
         <v>0.00915437350421369</v>
       </c>
       <c r="I1892">
-        <v>0.3001683957973023</v>
+        <v>0.2653306065119807</v>
       </c>
       <c r="J1892">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1892">
-        <v>4.76</v>
+        <v>4.93</v>
       </c>
       <c r="L1892">
-        <v>4.37</v>
+        <v>4.54</v>
       </c>
       <c r="M1892">
         <v>5.2</v>
@@ -96791,46 +96791,46 @@
     </row>
     <row r="1893" spans="1:16">
       <c r="A1893" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1893" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C1893">
-        <v>0.5964437344423246</v>
+        <v>1.197610134858196</v>
       </c>
       <c r="D1893" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E1893">
-        <v>0.8856264957863074</v>
+        <v>0.838973463226401</v>
       </c>
       <c r="F1893">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1893">
-        <v>0.008483556265557676</v>
+        <v>0.0120423898651418</v>
       </c>
       <c r="H1893">
-        <v>0.00915437350421369</v>
+        <v>0.006961026536773598</v>
       </c>
       <c r="I1893">
-        <v>0.2891827613439828</v>
+        <v>0.3586366716317948</v>
       </c>
       <c r="J1893">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1893">
-        <v>4.96</v>
+        <v>6.82</v>
       </c>
       <c r="L1893">
-        <v>4.54</v>
+        <v>6.62</v>
       </c>
       <c r="M1893">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="N1893">
-        <v>5.02</v>
+        <v>3.9</v>
       </c>
       <c r="O1893">
         <v>1</v>
@@ -96841,46 +96841,46 @@
     </row>
     <row r="1894" spans="1:16">
       <c r="A1894" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1894" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C1894">
-        <v>0.6202958892743267</v>
+        <v>1.200061850826246</v>
       </c>
       <c r="D1894" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E1894">
-        <v>0.8856264957863074</v>
+        <v>0.838973463226401</v>
       </c>
       <c r="F1894">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1894">
-        <v>0.008459704110725675</v>
+        <v>0.01089993814917375</v>
       </c>
       <c r="H1894">
-        <v>0.00915437350421369</v>
+        <v>0.006961026536773598</v>
       </c>
       <c r="I1894">
-        <v>0.2653306065119807</v>
+        <v>0.3610883875998447</v>
       </c>
       <c r="J1894">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1894">
-        <v>4.93</v>
+        <v>6.1</v>
       </c>
       <c r="L1894">
-        <v>4.54</v>
+        <v>6.05</v>
       </c>
       <c r="M1894">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="N1894">
-        <v>5.02</v>
+        <v>3.9</v>
       </c>
       <c r="O1894">
         <v>1</v>
@@ -96891,13 +96891,13 @@
     </row>
     <row r="1895" spans="1:16">
       <c r="A1895" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1895" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C1895">
-        <v>1.197610134858196</v>
+        <v>1.10776616049025</v>
       </c>
       <c r="D1895" t="s">
         <v>443</v>
@@ -96909,22 +96909,22 @@
         <v>-1</v>
       </c>
       <c r="G1895">
-        <v>0.0120423898651418</v>
+        <v>0.01071223383950975</v>
       </c>
       <c r="H1895">
         <v>0.006961026536773598</v>
       </c>
       <c r="I1895">
-        <v>0.3586366716317948</v>
+        <v>0.2687926972638492</v>
       </c>
       <c r="J1895">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1895">
-        <v>6.82</v>
+        <v>6.04</v>
       </c>
       <c r="L1895">
-        <v>6.62</v>
+        <v>5.91</v>
       </c>
       <c r="M1895">
         <v>3.85</v>
@@ -96941,13 +96941,13 @@
     </row>
     <row r="1896" spans="1:16">
       <c r="A1896" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1896" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C1896">
-        <v>1.200061850826246</v>
+        <v>1.128078211754358</v>
       </c>
       <c r="D1896" t="s">
         <v>443</v>
@@ -96959,22 +96959,22 @@
         <v>-1</v>
       </c>
       <c r="G1896">
-        <v>0.01089993814917375</v>
+        <v>0.008251921788245643</v>
       </c>
       <c r="H1896">
         <v>0.006961026536773598</v>
       </c>
       <c r="I1896">
-        <v>0.3610883875998447</v>
+        <v>0.2891047485279565</v>
       </c>
       <c r="J1896">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1896">
-        <v>6.1</v>
+        <v>4.48</v>
       </c>
       <c r="L1896">
-        <v>6.05</v>
+        <v>4.69</v>
       </c>
       <c r="M1896">
         <v>3.85</v>
@@ -96991,13 +96991,13 @@
     </row>
     <row r="1897" spans="1:16">
       <c r="A1897" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1897" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1897">
-        <v>1.10776616049025</v>
+        <v>1.062423183813019</v>
       </c>
       <c r="D1897" t="s">
         <v>443</v>
@@ -97009,22 +97009,22 @@
         <v>-1</v>
       </c>
       <c r="G1897">
-        <v>0.01071223383950975</v>
+        <v>0.00829757681618698</v>
       </c>
       <c r="H1897">
         <v>0.006961026536773598</v>
       </c>
       <c r="I1897">
-        <v>0.2687926972638492</v>
+        <v>0.2234497205866184</v>
       </c>
       <c r="J1897">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1897">
-        <v>6.04</v>
+        <v>4.55</v>
       </c>
       <c r="L1897">
-        <v>5.91</v>
+        <v>4.68</v>
       </c>
       <c r="M1897">
         <v>3.85</v>
@@ -97041,46 +97041,46 @@
     </row>
     <row r="1898" spans="1:16">
       <c r="A1898" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B1898" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C1898">
-        <v>1.128078211754358</v>
+        <v>0.6328256180584031</v>
       </c>
       <c r="D1898" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E1898">
-        <v>0.838973463226401</v>
+        <v>0.6720863922184135</v>
       </c>
       <c r="F1898">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1898">
-        <v>0.008251921788245643</v>
+        <v>0.006707174381941597</v>
       </c>
       <c r="H1898">
-        <v>0.006961026536773598</v>
+        <v>0.006507913607781586</v>
       </c>
       <c r="I1898">
-        <v>0.2891047485279565</v>
+        <v>0.03926077416001039</v>
       </c>
       <c r="J1898">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1898">
-        <v>4.48</v>
+        <v>3.82</v>
       </c>
       <c r="L1898">
-        <v>4.69</v>
+        <v>3.67</v>
       </c>
       <c r="M1898">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="N1898">
-        <v>3.9</v>
+        <v>3.59</v>
       </c>
       <c r="O1898">
         <v>1</v>
@@ -97091,113 +97091,113 @@
     </row>
     <row r="1899" spans="1:16">
       <c r="A1899" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1899" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C1899">
-        <v>1.062423183813019</v>
+        <v>0.5696561779646796</v>
       </c>
       <c r="D1899" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E1899">
-        <v>0.838973463226401</v>
+        <v>0.8683638918941865</v>
       </c>
       <c r="F1899">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1899">
-        <v>0.00829757681618698</v>
+        <v>0.00817034382203532</v>
       </c>
       <c r="H1899">
-        <v>0.006961026536773598</v>
+        <v>0.009171636108105811</v>
       </c>
       <c r="I1899">
-        <v>0.2234497205866184</v>
+        <v>0.2987077139295069</v>
       </c>
       <c r="J1899">
-        <v>0.7950718277334023</v>
+        <v>0.7983915592511178</v>
       </c>
       <c r="K1899">
-        <v>4.55</v>
+        <v>4.76</v>
       </c>
       <c r="L1899">
-        <v>4.68</v>
+        <v>4.37</v>
       </c>
       <c r="M1899">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="N1899">
-        <v>3.9</v>
+        <v>5.02</v>
       </c>
       <c r="O1899">
         <v>1</v>
       </c>
       <c r="P1899" t="s">
-        <v>225</v>
+        <v>428</v>
       </c>
     </row>
     <row r="1900" spans="1:16">
       <c r="A1900" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B1900" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C1900">
-        <v>0.6328256180584031</v>
+        <v>0.5799778661144557</v>
       </c>
       <c r="D1900" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E1900">
-        <v>0.7182342373864112</v>
+        <v>0.8683638918941865</v>
       </c>
       <c r="F1900">
         <v>1</v>
       </c>
       <c r="G1900">
-        <v>0.006707174381941597</v>
+        <v>0.008500022133885544</v>
       </c>
       <c r="H1900">
-        <v>0.006601765762613588</v>
+        <v>0.009171636108105811</v>
       </c>
       <c r="I1900">
-        <v>0.08540861932800814</v>
+        <v>0.2883860257797308</v>
       </c>
       <c r="J1900">
-        <v>0.7950718277334023</v>
+        <v>0.7983915592511178</v>
       </c>
       <c r="K1900">
-        <v>3.82</v>
+        <v>4.96</v>
       </c>
       <c r="L1900">
-        <v>3.67</v>
+        <v>4.54</v>
       </c>
       <c r="M1900">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="N1900">
-        <v>3.66</v>
+        <v>5.02</v>
       </c>
       <c r="O1900">
         <v>1</v>
       </c>
       <c r="P1900" t="s">
-        <v>225</v>
+        <v>428</v>
       </c>
     </row>
     <row r="1901" spans="1:16">
       <c r="A1901" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1901" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C1901">
-        <v>0.5696561779646796</v>
+        <v>0.6039296128919895</v>
       </c>
       <c r="D1901" t="s">
         <v>440</v>
@@ -97209,22 +97209,22 @@
         <v>1</v>
       </c>
       <c r="G1901">
-        <v>0.00817034382203532</v>
+        <v>0.008476070387108009</v>
       </c>
       <c r="H1901">
         <v>0.009171636108105811</v>
       </c>
       <c r="I1901">
-        <v>0.2987077139295069</v>
+        <v>0.264434279002197</v>
       </c>
       <c r="J1901">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1901">
-        <v>4.76</v>
+        <v>4.93</v>
       </c>
       <c r="L1901">
-        <v>4.37</v>
+        <v>4.54</v>
       </c>
       <c r="M1901">
         <v>5.2</v>
@@ -97241,46 +97241,46 @@
     </row>
     <row r="1902" spans="1:16">
       <c r="A1902" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1902" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C1902">
-        <v>0.5799778661144557</v>
+        <v>1.174969565907376</v>
       </c>
       <c r="D1902" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E1902">
-        <v>0.8683638918941865</v>
+        <v>0.8261924968831962</v>
       </c>
       <c r="F1902">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1902">
-        <v>0.008500022133885544</v>
+        <v>0.01206503043409262</v>
       </c>
       <c r="H1902">
-        <v>0.009171636108105811</v>
+        <v>0.006973807503116805</v>
       </c>
       <c r="I1902">
-        <v>0.2883860257797308</v>
+        <v>0.3487770690241798</v>
       </c>
       <c r="J1902">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1902">
-        <v>4.96</v>
+        <v>6.82</v>
       </c>
       <c r="L1902">
-        <v>4.54</v>
+        <v>6.62</v>
       </c>
       <c r="M1902">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="N1902">
-        <v>5.02</v>
+        <v>3.9</v>
       </c>
       <c r="O1902">
         <v>1</v>
@@ -97291,46 +97291,46 @@
     </row>
     <row r="1903" spans="1:16">
       <c r="A1903" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1903" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C1903">
-        <v>0.6039296128919895</v>
+        <v>1.179811488568181</v>
       </c>
       <c r="D1903" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E1903">
-        <v>0.8683638918941865</v>
+        <v>0.8261924968831962</v>
       </c>
       <c r="F1903">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1903">
-        <v>0.008476070387108009</v>
+        <v>0.01092018851143182</v>
       </c>
       <c r="H1903">
-        <v>0.009171636108105811</v>
+        <v>0.006973807503116805</v>
       </c>
       <c r="I1903">
-        <v>0.264434279002197</v>
+        <v>0.3536189916849852</v>
       </c>
       <c r="J1903">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1903">
-        <v>4.93</v>
+        <v>6.1</v>
       </c>
       <c r="L1903">
-        <v>4.54</v>
+        <v>6.05</v>
       </c>
       <c r="M1903">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="N1903">
-        <v>5.02</v>
+        <v>3.9</v>
       </c>
       <c r="O1903">
         <v>1</v>
@@ -97341,13 +97341,13 @@
     </row>
     <row r="1904" spans="1:16">
       <c r="A1904" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1904" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C1904">
-        <v>1.174969565907376</v>
+        <v>1.087714982123249</v>
       </c>
       <c r="D1904" t="s">
         <v>443</v>
@@ -97359,22 +97359,22 @@
         <v>-1</v>
       </c>
       <c r="G1904">
-        <v>0.01206503043409262</v>
+        <v>0.01073228501787675</v>
       </c>
       <c r="H1904">
         <v>0.006973807503116805</v>
       </c>
       <c r="I1904">
-        <v>0.3487770690241798</v>
+        <v>0.2615224852400524</v>
       </c>
       <c r="J1904">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1904">
-        <v>6.82</v>
+        <v>6.04</v>
       </c>
       <c r="L1904">
-        <v>6.62</v>
+        <v>5.91</v>
       </c>
       <c r="M1904">
         <v>3.85</v>
@@ -97391,13 +97391,13 @@
     </row>
     <row r="1905" spans="1:16">
       <c r="A1905" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1905" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C1905">
-        <v>1.179811488568181</v>
+        <v>1.113205814554992</v>
       </c>
       <c r="D1905" t="s">
         <v>443</v>
@@ -97409,22 +97409,22 @@
         <v>-1</v>
       </c>
       <c r="G1905">
-        <v>0.01092018851143182</v>
+        <v>0.008266794185445007</v>
       </c>
       <c r="H1905">
         <v>0.006973807503116805</v>
       </c>
       <c r="I1905">
-        <v>0.3536189916849852</v>
+        <v>0.2870133176717959</v>
       </c>
       <c r="J1905">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1905">
-        <v>6.1</v>
+        <v>4.48</v>
       </c>
       <c r="L1905">
-        <v>6.05</v>
+        <v>4.69</v>
       </c>
       <c r="M1905">
         <v>3.85</v>
@@ -97441,13 +97441,13 @@
     </row>
     <row r="1906" spans="1:16">
       <c r="A1906" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1906" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1906">
-        <v>1.087714982123249</v>
+        <v>1.047318405407414</v>
       </c>
       <c r="D1906" t="s">
         <v>443</v>
@@ -97459,22 +97459,22 @@
         <v>-1</v>
       </c>
       <c r="G1906">
-        <v>0.01073228501787675</v>
+        <v>0.008312681594592586</v>
       </c>
       <c r="H1906">
         <v>0.006973807503116805</v>
       </c>
       <c r="I1906">
-        <v>0.2615224852400524</v>
+        <v>0.2211259085242174</v>
       </c>
       <c r="J1906">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1906">
-        <v>6.04</v>
+        <v>4.55</v>
       </c>
       <c r="L1906">
-        <v>5.91</v>
+        <v>4.68</v>
       </c>
       <c r="M1906">
         <v>3.85</v>
@@ -97491,46 +97491,46 @@
     </row>
     <row r="1907" spans="1:16">
       <c r="A1907" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B1907" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C1907">
-        <v>1.113205814554992</v>
+        <v>0.6201442436607301</v>
       </c>
       <c r="D1907" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E1907">
-        <v>0.8261924968831962</v>
+        <v>0.6599029775483976</v>
       </c>
       <c r="F1907">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1907">
-        <v>0.008266794185445007</v>
+        <v>0.006719855756339269</v>
       </c>
       <c r="H1907">
-        <v>0.006973807503116805</v>
+        <v>0.006520097022451602</v>
       </c>
       <c r="I1907">
-        <v>0.2870133176717959</v>
+        <v>0.03975873388766749</v>
       </c>
       <c r="J1907">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1907">
-        <v>4.48</v>
+        <v>3.82</v>
       </c>
       <c r="L1907">
-        <v>4.69</v>
+        <v>3.67</v>
       </c>
       <c r="M1907">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="N1907">
-        <v>3.9</v>
+        <v>3.59</v>
       </c>
       <c r="O1907">
         <v>1</v>
@@ -97541,113 +97541,113 @@
     </row>
     <row r="1908" spans="1:16">
       <c r="A1908" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1908" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1908">
-        <v>1.047318405407414</v>
+        <v>0.580033038204439</v>
       </c>
       <c r="D1908" t="s">
-        <v>443</v>
+        <v>250</v>
       </c>
       <c r="E1908">
-        <v>0.8261924968831962</v>
+        <v>0.8773067240324215</v>
       </c>
       <c r="F1908">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1908">
-        <v>0.008312681594592586</v>
+        <v>0.00903996696179556</v>
       </c>
       <c r="H1908">
-        <v>0.006973807503116805</v>
+        <v>0.009582693275967578</v>
       </c>
       <c r="I1908">
-        <v>0.2211259085242174</v>
+        <v>0.2972736858279825</v>
       </c>
       <c r="J1908">
-        <v>0.7983915592511178</v>
+        <v>0.8181754278134546</v>
       </c>
       <c r="K1908">
-        <v>4.55</v>
+        <v>5.17</v>
       </c>
       <c r="L1908">
-        <v>4.68</v>
+        <v>4.81</v>
       </c>
       <c r="M1908">
-        <v>3.85</v>
+        <v>5.32</v>
       </c>
       <c r="N1908">
-        <v>3.9</v>
+        <v>5.23</v>
       </c>
       <c r="O1908">
         <v>1</v>
       </c>
       <c r="P1908" t="s">
-        <v>428</v>
+        <v>246</v>
       </c>
     </row>
     <row r="1909" spans="1:16">
       <c r="A1909" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B1909" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C1909">
-        <v>0.6201442436607301</v>
+        <v>0.4818498780452654</v>
       </c>
       <c r="D1909" t="s">
-        <v>444</v>
+        <v>250</v>
       </c>
       <c r="E1909">
-        <v>0.705951230770864</v>
+        <v>0.8773067240324215</v>
       </c>
       <c r="F1909">
         <v>1</v>
       </c>
       <c r="G1909">
-        <v>0.006719855756339269</v>
+        <v>0.008598150121954735</v>
       </c>
       <c r="H1909">
-        <v>0.006614048769229136</v>
+        <v>0.009582693275967578</v>
       </c>
       <c r="I1909">
-        <v>0.0858069871101339</v>
+        <v>0.3954568459871561</v>
       </c>
       <c r="J1909">
-        <v>0.7983915592511178</v>
+        <v>0.8181754278134546</v>
       </c>
       <c r="K1909">
-        <v>3.82</v>
+        <v>4.96</v>
       </c>
       <c r="L1909">
-        <v>3.67</v>
+        <v>4.54</v>
       </c>
       <c r="M1909">
-        <v>3.7</v>
+        <v>5.32</v>
       </c>
       <c r="N1909">
-        <v>3.66</v>
+        <v>5.23</v>
       </c>
       <c r="O1909">
         <v>1</v>
       </c>
       <c r="P1909" t="s">
-        <v>428</v>
+        <v>246</v>
       </c>
     </row>
     <row r="1910" spans="1:16">
       <c r="A1910" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1910" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C1910">
-        <v>0.580033038204439</v>
+        <v>0.5063951408796692</v>
       </c>
       <c r="D1910" t="s">
         <v>250</v>
@@ -97659,22 +97659,22 @@
         <v>1</v>
       </c>
       <c r="G1910">
-        <v>0.00903996696179556</v>
+        <v>0.008573604859120331</v>
       </c>
       <c r="H1910">
         <v>0.009582693275967578</v>
       </c>
       <c r="I1910">
-        <v>0.2972736858279825</v>
+        <v>0.3709115831527523</v>
       </c>
       <c r="J1910">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1910">
-        <v>5.17</v>
+        <v>4.93</v>
       </c>
       <c r="L1910">
-        <v>4.81</v>
+        <v>4.54</v>
       </c>
       <c r="M1910">
         <v>5.32</v>
@@ -97691,46 +97691,46 @@
     </row>
     <row r="1911" spans="1:16">
       <c r="A1911" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1911" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="C1911">
-        <v>0.4818498780452654</v>
+        <v>0.5518576103909849</v>
       </c>
       <c r="D1911" t="s">
-        <v>250</v>
+        <v>445</v>
       </c>
       <c r="E1911">
-        <v>0.8773067240324215</v>
+        <v>0.7845874392656027</v>
       </c>
       <c r="F1911">
         <v>1</v>
       </c>
       <c r="G1911">
-        <v>0.008598150121954735</v>
+        <v>0.01064814238960901</v>
       </c>
       <c r="H1911">
-        <v>0.009582693275967578</v>
+        <v>0.0115354125607344</v>
       </c>
       <c r="I1911">
-        <v>0.3954568459871561</v>
+        <v>0.2327298288746178</v>
       </c>
       <c r="J1911">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1911">
-        <v>4.96</v>
+        <v>6.17</v>
       </c>
       <c r="L1911">
-        <v>4.54</v>
+        <v>5.6</v>
       </c>
       <c r="M1911">
-        <v>5.32</v>
+        <v>6.57</v>
       </c>
       <c r="N1911">
-        <v>5.23</v>
+        <v>6.16</v>
       </c>
       <c r="O1911">
         <v>1</v>
@@ -97741,46 +97741,46 @@
     </row>
     <row r="1912" spans="1:16">
       <c r="A1912" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1912" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C1912">
-        <v>0.5063951408796692</v>
+        <v>1.059129890337926</v>
       </c>
       <c r="D1912" t="s">
-        <v>250</v>
+        <v>443</v>
       </c>
       <c r="E1912">
-        <v>0.8773067240324215</v>
+        <v>0.7500246029181996</v>
       </c>
       <c r="F1912">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1912">
-        <v>0.008573604859120331</v>
+        <v>0.01104087010966207</v>
       </c>
       <c r="H1912">
-        <v>0.009582693275967578</v>
+        <v>0.007049975397081801</v>
       </c>
       <c r="I1912">
-        <v>0.3709115831527523</v>
+        <v>0.3091052874197269</v>
       </c>
       <c r="J1912">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1912">
-        <v>4.93</v>
+        <v>6.1</v>
       </c>
       <c r="L1912">
-        <v>4.54</v>
+        <v>6.05</v>
       </c>
       <c r="M1912">
-        <v>5.32</v>
+        <v>3.85</v>
       </c>
       <c r="N1912">
-        <v>5.23</v>
+        <v>3.9</v>
       </c>
       <c r="O1912">
         <v>1</v>
@@ -97791,46 +97791,46 @@
     </row>
     <row r="1913" spans="1:16">
       <c r="A1913" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1913" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C1913">
-        <v>0.5518576103909849</v>
+        <v>0.9682204160067345</v>
       </c>
       <c r="D1913" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E1913">
-        <v>0.7845874392656027</v>
+        <v>0.7500246029181996</v>
       </c>
       <c r="F1913">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1913">
-        <v>0.01064814238960901</v>
+        <v>0.01085177958399327</v>
       </c>
       <c r="H1913">
-        <v>0.0115354125607344</v>
+        <v>0.007049975397081801</v>
       </c>
       <c r="I1913">
-        <v>0.2327298288746178</v>
+        <v>0.2181958130885349</v>
       </c>
       <c r="J1913">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1913">
-        <v>6.17</v>
+        <v>6.04</v>
       </c>
       <c r="L1913">
-        <v>5.6</v>
+        <v>5.91</v>
       </c>
       <c r="M1913">
-        <v>6.57</v>
+        <v>3.85</v>
       </c>
       <c r="N1913">
-        <v>6.16</v>
+        <v>3.9</v>
       </c>
       <c r="O1913">
         <v>1</v>
@@ -97841,13 +97841,13 @@
     </row>
     <row r="1914" spans="1:16">
       <c r="A1914" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1914" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C1914">
-        <v>1.059129890337926</v>
+        <v>1.024574083395723</v>
       </c>
       <c r="D1914" t="s">
         <v>443</v>
@@ -97859,22 +97859,22 @@
         <v>-1</v>
       </c>
       <c r="G1914">
-        <v>0.01104087010966207</v>
+        <v>0.008355425916604278</v>
       </c>
       <c r="H1914">
         <v>0.007049975397081801</v>
       </c>
       <c r="I1914">
-        <v>0.3091052874197269</v>
+        <v>0.2745494804775235</v>
       </c>
       <c r="J1914">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1914">
-        <v>6.1</v>
+        <v>4.48</v>
       </c>
       <c r="L1914">
-        <v>6.05</v>
+        <v>4.69</v>
       </c>
       <c r="M1914">
         <v>3.85</v>
@@ -97891,13 +97891,13 @@
     </row>
     <row r="1915" spans="1:16">
       <c r="A1915" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1915" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1915">
-        <v>0.9682204160067345</v>
+        <v>0.957301803448781</v>
       </c>
       <c r="D1915" t="s">
         <v>443</v>
@@ -97909,22 +97909,22 @@
         <v>-1</v>
       </c>
       <c r="G1915">
-        <v>0.01085177958399327</v>
+        <v>0.00840269819655122</v>
       </c>
       <c r="H1915">
         <v>0.007049975397081801</v>
       </c>
       <c r="I1915">
-        <v>0.2181958130885349</v>
+        <v>0.2072772005305814</v>
       </c>
       <c r="J1915">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1915">
-        <v>6.04</v>
+        <v>4.55</v>
       </c>
       <c r="L1915">
-        <v>5.91</v>
+        <v>4.68</v>
       </c>
       <c r="M1915">
         <v>3.85</v>
@@ -97941,46 +97941,46 @@
     </row>
     <row r="1916" spans="1:16">
       <c r="A1916" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B1916" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C1916">
-        <v>1.024574083395723</v>
+        <v>0.5445698657526035</v>
       </c>
       <c r="D1916" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E1916">
-        <v>0.7500246029181996</v>
+        <v>0.5872961799246212</v>
       </c>
       <c r="F1916">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1916">
-        <v>0.008355425916604278</v>
+        <v>0.006795430134247397</v>
       </c>
       <c r="H1916">
-        <v>0.007049975397081801</v>
+        <v>0.006592703820075378</v>
       </c>
       <c r="I1916">
-        <v>0.2745494804775235</v>
+        <v>0.04272631417201778</v>
       </c>
       <c r="J1916">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1916">
-        <v>4.48</v>
+        <v>3.82</v>
       </c>
       <c r="L1916">
-        <v>4.69</v>
+        <v>3.67</v>
       </c>
       <c r="M1916">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="N1916">
-        <v>3.9</v>
+        <v>3.59</v>
       </c>
       <c r="O1916">
         <v>1</v>
@@ -97991,146 +97991,146 @@
     </row>
     <row r="1917" spans="1:16">
       <c r="A1917" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1917" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C1917">
-        <v>0.957301803448781</v>
+        <v>0.4840236862109606</v>
       </c>
       <c r="D1917" t="s">
-        <v>443</v>
+        <v>256</v>
       </c>
       <c r="E1917">
-        <v>0.7500246029181996</v>
+        <v>0.8503069233264586</v>
       </c>
       <c r="F1917">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1917">
-        <v>0.00840269819655122</v>
+        <v>0.01063597631378904</v>
       </c>
       <c r="H1917">
-        <v>0.007049975397081801</v>
+        <v>0.01238969307667354</v>
       </c>
       <c r="I1917">
-        <v>0.2072772005305814</v>
+        <v>0.366283237115498</v>
       </c>
       <c r="J1917">
-        <v>0.8181754278134546</v>
+        <v>0.8459960522981732</v>
       </c>
       <c r="K1917">
-        <v>4.55</v>
+        <v>6</v>
       </c>
       <c r="L1917">
-        <v>4.68</v>
+        <v>5.56</v>
       </c>
       <c r="M1917">
-        <v>3.85</v>
+        <v>6.82</v>
       </c>
       <c r="N1917">
-        <v>3.9</v>
+        <v>6.62</v>
       </c>
       <c r="O1917">
         <v>1</v>
       </c>
       <c r="P1917" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1918" spans="1:16">
       <c r="A1918" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B1918" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1918">
-        <v>0.5445698657526035</v>
+        <v>0.8894240809811436</v>
       </c>
       <c r="D1918" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E1918">
-        <v>0.6327509170902177</v>
+        <v>1.045399620078079</v>
       </c>
       <c r="F1918">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1918">
-        <v>0.006795430134247397</v>
+        <v>0.01121057591901886</v>
       </c>
       <c r="H1918">
-        <v>0.006687249082909782</v>
+        <v>0.009454600379921921</v>
       </c>
       <c r="I1918">
-        <v>0.08818105133761422</v>
+        <v>-0.1559755390969357</v>
       </c>
       <c r="J1918">
-        <v>0.8181754278134546</v>
+        <v>0.8459960522981732</v>
       </c>
       <c r="K1918">
-        <v>3.82</v>
+        <v>6.1</v>
       </c>
       <c r="L1918">
-        <v>3.67</v>
+        <v>6.05</v>
       </c>
       <c r="M1918">
-        <v>3.7</v>
+        <v>4.97</v>
       </c>
       <c r="N1918">
-        <v>3.66</v>
+        <v>5.25</v>
       </c>
       <c r="O1918">
         <v>1</v>
       </c>
       <c r="P1918" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1919" spans="1:16">
       <c r="A1919" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1919" t="s">
         <v>265</v>
       </c>
       <c r="C1919">
-        <v>0.4840236862109606</v>
+        <v>1.019321514974956</v>
       </c>
       <c r="D1919" t="s">
-        <v>256</v>
+        <v>446</v>
       </c>
       <c r="E1919">
-        <v>0.8503069233264586</v>
+        <v>1.045399620078079</v>
       </c>
       <c r="F1919">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1919">
-        <v>0.01063597631378904</v>
+        <v>0.01024067848502504</v>
       </c>
       <c r="H1919">
-        <v>0.01238969307667354</v>
+        <v>0.009454600379921921</v>
       </c>
       <c r="I1919">
-        <v>0.366283237115498</v>
+        <v>-0.02607810510312358</v>
       </c>
       <c r="J1919">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1919">
-        <v>6</v>
+        <v>5.45</v>
       </c>
       <c r="L1919">
-        <v>5.56</v>
+        <v>5.63</v>
       </c>
       <c r="M1919">
-        <v>6.82</v>
+        <v>4.97</v>
       </c>
       <c r="N1919">
-        <v>6.62</v>
+        <v>5.25</v>
       </c>
       <c r="O1919">
         <v>1</v>
@@ -98141,46 +98141,46 @@
     </row>
     <row r="1920" spans="1:16">
       <c r="A1920" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1920" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C1920">
-        <v>0.8894240809811436</v>
+        <v>0.8999376857041841</v>
       </c>
       <c r="D1920" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1920">
-        <v>1.045399620078079</v>
+        <v>0.6852765408706545</v>
       </c>
       <c r="F1920">
         <v>-1</v>
       </c>
       <c r="G1920">
-        <v>0.01121057591901886</v>
+        <v>0.008480062314295817</v>
       </c>
       <c r="H1920">
-        <v>0.009454600379921921</v>
+        <v>0.007774723459129346</v>
       </c>
       <c r="I1920">
-        <v>-0.1559755390969357</v>
+        <v>0.2146611448335296</v>
       </c>
       <c r="J1920">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1920">
-        <v>6.1</v>
+        <v>4.48</v>
       </c>
       <c r="L1920">
-        <v>6.05</v>
+        <v>4.69</v>
       </c>
       <c r="M1920">
-        <v>4.97</v>
+        <v>4.19</v>
       </c>
       <c r="N1920">
-        <v>5.25</v>
+        <v>4.23</v>
       </c>
       <c r="O1920">
         <v>1</v>
@@ -98191,46 +98191,46 @@
     </row>
     <row r="1921" spans="1:16">
       <c r="A1921" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1921" t="s">
         <v>266</v>
       </c>
       <c r="C1921">
-        <v>1.019321514974956</v>
+        <v>0.8360978436122575</v>
       </c>
       <c r="D1921" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1921">
-        <v>1.045399620078079</v>
+        <v>0.6852765408706545</v>
       </c>
       <c r="F1921">
         <v>-1</v>
       </c>
       <c r="G1921">
-        <v>0.01024067848502504</v>
+        <v>0.008483902156387743</v>
       </c>
       <c r="H1921">
-        <v>0.009454600379921921</v>
+        <v>0.007774723459129346</v>
       </c>
       <c r="I1921">
-        <v>-0.02607810510312358</v>
+        <v>0.150821302741603</v>
       </c>
       <c r="J1921">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1921">
-        <v>5.45</v>
+        <v>4.52</v>
       </c>
       <c r="L1921">
-        <v>5.63</v>
+        <v>4.66</v>
       </c>
       <c r="M1921">
-        <v>4.97</v>
+        <v>4.19</v>
       </c>
       <c r="N1921">
-        <v>5.25</v>
+        <v>4.23</v>
       </c>
       <c r="O1921">
         <v>1</v>
@@ -98241,151 +98241,51 @@
     </row>
     <row r="1922" spans="1:16">
       <c r="A1922" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1922" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C1922">
-        <v>0.8999376857041841</v>
+        <v>0.5405948828358871</v>
       </c>
       <c r="D1922" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E1922">
-        <v>0.6852765408706545</v>
+        <v>0.4851944880657042</v>
       </c>
       <c r="F1922">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1922">
-        <v>0.008480062314295817</v>
+        <v>0.006919405117164113</v>
       </c>
       <c r="H1922">
-        <v>0.007774723459129346</v>
+        <v>0.006694805511934296</v>
       </c>
       <c r="I1922">
-        <v>0.2146611448335296</v>
+        <v>-0.05540039477018288</v>
       </c>
       <c r="J1922">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1922">
-        <v>4.48</v>
+        <v>3.77</v>
       </c>
       <c r="L1922">
-        <v>4.69</v>
+        <v>3.73</v>
       </c>
       <c r="M1922">
-        <v>4.19</v>
+        <v>3.67</v>
       </c>
       <c r="N1922">
-        <v>4.23</v>
+        <v>3.59</v>
       </c>
       <c r="O1922">
         <v>1</v>
       </c>
       <c r="P1922" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="1923" spans="1:16">
-      <c r="A1923" s="1">
-        <v>4</v>
-      </c>
-      <c r="B1923" t="s">
-        <v>259</v>
-      </c>
-      <c r="C1923">
-        <v>0.8360978436122575</v>
-      </c>
-      <c r="D1923" t="s">
-        <v>447</v>
-      </c>
-      <c r="E1923">
-        <v>0.6852765408706545</v>
-      </c>
-      <c r="F1923">
-        <v>-1</v>
-      </c>
-      <c r="G1923">
-        <v>0.008483902156387743</v>
-      </c>
-      <c r="H1923">
-        <v>0.007774723459129346</v>
-      </c>
-      <c r="I1923">
-        <v>0.150821302741603</v>
-      </c>
-      <c r="J1923">
-        <v>0.8459960522981732</v>
-      </c>
-      <c r="K1923">
-        <v>4.52</v>
-      </c>
-      <c r="L1923">
-        <v>4.66</v>
-      </c>
-      <c r="M1923">
-        <v>4.19</v>
-      </c>
-      <c r="N1923">
-        <v>4.23</v>
-      </c>
-      <c r="O1923">
-        <v>1</v>
-      </c>
-      <c r="P1923" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="1924" spans="1:16">
-      <c r="A1924" s="1">
-        <v>5</v>
-      </c>
-      <c r="B1924" t="s">
-        <v>267</v>
-      </c>
-      <c r="C1924">
-        <v>0.5405948828358871</v>
-      </c>
-      <c r="D1924" t="s">
-        <v>444</v>
-      </c>
-      <c r="E1924">
-        <v>0.529814606496759</v>
-      </c>
-      <c r="F1924">
-        <v>1</v>
-      </c>
-      <c r="G1924">
-        <v>0.006919405117164113</v>
-      </c>
-      <c r="H1924">
-        <v>0.006790185393503242</v>
-      </c>
-      <c r="I1924">
-        <v>-0.01078027633912804</v>
-      </c>
-      <c r="J1924">
-        <v>0.8459960522981732</v>
-      </c>
-      <c r="K1924">
-        <v>3.77</v>
-      </c>
-      <c r="L1924">
-        <v>3.73</v>
-      </c>
-      <c r="M1924">
-        <v>3.7</v>
-      </c>
-      <c r="N1924">
-        <v>3.66</v>
-      </c>
-      <c r="O1924">
-        <v>1</v>
-      </c>
-      <c r="P1924" t="s">
         <v>247</v>
       </c>
     </row>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -1348,7 +1348,7 @@
     <t>2021-11-04</t>
   </si>
   <si>
-    <t>2021-11-23</t>
+    <t>2021-11-24</t>
   </si>
   <si>
     <t>2021-09-07</t>
@@ -95803,7 +95803,7 @@
         <v>444</v>
       </c>
       <c r="E1873">
-        <v>0.8113677126979195</v>
+        <v>0.8800763637231457</v>
       </c>
       <c r="F1873">
         <v>1</v>
@@ -95812,10 +95812,10 @@
         <v>0.006627340938327307</v>
       </c>
       <c r="H1873">
-        <v>0.00664863228730208</v>
+        <v>0.006639923636276854</v>
       </c>
       <c r="I1873">
-        <v>0.09870865102522641</v>
+        <v>0.1674173020504526</v>
       </c>
       <c r="J1873">
         <v>0.7741730205045306</v>
@@ -95827,10 +95827,10 @@
         <v>3.67</v>
       </c>
       <c r="M1873">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="N1873">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="O1873">
         <v>1</v>
@@ -96153,7 +96153,7 @@
         <v>444</v>
       </c>
       <c r="E1880">
-        <v>0.7968328207370989</v>
+        <v>0.8657342422127337</v>
       </c>
       <c r="F1880">
         <v>1</v>
@@ -96162,10 +96162,10 @@
         <v>0.006642068600738536</v>
       </c>
       <c r="H1880">
-        <v>0.006663167179262901</v>
+        <v>0.006654265757787266</v>
       </c>
       <c r="I1880">
-        <v>0.09890142147563541</v>
+        <v>0.1678028429512701</v>
       </c>
       <c r="J1880">
         <v>0.7780284295127059</v>
@@ -96177,10 +96177,10 @@
         <v>3.67</v>
       </c>
       <c r="M1880">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="N1880">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="O1880">
         <v>1</v>
@@ -96553,7 +96553,7 @@
         <v>444</v>
       </c>
       <c r="E1888">
-        <v>0.7621068660274157</v>
+        <v>0.8314688439315612</v>
       </c>
       <c r="F1888">
         <v>1</v>
@@ -96562,10 +96562,10 @@
         <v>0.00667725511187673</v>
       </c>
       <c r="H1888">
-        <v>0.006697893133972585</v>
+        <v>0.006688531156068439</v>
       </c>
       <c r="I1888">
-        <v>0.09936197790414569</v>
+        <v>0.1687239558082911</v>
       </c>
       <c r="J1888">
         <v>0.7872395580829136</v>
@@ -96577,10 +96577,10 @@
         <v>3.67</v>
       </c>
       <c r="M1888">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="N1888">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="O1888">
         <v>1</v>
@@ -97003,7 +97003,7 @@
         <v>444</v>
       </c>
       <c r="E1897">
-        <v>0.7325792094450732</v>
+        <v>0.802332800831743</v>
       </c>
       <c r="F1897">
         <v>1</v>
@@ -97012,10 +97012,10 @@
         <v>0.006707174381941597</v>
       </c>
       <c r="H1897">
-        <v>0.006727420790554927</v>
+        <v>0.006717667199168257</v>
       </c>
       <c r="I1897">
-        <v>0.09975359138667006</v>
+        <v>0.1695071827733399</v>
       </c>
       <c r="J1897">
         <v>0.7950718277334023</v>
@@ -97027,10 +97027,10 @@
         <v>3.67</v>
       </c>
       <c r="M1897">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="N1897">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="O1897">
         <v>1</v>
@@ -97453,7 +97453,7 @@
         <v>444</v>
       </c>
       <c r="E1906">
-        <v>0.720063821623286</v>
+        <v>0.7899833995858412</v>
       </c>
       <c r="F1906">
         <v>1</v>
@@ -97462,10 +97462,10 @@
         <v>0.006719855756339269</v>
       </c>
       <c r="H1906">
-        <v>0.006739936178376715</v>
+        <v>0.006730016600414159</v>
       </c>
       <c r="I1906">
-        <v>0.09991957796255591</v>
+        <v>0.1698391559251111</v>
       </c>
       <c r="J1906">
         <v>0.7983915592511178</v>
@@ -97477,10 +97477,10 @@
         <v>3.67</v>
       </c>
       <c r="M1906">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="N1906">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="O1906">
         <v>1</v>
@@ -97953,7 +97953,7 @@
         <v>444</v>
       </c>
       <c r="E1916">
-        <v>0.6454786371432761</v>
+        <v>0.7163874085339486</v>
       </c>
       <c r="F1916">
         <v>1</v>
@@ -97962,10 +97962,10 @@
         <v>0.006795430134247397</v>
       </c>
       <c r="H1916">
-        <v>0.006814521362856723</v>
+        <v>0.00680361259146605</v>
       </c>
       <c r="I1916">
-        <v>0.1009087713906727</v>
+        <v>0.1718175427813451</v>
       </c>
       <c r="J1916">
         <v>0.8181754278134546</v>
@@ -97977,10 +97977,10 @@
         <v>3.67</v>
       </c>
       <c r="M1916">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="N1916">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="O1916">
         <v>1</v>
@@ -98003,7 +98003,7 @@
         <v>444</v>
       </c>
       <c r="E1917">
-        <v>0.6454786371432761</v>
+        <v>0.7163874085339486</v>
       </c>
       <c r="F1917">
         <v>1</v>
@@ -98012,10 +98012,10 @@
         <v>0.006637249082909783</v>
       </c>
       <c r="H1917">
-        <v>0.006814521362856723</v>
+        <v>0.00680361259146605</v>
       </c>
       <c r="I1917">
-        <v>0.06272772005305871</v>
+        <v>0.1336364914437311</v>
       </c>
       <c r="J1917">
         <v>0.8181754278134546</v>
@@ -98027,10 +98027,10 @@
         <v>3.61</v>
       </c>
       <c r="M1917">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="N1917">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="O1917">
         <v>1</v>
@@ -98353,7 +98353,7 @@
         <v>444</v>
       </c>
       <c r="E1924">
-        <v>0.5405948828358871</v>
+        <v>0.6128946854507955</v>
       </c>
       <c r="F1924">
         <v>1</v>
@@ -98362,10 +98362,10 @@
         <v>0.007136304525008839</v>
       </c>
       <c r="H1924">
-        <v>0.006919405117164113</v>
+        <v>0.006907105314549205</v>
       </c>
       <c r="I1924">
-        <v>0.03689940784472601</v>
+        <v>0.1091992104596344</v>
       </c>
       <c r="J1924">
         <v>0.8459960522981732</v>
@@ -98377,10 +98377,10 @@
         <v>3.82</v>
       </c>
       <c r="M1924">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="N1924">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="O1924">
         <v>1</v>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -790,16 +790,13 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-10-20</t>
+    <t>2021-10-19</t>
   </si>
   <si>
     <t>2021-11-12</t>
   </si>
   <si>
     <t>2021-09-16</t>
-  </si>
-  <si>
-    <t>2021-10-19</t>
   </si>
   <si>
     <t>2021-09-14</t>
@@ -818,6 +815,9 @@
   </si>
   <si>
     <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>2021-10-20</t>
   </si>
   <si>
     <t>2021-11-11</t>
@@ -1351,7 +1351,7 @@
     <t>2021-11-04</t>
   </si>
   <si>
-    <t>2021-11-25</t>
+    <t>2021-11-29</t>
   </si>
   <si>
     <t>2021-09-07</t>
@@ -87700,7 +87700,7 @@
         <v>2.431411491361336</v>
       </c>
       <c r="D1711" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E1711">
         <v>2.538213707664756</v>
@@ -87750,7 +87750,7 @@
         <v>2.532009684902152</v>
       </c>
       <c r="D1712" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E1712">
         <v>2.538213707664756</v>
@@ -87800,7 +87800,7 @@
         <v>2.427002049221179</v>
       </c>
       <c r="D1713" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E1713">
         <v>2.538213707664756</v>
@@ -87850,7 +87850,7 @@
         <v>2.549425366108334</v>
       </c>
       <c r="D1714" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E1714">
         <v>2.538213707664756</v>
@@ -95747,7 +95747,7 @@
         <v>258</v>
       </c>
       <c r="C1872">
-        <v>1.157512756704385</v>
+        <v>1.140095454653932</v>
       </c>
       <c r="D1872" t="s">
         <v>444</v>
@@ -95759,22 +95759,22 @@
         <v>-1</v>
       </c>
       <c r="G1872">
-        <v>0.008202487243295614</v>
+        <v>0.008339904545346067</v>
       </c>
       <c r="H1872">
         <v>0.006880566128942443</v>
       </c>
       <c r="I1872">
-        <v>0.2380788856468286</v>
+        <v>0.2206615835963754</v>
       </c>
       <c r="J1872">
         <v>0.7741730205045306</v>
       </c>
       <c r="K1872">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="L1872">
-        <v>4.68</v>
+        <v>4.74</v>
       </c>
       <c r="M1872">
         <v>3.85</v>
@@ -95803,7 +95803,7 @@
         <v>445</v>
       </c>
       <c r="E1873">
-        <v>0.8433015543382822</v>
+        <v>0.9294275074139615</v>
       </c>
       <c r="F1873">
         <v>1</v>
@@ -95812,10 +95812,10 @@
         <v>0.006627340938327307</v>
       </c>
       <c r="H1873">
-        <v>0.006556698445661718</v>
+        <v>0.006410572492586038</v>
       </c>
       <c r="I1873">
-        <v>0.1306424926655891</v>
+        <v>0.2167684457412684</v>
       </c>
       <c r="J1873">
         <v>0.7741730205045306</v>
@@ -95827,10 +95827,10 @@
         <v>3.67</v>
       </c>
       <c r="M1873">
-        <v>3.69</v>
+        <v>3.54</v>
       </c>
       <c r="N1873">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="O1873">
         <v>1</v>
@@ -96097,7 +96097,7 @@
         <v>258</v>
       </c>
       <c r="C1879">
-        <v>1.139970645717188</v>
+        <v>1.122167802765917</v>
       </c>
       <c r="D1879" t="s">
         <v>444</v>
@@ -96109,22 +96109,22 @@
         <v>-1</v>
       </c>
       <c r="G1879">
-        <v>0.008220029354282812</v>
+        <v>0.008357832197234084</v>
       </c>
       <c r="H1879">
         <v>0.006895409453623918</v>
       </c>
       <c r="I1879">
-        <v>0.2353800993411062</v>
+        <v>0.2175772563898355</v>
       </c>
       <c r="J1879">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1879">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="L1879">
-        <v>4.68</v>
+        <v>4.74</v>
       </c>
       <c r="M1879">
         <v>3.85</v>
@@ -96153,7 +96153,7 @@
         <v>445</v>
       </c>
       <c r="E1880">
-        <v>0.8290750950981156</v>
+        <v>0.915779359525021</v>
       </c>
       <c r="F1880">
         <v>1</v>
@@ -96162,10 +96162,10 @@
         <v>0.006642068600738536</v>
       </c>
       <c r="H1880">
-        <v>0.006570924904901885</v>
+        <v>0.006424220640474979</v>
       </c>
       <c r="I1880">
-        <v>0.1311436958366521</v>
+        <v>0.2178479602635575</v>
       </c>
       <c r="J1880">
         <v>0.7780284295127059</v>
@@ -96177,10 +96177,10 @@
         <v>3.67</v>
       </c>
       <c r="M1880">
-        <v>3.69</v>
+        <v>3.54</v>
       </c>
       <c r="N1880">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="O1880">
         <v>1</v>
@@ -96497,7 +96497,7 @@
         <v>258</v>
       </c>
       <c r="C1887">
-        <v>1.098060010722743</v>
+        <v>1.079336054914452</v>
       </c>
       <c r="D1887" t="s">
         <v>444</v>
@@ -96509,22 +96509,22 @@
         <v>-1</v>
       </c>
       <c r="G1887">
-        <v>0.008261939989277255</v>
+        <v>0.008400663945085549</v>
       </c>
       <c r="H1887">
         <v>0.006930872298619217</v>
       </c>
       <c r="I1887">
-        <v>0.2289323093419604</v>
+        <v>0.2102083535336692</v>
       </c>
       <c r="J1887">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1887">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="L1887">
-        <v>4.68</v>
+        <v>4.74</v>
       </c>
       <c r="M1887">
         <v>3.85</v>
@@ -96553,7 +96553,7 @@
         <v>445</v>
       </c>
       <c r="E1888">
-        <v>0.795086030674049</v>
+        <v>0.8831719643864857</v>
       </c>
       <c r="F1888">
         <v>1</v>
@@ -96562,10 +96562,10 @@
         <v>0.00667725511187673</v>
       </c>
       <c r="H1888">
-        <v>0.006604913969325951</v>
+        <v>0.006456828035613514</v>
       </c>
       <c r="I1888">
-        <v>0.132341142550779</v>
+        <v>0.2204270762632157</v>
       </c>
       <c r="J1888">
         <v>0.7872395580829136</v>
@@ -96577,10 +96577,10 @@
         <v>3.67</v>
       </c>
       <c r="M1888">
-        <v>3.69</v>
+        <v>3.54</v>
       </c>
       <c r="N1888">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="O1888">
         <v>1</v>
@@ -96894,7 +96894,7 @@
         <v>6</v>
       </c>
       <c r="B1895" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1895">
         <v>1.042916001039679</v>
@@ -96953,7 +96953,7 @@
         <v>445</v>
       </c>
       <c r="E1896">
-        <v>0.7661849556637454</v>
+        <v>0.8554457298237557</v>
       </c>
       <c r="F1896">
         <v>1</v>
@@ -96962,10 +96962,10 @@
         <v>0.006707174381941597</v>
       </c>
       <c r="H1896">
-        <v>0.006633815044336255</v>
+        <v>0.006484554270176244</v>
       </c>
       <c r="I1896">
-        <v>0.1333593376053424</v>
+        <v>0.2226201117653526</v>
       </c>
       <c r="J1896">
         <v>0.7950718277334023</v>
@@ -96977,10 +96977,10 @@
         <v>3.67</v>
       </c>
       <c r="M1896">
-        <v>3.69</v>
+        <v>3.54</v>
       </c>
       <c r="N1896">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="O1896">
         <v>1</v>
@@ -97194,7 +97194,7 @@
         <v>4</v>
       </c>
       <c r="B1901" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C1901">
         <v>1.179811488568181</v>
@@ -97344,7 +97344,7 @@
         <v>7</v>
       </c>
       <c r="B1904" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1904">
         <v>1.027479249482302</v>
@@ -97403,7 +97403,7 @@
         <v>445</v>
       </c>
       <c r="E1905">
-        <v>0.7539351463633754</v>
+        <v>0.8436938802510427</v>
       </c>
       <c r="F1905">
         <v>1</v>
@@ -97412,10 +97412,10 @@
         <v>0.006719855756339269</v>
       </c>
       <c r="H1905">
-        <v>0.006646064853636625</v>
+        <v>0.006496306119748958</v>
       </c>
       <c r="I1905">
-        <v>0.1337909027026454</v>
+        <v>0.2235496365903127</v>
       </c>
       <c r="J1905">
         <v>0.7983915592511178</v>
@@ -97427,10 +97427,10 @@
         <v>3.67</v>
       </c>
       <c r="M1905">
-        <v>3.69</v>
+        <v>3.54</v>
       </c>
       <c r="N1905">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="O1905">
         <v>1</v>
@@ -97444,7 +97444,7 @@
         <v>0</v>
       </c>
       <c r="B1906" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1906">
         <v>0.580033038204439</v>
@@ -97594,7 +97594,7 @@
         <v>3</v>
       </c>
       <c r="B1909" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C1909">
         <v>0.5518576103909849</v>
@@ -97694,7 +97694,7 @@
         <v>5</v>
       </c>
       <c r="B1911" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C1911">
         <v>1.059129890337926</v>
@@ -97847,7 +97847,7 @@
         <v>258</v>
       </c>
       <c r="C1914">
-        <v>0.957301803448781</v>
+        <v>0.9354842606674358</v>
       </c>
       <c r="D1914" t="s">
         <v>444</v>
@@ -97859,22 +97859,22 @@
         <v>-1</v>
       </c>
       <c r="G1914">
-        <v>0.00840269819655122</v>
+        <v>0.008544515739332565</v>
       </c>
       <c r="H1914">
         <v>0.007049975397081801</v>
       </c>
       <c r="I1914">
-        <v>0.2072772005305814</v>
+        <v>0.1854596577492362</v>
       </c>
       <c r="J1914">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1914">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="L1914">
-        <v>4.68</v>
+        <v>4.74</v>
       </c>
       <c r="M1914">
         <v>3.85</v>
@@ -97903,7 +97903,7 @@
         <v>445</v>
       </c>
       <c r="E1915">
-        <v>0.6809326713683528</v>
+        <v>0.7736589855403704</v>
       </c>
       <c r="F1915">
         <v>1</v>
@@ -97912,10 +97912,10 @@
         <v>0.006795430134247397</v>
       </c>
       <c r="H1915">
-        <v>0.006719067328631648</v>
+        <v>0.00656634101445963</v>
       </c>
       <c r="I1915">
-        <v>0.1363628056157493</v>
+        <v>0.2290891197877669</v>
       </c>
       <c r="J1915">
         <v>0.8181754278134546</v>
@@ -97927,10 +97927,10 @@
         <v>3.67</v>
       </c>
       <c r="M1915">
-        <v>3.69</v>
+        <v>3.54</v>
       </c>
       <c r="N1915">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="O1915">
         <v>1</v>
@@ -97944,7 +97944,7 @@
         <v>10</v>
       </c>
       <c r="B1916" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1916">
         <v>0.5827509170902174</v>
@@ -97953,7 +97953,7 @@
         <v>445</v>
       </c>
       <c r="E1916">
-        <v>0.6809326713683528</v>
+        <v>0.7736589855403704</v>
       </c>
       <c r="F1916">
         <v>1</v>
@@ -97962,10 +97962,10 @@
         <v>0.006637249082909783</v>
       </c>
       <c r="H1916">
-        <v>0.006719067328631648</v>
+        <v>0.00656634101445963</v>
       </c>
       <c r="I1916">
-        <v>0.09818175427813536</v>
+        <v>0.190908068450153</v>
       </c>
       <c r="J1916">
         <v>0.8181754278134546</v>
@@ -97977,10 +97977,10 @@
         <v>3.61</v>
       </c>
       <c r="M1916">
-        <v>3.69</v>
+        <v>3.54</v>
       </c>
       <c r="N1916">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="O1916">
         <v>1</v>
@@ -98044,7 +98044,7 @@
         <v>1</v>
       </c>
       <c r="B1918" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C1918">
         <v>0.4840236862109606</v>
@@ -98094,7 +98094,7 @@
         <v>2</v>
       </c>
       <c r="B1919" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C1919">
         <v>0.8894240809811436</v>
@@ -98144,7 +98144,7 @@
         <v>3</v>
       </c>
       <c r="B1920" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1920">
         <v>0.8278225019004131</v>
@@ -98244,7 +98244,7 @@
         <v>5</v>
       </c>
       <c r="B1922" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C1922">
         <v>0.8307179620433116</v>
@@ -98303,7 +98303,7 @@
         <v>445</v>
       </c>
       <c r="E1923">
-        <v>0.5782745670197409</v>
+        <v>0.675173974864467</v>
       </c>
       <c r="F1923">
         <v>1</v>
@@ -98312,10 +98312,10 @@
         <v>0.007136304525008839</v>
       </c>
       <c r="H1923">
-        <v>0.00682172543298026</v>
+        <v>0.006664826025135533</v>
       </c>
       <c r="I1923">
-        <v>0.07457909202857982</v>
+        <v>0.1714784998733059</v>
       </c>
       <c r="J1923">
         <v>0.8459960522981732</v>
@@ -98327,10 +98327,10 @@
         <v>3.82</v>
       </c>
       <c r="M1923">
-        <v>3.69</v>
+        <v>3.54</v>
       </c>
       <c r="N1923">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="O1923">
         <v>1</v>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -805,13 +805,13 @@
     <t>2021-09-14</t>
   </si>
   <si>
+    <t>2021-11-16</t>
+  </si>
+  <si>
     <t>2021-07-26</t>
   </si>
   <si>
     <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>2021-11-16</t>
   </si>
   <si>
     <t>2021-09-02</t>
@@ -87712,7 +87712,7 @@
         <v>2.431411491361336</v>
       </c>
       <c r="D1711" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E1711">
         <v>2.538213707664756</v>
@@ -87762,7 +87762,7 @@
         <v>2.532009684902152</v>
       </c>
       <c r="D1712" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E1712">
         <v>2.538213707664756</v>
@@ -87812,7 +87812,7 @@
         <v>2.427002049221179</v>
       </c>
       <c r="D1713" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E1713">
         <v>2.538213707664756</v>
@@ -87862,7 +87862,7 @@
         <v>2.549425366108334</v>
       </c>
       <c r="D1714" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E1714">
         <v>2.538213707664756</v>
@@ -96162,10 +96162,10 @@
         <v>0.6979313992614635</v>
       </c>
       <c r="D1880" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E1880">
-        <v>0.9224610652957832</v>
+        <v>1.00690049670553</v>
       </c>
       <c r="F1880">
         <v>1</v>
@@ -96174,10 +96174,10 @@
         <v>0.006642068600738536</v>
       </c>
       <c r="H1880">
-        <v>0.006337538934704217</v>
+        <v>0.006453099503294471</v>
       </c>
       <c r="I1880">
-        <v>0.2245296660343197</v>
+        <v>0.308969097444066</v>
       </c>
       <c r="J1880">
         <v>0.7780284295127059</v>
@@ -96189,10 +96189,10 @@
         <v>3.67</v>
       </c>
       <c r="M1880">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="N1880">
-        <v>3.63</v>
+        <v>3.73</v>
       </c>
       <c r="O1880">
         <v>1</v>
@@ -97506,10 +97506,10 @@
         <v>9</v>
       </c>
       <c r="B1907" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C1907">
-        <v>0.6559512307708637</v>
+        <v>0.6599029775483976</v>
       </c>
       <c r="D1907" t="s">
         <v>448</v>
@@ -97521,22 +97521,22 @@
         <v>1</v>
       </c>
       <c r="G1907">
-        <v>0.006564048769229136</v>
+        <v>0.006520097022451602</v>
       </c>
       <c r="H1907">
         <v>0.006496306119748958</v>
       </c>
       <c r="I1907">
-        <v>0.187742649480179</v>
+        <v>0.1837909027026452</v>
       </c>
       <c r="J1907">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1907">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="L1907">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="M1907">
         <v>3.54</v>
@@ -97556,16 +97556,16 @@
         <v>0</v>
       </c>
       <c r="B1908" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C1908">
         <v>0.580033038204439</v>
       </c>
       <c r="D1908" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="E1908">
-        <v>0.7654877753700351</v>
+        <v>0.331849878045265</v>
       </c>
       <c r="F1908">
         <v>1</v>
@@ -97574,10 +97574,10 @@
         <v>0.00903996696179556</v>
       </c>
       <c r="H1908">
-        <v>0.009274512224629964</v>
+        <v>0.008448150121954734</v>
       </c>
       <c r="I1908">
-        <v>0.1854547371655961</v>
+        <v>-0.248183160159174</v>
       </c>
       <c r="J1908">
         <v>0.8181754278134546</v>
@@ -97589,10 +97589,10 @@
         <v>4.81</v>
       </c>
       <c r="M1908">
-        <v>5.2</v>
+        <v>4.96</v>
       </c>
       <c r="N1908">
-        <v>5.02</v>
+        <v>4.39</v>
       </c>
       <c r="O1908">
         <v>1</v>
@@ -97612,10 +97612,10 @@
         <v>0.4818498780452654</v>
       </c>
       <c r="D1909" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="E1909">
-        <v>0.7654877753700351</v>
+        <v>0.331849878045265</v>
       </c>
       <c r="F1909">
         <v>1</v>
@@ -97624,10 +97624,10 @@
         <v>0.008598150121954735</v>
       </c>
       <c r="H1909">
-        <v>0.009274512224629964</v>
+        <v>0.008448150121954734</v>
       </c>
       <c r="I1909">
-        <v>0.2836378973247697</v>
+        <v>-0.1500000000000004</v>
       </c>
       <c r="J1909">
         <v>0.8181754278134546</v>
@@ -97639,10 +97639,10 @@
         <v>4.54</v>
       </c>
       <c r="M1909">
-        <v>5.2</v>
+        <v>4.96</v>
       </c>
       <c r="N1909">
-        <v>5.02</v>
+        <v>4.39</v>
       </c>
       <c r="O1909">
         <v>1</v>
@@ -97706,7 +97706,7 @@
         <v>3</v>
       </c>
       <c r="B1911" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1911">
         <v>0.5518576103909849</v>
@@ -98056,7 +98056,7 @@
         <v>10</v>
       </c>
       <c r="B1918" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C1918">
         <v>0.5872961799246212</v>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5787" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5790" uniqueCount="610">
   <si>
     <t>trade_time</t>
   </si>
@@ -799,13 +799,10 @@
     <t>2021-09-16</t>
   </si>
   <si>
-    <t>2021-11-17</t>
+    <t>2021-11-16</t>
   </si>
   <si>
     <t>2021-09-14</t>
-  </si>
-  <si>
-    <t>2021-11-16</t>
   </si>
   <si>
     <t>2021-07-26</t>
@@ -823,7 +820,10 @@
     <t>2021-10-20</t>
   </si>
   <si>
-    <t>2021-11-11</t>
+    <t>2021-11-10</t>
+  </si>
+  <si>
+    <t>2021-11-23</t>
   </si>
   <si>
     <t>2016-12-07</t>
@@ -1360,13 +1360,13 @@
     <t>2021-11-30</t>
   </si>
   <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
     <t>2021-11-29</t>
   </si>
   <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>2021-09-24</t>
+    <t>2021-09-23</t>
   </si>
   <si>
     <t>2021-10-29</t>
@@ -2201,7 +2201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1925"/>
+  <dimension ref="A1:P1926"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -87712,7 +87712,7 @@
         <v>2.431411491361336</v>
       </c>
       <c r="D1711" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E1711">
         <v>2.538213707664756</v>
@@ -87762,7 +87762,7 @@
         <v>2.532009684902152</v>
       </c>
       <c r="D1712" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E1712">
         <v>2.538213707664756</v>
@@ -87812,7 +87812,7 @@
         <v>2.427002049221179</v>
       </c>
       <c r="D1713" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E1713">
         <v>2.538213707664756</v>
@@ -87862,7 +87862,7 @@
         <v>2.549425366108334</v>
       </c>
       <c r="D1714" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E1714">
         <v>2.538213707664756</v>
@@ -96962,10 +96962,10 @@
         <v>0.6328256180584031</v>
       </c>
       <c r="D1896" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E1896">
-        <v>0.8554457298237557</v>
+        <v>0.8631500394877598</v>
       </c>
       <c r="F1896">
         <v>1</v>
@@ -96974,10 +96974,10 @@
         <v>0.006707174381941597</v>
       </c>
       <c r="H1896">
-        <v>0.006484554270176244</v>
+        <v>0.006396849960512241</v>
       </c>
       <c r="I1896">
-        <v>0.2226201117653526</v>
+        <v>0.2303244214293567</v>
       </c>
       <c r="J1896">
         <v>0.7950718277334023</v>
@@ -96989,10 +96989,10 @@
         <v>3.67</v>
       </c>
       <c r="M1896">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="N1896">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="O1896">
         <v>1</v>
@@ -97009,40 +97009,40 @@
         <v>261</v>
       </c>
       <c r="C1897">
-        <v>0.668234237386411</v>
+        <v>0.6720863922184135</v>
       </c>
       <c r="D1897" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E1897">
-        <v>0.8554457298237557</v>
+        <v>0.8631500394877598</v>
       </c>
       <c r="F1897">
         <v>1</v>
       </c>
       <c r="G1897">
-        <v>0.006551765762613589</v>
+        <v>0.006507913607781586</v>
       </c>
       <c r="H1897">
-        <v>0.006484554270176244</v>
+        <v>0.006396849960512241</v>
       </c>
       <c r="I1897">
-        <v>0.1872114924373447</v>
+        <v>0.1910636472693463</v>
       </c>
       <c r="J1897">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1897">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="L1897">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="M1897">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="N1897">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="O1897">
         <v>1</v>
@@ -97462,10 +97462,10 @@
         <v>0.6201442436607301</v>
       </c>
       <c r="D1906" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E1906">
-        <v>0.8436938802510427</v>
+        <v>0.85159737380611</v>
       </c>
       <c r="F1906">
         <v>1</v>
@@ -97474,10 +97474,10 @@
         <v>0.006719855756339269</v>
       </c>
       <c r="H1906">
-        <v>0.006496306119748958</v>
+        <v>0.006408402626193891</v>
       </c>
       <c r="I1906">
-        <v>0.2235496365903127</v>
+        <v>0.2314531301453799</v>
       </c>
       <c r="J1906">
         <v>0.7983915592511178</v>
@@ -97489,10 +97489,10 @@
         <v>3.67</v>
       </c>
       <c r="M1906">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="N1906">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="O1906">
         <v>1</v>
@@ -97506,16 +97506,16 @@
         <v>9</v>
       </c>
       <c r="B1907" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1907">
         <v>0.6599029775483976</v>
       </c>
       <c r="D1907" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E1907">
-        <v>0.8436938802510427</v>
+        <v>0.85159737380611</v>
       </c>
       <c r="F1907">
         <v>1</v>
@@ -97524,10 +97524,10 @@
         <v>0.006520097022451602</v>
       </c>
       <c r="H1907">
-        <v>0.006496306119748958</v>
+        <v>0.006408402626193891</v>
       </c>
       <c r="I1907">
-        <v>0.1837909027026452</v>
+        <v>0.1916943962577125</v>
       </c>
       <c r="J1907">
         <v>0.7983915592511178</v>
@@ -97539,10 +97539,10 @@
         <v>3.59</v>
       </c>
       <c r="M1907">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="N1907">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="O1907">
         <v>1</v>
@@ -97556,7 +97556,7 @@
         <v>0</v>
       </c>
       <c r="B1908" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C1908">
         <v>0.580033038204439</v>
@@ -97706,13 +97706,13 @@
         <v>3</v>
       </c>
       <c r="B1911" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1911">
         <v>0.5518576103909849</v>
       </c>
       <c r="D1911" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E1911">
         <v>0.7845874392656027</v>
@@ -98012,7 +98012,7 @@
         <v>0.5445698657526035</v>
       </c>
       <c r="D1917" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E1917">
         <v>0.7736589855403704</v>
@@ -98056,13 +98056,13 @@
         <v>10</v>
       </c>
       <c r="B1918" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1918">
         <v>0.5872961799246212</v>
       </c>
       <c r="D1918" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E1918">
         <v>0.7736589855403704</v>
@@ -98156,7 +98156,7 @@
         <v>1</v>
       </c>
       <c r="B1920" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C1920">
         <v>0.4840236862109606</v>
@@ -98215,7 +98215,7 @@
         <v>450</v>
       </c>
       <c r="E1921">
-        <v>1.045399620078079</v>
+        <v>1.019321514974956</v>
       </c>
       <c r="F1921">
         <v>-1</v>
@@ -98224,10 +98224,10 @@
         <v>0.01121057591901886</v>
       </c>
       <c r="H1921">
-        <v>0.009454600379921921</v>
+        <v>0.01024067848502504</v>
       </c>
       <c r="I1921">
-        <v>-0.1559755390969357</v>
+        <v>-0.1298974339938122</v>
       </c>
       <c r="J1921">
         <v>0.8459960522981732</v>
@@ -98239,10 +98239,10 @@
         <v>6.05</v>
       </c>
       <c r="M1921">
-        <v>4.97</v>
+        <v>5.45</v>
       </c>
       <c r="N1921">
-        <v>5.25</v>
+        <v>5.63</v>
       </c>
       <c r="O1921">
         <v>1</v>
@@ -98256,7 +98256,7 @@
         <v>3</v>
       </c>
       <c r="B1922" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1922">
         <v>0.8278225019004131</v>
@@ -98265,7 +98265,7 @@
         <v>450</v>
       </c>
       <c r="E1922">
-        <v>1.045399620078079</v>
+        <v>1.019321514974956</v>
       </c>
       <c r="F1922">
         <v>-1</v>
@@ -98274,10 +98274,10 @@
         <v>0.01047217749809959</v>
       </c>
       <c r="H1922">
-        <v>0.009454600379921921</v>
+        <v>0.01024067848502504</v>
       </c>
       <c r="I1922">
-        <v>-0.2175771181776662</v>
+        <v>-0.1914990130745426</v>
       </c>
       <c r="J1922">
         <v>0.8459960522981732</v>
@@ -98289,10 +98289,10 @@
         <v>5.65</v>
       </c>
       <c r="M1922">
-        <v>4.97</v>
+        <v>5.45</v>
       </c>
       <c r="N1922">
-        <v>5.25</v>
+        <v>5.63</v>
       </c>
       <c r="O1922">
         <v>1</v>
@@ -98356,7 +98356,7 @@
         <v>5</v>
       </c>
       <c r="B1924" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1924">
         <v>0.8307179620433116</v>
@@ -98406,10 +98406,10 @@
         <v>6</v>
       </c>
       <c r="B1925" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C1925">
-        <v>0.5036954749911611</v>
+        <v>0.5405948828358871</v>
       </c>
       <c r="D1925" t="s">
         <v>447</v>
@@ -98421,22 +98421,22 @@
         <v>1</v>
       </c>
       <c r="G1925">
-        <v>0.007136304525008839</v>
+        <v>0.006919405117164113</v>
       </c>
       <c r="H1925">
         <v>0.006574066261997642</v>
       </c>
       <c r="I1925">
-        <v>0.1822382630111963</v>
+        <v>0.1453388551664703</v>
       </c>
       <c r="J1925">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1925">
-        <v>3.92</v>
+        <v>3.77</v>
       </c>
       <c r="L1925">
-        <v>3.82</v>
+        <v>3.73</v>
       </c>
       <c r="M1925">
         <v>3.48</v>
@@ -98448,6 +98448,56 @@
         <v>1</v>
       </c>
       <c r="P1925" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:16">
+      <c r="A1926" s="1">
+        <v>7</v>
+      </c>
+      <c r="B1926" t="s">
+        <v>269</v>
+      </c>
+      <c r="C1926">
+        <v>0.5405948828358871</v>
+      </c>
+      <c r="D1926" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1926">
+        <v>0.6859337380023574</v>
+      </c>
+      <c r="F1926">
+        <v>1</v>
+      </c>
+      <c r="G1926">
+        <v>0.006919405117164113</v>
+      </c>
+      <c r="H1926">
+        <v>0.006574066261997642</v>
+      </c>
+      <c r="I1926">
+        <v>0.1453388551664703</v>
+      </c>
+      <c r="J1926">
+        <v>0.8459960522981732</v>
+      </c>
+      <c r="K1926">
+        <v>3.77</v>
+      </c>
+      <c r="L1926">
+        <v>3.73</v>
+      </c>
+      <c r="M1926">
+        <v>3.48</v>
+      </c>
+      <c r="N1926">
+        <v>3.63</v>
+      </c>
+      <c r="O1926">
+        <v>1</v>
+      </c>
+      <c r="P1926" t="s">
         <v>247</v>
       </c>
     </row>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5793" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5796" uniqueCount="611">
   <si>
     <t>trade_time</t>
   </si>
@@ -2204,7 +2204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1927"/>
+  <dimension ref="A1:P1928"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -96656,63 +96656,63 @@
     </row>
     <row r="1890" spans="1:16">
       <c r="A1890" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1890" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C1890">
-        <v>0.5854580999890051</v>
+        <v>0.6972136350932194</v>
       </c>
       <c r="D1890" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E1890">
-        <v>0.8856264957863074</v>
+        <v>0.8904063378714606</v>
       </c>
       <c r="F1890">
         <v>1</v>
       </c>
       <c r="G1890">
-        <v>0.008154541900010996</v>
+        <v>0.00652278636490678</v>
       </c>
       <c r="H1890">
-        <v>0.00915437350421369</v>
+        <v>0.006369593662128539</v>
       </c>
       <c r="I1890">
-        <v>0.3001683957973023</v>
+        <v>0.1931927027782412</v>
       </c>
       <c r="J1890">
-        <v>0.7950718277334023</v>
+        <v>0.7872395580829136</v>
       </c>
       <c r="K1890">
-        <v>4.76</v>
+        <v>3.7</v>
       </c>
       <c r="L1890">
-        <v>4.37</v>
+        <v>3.61</v>
       </c>
       <c r="M1890">
-        <v>5.2</v>
+        <v>3.48</v>
       </c>
       <c r="N1890">
-        <v>5.02</v>
+        <v>3.63</v>
       </c>
       <c r="O1890">
         <v>1</v>
       </c>
       <c r="P1890" t="s">
-        <v>225</v>
+        <v>429</v>
       </c>
     </row>
     <row r="1891" spans="1:16">
       <c r="A1891" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1891" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C1891">
-        <v>0.5964437344423246</v>
+        <v>0.5854580999890051</v>
       </c>
       <c r="D1891" t="s">
         <v>443</v>
@@ -96724,22 +96724,22 @@
         <v>1</v>
       </c>
       <c r="G1891">
-        <v>0.008483556265557676</v>
+        <v>0.008154541900010996</v>
       </c>
       <c r="H1891">
         <v>0.00915437350421369</v>
       </c>
       <c r="I1891">
-        <v>0.2891827613439828</v>
+        <v>0.3001683957973023</v>
       </c>
       <c r="J1891">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1891">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="L1891">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1891">
         <v>5.2</v>
@@ -96756,13 +96756,13 @@
     </row>
     <row r="1892" spans="1:16">
       <c r="A1892" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1892" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C1892">
-        <v>0.6202958892743267</v>
+        <v>0.5964437344423246</v>
       </c>
       <c r="D1892" t="s">
         <v>443</v>
@@ -96774,19 +96774,19 @@
         <v>1</v>
       </c>
       <c r="G1892">
-        <v>0.008459704110725675</v>
+        <v>0.008483556265557676</v>
       </c>
       <c r="H1892">
         <v>0.00915437350421369</v>
       </c>
       <c r="I1892">
-        <v>0.2653306065119807</v>
+        <v>0.2891827613439828</v>
       </c>
       <c r="J1892">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1892">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="L1892">
         <v>4.54</v>
@@ -96806,46 +96806,46 @@
     </row>
     <row r="1893" spans="1:16">
       <c r="A1893" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1893" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1893">
-        <v>1.197610134858196</v>
+        <v>0.6202958892743267</v>
       </c>
       <c r="D1893" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E1893">
-        <v>0.838973463226401</v>
+        <v>0.8856264957863074</v>
       </c>
       <c r="F1893">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1893">
-        <v>0.0120423898651418</v>
+        <v>0.008459704110725675</v>
       </c>
       <c r="H1893">
-        <v>0.006961026536773598</v>
+        <v>0.00915437350421369</v>
       </c>
       <c r="I1893">
-        <v>0.3586366716317948</v>
+        <v>0.2653306065119807</v>
       </c>
       <c r="J1893">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1893">
-        <v>6.82</v>
+        <v>4.93</v>
       </c>
       <c r="L1893">
-        <v>6.62</v>
+        <v>4.54</v>
       </c>
       <c r="M1893">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="N1893">
-        <v>3.9</v>
+        <v>5.02</v>
       </c>
       <c r="O1893">
         <v>1</v>
@@ -96856,13 +96856,13 @@
     </row>
     <row r="1894" spans="1:16">
       <c r="A1894" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1894" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C1894">
-        <v>1.10776616049025</v>
+        <v>1.197610134858196</v>
       </c>
       <c r="D1894" t="s">
         <v>446</v>
@@ -96874,22 +96874,22 @@
         <v>-1</v>
       </c>
       <c r="G1894">
-        <v>0.01071223383950975</v>
+        <v>0.0120423898651418</v>
       </c>
       <c r="H1894">
         <v>0.006961026536773598</v>
       </c>
       <c r="I1894">
-        <v>0.2687926972638492</v>
+        <v>0.3586366716317948</v>
       </c>
       <c r="J1894">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1894">
-        <v>6.04</v>
+        <v>6.82</v>
       </c>
       <c r="L1894">
-        <v>5.91</v>
+        <v>6.62</v>
       </c>
       <c r="M1894">
         <v>3.85</v>
@@ -96906,13 +96906,13 @@
     </row>
     <row r="1895" spans="1:16">
       <c r="A1895" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1895" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C1895">
-        <v>1.128078211754358</v>
+        <v>1.10776616049025</v>
       </c>
       <c r="D1895" t="s">
         <v>446</v>
@@ -96924,22 +96924,22 @@
         <v>-1</v>
       </c>
       <c r="G1895">
-        <v>0.008251921788245643</v>
+        <v>0.01071223383950975</v>
       </c>
       <c r="H1895">
         <v>0.006961026536773598</v>
       </c>
       <c r="I1895">
-        <v>0.2891047485279565</v>
+        <v>0.2687926972638492</v>
       </c>
       <c r="J1895">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1895">
-        <v>4.48</v>
+        <v>6.04</v>
       </c>
       <c r="L1895">
-        <v>4.69</v>
+        <v>5.91</v>
       </c>
       <c r="M1895">
         <v>3.85</v>
@@ -96956,13 +96956,13 @@
     </row>
     <row r="1896" spans="1:16">
       <c r="A1896" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1896" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C1896">
-        <v>1.042916001039679</v>
+        <v>1.128078211754358</v>
       </c>
       <c r="D1896" t="s">
         <v>446</v>
@@ -96974,22 +96974,22 @@
         <v>-1</v>
       </c>
       <c r="G1896">
-        <v>0.008437083998960322</v>
+        <v>0.008251921788245643</v>
       </c>
       <c r="H1896">
         <v>0.006961026536773598</v>
       </c>
       <c r="I1896">
-        <v>0.203942537813278</v>
+        <v>0.2891047485279565</v>
       </c>
       <c r="J1896">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1896">
-        <v>4.65</v>
+        <v>4.48</v>
       </c>
       <c r="L1896">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="M1896">
         <v>3.85</v>
@@ -97006,46 +97006,46 @@
     </row>
     <row r="1897" spans="1:16">
       <c r="A1897" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1897" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C1897">
-        <v>0.6328256180584031</v>
+        <v>1.042916001039679</v>
       </c>
       <c r="D1897" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1897">
-        <v>0.8631500394877598</v>
+        <v>0.838973463226401</v>
       </c>
       <c r="F1897">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1897">
-        <v>0.006707174381941597</v>
+        <v>0.008437083998960322</v>
       </c>
       <c r="H1897">
-        <v>0.006396849960512241</v>
+        <v>0.006961026536773598</v>
       </c>
       <c r="I1897">
-        <v>0.2303244214293567</v>
+        <v>0.203942537813278</v>
       </c>
       <c r="J1897">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1897">
-        <v>3.82</v>
+        <v>4.65</v>
       </c>
       <c r="L1897">
-        <v>3.67</v>
+        <v>4.74</v>
       </c>
       <c r="M1897">
-        <v>3.48</v>
+        <v>3.85</v>
       </c>
       <c r="N1897">
-        <v>3.63</v>
+        <v>3.9</v>
       </c>
       <c r="O1897">
         <v>1</v>
@@ -97056,13 +97056,13 @@
     </row>
     <row r="1898" spans="1:16">
       <c r="A1898" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1898" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C1898">
-        <v>0.6720863922184135</v>
+        <v>0.6328256180584031</v>
       </c>
       <c r="D1898" t="s">
         <v>448</v>
@@ -97074,22 +97074,22 @@
         <v>1</v>
       </c>
       <c r="G1898">
-        <v>0.006507913607781586</v>
+        <v>0.006707174381941597</v>
       </c>
       <c r="H1898">
         <v>0.006396849960512241</v>
       </c>
       <c r="I1898">
-        <v>0.1910636472693463</v>
+        <v>0.2303244214293567</v>
       </c>
       <c r="J1898">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1898">
+        <v>3.82</v>
+      </c>
+      <c r="L1898">
         <v>3.67</v>
-      </c>
-      <c r="L1898">
-        <v>3.59</v>
       </c>
       <c r="M1898">
         <v>3.48</v>
@@ -97106,63 +97106,63 @@
     </row>
     <row r="1899" spans="1:16">
       <c r="A1899" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1899" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C1899">
-        <v>0.5696561779646796</v>
+        <v>0.6720863922184135</v>
       </c>
       <c r="D1899" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E1899">
-        <v>0.8683638918941865</v>
+        <v>0.8631500394877598</v>
       </c>
       <c r="F1899">
         <v>1</v>
       </c>
       <c r="G1899">
-        <v>0.00817034382203532</v>
+        <v>0.006507913607781586</v>
       </c>
       <c r="H1899">
-        <v>0.009171636108105811</v>
+        <v>0.006396849960512241</v>
       </c>
       <c r="I1899">
-        <v>0.2987077139295069</v>
+        <v>0.1910636472693463</v>
       </c>
       <c r="J1899">
-        <v>0.7983915592511178</v>
+        <v>0.7950718277334023</v>
       </c>
       <c r="K1899">
-        <v>4.76</v>
+        <v>3.67</v>
       </c>
       <c r="L1899">
-        <v>4.37</v>
+        <v>3.59</v>
       </c>
       <c r="M1899">
-        <v>5.2</v>
+        <v>3.48</v>
       </c>
       <c r="N1899">
-        <v>5.02</v>
+        <v>3.63</v>
       </c>
       <c r="O1899">
         <v>1</v>
       </c>
       <c r="P1899" t="s">
-        <v>431</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1900" spans="1:16">
       <c r="A1900" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1900" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C1900">
-        <v>0.5799778661144557</v>
+        <v>0.5696561779646796</v>
       </c>
       <c r="D1900" t="s">
         <v>443</v>
@@ -97174,22 +97174,22 @@
         <v>1</v>
       </c>
       <c r="G1900">
-        <v>0.008500022133885544</v>
+        <v>0.00817034382203532</v>
       </c>
       <c r="H1900">
         <v>0.009171636108105811</v>
       </c>
       <c r="I1900">
-        <v>0.2883860257797308</v>
+        <v>0.2987077139295069</v>
       </c>
       <c r="J1900">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1900">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="L1900">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1900">
         <v>5.2</v>
@@ -97206,13 +97206,13 @@
     </row>
     <row r="1901" spans="1:16">
       <c r="A1901" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1901" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C1901">
-        <v>0.6039296128919895</v>
+        <v>0.5799778661144557</v>
       </c>
       <c r="D1901" t="s">
         <v>443</v>
@@ -97224,19 +97224,19 @@
         <v>1</v>
       </c>
       <c r="G1901">
-        <v>0.008476070387108009</v>
+        <v>0.008500022133885544</v>
       </c>
       <c r="H1901">
         <v>0.009171636108105811</v>
       </c>
       <c r="I1901">
-        <v>0.264434279002197</v>
+        <v>0.2883860257797308</v>
       </c>
       <c r="J1901">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1901">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="L1901">
         <v>4.54</v>
@@ -97256,46 +97256,46 @@
     </row>
     <row r="1902" spans="1:16">
       <c r="A1902" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1902" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1902">
-        <v>1.174969565907376</v>
+        <v>0.6039296128919895</v>
       </c>
       <c r="D1902" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E1902">
-        <v>0.8261924968831962</v>
+        <v>0.8683638918941865</v>
       </c>
       <c r="F1902">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1902">
-        <v>0.01206503043409262</v>
+        <v>0.008476070387108009</v>
       </c>
       <c r="H1902">
-        <v>0.006973807503116805</v>
+        <v>0.009171636108105811</v>
       </c>
       <c r="I1902">
-        <v>0.3487770690241798</v>
+        <v>0.264434279002197</v>
       </c>
       <c r="J1902">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1902">
-        <v>6.82</v>
+        <v>4.93</v>
       </c>
       <c r="L1902">
-        <v>6.62</v>
+        <v>4.54</v>
       </c>
       <c r="M1902">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="N1902">
-        <v>3.9</v>
+        <v>5.02</v>
       </c>
       <c r="O1902">
         <v>1</v>
@@ -97306,13 +97306,13 @@
     </row>
     <row r="1903" spans="1:16">
       <c r="A1903" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1903" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C1903">
-        <v>1.179811488568181</v>
+        <v>1.174969565907376</v>
       </c>
       <c r="D1903" t="s">
         <v>446</v>
@@ -97324,22 +97324,22 @@
         <v>-1</v>
       </c>
       <c r="G1903">
-        <v>0.01092018851143182</v>
+        <v>0.01206503043409262</v>
       </c>
       <c r="H1903">
         <v>0.006973807503116805</v>
       </c>
       <c r="I1903">
-        <v>0.3536189916849852</v>
+        <v>0.3487770690241798</v>
       </c>
       <c r="J1903">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1903">
-        <v>6.1</v>
+        <v>6.82</v>
       </c>
       <c r="L1903">
-        <v>6.05</v>
+        <v>6.62</v>
       </c>
       <c r="M1903">
         <v>3.85</v>
@@ -97356,13 +97356,13 @@
     </row>
     <row r="1904" spans="1:16">
       <c r="A1904" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1904" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C1904">
-        <v>1.087714982123249</v>
+        <v>1.179811488568181</v>
       </c>
       <c r="D1904" t="s">
         <v>446</v>
@@ -97374,22 +97374,22 @@
         <v>-1</v>
       </c>
       <c r="G1904">
-        <v>0.01073228501787675</v>
+        <v>0.01092018851143182</v>
       </c>
       <c r="H1904">
         <v>0.006973807503116805</v>
       </c>
       <c r="I1904">
-        <v>0.2615224852400524</v>
+        <v>0.3536189916849852</v>
       </c>
       <c r="J1904">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1904">
-        <v>6.04</v>
+        <v>6.1</v>
       </c>
       <c r="L1904">
-        <v>5.91</v>
+        <v>6.05</v>
       </c>
       <c r="M1904">
         <v>3.85</v>
@@ -97406,13 +97406,13 @@
     </row>
     <row r="1905" spans="1:16">
       <c r="A1905" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1905" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C1905">
-        <v>1.113205814554992</v>
+        <v>1.087714982123249</v>
       </c>
       <c r="D1905" t="s">
         <v>446</v>
@@ -97424,22 +97424,22 @@
         <v>-1</v>
       </c>
       <c r="G1905">
-        <v>0.008266794185445007</v>
+        <v>0.01073228501787675</v>
       </c>
       <c r="H1905">
         <v>0.006973807503116805</v>
       </c>
       <c r="I1905">
-        <v>0.2870133176717959</v>
+        <v>0.2615224852400524</v>
       </c>
       <c r="J1905">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1905">
-        <v>4.48</v>
+        <v>6.04</v>
       </c>
       <c r="L1905">
-        <v>4.69</v>
+        <v>5.91</v>
       </c>
       <c r="M1905">
         <v>3.85</v>
@@ -97456,13 +97456,13 @@
     </row>
     <row r="1906" spans="1:16">
       <c r="A1906" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1906" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C1906">
-        <v>1.027479249482302</v>
+        <v>1.113205814554992</v>
       </c>
       <c r="D1906" t="s">
         <v>446</v>
@@ -97474,22 +97474,22 @@
         <v>-1</v>
       </c>
       <c r="G1906">
-        <v>0.0084525207505177</v>
+        <v>0.008266794185445007</v>
       </c>
       <c r="H1906">
         <v>0.006973807503116805</v>
       </c>
       <c r="I1906">
-        <v>0.2012867525991058</v>
+        <v>0.2870133176717959</v>
       </c>
       <c r="J1906">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1906">
-        <v>4.65</v>
+        <v>4.48</v>
       </c>
       <c r="L1906">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="M1906">
         <v>3.85</v>
@@ -97506,46 +97506,46 @@
     </row>
     <row r="1907" spans="1:16">
       <c r="A1907" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1907" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C1907">
-        <v>0.6201442436607301</v>
+        <v>1.027479249482302</v>
       </c>
       <c r="D1907" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1907">
-        <v>0.85159737380611</v>
+        <v>0.8261924968831962</v>
       </c>
       <c r="F1907">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1907">
-        <v>0.006719855756339269</v>
+        <v>0.0084525207505177</v>
       </c>
       <c r="H1907">
-        <v>0.006408402626193891</v>
+        <v>0.006973807503116805</v>
       </c>
       <c r="I1907">
-        <v>0.2314531301453799</v>
+        <v>0.2012867525991058</v>
       </c>
       <c r="J1907">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1907">
-        <v>3.82</v>
+        <v>4.65</v>
       </c>
       <c r="L1907">
-        <v>3.67</v>
+        <v>4.74</v>
       </c>
       <c r="M1907">
-        <v>3.48</v>
+        <v>3.85</v>
       </c>
       <c r="N1907">
-        <v>3.63</v>
+        <v>3.9</v>
       </c>
       <c r="O1907">
         <v>1</v>
@@ -97556,13 +97556,13 @@
     </row>
     <row r="1908" spans="1:16">
       <c r="A1908" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1908" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C1908">
-        <v>0.6599029775483976</v>
+        <v>0.6201442436607301</v>
       </c>
       <c r="D1908" t="s">
         <v>448</v>
@@ -97574,22 +97574,22 @@
         <v>1</v>
       </c>
       <c r="G1908">
-        <v>0.006520097022451602</v>
+        <v>0.006719855756339269</v>
       </c>
       <c r="H1908">
         <v>0.006408402626193891</v>
       </c>
       <c r="I1908">
-        <v>0.1916943962577125</v>
+        <v>0.2314531301453799</v>
       </c>
       <c r="J1908">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1908">
+        <v>3.82</v>
+      </c>
+      <c r="L1908">
         <v>3.67</v>
-      </c>
-      <c r="L1908">
-        <v>3.59</v>
       </c>
       <c r="M1908">
         <v>3.48</v>
@@ -97606,63 +97606,63 @@
     </row>
     <row r="1909" spans="1:16">
       <c r="A1909" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1909" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C1909">
-        <v>0.580033038204439</v>
+        <v>0.6599029775483976</v>
       </c>
       <c r="D1909" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="E1909">
-        <v>0.331849878045265</v>
+        <v>0.85159737380611</v>
       </c>
       <c r="F1909">
         <v>1</v>
       </c>
       <c r="G1909">
-        <v>0.00903996696179556</v>
+        <v>0.006520097022451602</v>
       </c>
       <c r="H1909">
-        <v>0.008448150121954734</v>
+        <v>0.006408402626193891</v>
       </c>
       <c r="I1909">
-        <v>-0.248183160159174</v>
+        <v>0.1916943962577125</v>
       </c>
       <c r="J1909">
-        <v>0.8181754278134546</v>
+        <v>0.7983915592511178</v>
       </c>
       <c r="K1909">
-        <v>5.17</v>
+        <v>3.67</v>
       </c>
       <c r="L1909">
-        <v>4.81</v>
+        <v>3.59</v>
       </c>
       <c r="M1909">
-        <v>4.96</v>
+        <v>3.48</v>
       </c>
       <c r="N1909">
-        <v>4.39</v>
+        <v>3.63</v>
       </c>
       <c r="O1909">
         <v>1</v>
       </c>
       <c r="P1909" t="s">
-        <v>246</v>
+        <v>431</v>
       </c>
     </row>
     <row r="1910" spans="1:16">
       <c r="A1910" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1910" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="C1910">
-        <v>0.4818498780452654</v>
+        <v>0.580033038204439</v>
       </c>
       <c r="D1910" t="s">
         <v>437</v>
@@ -97674,22 +97674,22 @@
         <v>1</v>
       </c>
       <c r="G1910">
-        <v>0.008598150121954735</v>
+        <v>0.00903996696179556</v>
       </c>
       <c r="H1910">
         <v>0.008448150121954734</v>
       </c>
       <c r="I1910">
-        <v>-0.1500000000000004</v>
+        <v>-0.248183160159174</v>
       </c>
       <c r="J1910">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1910">
-        <v>4.96</v>
+        <v>5.17</v>
       </c>
       <c r="L1910">
-        <v>4.54</v>
+        <v>4.81</v>
       </c>
       <c r="M1910">
         <v>4.96</v>
@@ -97706,46 +97706,46 @@
     </row>
     <row r="1911" spans="1:16">
       <c r="A1911" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1911" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C1911">
-        <v>0.5063951408796692</v>
+        <v>0.4818498780452654</v>
       </c>
       <c r="D1911" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E1911">
-        <v>0.7654877753700351</v>
+        <v>0.331849878045265</v>
       </c>
       <c r="F1911">
         <v>1</v>
       </c>
       <c r="G1911">
-        <v>0.008573604859120331</v>
+        <v>0.008598150121954735</v>
       </c>
       <c r="H1911">
-        <v>0.009274512224629964</v>
+        <v>0.008448150121954734</v>
       </c>
       <c r="I1911">
-        <v>0.2590926344903659</v>
+        <v>-0.1500000000000004</v>
       </c>
       <c r="J1911">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1911">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="L1911">
         <v>4.54</v>
       </c>
       <c r="M1911">
-        <v>5.2</v>
+        <v>4.96</v>
       </c>
       <c r="N1911">
-        <v>5.02</v>
+        <v>4.39</v>
       </c>
       <c r="O1911">
         <v>1</v>
@@ -97756,46 +97756,46 @@
     </row>
     <row r="1912" spans="1:16">
       <c r="A1912" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1912" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C1912">
-        <v>0.5518576103909849</v>
+        <v>0.5063951408796692</v>
       </c>
       <c r="D1912" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="E1912">
-        <v>0.7845874392656027</v>
+        <v>0.7654877753700351</v>
       </c>
       <c r="F1912">
         <v>1</v>
       </c>
       <c r="G1912">
-        <v>0.01064814238960901</v>
+        <v>0.008573604859120331</v>
       </c>
       <c r="H1912">
-        <v>0.0115354125607344</v>
+        <v>0.009274512224629964</v>
       </c>
       <c r="I1912">
-        <v>0.2327298288746178</v>
+        <v>0.2590926344903659</v>
       </c>
       <c r="J1912">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1912">
-        <v>6.17</v>
+        <v>4.93</v>
       </c>
       <c r="L1912">
-        <v>5.6</v>
+        <v>4.54</v>
       </c>
       <c r="M1912">
-        <v>6.57</v>
+        <v>5.2</v>
       </c>
       <c r="N1912">
-        <v>6.16</v>
+        <v>5.02</v>
       </c>
       <c r="O1912">
         <v>1</v>
@@ -97806,46 +97806,46 @@
     </row>
     <row r="1913" spans="1:16">
       <c r="A1913" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1913" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="C1913">
-        <v>1.040043582312239</v>
+        <v>0.5518576103909849</v>
       </c>
       <c r="D1913" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E1913">
-        <v>0.7500246029181996</v>
+        <v>0.7845874392656027</v>
       </c>
       <c r="F1913">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1913">
-        <v>0.01219995641768776</v>
+        <v>0.01064814238960901</v>
       </c>
       <c r="H1913">
-        <v>0.007049975397081801</v>
+        <v>0.0115354125607344</v>
       </c>
       <c r="I1913">
-        <v>0.2900189793940395</v>
+        <v>0.2327298288746178</v>
       </c>
       <c r="J1913">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1913">
-        <v>6.82</v>
+        <v>6.17</v>
       </c>
       <c r="L1913">
-        <v>6.62</v>
+        <v>5.6</v>
       </c>
       <c r="M1913">
-        <v>3.85</v>
+        <v>6.57</v>
       </c>
       <c r="N1913">
-        <v>3.9</v>
+        <v>6.16</v>
       </c>
       <c r="O1913">
         <v>1</v>
@@ -97856,13 +97856,13 @@
     </row>
     <row r="1914" spans="1:16">
       <c r="A1914" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1914" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C1914">
-        <v>1.059129890337926</v>
+        <v>1.040043582312239</v>
       </c>
       <c r="D1914" t="s">
         <v>446</v>
@@ -97874,22 +97874,22 @@
         <v>-1</v>
       </c>
       <c r="G1914">
-        <v>0.01104087010966207</v>
+        <v>0.01219995641768776</v>
       </c>
       <c r="H1914">
         <v>0.007049975397081801</v>
       </c>
       <c r="I1914">
-        <v>0.3091052874197269</v>
+        <v>0.2900189793940395</v>
       </c>
       <c r="J1914">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1914">
-        <v>6.1</v>
+        <v>6.82</v>
       </c>
       <c r="L1914">
-        <v>6.05</v>
+        <v>6.62</v>
       </c>
       <c r="M1914">
         <v>3.85</v>
@@ -97906,13 +97906,13 @@
     </row>
     <row r="1915" spans="1:16">
       <c r="A1915" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1915" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C1915">
-        <v>0.9682204160067345</v>
+        <v>1.059129890337926</v>
       </c>
       <c r="D1915" t="s">
         <v>446</v>
@@ -97924,22 +97924,22 @@
         <v>-1</v>
       </c>
       <c r="G1915">
-        <v>0.01085177958399327</v>
+        <v>0.01104087010966207</v>
       </c>
       <c r="H1915">
         <v>0.007049975397081801</v>
       </c>
       <c r="I1915">
-        <v>0.2181958130885349</v>
+        <v>0.3091052874197269</v>
       </c>
       <c r="J1915">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1915">
-        <v>6.04</v>
+        <v>6.1</v>
       </c>
       <c r="L1915">
-        <v>5.91</v>
+        <v>6.05</v>
       </c>
       <c r="M1915">
         <v>3.85</v>
@@ -97956,13 +97956,13 @@
     </row>
     <row r="1916" spans="1:16">
       <c r="A1916" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1916" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C1916">
-        <v>1.024574083395723</v>
+        <v>0.9682204160067345</v>
       </c>
       <c r="D1916" t="s">
         <v>446</v>
@@ -97974,22 +97974,22 @@
         <v>-1</v>
       </c>
       <c r="G1916">
-        <v>0.008355425916604278</v>
+        <v>0.01085177958399327</v>
       </c>
       <c r="H1916">
         <v>0.007049975397081801</v>
       </c>
       <c r="I1916">
-        <v>0.2745494804775235</v>
+        <v>0.2181958130885349</v>
       </c>
       <c r="J1916">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1916">
-        <v>4.48</v>
+        <v>6.04</v>
       </c>
       <c r="L1916">
-        <v>4.69</v>
+        <v>5.91</v>
       </c>
       <c r="M1916">
         <v>3.85</v>
@@ -98006,13 +98006,13 @@
     </row>
     <row r="1917" spans="1:16">
       <c r="A1917" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1917" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C1917">
-        <v>0.9354842606674358</v>
+        <v>1.024574083395723</v>
       </c>
       <c r="D1917" t="s">
         <v>446</v>
@@ -98024,22 +98024,22 @@
         <v>-1</v>
       </c>
       <c r="G1917">
-        <v>0.008544515739332565</v>
+        <v>0.008355425916604278</v>
       </c>
       <c r="H1917">
         <v>0.007049975397081801</v>
       </c>
       <c r="I1917">
-        <v>0.1854596577492362</v>
+        <v>0.2745494804775235</v>
       </c>
       <c r="J1917">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1917">
-        <v>4.65</v>
+        <v>4.48</v>
       </c>
       <c r="L1917">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="M1917">
         <v>3.85</v>
@@ -98056,46 +98056,46 @@
     </row>
     <row r="1918" spans="1:16">
       <c r="A1918" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1918" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C1918">
-        <v>0.5445698657526035</v>
+        <v>0.9354842606674358</v>
       </c>
       <c r="D1918" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E1918">
-        <v>0.7736589855403704</v>
+        <v>0.7500246029181996</v>
       </c>
       <c r="F1918">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1918">
-        <v>0.006795430134247397</v>
+        <v>0.008544515739332565</v>
       </c>
       <c r="H1918">
-        <v>0.00656634101445963</v>
+        <v>0.007049975397081801</v>
       </c>
       <c r="I1918">
-        <v>0.2290891197877669</v>
+        <v>0.1854596577492362</v>
       </c>
       <c r="J1918">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1918">
-        <v>3.82</v>
+        <v>4.65</v>
       </c>
       <c r="L1918">
-        <v>3.67</v>
+        <v>4.74</v>
       </c>
       <c r="M1918">
-        <v>3.54</v>
+        <v>3.85</v>
       </c>
       <c r="N1918">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="O1918">
         <v>1</v>
@@ -98106,13 +98106,13 @@
     </row>
     <row r="1919" spans="1:16">
       <c r="A1919" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1919" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C1919">
-        <v>0.5872961799246212</v>
+        <v>0.5445698657526035</v>
       </c>
       <c r="D1919" t="s">
         <v>450</v>
@@ -98124,22 +98124,22 @@
         <v>1</v>
       </c>
       <c r="G1919">
-        <v>0.006592703820075378</v>
+        <v>0.006795430134247397</v>
       </c>
       <c r="H1919">
         <v>0.00656634101445963</v>
       </c>
       <c r="I1919">
-        <v>0.1863628056157491</v>
+        <v>0.2290891197877669</v>
       </c>
       <c r="J1919">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1919">
+        <v>3.82</v>
+      </c>
+      <c r="L1919">
         <v>3.67</v>
-      </c>
-      <c r="L1919">
-        <v>3.59</v>
       </c>
       <c r="M1919">
         <v>3.54</v>
@@ -98156,63 +98156,63 @@
     </row>
     <row r="1920" spans="1:16">
       <c r="A1920" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B1920" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="C1920">
-        <v>0.479362541377431</v>
+        <v>0.5872961799246212</v>
       </c>
       <c r="D1920" t="s">
-        <v>256</v>
+        <v>450</v>
       </c>
       <c r="E1920">
-        <v>0.8503069233264586</v>
+        <v>0.7736589855403704</v>
       </c>
       <c r="F1920">
         <v>1</v>
       </c>
       <c r="G1920">
-        <v>0.01014063745862257</v>
+        <v>0.006592703820075378</v>
       </c>
       <c r="H1920">
-        <v>0.01238969307667354</v>
+        <v>0.00656634101445963</v>
       </c>
       <c r="I1920">
-        <v>0.3709443819490277</v>
+        <v>0.1863628056157491</v>
       </c>
       <c r="J1920">
-        <v>0.8459960522981732</v>
+        <v>0.8181754278134546</v>
       </c>
       <c r="K1920">
-        <v>5.71</v>
+        <v>3.67</v>
       </c>
       <c r="L1920">
-        <v>5.31</v>
+        <v>3.59</v>
       </c>
       <c r="M1920">
-        <v>6.82</v>
+        <v>3.54</v>
       </c>
       <c r="N1920">
-        <v>6.62</v>
+        <v>3.67</v>
       </c>
       <c r="O1920">
         <v>1</v>
       </c>
       <c r="P1920" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="1921" spans="1:16">
       <c r="A1921" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1921" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="C1921">
-        <v>0.4840236862109606</v>
+        <v>0.479362541377431</v>
       </c>
       <c r="D1921" t="s">
         <v>256</v>
@@ -98224,22 +98224,22 @@
         <v>1</v>
       </c>
       <c r="G1921">
-        <v>0.01063597631378904</v>
+        <v>0.01014063745862257</v>
       </c>
       <c r="H1921">
         <v>0.01238969307667354</v>
       </c>
       <c r="I1921">
-        <v>0.366283237115498</v>
+        <v>0.3709443819490277</v>
       </c>
       <c r="J1921">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1921">
-        <v>6</v>
+        <v>5.71</v>
       </c>
       <c r="L1921">
-        <v>5.56</v>
+        <v>5.31</v>
       </c>
       <c r="M1921">
         <v>6.82</v>
@@ -98256,46 +98256,46 @@
     </row>
     <row r="1922" spans="1:16">
       <c r="A1922" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1922" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C1922">
-        <v>0.8894240809811436</v>
+        <v>0.4840236862109606</v>
       </c>
       <c r="D1922" t="s">
-        <v>451</v>
+        <v>256</v>
       </c>
       <c r="E1922">
-        <v>1.019321514974956</v>
+        <v>0.8503069233264586</v>
       </c>
       <c r="F1922">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1922">
-        <v>0.01121057591901886</v>
+        <v>0.01063597631378904</v>
       </c>
       <c r="H1922">
-        <v>0.01024067848502504</v>
+        <v>0.01238969307667354</v>
       </c>
       <c r="I1922">
-        <v>-0.1298974339938122</v>
+        <v>0.366283237115498</v>
       </c>
       <c r="J1922">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1922">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="L1922">
-        <v>6.05</v>
+        <v>5.56</v>
       </c>
       <c r="M1922">
-        <v>5.45</v>
+        <v>6.82</v>
       </c>
       <c r="N1922">
-        <v>5.63</v>
+        <v>6.62</v>
       </c>
       <c r="O1922">
         <v>1</v>
@@ -98306,13 +98306,13 @@
     </row>
     <row r="1923" spans="1:16">
       <c r="A1923" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1923" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C1923">
-        <v>0.8278225019004131</v>
+        <v>0.8894240809811436</v>
       </c>
       <c r="D1923" t="s">
         <v>451</v>
@@ -98324,22 +98324,22 @@
         <v>-1</v>
       </c>
       <c r="G1923">
-        <v>0.01047217749809959</v>
+        <v>0.01121057591901886</v>
       </c>
       <c r="H1923">
         <v>0.01024067848502504</v>
       </c>
       <c r="I1923">
-        <v>-0.1914990130745426</v>
+        <v>-0.1298974339938122</v>
       </c>
       <c r="J1923">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1923">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="L1923">
-        <v>5.65</v>
+        <v>6.05</v>
       </c>
       <c r="M1923">
         <v>5.45</v>
@@ -98356,46 +98356,46 @@
     </row>
     <row r="1924" spans="1:16">
       <c r="A1924" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1924" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="C1924">
-        <v>0.8999376857041841</v>
+        <v>0.8278225019004131</v>
       </c>
       <c r="D1924" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E1924">
-        <v>0.6752765408706538</v>
+        <v>1.019321514974956</v>
       </c>
       <c r="F1924">
         <v>-1</v>
       </c>
       <c r="G1924">
-        <v>0.008480062314295817</v>
+        <v>0.01047217749809959</v>
       </c>
       <c r="H1924">
-        <v>0.007764723459129346</v>
+        <v>0.01024067848502504</v>
       </c>
       <c r="I1924">
-        <v>0.2246611448335303</v>
+        <v>-0.1914990130745426</v>
       </c>
       <c r="J1924">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1924">
-        <v>4.48</v>
+        <v>5.7</v>
       </c>
       <c r="L1924">
-        <v>4.69</v>
+        <v>5.65</v>
       </c>
       <c r="M1924">
-        <v>4.19</v>
+        <v>5.45</v>
       </c>
       <c r="N1924">
-        <v>4.22</v>
+        <v>5.63</v>
       </c>
       <c r="O1924">
         <v>1</v>
@@ -98406,13 +98406,13 @@
     </row>
     <row r="1925" spans="1:16">
       <c r="A1925" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1925" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="C1925">
-        <v>0.8307179620433116</v>
+        <v>0.8999376857041841</v>
       </c>
       <c r="D1925" t="s">
         <v>452</v>
@@ -98424,22 +98424,22 @@
         <v>-1</v>
       </c>
       <c r="G1925">
-        <v>0.008529282037956687</v>
+        <v>0.008480062314295817</v>
       </c>
       <c r="H1925">
         <v>0.007764723459129346</v>
       </c>
       <c r="I1925">
-        <v>0.1554414211726578</v>
+        <v>0.2246611448335303</v>
       </c>
       <c r="J1925">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1925">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="L1925">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="M1925">
         <v>4.19</v>
@@ -98456,46 +98456,46 @@
     </row>
     <row r="1926" spans="1:16">
       <c r="A1926" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1926" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C1926">
-        <v>0.5405948828358871</v>
+        <v>0.8307179620433116</v>
       </c>
       <c r="D1926" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E1926">
-        <v>0.6859337380023574</v>
+        <v>0.6752765408706538</v>
       </c>
       <c r="F1926">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1926">
-        <v>0.006919405117164113</v>
+        <v>0.008529282037956687</v>
       </c>
       <c r="H1926">
-        <v>0.006574066261997642</v>
+        <v>0.007764723459129346</v>
       </c>
       <c r="I1926">
-        <v>0.1453388551664703</v>
+        <v>0.1554414211726578</v>
       </c>
       <c r="J1926">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1926">
-        <v>3.77</v>
+        <v>4.55</v>
       </c>
       <c r="L1926">
-        <v>3.73</v>
+        <v>4.68</v>
       </c>
       <c r="M1926">
-        <v>3.48</v>
+        <v>4.19</v>
       </c>
       <c r="N1926">
-        <v>3.63</v>
+        <v>4.22</v>
       </c>
       <c r="O1926">
         <v>1</v>
@@ -98506,10 +98506,10 @@
     </row>
     <row r="1927" spans="1:16">
       <c r="A1927" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1927" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C1927">
         <v>0.5405948828358871</v>
@@ -98551,6 +98551,56 @@
         <v>1</v>
       </c>
       <c r="P1927" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:16">
+      <c r="A1928" s="1">
+        <v>7</v>
+      </c>
+      <c r="B1928" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1928">
+        <v>0.5405948828358871</v>
+      </c>
+      <c r="D1928" t="s">
+        <v>448</v>
+      </c>
+      <c r="E1928">
+        <v>0.6859337380023574</v>
+      </c>
+      <c r="F1928">
+        <v>1</v>
+      </c>
+      <c r="G1928">
+        <v>0.006919405117164113</v>
+      </c>
+      <c r="H1928">
+        <v>0.006574066261997642</v>
+      </c>
+      <c r="I1928">
+        <v>0.1453388551664703</v>
+      </c>
+      <c r="J1928">
+        <v>0.8459960522981732</v>
+      </c>
+      <c r="K1928">
+        <v>3.77</v>
+      </c>
+      <c r="L1928">
+        <v>3.73</v>
+      </c>
+      <c r="M1928">
+        <v>3.48</v>
+      </c>
+      <c r="N1928">
+        <v>3.63</v>
+      </c>
+      <c r="O1928">
+        <v>1</v>
+      </c>
+      <c r="P1928" t="s">
         <v>247</v>
       </c>
     </row>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -799,19 +799,19 @@
     <t>2021-11-17</t>
   </si>
   <si>
-    <t>2021-09-16</t>
-  </si>
-  <si>
     <t>2021-11-16</t>
   </si>
   <si>
-    <t>2021-09-14</t>
+    <t>2021-09-16</t>
   </si>
   <si>
     <t>2021-07-26</t>
   </si>
   <si>
     <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>2021-09-14</t>
   </si>
   <si>
     <t>2021-09-02</t>
@@ -87718,7 +87718,7 @@
         <v>2.431411491361336</v>
       </c>
       <c r="D1711" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E1711">
         <v>2.538213707664756</v>
@@ -87768,7 +87768,7 @@
         <v>2.532009684902152</v>
       </c>
       <c r="D1712" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E1712">
         <v>2.538213707664756</v>
@@ -87818,7 +87818,7 @@
         <v>2.427002049221179</v>
       </c>
       <c r="D1713" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E1713">
         <v>2.538213707664756</v>
@@ -87868,7 +87868,7 @@
         <v>2.549425366108334</v>
       </c>
       <c r="D1714" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E1714">
         <v>2.538213707664756</v>
@@ -95859,63 +95859,63 @@
     </row>
     <row r="1874" spans="1:16">
       <c r="A1874" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1874" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C1874">
-        <v>0.6665846755195202</v>
+        <v>0.7455598241332364</v>
       </c>
       <c r="D1874" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E1874">
-        <v>0.9742521665339288</v>
+        <v>1.020394428234143</v>
       </c>
       <c r="F1874">
         <v>1</v>
       </c>
       <c r="G1874">
-        <v>0.008073415324480481</v>
+        <v>0.006474440175866764</v>
       </c>
       <c r="H1874">
-        <v>0.009065747833466069</v>
+        <v>0.006439605571765857</v>
       </c>
       <c r="I1874">
-        <v>0.3076674910144086</v>
+        <v>0.2748346041009064</v>
       </c>
       <c r="J1874">
-        <v>0.7780284295127059</v>
+        <v>0.7741730205045306</v>
       </c>
       <c r="K1874">
-        <v>4.76</v>
+        <v>3.7</v>
       </c>
       <c r="L1874">
-        <v>4.37</v>
+        <v>3.61</v>
       </c>
       <c r="M1874">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="N1874">
-        <v>5.02</v>
+        <v>3.73</v>
       </c>
       <c r="O1874">
         <v>1</v>
       </c>
       <c r="P1874" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="1875" spans="1:16">
       <c r="A1875" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1875" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C1875">
-        <v>0.6809789896169787</v>
+        <v>0.6665846755195202</v>
       </c>
       <c r="D1875" t="s">
         <v>443</v>
@@ -95927,22 +95927,22 @@
         <v>1</v>
       </c>
       <c r="G1875">
-        <v>0.008399021010383022</v>
+        <v>0.008073415324480481</v>
       </c>
       <c r="H1875">
         <v>0.009065747833466069</v>
       </c>
       <c r="I1875">
-        <v>0.2932731769169501</v>
+        <v>0.3076674910144086</v>
       </c>
       <c r="J1875">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1875">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="L1875">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1875">
         <v>5.2</v>
@@ -95959,13 +95959,13 @@
     </row>
     <row r="1876" spans="1:16">
       <c r="A1876" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1876" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C1876">
-        <v>0.7043198425023602</v>
+        <v>0.6809789896169787</v>
       </c>
       <c r="D1876" t="s">
         <v>443</v>
@@ -95977,19 +95977,19 @@
         <v>1</v>
       </c>
       <c r="G1876">
-        <v>0.008375680157497642</v>
+        <v>0.008399021010383022</v>
       </c>
       <c r="H1876">
         <v>0.009065747833466069</v>
       </c>
       <c r="I1876">
-        <v>0.2699323240315685</v>
+        <v>0.2932731769169501</v>
       </c>
       <c r="J1876">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1876">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="L1876">
         <v>4.54</v>
@@ -96009,46 +96009,46 @@
     </row>
     <row r="1877" spans="1:16">
       <c r="A1877" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1877" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1877">
-        <v>1.313846110723346</v>
+        <v>0.7043198425023602</v>
       </c>
       <c r="D1877" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E1877">
-        <v>0.9045905463760819</v>
+        <v>0.9742521665339288</v>
       </c>
       <c r="F1877">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1877">
-        <v>0.01192615388927666</v>
+        <v>0.008375680157497642</v>
       </c>
       <c r="H1877">
-        <v>0.006895409453623918</v>
+        <v>0.009065747833466069</v>
       </c>
       <c r="I1877">
-        <v>0.409255564347264</v>
+        <v>0.2699323240315685</v>
       </c>
       <c r="J1877">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1877">
-        <v>6.82</v>
+        <v>4.93</v>
       </c>
       <c r="L1877">
-        <v>6.62</v>
+        <v>4.54</v>
       </c>
       <c r="M1877">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="N1877">
-        <v>3.9</v>
+        <v>5.02</v>
       </c>
       <c r="O1877">
         <v>1</v>
@@ -96059,13 +96059,13 @@
     </row>
     <row r="1878" spans="1:16">
       <c r="A1878" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1878" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1878">
-        <v>1.204432635783077</v>
+        <v>1.313846110723346</v>
       </c>
       <c r="D1878" t="s">
         <v>446</v>
@@ -96077,22 +96077,22 @@
         <v>-1</v>
       </c>
       <c r="G1878">
-        <v>0.008175567364216924</v>
+        <v>0.01192615388927666</v>
       </c>
       <c r="H1878">
         <v>0.006895409453623918</v>
       </c>
       <c r="I1878">
-        <v>0.2998420894069955</v>
+        <v>0.409255564347264</v>
       </c>
       <c r="J1878">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1878">
-        <v>4.48</v>
+        <v>6.82</v>
       </c>
       <c r="L1878">
-        <v>4.69</v>
+        <v>6.62</v>
       </c>
       <c r="M1878">
         <v>3.85</v>
@@ -96109,13 +96109,13 @@
     </row>
     <row r="1879" spans="1:16">
       <c r="A1879" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1879" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C1879">
-        <v>1.122167802765917</v>
+        <v>1.204432635783077</v>
       </c>
       <c r="D1879" t="s">
         <v>446</v>
@@ -96127,22 +96127,22 @@
         <v>-1</v>
       </c>
       <c r="G1879">
-        <v>0.008357832197234084</v>
+        <v>0.008175567364216924</v>
       </c>
       <c r="H1879">
         <v>0.006895409453623918</v>
       </c>
       <c r="I1879">
-        <v>0.2175772563898355</v>
+        <v>0.2998420894069955</v>
       </c>
       <c r="J1879">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1879">
-        <v>4.65</v>
+        <v>4.48</v>
       </c>
       <c r="L1879">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="M1879">
         <v>3.85</v>
@@ -96159,46 +96159,46 @@
     </row>
     <row r="1880" spans="1:16">
       <c r="A1880" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1880" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C1880">
-        <v>0.6979313992614635</v>
+        <v>1.122167802765917</v>
       </c>
       <c r="D1880" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E1880">
-        <v>1.00690049670553</v>
+        <v>0.9045905463760819</v>
       </c>
       <c r="F1880">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1880">
-        <v>0.006642068600738536</v>
+        <v>0.008357832197234084</v>
       </c>
       <c r="H1880">
-        <v>0.006453099503294471</v>
+        <v>0.006895409453623918</v>
       </c>
       <c r="I1880">
-        <v>0.308969097444066</v>
+        <v>0.2175772563898355</v>
       </c>
       <c r="J1880">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1880">
-        <v>3.82</v>
+        <v>4.65</v>
       </c>
       <c r="L1880">
-        <v>3.67</v>
+        <v>4.74</v>
       </c>
       <c r="M1880">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="N1880">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="O1880">
         <v>1</v>
@@ -96209,13 +96209,13 @@
     </row>
     <row r="1881" spans="1:16">
       <c r="A1881" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1881" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C1881">
-        <v>0.731294810802988</v>
+        <v>0.6979313992614635</v>
       </c>
       <c r="D1881" t="s">
         <v>447</v>
@@ -96227,22 +96227,22 @@
         <v>1</v>
       </c>
       <c r="G1881">
-        <v>0.006488705189197011</v>
+        <v>0.006642068600738536</v>
       </c>
       <c r="H1881">
         <v>0.006453099503294471</v>
       </c>
       <c r="I1881">
-        <v>0.2756056859025415</v>
+        <v>0.308969097444066</v>
       </c>
       <c r="J1881">
         <v>0.7780284295127059</v>
       </c>
       <c r="K1881">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="L1881">
-        <v>3.61</v>
+        <v>3.67</v>
       </c>
       <c r="M1881">
         <v>3.5</v>
@@ -96259,63 +96259,63 @@
     </row>
     <row r="1882" spans="1:16">
       <c r="A1882" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1882" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C1882">
-        <v>0.6227397035253315</v>
+        <v>0.7346356636883691</v>
       </c>
       <c r="D1882" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E1882">
-        <v>0.9263542979688486</v>
+        <v>1.00690049670553</v>
       </c>
       <c r="F1882">
         <v>1</v>
       </c>
       <c r="G1882">
-        <v>0.008117260296474669</v>
+        <v>0.006445364336311631</v>
       </c>
       <c r="H1882">
-        <v>0.00911364570203115</v>
+        <v>0.006453099503294471</v>
       </c>
       <c r="I1882">
-        <v>0.3036145944435171</v>
+        <v>0.2722648330171604</v>
       </c>
       <c r="J1882">
-        <v>0.7872395580829136</v>
+        <v>0.7780284295127059</v>
       </c>
       <c r="K1882">
-        <v>4.76</v>
+        <v>3.67</v>
       </c>
       <c r="L1882">
-        <v>4.37</v>
+        <v>3.59</v>
       </c>
       <c r="M1882">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="N1882">
-        <v>5.02</v>
+        <v>3.73</v>
       </c>
       <c r="O1882">
         <v>1</v>
       </c>
       <c r="P1882" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="1883" spans="1:16">
       <c r="A1883" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1883" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C1883">
-        <v>0.6352917919087488</v>
+        <v>0.6227397035253315</v>
       </c>
       <c r="D1883" t="s">
         <v>443</v>
@@ -96327,22 +96327,22 @@
         <v>1</v>
       </c>
       <c r="G1883">
-        <v>0.008444708208091251</v>
+        <v>0.008117260296474669</v>
       </c>
       <c r="H1883">
         <v>0.00911364570203115</v>
       </c>
       <c r="I1883">
-        <v>0.2910625060600998</v>
+        <v>0.3036145944435171</v>
       </c>
       <c r="J1883">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1883">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="L1883">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1883">
         <v>5.2</v>
@@ -96359,13 +96359,13 @@
     </row>
     <row r="1884" spans="1:16">
       <c r="A1884" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1884" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C1884">
-        <v>0.6589089786512363</v>
+        <v>0.6352917919087488</v>
       </c>
       <c r="D1884" t="s">
         <v>443</v>
@@ -96377,19 +96377,19 @@
         <v>1</v>
       </c>
       <c r="G1884">
-        <v>0.008421091021348763</v>
+        <v>0.008444708208091251</v>
       </c>
       <c r="H1884">
         <v>0.00911364570203115</v>
       </c>
       <c r="I1884">
-        <v>0.2674453193176123</v>
+        <v>0.2910625060600998</v>
       </c>
       <c r="J1884">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1884">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="L1884">
         <v>4.54</v>
@@ -96409,46 +96409,46 @@
     </row>
     <row r="1885" spans="1:16">
       <c r="A1885" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1885" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1885">
-        <v>1.251026213874529</v>
+        <v>0.6589089786512363</v>
       </c>
       <c r="D1885" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E1885">
-        <v>0.8691277013807825</v>
+        <v>0.9263542979688486</v>
       </c>
       <c r="F1885">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1885">
-        <v>0.01198897378612547</v>
+        <v>0.008421091021348763</v>
       </c>
       <c r="H1885">
-        <v>0.006930872298619217</v>
+        <v>0.00911364570203115</v>
       </c>
       <c r="I1885">
-        <v>0.3818985124937466</v>
+        <v>0.2674453193176123</v>
       </c>
       <c r="J1885">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1885">
-        <v>6.82</v>
+        <v>4.93</v>
       </c>
       <c r="L1885">
-        <v>6.62</v>
+        <v>4.54</v>
       </c>
       <c r="M1885">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="N1885">
-        <v>3.9</v>
+        <v>5.02</v>
       </c>
       <c r="O1885">
         <v>1</v>
@@ -96459,13 +96459,13 @@
     </row>
     <row r="1886" spans="1:16">
       <c r="A1886" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1886" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1886">
-        <v>1.163166779788547</v>
+        <v>1.251026213874529</v>
       </c>
       <c r="D1886" t="s">
         <v>446</v>
@@ -96477,22 +96477,22 @@
         <v>-1</v>
       </c>
       <c r="G1886">
-        <v>0.008216833220211455</v>
+        <v>0.01198897378612547</v>
       </c>
       <c r="H1886">
         <v>0.006930872298619217</v>
       </c>
       <c r="I1886">
-        <v>0.2940390784077649</v>
+        <v>0.3818985124937466</v>
       </c>
       <c r="J1886">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1886">
-        <v>4.48</v>
+        <v>6.82</v>
       </c>
       <c r="L1886">
-        <v>4.69</v>
+        <v>6.62</v>
       </c>
       <c r="M1886">
         <v>3.85</v>
@@ -96509,13 +96509,13 @@
     </row>
     <row r="1887" spans="1:16">
       <c r="A1887" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1887" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C1887">
-        <v>1.079336054914452</v>
+        <v>1.163166779788547</v>
       </c>
       <c r="D1887" t="s">
         <v>446</v>
@@ -96527,22 +96527,22 @@
         <v>-1</v>
       </c>
       <c r="G1887">
-        <v>0.008400663945085549</v>
+        <v>0.008216833220211455</v>
       </c>
       <c r="H1887">
         <v>0.006930872298619217</v>
       </c>
       <c r="I1887">
-        <v>0.2102083535336692</v>
+        <v>0.2940390784077649</v>
       </c>
       <c r="J1887">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1887">
-        <v>4.65</v>
+        <v>4.48</v>
       </c>
       <c r="L1887">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="M1887">
         <v>3.85</v>
@@ -96559,46 +96559,46 @@
     </row>
     <row r="1888" spans="1:16">
       <c r="A1888" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1888" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C1888">
-        <v>0.66274488812327</v>
+        <v>1.079336054914452</v>
       </c>
       <c r="D1888" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1888">
-        <v>0.8904063378714606</v>
+        <v>0.8691277013807825</v>
       </c>
       <c r="F1888">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1888">
-        <v>0.00667725511187673</v>
+        <v>0.008400663945085549</v>
       </c>
       <c r="H1888">
-        <v>0.006369593662128539</v>
+        <v>0.006930872298619217</v>
       </c>
       <c r="I1888">
-        <v>0.2276614497481906</v>
+        <v>0.2102083535336692</v>
       </c>
       <c r="J1888">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1888">
-        <v>3.82</v>
+        <v>4.65</v>
       </c>
       <c r="L1888">
-        <v>3.67</v>
+        <v>4.74</v>
       </c>
       <c r="M1888">
-        <v>3.48</v>
+        <v>3.85</v>
       </c>
       <c r="N1888">
-        <v>3.63</v>
+        <v>3.9</v>
       </c>
       <c r="O1888">
         <v>1</v>
@@ -96609,13 +96609,13 @@
     </row>
     <row r="1889" spans="1:16">
       <c r="A1889" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1889" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C1889">
-        <v>0.6972136350932194</v>
+        <v>0.66274488812327</v>
       </c>
       <c r="D1889" t="s">
         <v>448</v>
@@ -96627,22 +96627,22 @@
         <v>1</v>
       </c>
       <c r="G1889">
-        <v>0.00652278636490678</v>
+        <v>0.00667725511187673</v>
       </c>
       <c r="H1889">
         <v>0.006369593662128539</v>
       </c>
       <c r="I1889">
-        <v>0.1931927027782412</v>
+        <v>0.2276614497481906</v>
       </c>
       <c r="J1889">
         <v>0.7872395580829136</v>
       </c>
       <c r="K1889">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="L1889">
-        <v>3.61</v>
+        <v>3.67</v>
       </c>
       <c r="M1889">
         <v>3.48</v>
@@ -96659,63 +96659,63 @@
     </row>
     <row r="1890" spans="1:16">
       <c r="A1890" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1890" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C1890">
-        <v>0.5854580999890051</v>
+        <v>0.7008308218357073</v>
       </c>
       <c r="D1890" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E1890">
-        <v>0.8856264957863074</v>
+        <v>0.8904063378714606</v>
       </c>
       <c r="F1890">
         <v>1</v>
       </c>
       <c r="G1890">
-        <v>0.008154541900010996</v>
+        <v>0.006479169178164293</v>
       </c>
       <c r="H1890">
-        <v>0.00915437350421369</v>
+        <v>0.006369593662128539</v>
       </c>
       <c r="I1890">
-        <v>0.3001683957973023</v>
+        <v>0.1895755160357533</v>
       </c>
       <c r="J1890">
-        <v>0.7950718277334023</v>
+        <v>0.7872395580829136</v>
       </c>
       <c r="K1890">
-        <v>4.76</v>
+        <v>3.67</v>
       </c>
       <c r="L1890">
-        <v>4.37</v>
+        <v>3.59</v>
       </c>
       <c r="M1890">
-        <v>5.2</v>
+        <v>3.48</v>
       </c>
       <c r="N1890">
-        <v>5.02</v>
+        <v>3.63</v>
       </c>
       <c r="O1890">
         <v>1</v>
       </c>
       <c r="P1890" t="s">
-        <v>225</v>
+        <v>429</v>
       </c>
     </row>
     <row r="1891" spans="1:16">
       <c r="A1891" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1891" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C1891">
-        <v>0.5964437344423246</v>
+        <v>0.5854580999890051</v>
       </c>
       <c r="D1891" t="s">
         <v>443</v>
@@ -96727,22 +96727,22 @@
         <v>1</v>
       </c>
       <c r="G1891">
-        <v>0.008483556265557676</v>
+        <v>0.008154541900010996</v>
       </c>
       <c r="H1891">
         <v>0.00915437350421369</v>
       </c>
       <c r="I1891">
-        <v>0.2891827613439828</v>
+        <v>0.3001683957973023</v>
       </c>
       <c r="J1891">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1891">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="L1891">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1891">
         <v>5.2</v>
@@ -96759,13 +96759,13 @@
     </row>
     <row r="1892" spans="1:16">
       <c r="A1892" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1892" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C1892">
-        <v>0.6202958892743267</v>
+        <v>0.5964437344423246</v>
       </c>
       <c r="D1892" t="s">
         <v>443</v>
@@ -96777,19 +96777,19 @@
         <v>1</v>
       </c>
       <c r="G1892">
-        <v>0.008459704110725675</v>
+        <v>0.008483556265557676</v>
       </c>
       <c r="H1892">
         <v>0.00915437350421369</v>
       </c>
       <c r="I1892">
-        <v>0.2653306065119807</v>
+        <v>0.2891827613439828</v>
       </c>
       <c r="J1892">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1892">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="L1892">
         <v>4.54</v>
@@ -96809,46 +96809,46 @@
     </row>
     <row r="1893" spans="1:16">
       <c r="A1893" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1893" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1893">
-        <v>1.197610134858196</v>
+        <v>0.6202958892743267</v>
       </c>
       <c r="D1893" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E1893">
-        <v>0.838973463226401</v>
+        <v>0.8856264957863074</v>
       </c>
       <c r="F1893">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1893">
-        <v>0.0120423898651418</v>
+        <v>0.008459704110725675</v>
       </c>
       <c r="H1893">
-        <v>0.006961026536773598</v>
+        <v>0.00915437350421369</v>
       </c>
       <c r="I1893">
-        <v>0.3586366716317948</v>
+        <v>0.2653306065119807</v>
       </c>
       <c r="J1893">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1893">
-        <v>6.82</v>
+        <v>4.93</v>
       </c>
       <c r="L1893">
-        <v>6.62</v>
+        <v>4.54</v>
       </c>
       <c r="M1893">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="N1893">
-        <v>3.9</v>
+        <v>5.02</v>
       </c>
       <c r="O1893">
         <v>1</v>
@@ -96859,13 +96859,13 @@
     </row>
     <row r="1894" spans="1:16">
       <c r="A1894" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1894" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C1894">
-        <v>1.10776616049025</v>
+        <v>1.197610134858196</v>
       </c>
       <c r="D1894" t="s">
         <v>446</v>
@@ -96877,22 +96877,22 @@
         <v>-1</v>
       </c>
       <c r="G1894">
-        <v>0.01071223383950975</v>
+        <v>0.0120423898651418</v>
       </c>
       <c r="H1894">
         <v>0.006961026536773598</v>
       </c>
       <c r="I1894">
-        <v>0.2687926972638492</v>
+        <v>0.3586366716317948</v>
       </c>
       <c r="J1894">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1894">
-        <v>6.04</v>
+        <v>6.82</v>
       </c>
       <c r="L1894">
-        <v>5.91</v>
+        <v>6.62</v>
       </c>
       <c r="M1894">
         <v>3.85</v>
@@ -96909,13 +96909,13 @@
     </row>
     <row r="1895" spans="1:16">
       <c r="A1895" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1895" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C1895">
-        <v>1.128078211754358</v>
+        <v>1.10776616049025</v>
       </c>
       <c r="D1895" t="s">
         <v>446</v>
@@ -96927,22 +96927,22 @@
         <v>-1</v>
       </c>
       <c r="G1895">
-        <v>0.008251921788245643</v>
+        <v>0.01071223383950975</v>
       </c>
       <c r="H1895">
         <v>0.006961026536773598</v>
       </c>
       <c r="I1895">
-        <v>0.2891047485279565</v>
+        <v>0.2687926972638492</v>
       </c>
       <c r="J1895">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1895">
-        <v>4.48</v>
+        <v>6.04</v>
       </c>
       <c r="L1895">
-        <v>4.69</v>
+        <v>5.91</v>
       </c>
       <c r="M1895">
         <v>3.85</v>
@@ -96959,13 +96959,13 @@
     </row>
     <row r="1896" spans="1:16">
       <c r="A1896" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1896" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C1896">
-        <v>1.042916001039679</v>
+        <v>1.128078211754358</v>
       </c>
       <c r="D1896" t="s">
         <v>446</v>
@@ -96977,22 +96977,22 @@
         <v>-1</v>
       </c>
       <c r="G1896">
-        <v>0.008437083998960322</v>
+        <v>0.008251921788245643</v>
       </c>
       <c r="H1896">
         <v>0.006961026536773598</v>
       </c>
       <c r="I1896">
-        <v>0.203942537813278</v>
+        <v>0.2891047485279565</v>
       </c>
       <c r="J1896">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1896">
-        <v>4.65</v>
+        <v>4.48</v>
       </c>
       <c r="L1896">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="M1896">
         <v>3.85</v>
@@ -97009,46 +97009,46 @@
     </row>
     <row r="1897" spans="1:16">
       <c r="A1897" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1897" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C1897">
-        <v>0.6328256180584031</v>
+        <v>1.042916001039679</v>
       </c>
       <c r="D1897" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1897">
-        <v>0.8631500394877598</v>
+        <v>0.838973463226401</v>
       </c>
       <c r="F1897">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1897">
-        <v>0.006707174381941597</v>
+        <v>0.008437083998960322</v>
       </c>
       <c r="H1897">
-        <v>0.006396849960512241</v>
+        <v>0.006961026536773598</v>
       </c>
       <c r="I1897">
-        <v>0.2303244214293567</v>
+        <v>0.203942537813278</v>
       </c>
       <c r="J1897">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1897">
-        <v>3.82</v>
+        <v>4.65</v>
       </c>
       <c r="L1897">
-        <v>3.67</v>
+        <v>4.74</v>
       </c>
       <c r="M1897">
-        <v>3.48</v>
+        <v>3.85</v>
       </c>
       <c r="N1897">
-        <v>3.63</v>
+        <v>3.9</v>
       </c>
       <c r="O1897">
         <v>1</v>
@@ -97059,13 +97059,13 @@
     </row>
     <row r="1898" spans="1:16">
       <c r="A1898" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1898" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C1898">
-        <v>0.6720863922184135</v>
+        <v>0.6328256180584031</v>
       </c>
       <c r="D1898" t="s">
         <v>448</v>
@@ -97077,22 +97077,22 @@
         <v>1</v>
       </c>
       <c r="G1898">
-        <v>0.006507913607781586</v>
+        <v>0.006707174381941597</v>
       </c>
       <c r="H1898">
         <v>0.006396849960512241</v>
       </c>
       <c r="I1898">
-        <v>0.1910636472693463</v>
+        <v>0.2303244214293567</v>
       </c>
       <c r="J1898">
         <v>0.7950718277334023</v>
       </c>
       <c r="K1898">
+        <v>3.82</v>
+      </c>
+      <c r="L1898">
         <v>3.67</v>
-      </c>
-      <c r="L1898">
-        <v>3.59</v>
       </c>
       <c r="M1898">
         <v>3.48</v>
@@ -97109,63 +97109,63 @@
     </row>
     <row r="1899" spans="1:16">
       <c r="A1899" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1899" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C1899">
-        <v>0.5696561779646796</v>
+        <v>0.6720863922184135</v>
       </c>
       <c r="D1899" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E1899">
-        <v>0.8683638918941865</v>
+        <v>0.8631500394877598</v>
       </c>
       <c r="F1899">
         <v>1</v>
       </c>
       <c r="G1899">
-        <v>0.00817034382203532</v>
+        <v>0.006507913607781586</v>
       </c>
       <c r="H1899">
-        <v>0.009171636108105811</v>
+        <v>0.006396849960512241</v>
       </c>
       <c r="I1899">
-        <v>0.2987077139295069</v>
+        <v>0.1910636472693463</v>
       </c>
       <c r="J1899">
-        <v>0.7983915592511178</v>
+        <v>0.7950718277334023</v>
       </c>
       <c r="K1899">
-        <v>4.76</v>
+        <v>3.67</v>
       </c>
       <c r="L1899">
-        <v>4.37</v>
+        <v>3.59</v>
       </c>
       <c r="M1899">
-        <v>5.2</v>
+        <v>3.48</v>
       </c>
       <c r="N1899">
-        <v>5.02</v>
+        <v>3.63</v>
       </c>
       <c r="O1899">
         <v>1</v>
       </c>
       <c r="P1899" t="s">
-        <v>431</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1900" spans="1:16">
       <c r="A1900" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1900" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C1900">
-        <v>0.5799778661144557</v>
+        <v>0.5696561779646796</v>
       </c>
       <c r="D1900" t="s">
         <v>443</v>
@@ -97177,22 +97177,22 @@
         <v>1</v>
       </c>
       <c r="G1900">
-        <v>0.008500022133885544</v>
+        <v>0.00817034382203532</v>
       </c>
       <c r="H1900">
         <v>0.009171636108105811</v>
       </c>
       <c r="I1900">
-        <v>0.2883860257797308</v>
+        <v>0.2987077139295069</v>
       </c>
       <c r="J1900">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1900">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="L1900">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="M1900">
         <v>5.2</v>
@@ -97209,13 +97209,13 @@
     </row>
     <row r="1901" spans="1:16">
       <c r="A1901" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1901" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C1901">
-        <v>0.6039296128919895</v>
+        <v>0.5799778661144557</v>
       </c>
       <c r="D1901" t="s">
         <v>443</v>
@@ -97227,19 +97227,19 @@
         <v>1</v>
       </c>
       <c r="G1901">
-        <v>0.008476070387108009</v>
+        <v>0.008500022133885544</v>
       </c>
       <c r="H1901">
         <v>0.009171636108105811</v>
       </c>
       <c r="I1901">
-        <v>0.264434279002197</v>
+        <v>0.2883860257797308</v>
       </c>
       <c r="J1901">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1901">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="L1901">
         <v>4.54</v>
@@ -97259,46 +97259,46 @@
     </row>
     <row r="1902" spans="1:16">
       <c r="A1902" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1902" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1902">
-        <v>1.174969565907376</v>
+        <v>0.6039296128919895</v>
       </c>
       <c r="D1902" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E1902">
-        <v>0.8261924968831962</v>
+        <v>0.8683638918941865</v>
       </c>
       <c r="F1902">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1902">
-        <v>0.01206503043409262</v>
+        <v>0.008476070387108009</v>
       </c>
       <c r="H1902">
-        <v>0.006973807503116805</v>
+        <v>0.009171636108105811</v>
       </c>
       <c r="I1902">
-        <v>0.3487770690241798</v>
+        <v>0.264434279002197</v>
       </c>
       <c r="J1902">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1902">
-        <v>6.82</v>
+        <v>4.93</v>
       </c>
       <c r="L1902">
-        <v>6.62</v>
+        <v>4.54</v>
       </c>
       <c r="M1902">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="N1902">
-        <v>3.9</v>
+        <v>5.02</v>
       </c>
       <c r="O1902">
         <v>1</v>
@@ -97309,13 +97309,13 @@
     </row>
     <row r="1903" spans="1:16">
       <c r="A1903" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1903" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C1903">
-        <v>1.179811488568181</v>
+        <v>1.174969565907376</v>
       </c>
       <c r="D1903" t="s">
         <v>446</v>
@@ -97327,22 +97327,22 @@
         <v>-1</v>
       </c>
       <c r="G1903">
-        <v>0.01092018851143182</v>
+        <v>0.01206503043409262</v>
       </c>
       <c r="H1903">
         <v>0.006973807503116805</v>
       </c>
       <c r="I1903">
-        <v>0.3536189916849852</v>
+        <v>0.3487770690241798</v>
       </c>
       <c r="J1903">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1903">
-        <v>6.1</v>
+        <v>6.82</v>
       </c>
       <c r="L1903">
-        <v>6.05</v>
+        <v>6.62</v>
       </c>
       <c r="M1903">
         <v>3.85</v>
@@ -97359,10 +97359,10 @@
     </row>
     <row r="1904" spans="1:16">
       <c r="A1904" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1904" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1904">
         <v>1.087714982123249</v>
@@ -97409,7 +97409,7 @@
     </row>
     <row r="1905" spans="1:16">
       <c r="A1905" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1905" t="s">
         <v>257</v>
@@ -97459,7 +97459,7 @@
     </row>
     <row r="1906" spans="1:16">
       <c r="A1906" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1906" t="s">
         <v>258</v>
@@ -97509,7 +97509,7 @@
     </row>
     <row r="1907" spans="1:16">
       <c r="A1907" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1907" t="s">
         <v>259</v>
@@ -97559,10 +97559,10 @@
     </row>
     <row r="1908" spans="1:16">
       <c r="A1908" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1908" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C1908">
         <v>0.6599029775483976</v>
@@ -97612,7 +97612,7 @@
         <v>0</v>
       </c>
       <c r="B1909" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C1909">
         <v>0.580033038204439</v>
@@ -97762,7 +97762,7 @@
         <v>3</v>
       </c>
       <c r="B1912" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1912">
         <v>0.5518576103909849</v>
@@ -97862,7 +97862,7 @@
         <v>5</v>
       </c>
       <c r="B1914" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C1914">
         <v>1.059129890337926</v>
@@ -97912,7 +97912,7 @@
         <v>6</v>
       </c>
       <c r="B1915" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1915">
         <v>0.9682204160067345</v>
@@ -98112,7 +98112,7 @@
         <v>10</v>
       </c>
       <c r="B1919" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C1919">
         <v>0.5872961799246212</v>
@@ -98212,7 +98212,7 @@
         <v>1</v>
       </c>
       <c r="B1921" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C1921">
         <v>0.8894240809811436</v>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -1363,10 +1363,10 @@
     <t>2021-11-30</t>
   </si>
   <si>
-    <t>2021-09-07</t>
+    <t>2021-09-24</t>
   </si>
   <si>
-    <t>2021-09-24</t>
+    <t>2021-09-07</t>
   </si>
   <si>
     <t>2021-11-29</t>
@@ -97318,10 +97318,10 @@
         <v>1.174969565907376</v>
       </c>
       <c r="D1903" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E1903">
-        <v>0.8261924968831962</v>
+        <v>1.281993950521945</v>
       </c>
       <c r="F1903">
         <v>-1</v>
@@ -97330,10 +97330,10 @@
         <v>0.01206503043409262</v>
       </c>
       <c r="H1903">
-        <v>0.006973807503116805</v>
+        <v>0.009218006049478056</v>
       </c>
       <c r="I1903">
-        <v>0.3487770690241798</v>
+        <v>-0.1070243846145686</v>
       </c>
       <c r="J1903">
         <v>0.7983915592511178</v>
@@ -97345,10 +97345,10 @@
         <v>6.62</v>
       </c>
       <c r="M1903">
-        <v>3.85</v>
+        <v>4.97</v>
       </c>
       <c r="N1903">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="O1903">
         <v>1</v>
@@ -97368,10 +97368,10 @@
         <v>1.087714982123249</v>
       </c>
       <c r="D1904" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E1904">
-        <v>0.8261924968831962</v>
+        <v>1.281993950521945</v>
       </c>
       <c r="F1904">
         <v>-1</v>
@@ -97380,10 +97380,10 @@
         <v>0.01073228501787675</v>
       </c>
       <c r="H1904">
-        <v>0.006973807503116805</v>
+        <v>0.009218006049478056</v>
       </c>
       <c r="I1904">
-        <v>0.2615224852400524</v>
+        <v>-0.1942789683986961</v>
       </c>
       <c r="J1904">
         <v>0.7983915592511178</v>
@@ -97395,10 +97395,10 @@
         <v>5.91</v>
       </c>
       <c r="M1904">
-        <v>3.85</v>
+        <v>4.97</v>
       </c>
       <c r="N1904">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="O1904">
         <v>1</v>
@@ -97768,7 +97768,7 @@
         <v>0.5518576103909849</v>
       </c>
       <c r="D1912" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E1912">
         <v>0.7845874392656027</v>
@@ -97818,7 +97818,7 @@
         <v>1.040043582312239</v>
       </c>
       <c r="D1913" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E1913">
         <v>1.183668123767131</v>
@@ -97868,7 +97868,7 @@
         <v>1.059129890337926</v>
       </c>
       <c r="D1914" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E1914">
         <v>1.183668123767131</v>
@@ -97918,7 +97918,7 @@
         <v>0.9682204160067345</v>
       </c>
       <c r="D1915" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E1915">
         <v>1.183668123767131</v>

--- a/s60_signal/position-00347-000898.xlsx
+++ b/s60_signal/position-00347-000898.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5784" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5790" uniqueCount="611">
   <si>
     <t>trade_time</t>
   </si>
@@ -802,13 +802,13 @@
     <t>2021-09-16</t>
   </si>
   <si>
-    <t>2021-07-26</t>
-  </si>
-  <si>
     <t>2021-09-06</t>
   </si>
   <si>
     <t>2021-09-14</t>
+  </si>
+  <si>
+    <t>2021-07-26</t>
   </si>
   <si>
     <t>2021-09-02</t>
@@ -1360,10 +1360,10 @@
     <t>2021-11-30</t>
   </si>
   <si>
-    <t>2021-09-24</t>
+    <t>2021-09-07</t>
   </si>
   <si>
-    <t>2021-09-07</t>
+    <t>2021-09-24</t>
   </si>
   <si>
     <t>2021-11-29</t>
@@ -2204,7 +2204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1924"/>
+  <dimension ref="A1:P1926"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -87715,7 +87715,7 @@
         <v>2.431411491361336</v>
       </c>
       <c r="D1711" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E1711">
         <v>2.538213707664756</v>
@@ -87765,7 +87765,7 @@
         <v>2.532009684902152</v>
       </c>
       <c r="D1712" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E1712">
         <v>2.538213707664756</v>
@@ -87815,7 +87815,7 @@
         <v>2.427002049221179</v>
       </c>
       <c r="D1713" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E1713">
         <v>2.538213707664756</v>
@@ -87865,7 +87865,7 @@
         <v>2.549425366108334</v>
       </c>
       <c r="D1714" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E1714">
         <v>2.538213707664756</v>
@@ -96615,10 +96615,10 @@
         <v>0.66274488812327</v>
       </c>
       <c r="D1889" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E1889">
-        <v>0.8904063378714606</v>
+        <v>0.9746615467098025</v>
       </c>
       <c r="F1889">
         <v>1</v>
@@ -96627,10 +96627,10 @@
         <v>0.00667725511187673</v>
       </c>
       <c r="H1889">
-        <v>0.006369593662128539</v>
+        <v>0.006485338453290197</v>
       </c>
       <c r="I1889">
-        <v>0.2276614497481906</v>
+        <v>0.3119166585865325</v>
       </c>
       <c r="J1889">
         <v>0.7872395580829136</v>
@@ -96642,10 +96642,10 @@
         <v>3.67</v>
       </c>
       <c r="M1889">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="N1889">
-        <v>3.63</v>
+        <v>3.73</v>
       </c>
       <c r="O1889">
         <v>1</v>
@@ -96665,10 +96665,10 @@
         <v>0.7008308218357073</v>
       </c>
       <c r="D1890" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E1890">
-        <v>0.8904063378714606</v>
+        <v>0.9746615467098025</v>
       </c>
       <c r="F1890">
         <v>1</v>
@@ -96677,10 +96677,10 @@
         <v>0.006479169178164293</v>
       </c>
       <c r="H1890">
-        <v>0.006369593662128539</v>
+        <v>0.006485338453290197</v>
       </c>
       <c r="I1890">
-        <v>0.1895755160357533</v>
+        <v>0.2738307248740952</v>
       </c>
       <c r="J1890">
         <v>0.7872395580829136</v>
@@ -96692,10 +96692,10 @@
         <v>3.59</v>
       </c>
       <c r="M1890">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="N1890">
-        <v>3.63</v>
+        <v>3.73</v>
       </c>
       <c r="O1890">
         <v>1</v>
@@ -97309,43 +97309,43 @@
         <v>3</v>
       </c>
       <c r="B1903" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C1903">
-        <v>1.174969565907376</v>
+        <v>0.673924079420603</v>
       </c>
       <c r="D1903" t="s">
         <v>448</v>
       </c>
       <c r="E1903">
-        <v>1.281993950521945</v>
+        <v>0.9145674557201557</v>
       </c>
       <c r="F1903">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1903">
-        <v>0.01206503043409262</v>
+        <v>0.0105260759205794</v>
       </c>
       <c r="H1903">
-        <v>0.009218006049478056</v>
+        <v>0.01140543254427984</v>
       </c>
       <c r="I1903">
-        <v>-0.1070243846145686</v>
+        <v>0.2406433762995528</v>
       </c>
       <c r="J1903">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1903">
-        <v>6.82</v>
+        <v>6.17</v>
       </c>
       <c r="L1903">
-        <v>6.62</v>
+        <v>5.6</v>
       </c>
       <c r="M1903">
-        <v>4.97</v>
+        <v>6.57</v>
       </c>
       <c r="N1903">
-        <v>5.25</v>
+        <v>6.16</v>
       </c>
       <c r="O1903">
         <v>1</v>
@@ -97359,13 +97359,13 @@
         <v>4</v>
       </c>
       <c r="B1904" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C1904">
-        <v>1.087714982123249</v>
+        <v>1.174969565907376</v>
       </c>
       <c r="D1904" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E1904">
         <v>1.281993950521945</v>
@@ -97374,22 +97374,22 @@
         <v>-1</v>
       </c>
       <c r="G1904">
-        <v>0.01073228501787675</v>
+        <v>0.01206503043409262</v>
       </c>
       <c r="H1904">
         <v>0.009218006049478056</v>
       </c>
       <c r="I1904">
-        <v>-0.1942789683986961</v>
+        <v>-0.1070243846145686</v>
       </c>
       <c r="J1904">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1904">
-        <v>6.04</v>
+        <v>6.82</v>
       </c>
       <c r="L1904">
-        <v>5.91</v>
+        <v>6.62</v>
       </c>
       <c r="M1904">
         <v>4.97</v>
@@ -97409,43 +97409,43 @@
         <v>5</v>
       </c>
       <c r="B1905" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1905">
-        <v>1.113205814554992</v>
+        <v>1.179811488568181</v>
       </c>
       <c r="D1905" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E1905">
-        <v>0.8261924968831962</v>
+        <v>1.281993950521945</v>
       </c>
       <c r="F1905">
         <v>-1</v>
       </c>
       <c r="G1905">
-        <v>0.008266794185445007</v>
+        <v>0.01092018851143182</v>
       </c>
       <c r="H1905">
-        <v>0.006973807503116805</v>
+        <v>0.009218006049478056</v>
       </c>
       <c r="I1905">
-        <v>0.2870133176717959</v>
+        <v>-0.1021824619537632</v>
       </c>
       <c r="J1905">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1905">
-        <v>4.48</v>
+        <v>6.1</v>
       </c>
       <c r="L1905">
-        <v>4.69</v>
+        <v>6.05</v>
       </c>
       <c r="M1905">
-        <v>3.85</v>
+        <v>4.97</v>
       </c>
       <c r="N1905">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="O1905">
         <v>1</v>
@@ -97459,43 +97459,43 @@
         <v>6</v>
       </c>
       <c r="B1906" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1906">
-        <v>1.027479249482302</v>
+        <v>1.087714982123249</v>
       </c>
       <c r="D1906" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E1906">
-        <v>0.8261924968831962</v>
+        <v>1.281993950521945</v>
       </c>
       <c r="F1906">
         <v>-1</v>
       </c>
       <c r="G1906">
-        <v>0.0084525207505177</v>
+        <v>0.01073228501787675</v>
       </c>
       <c r="H1906">
-        <v>0.006973807503116805</v>
+        <v>0.009218006049478056</v>
       </c>
       <c r="I1906">
-        <v>0.2012867525991058</v>
+        <v>-0.1942789683986961</v>
       </c>
       <c r="J1906">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1906">
-        <v>4.65</v>
+        <v>6.04</v>
       </c>
       <c r="L1906">
-        <v>4.74</v>
+        <v>5.91</v>
       </c>
       <c r="M1906">
-        <v>3.85</v>
+        <v>4.97</v>
       </c>
       <c r="N1906">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="O1906">
         <v>1</v>
@@ -97509,43 +97509,43 @@
         <v>7</v>
       </c>
       <c r="B1907" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C1907">
-        <v>0.6201442436607301</v>
+        <v>1.113205814554992</v>
       </c>
       <c r="D1907" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E1907">
-        <v>0.85159737380611</v>
+        <v>0.8261924968831962</v>
       </c>
       <c r="F1907">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1907">
-        <v>0.006719855756339269</v>
+        <v>0.008266794185445007</v>
       </c>
       <c r="H1907">
-        <v>0.006408402626193891</v>
+        <v>0.006973807503116805</v>
       </c>
       <c r="I1907">
-        <v>0.2314531301453799</v>
+        <v>0.2870133176717959</v>
       </c>
       <c r="J1907">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1907">
-        <v>3.82</v>
+        <v>4.48</v>
       </c>
       <c r="L1907">
-        <v>3.67</v>
+        <v>4.69</v>
       </c>
       <c r="M1907">
-        <v>3.48</v>
+        <v>3.85</v>
       </c>
       <c r="N1907">
-        <v>3.63</v>
+        <v>3.9</v>
       </c>
       <c r="O1907">
         <v>1</v>
@@ -97559,43 +97559,43 @@
         <v>8</v>
       </c>
       <c r="B1908" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C1908">
-        <v>0.6599029775483976</v>
+        <v>1.027479249482302</v>
       </c>
       <c r="D1908" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E1908">
-        <v>0.85159737380611</v>
+        <v>0.8261924968831962</v>
       </c>
       <c r="F1908">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1908">
-        <v>0.006520097022451602</v>
+        <v>0.0084525207505177</v>
       </c>
       <c r="H1908">
-        <v>0.006408402626193891</v>
+        <v>0.006973807503116805</v>
       </c>
       <c r="I1908">
-        <v>0.1916943962577125</v>
+        <v>0.2012867525991058</v>
       </c>
       <c r="J1908">
         <v>0.7983915592511178</v>
       </c>
       <c r="K1908">
-        <v>3.67</v>
+        <v>4.65</v>
       </c>
       <c r="L1908">
-        <v>3.59</v>
+        <v>4.74</v>
       </c>
       <c r="M1908">
-        <v>3.48</v>
+        <v>3.85</v>
       </c>
       <c r="N1908">
-        <v>3.63</v>
+        <v>3.9</v>
       </c>
       <c r="O1908">
         <v>1</v>
@@ -97606,146 +97606,146 @@
     </row>
     <row r="1909" spans="1:16">
       <c r="A1909" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1909" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C1909">
-        <v>0.580033038204439</v>
+        <v>0.6201442436607301</v>
       </c>
       <c r="D1909" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="E1909">
-        <v>0.331849878045265</v>
+        <v>0.85159737380611</v>
       </c>
       <c r="F1909">
         <v>1</v>
       </c>
       <c r="G1909">
-        <v>0.00903996696179556</v>
+        <v>0.006719855756339269</v>
       </c>
       <c r="H1909">
-        <v>0.008448150121954734</v>
+        <v>0.006408402626193891</v>
       </c>
       <c r="I1909">
-        <v>-0.248183160159174</v>
+        <v>0.2314531301453799</v>
       </c>
       <c r="J1909">
-        <v>0.8181754278134546</v>
+        <v>0.7983915592511178</v>
       </c>
       <c r="K1909">
-        <v>5.17</v>
+        <v>3.82</v>
       </c>
       <c r="L1909">
-        <v>4.81</v>
+        <v>3.67</v>
       </c>
       <c r="M1909">
-        <v>4.96</v>
+        <v>3.48</v>
       </c>
       <c r="N1909">
-        <v>4.39</v>
+        <v>3.63</v>
       </c>
       <c r="O1909">
         <v>1</v>
       </c>
       <c r="P1909" t="s">
-        <v>246</v>
+        <v>430</v>
       </c>
     </row>
     <row r="1910" spans="1:16">
       <c r="A1910" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B1910" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C1910">
-        <v>0.4818498780452654</v>
+        <v>0.6599029775483976</v>
       </c>
       <c r="D1910" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="E1910">
-        <v>0.331849878045265</v>
+        <v>0.85159737380611</v>
       </c>
       <c r="F1910">
         <v>1</v>
       </c>
       <c r="G1910">
-        <v>0.008598150121954735</v>
+        <v>0.006520097022451602</v>
       </c>
       <c r="H1910">
-        <v>0.008448150121954734</v>
+        <v>0.006408402626193891</v>
       </c>
       <c r="I1910">
-        <v>-0.1500000000000004</v>
+        <v>0.1916943962577125</v>
       </c>
       <c r="J1910">
-        <v>0.8181754278134546</v>
+        <v>0.7983915592511178</v>
       </c>
       <c r="K1910">
-        <v>4.96</v>
+        <v>3.67</v>
       </c>
       <c r="L1910">
-        <v>4.54</v>
+        <v>3.59</v>
       </c>
       <c r="M1910">
-        <v>4.96</v>
+        <v>3.48</v>
       </c>
       <c r="N1910">
-        <v>4.39</v>
+        <v>3.63</v>
       </c>
       <c r="O1910">
         <v>1</v>
       </c>
       <c r="P1910" t="s">
-        <v>246</v>
+        <v>430</v>
       </c>
     </row>
     <row r="1911" spans="1:16">
       <c r="A1911" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1911" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C1911">
-        <v>0.5518576103909849</v>
+        <v>0.580033038204439</v>
       </c>
       <c r="D1911" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="E1911">
-        <v>0.7845874392656027</v>
+        <v>0.331849878045265</v>
       </c>
       <c r="F1911">
         <v>1</v>
       </c>
       <c r="G1911">
-        <v>0.01064814238960901</v>
+        <v>0.00903996696179556</v>
       </c>
       <c r="H1911">
-        <v>0.0115354125607344</v>
+        <v>0.008448150121954734</v>
       </c>
       <c r="I1911">
-        <v>0.2327298288746178</v>
+        <v>-0.248183160159174</v>
       </c>
       <c r="J1911">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1911">
-        <v>6.17</v>
+        <v>5.17</v>
       </c>
       <c r="L1911">
-        <v>5.6</v>
+        <v>4.81</v>
       </c>
       <c r="M1911">
-        <v>6.57</v>
+        <v>4.96</v>
       </c>
       <c r="N1911">
-        <v>6.16</v>
+        <v>4.39</v>
       </c>
       <c r="O1911">
         <v>1</v>
@@ -97756,46 +97756,46 @@
     </row>
     <row r="1912" spans="1:16">
       <c r="A1912" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1912" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C1912">
-        <v>1.059129890337926</v>
+        <v>0.4818498780452654</v>
       </c>
       <c r="D1912" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="E1912">
-        <v>1.183668123767131</v>
+        <v>0.331849878045265</v>
       </c>
       <c r="F1912">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1912">
-        <v>0.01104087010966207</v>
+        <v>0.008598150121954735</v>
       </c>
       <c r="H1912">
-        <v>0.00931633187623287</v>
+        <v>0.008448150121954734</v>
       </c>
       <c r="I1912">
-        <v>-0.1245382334292042</v>
+        <v>-0.1500000000000004</v>
       </c>
       <c r="J1912">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1912">
-        <v>6.1</v>
+        <v>4.96</v>
       </c>
       <c r="L1912">
-        <v>6.05</v>
+        <v>4.54</v>
       </c>
       <c r="M1912">
-        <v>4.97</v>
+        <v>4.96</v>
       </c>
       <c r="N1912">
-        <v>5.25</v>
+        <v>4.39</v>
       </c>
       <c r="O1912">
         <v>1</v>
@@ -97806,46 +97806,46 @@
     </row>
     <row r="1913" spans="1:16">
       <c r="A1913" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1913" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1913">
-        <v>0.9682204160067345</v>
+        <v>0.5518576103909849</v>
       </c>
       <c r="D1913" t="s">
         <v>448</v>
       </c>
       <c r="E1913">
-        <v>1.183668123767131</v>
+        <v>0.7845874392656027</v>
       </c>
       <c r="F1913">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1913">
-        <v>0.01085177958399327</v>
+        <v>0.01064814238960901</v>
       </c>
       <c r="H1913">
-        <v>0.00931633187623287</v>
+        <v>0.0115354125607344</v>
       </c>
       <c r="I1913">
-        <v>-0.2154477077603962</v>
+        <v>0.2327298288746178</v>
       </c>
       <c r="J1913">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1913">
-        <v>6.04</v>
+        <v>6.17</v>
       </c>
       <c r="L1913">
-        <v>5.91</v>
+        <v>5.6</v>
       </c>
       <c r="M1913">
-        <v>4.97</v>
+        <v>6.57</v>
       </c>
       <c r="N1913">
-        <v>5.25</v>
+        <v>6.16</v>
       </c>
       <c r="O1913">
         <v>1</v>
@@ -97856,46 +97856,46 @@
     </row>
     <row r="1914" spans="1:16">
       <c r="A1914" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1914" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1914">
-        <v>1.024574083395723</v>
+        <v>1.059129890337926</v>
       </c>
       <c r="D1914" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E1914">
-        <v>0.7500246029181996</v>
+        <v>1.183668123767131</v>
       </c>
       <c r="F1914">
         <v>-1</v>
       </c>
       <c r="G1914">
-        <v>0.008355425916604278</v>
+        <v>0.01104087010966207</v>
       </c>
       <c r="H1914">
-        <v>0.007049975397081801</v>
+        <v>0.00931633187623287</v>
       </c>
       <c r="I1914">
-        <v>0.2745494804775235</v>
+        <v>-0.1245382334292042</v>
       </c>
       <c r="J1914">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1914">
-        <v>4.48</v>
+        <v>6.1</v>
       </c>
       <c r="L1914">
-        <v>4.69</v>
+        <v>6.05</v>
       </c>
       <c r="M1914">
-        <v>3.85</v>
+        <v>4.97</v>
       </c>
       <c r="N1914">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="O1914">
         <v>1</v>
@@ -97906,46 +97906,46 @@
     </row>
     <row r="1915" spans="1:16">
       <c r="A1915" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1915" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1915">
-        <v>0.9354842606674358</v>
+        <v>0.9682204160067345</v>
       </c>
       <c r="D1915" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E1915">
-        <v>0.7500246029181996</v>
+        <v>1.183668123767131</v>
       </c>
       <c r="F1915">
         <v>-1</v>
       </c>
       <c r="G1915">
-        <v>0.008544515739332565</v>
+        <v>0.01085177958399327</v>
       </c>
       <c r="H1915">
-        <v>0.007049975397081801</v>
+        <v>0.00931633187623287</v>
       </c>
       <c r="I1915">
-        <v>0.1854596577492362</v>
+        <v>-0.2154477077603962</v>
       </c>
       <c r="J1915">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1915">
-        <v>4.65</v>
+        <v>6.04</v>
       </c>
       <c r="L1915">
-        <v>4.74</v>
+        <v>5.91</v>
       </c>
       <c r="M1915">
-        <v>3.85</v>
+        <v>4.97</v>
       </c>
       <c r="N1915">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="O1915">
         <v>1</v>
@@ -97956,46 +97956,46 @@
     </row>
     <row r="1916" spans="1:16">
       <c r="A1916" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1916" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C1916">
-        <v>0.5445698657526035</v>
+        <v>1.024574083395723</v>
       </c>
       <c r="D1916" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="E1916">
-        <v>0.7736589855403704</v>
+        <v>0.7500246029181996</v>
       </c>
       <c r="F1916">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1916">
-        <v>0.006795430134247397</v>
+        <v>0.008355425916604278</v>
       </c>
       <c r="H1916">
-        <v>0.00656634101445963</v>
+        <v>0.007049975397081801</v>
       </c>
       <c r="I1916">
-        <v>0.2290891197877669</v>
+        <v>0.2745494804775235</v>
       </c>
       <c r="J1916">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1916">
-        <v>3.82</v>
+        <v>4.48</v>
       </c>
       <c r="L1916">
-        <v>3.67</v>
+        <v>4.69</v>
       </c>
       <c r="M1916">
-        <v>3.54</v>
+        <v>3.85</v>
       </c>
       <c r="N1916">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="O1916">
         <v>1</v>
@@ -98006,46 +98006,46 @@
     </row>
     <row r="1917" spans="1:16">
       <c r="A1917" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1917" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C1917">
-        <v>0.5872961799246212</v>
+        <v>0.9354842606674358</v>
       </c>
       <c r="D1917" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="E1917">
-        <v>0.7736589855403704</v>
+        <v>0.7500246029181996</v>
       </c>
       <c r="F1917">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1917">
-        <v>0.006592703820075378</v>
+        <v>0.008544515739332565</v>
       </c>
       <c r="H1917">
-        <v>0.00656634101445963</v>
+        <v>0.007049975397081801</v>
       </c>
       <c r="I1917">
-        <v>0.1863628056157491</v>
+        <v>0.1854596577492362</v>
       </c>
       <c r="J1917">
         <v>0.8181754278134546</v>
       </c>
       <c r="K1917">
-        <v>3.67</v>
+        <v>4.65</v>
       </c>
       <c r="L1917">
-        <v>3.59</v>
+        <v>4.74</v>
       </c>
       <c r="M1917">
-        <v>3.54</v>
+        <v>3.85</v>
       </c>
       <c r="N1917">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="O1917">
         <v>1</v>
@@ -98056,146 +98056,146 @@
     </row>
     <row r="1918" spans="1:16">
       <c r="A1918" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1918" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C1918">
-        <v>0.4840236862109606</v>
+        <v>0.5445698657526035</v>
       </c>
       <c r="D1918" t="s">
-        <v>256</v>
+        <v>450</v>
       </c>
       <c r="E1918">
-        <v>0.8503069233264586</v>
+        <v>0.7736589855403704</v>
       </c>
       <c r="F1918">
         <v>1</v>
       </c>
       <c r="G1918">
-        <v>0.01063597631378904</v>
+        <v>0.006795430134247397</v>
       </c>
       <c r="H1918">
-        <v>0.01238969307667354</v>
+        <v>0.00656634101445963</v>
       </c>
       <c r="I1918">
-        <v>0.366283237115498</v>
+        <v>0.2290891197877669</v>
       </c>
       <c r="J1918">
-        <v>0.8459960522981732</v>
+        <v>0.8181754278134546</v>
       </c>
       <c r="K1918">
-        <v>6</v>
+        <v>3.82</v>
       </c>
       <c r="L1918">
-        <v>5.56</v>
+        <v>3.67</v>
       </c>
       <c r="M1918">
-        <v>6.82</v>
+        <v>3.54</v>
       </c>
       <c r="N1918">
-        <v>6.62</v>
+        <v>3.67</v>
       </c>
       <c r="O1918">
         <v>1</v>
       </c>
       <c r="P1918" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="1919" spans="1:16">
       <c r="A1919" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B1919" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C1919">
-        <v>0.8894240809811436</v>
+        <v>0.5872961799246212</v>
       </c>
       <c r="D1919" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E1919">
-        <v>1.019321514974956</v>
+        <v>0.7736589855403704</v>
       </c>
       <c r="F1919">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1919">
-        <v>0.01121057591901886</v>
+        <v>0.006592703820075378</v>
       </c>
       <c r="H1919">
-        <v>0.01024067848502504</v>
+        <v>0.00656634101445963</v>
       </c>
       <c r="I1919">
-        <v>-0.1298974339938122</v>
+        <v>0.1863628056157491</v>
       </c>
       <c r="J1919">
-        <v>0.8459960522981732</v>
+        <v>0.8181754278134546</v>
       </c>
       <c r="K1919">
-        <v>6.1</v>
+        <v>3.67</v>
       </c>
       <c r="L1919">
-        <v>6.05</v>
+        <v>3.59</v>
       </c>
       <c r="M1919">
-        <v>5.45</v>
+        <v>3.54</v>
       </c>
       <c r="N1919">
-        <v>5.63</v>
+        <v>3.67</v>
       </c>
       <c r="O1919">
         <v>1</v>
       </c>
       <c r="P1919" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="1920" spans="1:16">
       <c r="A1920" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1920" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C1920">
-        <v>0.8278225019004131</v>
+        <v>0.4840236862109606</v>
       </c>
       <c r="D1920" t="s">
-        <v>451</v>
+        <v>256</v>
       </c>
       <c r="E1920">
-        <v>1.019321514974956</v>
+        <v>0.8503069233264586</v>
       </c>
       <c r="F1920">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1920">
-        <v>0.01047217749809959</v>
+        <v>0.01063597631378904</v>
       </c>
       <c r="H1920">
-        <v>0.01024067848502504</v>
+        <v>0.01238969307667354</v>
       </c>
       <c r="I1920">
-        <v>-0.1914990130745426</v>
+        <v>0.366283237115498</v>
       </c>
       <c r="J1920">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1920">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L1920">
-        <v>5.65</v>
+        <v>5.56</v>
       </c>
       <c r="M1920">
-        <v>5.45</v>
+        <v>6.82</v>
       </c>
       <c r="N1920">
-        <v>5.63</v>
+        <v>6.62</v>
       </c>
       <c r="O1920">
         <v>1</v>
@@ -98206,46 +98206,46 @@
     </row>
     <row r="1921" spans="1:16">
       <c r="A1921" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1921" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1921">
-        <v>0.8999376857041841</v>
+        <v>0.8894240809811436</v>
       </c>
       <c r="D1921" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E1921">
-        <v>0.6752765408706538</v>
+        <v>1.019321514974956</v>
       </c>
       <c r="F1921">
         <v>-1</v>
       </c>
       <c r="G1921">
-        <v>0.008480062314295817</v>
+        <v>0.01121057591901886</v>
       </c>
       <c r="H1921">
-        <v>0.007764723459129346</v>
+        <v>0.01024067848502504</v>
       </c>
       <c r="I1921">
-        <v>0.2246611448335303</v>
+        <v>-0.1298974339938122</v>
       </c>
       <c r="J1921">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1921">
-        <v>4.48</v>
+        <v>6.1</v>
       </c>
       <c r="L1921">
-        <v>4.69</v>
+        <v>6.05</v>
       </c>
       <c r="M1921">
-        <v>4.19</v>
+        <v>5.45</v>
       </c>
       <c r="N1921">
-        <v>4.22</v>
+        <v>5.63</v>
       </c>
       <c r="O1921">
         <v>1</v>
@@ -98256,46 +98256,46 @@
     </row>
     <row r="1922" spans="1:16">
       <c r="A1922" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1922" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C1922">
-        <v>0.8307179620433116</v>
+        <v>0.8278225019004131</v>
       </c>
       <c r="D1922" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E1922">
-        <v>0.6752765408706538</v>
+        <v>1.019321514974956</v>
       </c>
       <c r="F1922">
         <v>-1</v>
       </c>
       <c r="G1922">
-        <v>0.008529282037956687</v>
+        <v>0.01047217749809959</v>
       </c>
       <c r="H1922">
-        <v>0.007764723459129346</v>
+        <v>0.01024067848502504</v>
       </c>
       <c r="I1922">
-        <v>0.1554414211726578</v>
+        <v>-0.1914990130745426</v>
       </c>
       <c r="J1922">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1922">
-        <v>4.55</v>
+        <v>5.7</v>
       </c>
       <c r="L1922">
-        <v>4.68</v>
+        <v>5.65</v>
       </c>
       <c r="M1922">
-        <v>4.19</v>
+        <v>5.45</v>
       </c>
       <c r="N1922">
-        <v>4.22</v>
+        <v>5.63</v>
       </c>
       <c r="O1922">
         <v>1</v>
@@ -98306,46 +98306,46 @@
     </row>
     <row r="1923" spans="1:16">
       <c r="A1923" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1923" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="C1923">
-        <v>0.5405948828358871</v>
+        <v>0.8999376857041841</v>
       </c>
       <c r="D1923" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="E1923">
-        <v>0.6859337380023574</v>
+        <v>0.6752765408706538</v>
       </c>
       <c r="F1923">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1923">
-        <v>0.006919405117164113</v>
+        <v>0.008480062314295817</v>
       </c>
       <c r="H1923">
-        <v>0.006574066261997642</v>
+        <v>0.007764723459129346</v>
       </c>
       <c r="I1923">
-        <v>0.1453388551664703</v>
+        <v>0.2246611448335303</v>
       </c>
       <c r="J1923">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1923">
-        <v>3.77</v>
+        <v>4.48</v>
       </c>
       <c r="L1923">
-        <v>3.73</v>
+        <v>4.69</v>
       </c>
       <c r="M1923">
-        <v>3.48</v>
+        <v>4.19</v>
       </c>
       <c r="N1923">
-        <v>3.63</v>
+        <v>4.22</v>
       </c>
       <c r="O1923">
         <v>1</v>
@@ -98356,51 +98356,151 @@
     </row>
     <row r="1924" spans="1:16">
       <c r="A1924" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1924" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C1924">
-        <v>0.5405948828358871</v>
+        <v>0.8307179620433116</v>
       </c>
       <c r="D1924" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="E1924">
-        <v>0.6859337380023574</v>
+        <v>0.6752765408706538</v>
       </c>
       <c r="F1924">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1924">
-        <v>0.006919405117164113</v>
+        <v>0.008529282037956687</v>
       </c>
       <c r="H1924">
-        <v>0.006574066261997642</v>
+        <v>0.007764723459129346</v>
       </c>
       <c r="I1924">
-        <v>0.1453388551664703</v>
+        <v>0.1554414211726578</v>
       </c>
       <c r="J1924">
         <v>0.8459960522981732</v>
       </c>
       <c r="K1924">
+        <v>4.55</v>
+      </c>
+      <c r="L1924">
+        <v>4.68</v>
+      </c>
+      <c r="M1924">
+        <v>4.19</v>
+      </c>
+      <c r="N1924">
+        <v>4.22</v>
+      </c>
+      <c r="O1924">
+        <v>1</v>
+      </c>
+      <c r="P1924" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:16">
+      <c r="A1925" s="1">
+        <v>5</v>
+      </c>
+      <c r="B1925" t="s">
+        <v>268</v>
+      </c>
+      <c r="C1925">
+        <v>0.5405948828358871</v>
+      </c>
+      <c r="D1925" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1925">
+        <v>0.6859337380023574</v>
+      </c>
+      <c r="F1925">
+        <v>1</v>
+      </c>
+      <c r="G1925">
+        <v>0.006919405117164113</v>
+      </c>
+      <c r="H1925">
+        <v>0.006574066261997642</v>
+      </c>
+      <c r="I1925">
+        <v>0.1453388551664703</v>
+      </c>
+      <c r="J1925">
+        <v>0.8459960522981732</v>
+      </c>
+      <c r="K1925">
         <v>3.77</v>
       </c>
-      <c r="L1924">
+      <c r="L1925">
         <v>3.73</v>
       </c>
-      <c r="M1924">
+      <c r="M1925">
         <v>3.48</v>
       </c>
-      <c r="N1924">
+      <c r="N1925">
         <v>3.63</v>
       </c>
-      <c r="O1924">
-        <v>1</v>
-      </c>
-      <c r="P1924" t="s">
+      <c r="O1925">
+        <v>1</v>
+      </c>
+      <c r="P1925" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:16">
+      <c r="A1926" s="1">
+        <v>6</v>
+      </c>
+      <c r="B1926" t="s">
+        <v>269</v>
+      </c>
+      <c r="C1926">
+        <v>0.5405948828358871</v>
+      </c>
+      <c r="D1926" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1926">
+        <v>0.6859337380023574</v>
+      </c>
+      <c r="F1926">
+        <v>1</v>
+      </c>
+      <c r="G1926">
+        <v>0.006919405117164113</v>
+      </c>
+      <c r="H1926">
+        <v>0.006574066261997642</v>
+      </c>
+      <c r="I1926">
+        <v>0.1453388551664703</v>
+      </c>
+      <c r="J1926">
+        <v>0.8459960522981732</v>
+      </c>
+      <c r="K1926">
+        <v>3.77</v>
+      </c>
+      <c r="L1926">
+        <v>3.73</v>
+      </c>
+      <c r="M1926">
+        <v>3.48</v>
+      </c>
+      <c r="N1926">
+        <v>3.63</v>
+      </c>
+      <c r="O1926">
+        <v>1</v>
+      </c>
+      <c r="P1926" t="s">
         <v>247</v>
       </c>
     </row>
